--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499607</v>
+        <v>135499608</v>
       </c>
       <c r="B2" t="n">
         <v>99101</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -715,21 +715,25 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490869</v>
+        <v>490867</v>
       </c>
       <c r="R2" t="n">
-        <v>7017370</v>
+        <v>7017387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +770,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,12 +785,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkrikt fuktstråk.</t>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,65 +808,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499608</v>
+        <v>135499603</v>
       </c>
       <c r="B3" t="n">
-        <v>99101</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490867</v>
+        <v>490968</v>
       </c>
       <c r="R3" t="n">
-        <v>7017387</v>
+        <v>7017430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis vid kanten av hänsynsyta som ger alldeles för lite skyddszon.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,9 +908,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,7 +943,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499603</v>
+        <v>135499604</v>
       </c>
       <c r="B4" t="n">
         <v>91970</v>
@@ -979,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490968</v>
+        <v>490893</v>
       </c>
       <c r="R4" t="n">
-        <v>7017430</v>
+        <v>7017459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1025,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,12 +1055,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1072,7 +1078,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499604</v>
+        <v>135499605</v>
       </c>
       <c r="B5" t="n">
         <v>91970</v>
@@ -1114,10 +1120,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490893</v>
+        <v>490741</v>
       </c>
       <c r="R5" t="n">
-        <v>7017459</v>
+        <v>7017465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1160,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,7 +1213,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499605</v>
+        <v>135499606</v>
       </c>
       <c r="B6" t="n">
         <v>91970</v>
@@ -1249,10 +1255,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490741</v>
+        <v>490951</v>
       </c>
       <c r="R6" t="n">
-        <v>7017465</v>
+        <v>7017411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1295,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1319,12 +1325,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1342,10 +1348,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135499606</v>
+        <v>75185503</v>
       </c>
       <c r="B7" t="n">
-        <v>91970</v>
+        <v>87322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,41 +1359,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1988</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490951</v>
+        <v>490758</v>
       </c>
       <c r="R7" t="n">
-        <v>7017411</v>
+        <v>7017384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,17 +1413,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,85 +1431,68 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75185503</v>
+        <v>135499557</v>
       </c>
       <c r="B8" t="n">
-        <v>87322</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1988</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490758</v>
+        <v>490738</v>
       </c>
       <c r="R8" t="n">
-        <v>7017384</v>
+        <v>7017396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,12 +1519,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,26 +1537,27 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499557</v>
+        <v>135499558</v>
       </c>
       <c r="B9" t="n">
         <v>96410</v>
@@ -1618,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490738</v>
+        <v>490991</v>
       </c>
       <c r="R9" t="n">
-        <v>7017396</v>
+        <v>7017297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,7 +1664,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499558</v>
+        <v>135499560</v>
       </c>
       <c r="B10" t="n">
         <v>96410</v>
@@ -1725,10 +1703,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490991</v>
+        <v>490966</v>
       </c>
       <c r="R10" t="n">
-        <v>7017297</v>
+        <v>7017426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1776,6 +1754,11 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1793,7 +1776,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499560</v>
+        <v>135499561</v>
       </c>
       <c r="B11" t="n">
         <v>96410</v>
@@ -1832,10 +1815,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490966</v>
+        <v>490929</v>
       </c>
       <c r="R11" t="n">
-        <v>7017426</v>
+        <v>7017441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1882,12 +1865,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1905,7 +1883,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499561</v>
+        <v>135499562</v>
       </c>
       <c r="B12" t="n">
         <v>96410</v>
@@ -1944,10 +1922,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490929</v>
+        <v>490910</v>
       </c>
       <c r="R12" t="n">
-        <v>7017441</v>
+        <v>7017467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2012,7 +1990,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499562</v>
+        <v>135499563</v>
       </c>
       <c r="B13" t="n">
         <v>96410</v>
@@ -2051,10 +2029,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490910</v>
+        <v>490878</v>
       </c>
       <c r="R13" t="n">
-        <v>7017467</v>
+        <v>7017474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2101,7 +2079,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2119,7 +2097,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499563</v>
+        <v>135499564</v>
       </c>
       <c r="B14" t="n">
         <v>96410</v>
@@ -2158,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490878</v>
+        <v>490883</v>
       </c>
       <c r="R14" t="n">
-        <v>7017474</v>
+        <v>7017462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,7 +2186,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2226,7 +2204,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499564</v>
+        <v>135499565</v>
       </c>
       <c r="B15" t="n">
         <v>96410</v>
@@ -2265,10 +2243,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490883</v>
+        <v>490756</v>
       </c>
       <c r="R15" t="n">
-        <v>7017462</v>
+        <v>7017472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2315,7 +2293,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2333,7 +2311,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499565</v>
+        <v>135499566</v>
       </c>
       <c r="B16" t="n">
         <v>96410</v>
@@ -2372,10 +2350,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490756</v>
+        <v>490790</v>
       </c>
       <c r="R16" t="n">
-        <v>7017472</v>
+        <v>7017441</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2440,7 +2418,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499566</v>
+        <v>135499567</v>
       </c>
       <c r="B17" t="n">
         <v>96410</v>
@@ -2479,10 +2457,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490790</v>
+        <v>490732</v>
       </c>
       <c r="R17" t="n">
-        <v>7017441</v>
+        <v>7017442</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2529,7 +2507,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2547,7 +2525,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499567</v>
+        <v>135499568</v>
       </c>
       <c r="B18" t="n">
         <v>96410</v>
@@ -2586,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490732</v>
+        <v>490781</v>
       </c>
       <c r="R18" t="n">
-        <v>7017442</v>
+        <v>7017407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2636,7 +2614,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2654,7 +2632,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499568</v>
+        <v>135499569</v>
       </c>
       <c r="B19" t="n">
         <v>96410</v>
@@ -2693,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490781</v>
+        <v>490731</v>
       </c>
       <c r="R19" t="n">
-        <v>7017407</v>
+        <v>7017371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2744,6 +2722,11 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2761,7 +2744,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499569</v>
+        <v>135499570</v>
       </c>
       <c r="B20" t="n">
         <v>96410</v>
@@ -2800,10 +2783,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490731</v>
+        <v>490854</v>
       </c>
       <c r="R20" t="n">
-        <v>7017371</v>
+        <v>7017345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2851,11 +2834,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2873,7 +2851,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499570</v>
+        <v>135499571</v>
       </c>
       <c r="B21" t="n">
         <v>96410</v>
@@ -2912,10 +2890,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490854</v>
+        <v>490878</v>
       </c>
       <c r="R21" t="n">
-        <v>7017345</v>
+        <v>7017366</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,6 +2926,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2980,7 +2963,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499571</v>
+        <v>135499572</v>
       </c>
       <c r="B22" t="n">
         <v>96410</v>
@@ -3019,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490878</v>
+        <v>490867</v>
       </c>
       <c r="R22" t="n">
-        <v>7017366</v>
+        <v>7017386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3055,11 +3038,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,7 +3070,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499572</v>
+        <v>135499573</v>
       </c>
       <c r="B23" t="n">
         <v>96410</v>
@@ -3131,10 +3109,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490867</v>
+        <v>490840</v>
       </c>
       <c r="R23" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3199,7 +3177,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499573</v>
+        <v>135499574</v>
       </c>
       <c r="B24" t="n">
         <v>96410</v>
@@ -3238,10 +3216,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490840</v>
+        <v>490844</v>
       </c>
       <c r="R24" t="n">
-        <v>7017433</v>
+        <v>7017436</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3306,7 +3284,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499574</v>
+        <v>135499575</v>
       </c>
       <c r="B25" t="n">
         <v>96410</v>
@@ -3345,10 +3323,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490844</v>
+        <v>490872</v>
       </c>
       <c r="R25" t="n">
-        <v>7017436</v>
+        <v>7017426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3413,7 +3391,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499575</v>
+        <v>135499576</v>
       </c>
       <c r="B26" t="n">
         <v>96410</v>
@@ -3452,10 +3430,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490872</v>
+        <v>490917</v>
       </c>
       <c r="R26" t="n">
-        <v>7017426</v>
+        <v>7017402</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3520,7 +3498,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499576</v>
+        <v>135499577</v>
       </c>
       <c r="B27" t="n">
         <v>96410</v>
@@ -3559,10 +3537,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490917</v>
+        <v>490931</v>
       </c>
       <c r="R27" t="n">
-        <v>7017402</v>
+        <v>7017371</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3610,6 +3588,11 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3627,7 +3610,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499577</v>
+        <v>135499578</v>
       </c>
       <c r="B28" t="n">
         <v>96410</v>
@@ -3666,10 +3649,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490931</v>
+        <v>490951</v>
       </c>
       <c r="R28" t="n">
-        <v>7017371</v>
+        <v>7017390</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3739,7 +3722,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499578</v>
+        <v>135499579</v>
       </c>
       <c r="B29" t="n">
         <v>96410</v>
@@ -3778,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490951</v>
+        <v>490976</v>
       </c>
       <c r="R29" t="n">
-        <v>7017390</v>
+        <v>7017311</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3851,10 +3834,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135499579</v>
+        <v>91488964</v>
       </c>
       <c r="B30" t="n">
-        <v>96410</v>
+        <v>92632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3862,41 +3845,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2812</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490976</v>
+        <v>490939</v>
       </c>
       <c r="R30" t="n">
-        <v>7017311</v>
+        <v>7017412</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3920,12 +3899,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,61 +3913,54 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>91488964</v>
+        <v>75185505</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>89156</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,13 +3970,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490939</v>
+        <v>490781</v>
       </c>
       <c r="R31" t="n">
-        <v>7017412</v>
+        <v>7017384</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4042,18 +4014,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4064,45 +4037,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>75185505</v>
+        <v>135499609</v>
       </c>
       <c r="B32" t="n">
-        <v>89156</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490781</v>
+        <v>490849</v>
       </c>
       <c r="R32" t="n">
-        <v>7017384</v>
+        <v>7017392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,12 +4105,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,26 +4128,47 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499609</v>
+        <v>135499610</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -4204,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490849</v>
+        <v>490859</v>
       </c>
       <c r="R33" t="n">
-        <v>7017392</v>
+        <v>7017416</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4242,11 +4244,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4274,12 +4271,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4297,48 +4294,61 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499610</v>
+        <v>135499531</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>58089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100090</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490859</v>
+        <v>490781</v>
       </c>
       <c r="R34" t="n">
-        <v>7017416</v>
+        <v>7017369</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4373,39 +4383,23 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Synobservation av en individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4423,10 +4417,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499531</v>
+        <v>135499510</v>
       </c>
       <c r="B35" t="n">
-        <v>58089</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4434,16 +4428,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100090</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4451,16 +4445,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4474,10 +4464,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490781</v>
+        <v>490891</v>
       </c>
       <c r="R35" t="n">
-        <v>7017369</v>
+        <v>7017451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4514,7 +4504,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Synobservation av en individ med lockläte.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4528,7 +4518,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4546,7 +4556,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499510</v>
+        <v>135499511</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4579,7 +4589,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4593,10 +4603,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490891</v>
+        <v>490785</v>
       </c>
       <c r="R36" t="n">
-        <v>7017451</v>
+        <v>7017521</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4633,7 +4643,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4647,7 +4657,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -4685,7 +4695,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499511</v>
+        <v>135499512</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4732,10 +4742,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490785</v>
+        <v>490783</v>
       </c>
       <c r="R37" t="n">
-        <v>7017521</v>
+        <v>7017360</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4772,7 +4782,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4787,6 +4797,11 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4824,27 +4839,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499512</v>
+        <v>135499596</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>58234</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4852,29 +4867,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490783</v>
+        <v>490875</v>
       </c>
       <c r="R38" t="n">
-        <v>7017360</v>
+        <v>7017470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4911,7 +4926,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4926,31 +4941,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4968,37 +4958,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499596</v>
+        <v>135499513</v>
       </c>
       <c r="B39" t="n">
-        <v>58234</v>
+        <v>58136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102981</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5008,17 +4998,21 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490875</v>
+        <v>490763</v>
       </c>
       <c r="R39" t="n">
-        <v>7017470</v>
+        <v>7017499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,7 +5049,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,7 +5063,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5087,7 +5086,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499513</v>
+        <v>135499514</v>
       </c>
       <c r="B40" t="n">
         <v>58136</v>
@@ -5117,7 +5116,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5138,10 +5137,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490763</v>
+        <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017499</v>
+        <v>7017397</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5178,7 +5177,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5192,12 +5191,12 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5215,61 +5214,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499514</v>
+        <v>135499611</v>
       </c>
       <c r="B41" t="n">
-        <v>58136</v>
+        <v>99112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490875</v>
+        <v>490821</v>
       </c>
       <c r="R41" t="n">
-        <v>7017397</v>
+        <v>7017504</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5306,7 +5297,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 2 ex med lockläte. Flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,17 +5306,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5343,7 +5330,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499611</v>
+        <v>135499612</v>
       </c>
       <c r="B42" t="n">
         <v>99112</v>
@@ -5375,7 +5362,7 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5386,10 +5373,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490821</v>
+        <v>490848</v>
       </c>
       <c r="R42" t="n">
-        <v>7017504</v>
+        <v>7017375</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5422,11 +5409,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5459,7 +5441,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499612</v>
+        <v>135499613</v>
       </c>
       <c r="B43" t="n">
         <v>99112</v>
@@ -5491,7 +5473,7 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5502,10 +5484,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490848</v>
+        <v>490878</v>
       </c>
       <c r="R43" t="n">
-        <v>7017375</v>
+        <v>7017368</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5538,6 +5520,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5570,7 +5557,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499613</v>
+        <v>135499614</v>
       </c>
       <c r="B44" t="n">
         <v>99112</v>
@@ -5602,7 +5589,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5613,10 +5600,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490878</v>
+        <v>490867</v>
       </c>
       <c r="R44" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5686,7 +5673,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499614</v>
+        <v>135499615</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5718,7 +5705,7 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -5729,7 +5716,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490867</v>
+        <v>490860</v>
       </c>
       <c r="R45" t="n">
         <v>7017386</v>
@@ -5802,10 +5789,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499615</v>
+        <v>135499509</v>
       </c>
       <c r="B46" t="n">
-        <v>99112</v>
+        <v>99219</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5813,28 +5800,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -5845,10 +5832,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490860</v>
+        <v>490880</v>
       </c>
       <c r="R46" t="n">
-        <v>7017386</v>
+        <v>7017365</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5885,7 +5872,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Flertalet plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5901,6 +5888,11 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5918,10 +5910,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499509</v>
+        <v>135499620</v>
       </c>
       <c r="B47" t="n">
-        <v>99219</v>
+        <v>108205</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5929,28 +5921,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -5961,10 +5953,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490880</v>
+        <v>490853</v>
       </c>
       <c r="R47" t="n">
-        <v>7017365</v>
+        <v>7017483</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5999,11 +5991,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Flertalet plantor.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6017,11 +6004,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6039,7 +6021,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499620</v>
+        <v>135499621</v>
       </c>
       <c r="B48" t="n">
         <v>108205</v>
@@ -6071,7 +6053,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6082,10 +6064,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490853</v>
+        <v>490837</v>
       </c>
       <c r="R48" t="n">
-        <v>7017483</v>
+        <v>7017379</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6150,7 +6132,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499621</v>
+        <v>135499623</v>
       </c>
       <c r="B49" t="n">
         <v>108205</v>
@@ -6193,10 +6175,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490837</v>
+        <v>490848</v>
       </c>
       <c r="R49" t="n">
-        <v>7017379</v>
+        <v>7017376</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6261,7 +6243,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499623</v>
+        <v>135499624</v>
       </c>
       <c r="B50" t="n">
         <v>108205</v>
@@ -6304,10 +6286,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490848</v>
+        <v>490861</v>
       </c>
       <c r="R50" t="n">
-        <v>7017376</v>
+        <v>7017386</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6372,7 +6354,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499624</v>
+        <v>135499625</v>
       </c>
       <c r="B51" t="n">
         <v>108205</v>
@@ -6404,7 +6386,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6415,10 +6397,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490861</v>
+        <v>490821</v>
       </c>
       <c r="R51" t="n">
-        <v>7017386</v>
+        <v>7017394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6483,7 +6465,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499625</v>
+        <v>135499626</v>
       </c>
       <c r="B52" t="n">
         <v>108205</v>
@@ -6526,10 +6508,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490821</v>
+        <v>490841</v>
       </c>
       <c r="R52" t="n">
-        <v>7017394</v>
+        <v>7017433</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6594,10 +6576,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499626</v>
+        <v>135499550</v>
       </c>
       <c r="B53" t="n">
-        <v>108205</v>
+        <v>108274</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,28 +6587,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6637,10 +6619,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490841</v>
+        <v>490929</v>
       </c>
       <c r="R53" t="n">
-        <v>7017433</v>
+        <v>7017429</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6705,7 +6687,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499550</v>
+        <v>135499551</v>
       </c>
       <c r="B54" t="n">
         <v>108274</v>
@@ -6748,10 +6730,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490929</v>
+        <v>490853</v>
       </c>
       <c r="R54" t="n">
-        <v>7017429</v>
+        <v>7017480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6784,6 +6766,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6816,7 +6803,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499551</v>
+        <v>135499552</v>
       </c>
       <c r="B55" t="n">
         <v>108274</v>
@@ -6859,7 +6846,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490853</v>
+        <v>490867</v>
       </c>
       <c r="R55" t="n">
         <v>7017480</v>
@@ -6895,11 +6882,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6932,7 +6914,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499552</v>
+        <v>135499553</v>
       </c>
       <c r="B56" t="n">
         <v>108274</v>
@@ -6975,10 +6957,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490867</v>
+        <v>490841</v>
       </c>
       <c r="R56" t="n">
-        <v>7017480</v>
+        <v>7017457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7043,7 +7025,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499553</v>
+        <v>135499554</v>
       </c>
       <c r="B57" t="n">
         <v>108274</v>
@@ -7086,10 +7068,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490841</v>
+        <v>490737</v>
       </c>
       <c r="R57" t="n">
-        <v>7017457</v>
+        <v>7017474</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7154,7 +7136,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499554</v>
+        <v>135499555</v>
       </c>
       <c r="B58" t="n">
         <v>108274</v>
@@ -7197,10 +7179,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490737</v>
+        <v>490873</v>
       </c>
       <c r="R58" t="n">
-        <v>7017474</v>
+        <v>7017368</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7265,7 +7247,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499555</v>
+        <v>135499556</v>
       </c>
       <c r="B59" t="n">
         <v>108274</v>
@@ -7308,10 +7290,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490873</v>
+        <v>490863</v>
       </c>
       <c r="R59" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7359,6 +7341,11 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7376,10 +7363,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499556</v>
+        <v>135499544</v>
       </c>
       <c r="B60" t="n">
-        <v>108274</v>
+        <v>111153</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7387,28 +7374,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7419,10 +7406,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490863</v>
+        <v>490844</v>
       </c>
       <c r="R60" t="n">
-        <v>7017386</v>
+        <v>7017468</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7470,11 +7457,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7492,7 +7474,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499544</v>
+        <v>135499546</v>
       </c>
       <c r="B61" t="n">
         <v>111153</v>
@@ -7535,10 +7517,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490844</v>
+        <v>490780</v>
       </c>
       <c r="R61" t="n">
-        <v>7017468</v>
+        <v>7017405</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7603,7 +7585,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499546</v>
+        <v>135499547</v>
       </c>
       <c r="B62" t="n">
         <v>111153</v>
@@ -7635,7 +7617,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7646,10 +7628,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490780</v>
+        <v>490858</v>
       </c>
       <c r="R62" t="n">
-        <v>7017405</v>
+        <v>7017416</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7714,7 +7696,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499547</v>
+        <v>135499548</v>
       </c>
       <c r="B63" t="n">
         <v>111153</v>
@@ -7746,7 +7728,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -7757,10 +7739,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490858</v>
+        <v>490964</v>
       </c>
       <c r="R63" t="n">
-        <v>7017416</v>
+        <v>7017356</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7808,6 +7790,11 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7825,10 +7812,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499548</v>
+        <v>135499617</v>
       </c>
       <c r="B64" t="n">
-        <v>111153</v>
+        <v>110150</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7836,28 +7823,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220240</v>
+        <v>220294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -7868,10 +7855,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490964</v>
+        <v>490864</v>
       </c>
       <c r="R64" t="n">
-        <v>7017356</v>
+        <v>7017486</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7906,6 +7893,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7919,11 +7911,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7941,39 +7928,47 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499617</v>
+        <v>135499580</v>
       </c>
       <c r="B65" t="n">
-        <v>110150</v>
+        <v>99195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220294</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -7984,10 +7979,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490864</v>
+        <v>490975</v>
       </c>
       <c r="R65" t="n">
-        <v>7017486</v>
+        <v>7017304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8024,7 +8019,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8040,6 +8035,11 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8057,7 +8057,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499580</v>
+        <v>135499583</v>
       </c>
       <c r="B66" t="n">
         <v>99195</v>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490975</v>
+        <v>490768</v>
       </c>
       <c r="R66" t="n">
-        <v>7017304</v>
+        <v>7017376</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8186,7 +8186,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499583</v>
+        <v>135499584</v>
       </c>
       <c r="B67" t="n">
         <v>99195</v>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8237,10 +8237,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490768</v>
+        <v>490839</v>
       </c>
       <c r="R67" t="n">
-        <v>7017376</v>
+        <v>7017351</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8292,12 +8292,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8315,7 +8310,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499584</v>
+        <v>135499585</v>
       </c>
       <c r="B68" t="n">
         <v>99195</v>
@@ -8345,7 +8340,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8366,10 +8361,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490839</v>
+        <v>490845</v>
       </c>
       <c r="R68" t="n">
-        <v>7017351</v>
+        <v>7017392</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8406,7 +8401,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8439,7 +8434,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499585</v>
+        <v>135499586</v>
       </c>
       <c r="B69" t="n">
         <v>99195</v>
@@ -8469,7 +8464,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8490,10 +8485,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490845</v>
+        <v>490812</v>
       </c>
       <c r="R69" t="n">
-        <v>7017392</v>
+        <v>7017401</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8530,7 +8525,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8545,7 +8540,12 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8563,7 +8563,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499586</v>
+        <v>135499588</v>
       </c>
       <c r="B70" t="n">
         <v>99195</v>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490812</v>
+        <v>490843</v>
       </c>
       <c r="R70" t="n">
-        <v>7017401</v>
+        <v>7017436</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8692,7 +8692,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499588</v>
+        <v>135499589</v>
       </c>
       <c r="B71" t="n">
         <v>99195</v>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490843</v>
+        <v>490967</v>
       </c>
       <c r="R71" t="n">
-        <v>7017436</v>
+        <v>7017335</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8821,7 +8821,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499589</v>
+        <v>135499590</v>
       </c>
       <c r="B72" t="n">
         <v>99195</v>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8872,10 +8872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490967</v>
+        <v>490979</v>
       </c>
       <c r="R72" t="n">
-        <v>7017335</v>
+        <v>7017360</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8950,7 +8950,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499590</v>
+        <v>135499591</v>
       </c>
       <c r="B73" t="n">
         <v>99195</v>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9001,10 +9001,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490979</v>
+        <v>490973</v>
       </c>
       <c r="R73" t="n">
-        <v>7017360</v>
+        <v>7017399</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9079,7 +9079,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499591</v>
+        <v>135499592</v>
       </c>
       <c r="B74" t="n">
         <v>99195</v>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9130,10 +9130,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490973</v>
+        <v>490951</v>
       </c>
       <c r="R74" t="n">
-        <v>7017399</v>
+        <v>7017408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9208,7 +9208,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499592</v>
+        <v>135499593</v>
       </c>
       <c r="B75" t="n">
         <v>99195</v>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9262,7 +9262,7 @@
         <v>490951</v>
       </c>
       <c r="R75" t="n">
-        <v>7017408</v>
+        <v>7017396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9337,7 +9337,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499593</v>
+        <v>135499594</v>
       </c>
       <c r="B76" t="n">
         <v>99195</v>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490951</v>
+        <v>490957</v>
       </c>
       <c r="R76" t="n">
-        <v>7017396</v>
+        <v>7017386</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9466,49 +9466,37 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499594</v>
+        <v>135499519</v>
       </c>
       <c r="B77" t="n">
-        <v>99195</v>
+        <v>98060</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9517,10 +9505,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490957</v>
+        <v>490752</v>
       </c>
       <c r="R77" t="n">
-        <v>7017386</v>
+        <v>7017499</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9557,7 +9545,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9573,11 +9561,6 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9595,10 +9578,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499519</v>
+        <v>135499516</v>
       </c>
       <c r="B78" t="n">
-        <v>98060</v>
+        <v>99217</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9606,26 +9589,30 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -9634,10 +9621,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490752</v>
+        <v>490844</v>
       </c>
       <c r="R78" t="n">
-        <v>7017499</v>
+        <v>7017394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9670,11 +9657,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9707,7 +9689,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499516</v>
+        <v>135499517</v>
       </c>
       <c r="B79" t="n">
         <v>99217</v>
@@ -9750,10 +9732,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490844</v>
+        <v>490814</v>
       </c>
       <c r="R79" t="n">
-        <v>7017394</v>
+        <v>7017404</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9818,10 +9800,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499517</v>
+        <v>135499627</v>
       </c>
       <c r="B80" t="n">
-        <v>99217</v>
+        <v>101403</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9829,28 +9811,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -9861,10 +9843,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490814</v>
+        <v>490803</v>
       </c>
       <c r="R80" t="n">
-        <v>7017404</v>
+        <v>7017492</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9929,7 +9911,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499627</v>
+        <v>135499628</v>
       </c>
       <c r="B81" t="n">
         <v>101403</v>
@@ -9972,10 +9954,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490803</v>
+        <v>490792</v>
       </c>
       <c r="R81" t="n">
-        <v>7017492</v>
+        <v>7017441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10040,7 +10022,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499628</v>
+        <v>135499629</v>
       </c>
       <c r="B82" t="n">
         <v>101403</v>
@@ -10083,7 +10065,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490792</v>
+        <v>490764</v>
       </c>
       <c r="R82" t="n">
         <v>7017441</v>
@@ -10151,7 +10133,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499629</v>
+        <v>135499630</v>
       </c>
       <c r="B83" t="n">
         <v>101403</v>
@@ -10194,10 +10176,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490764</v>
+        <v>490798</v>
       </c>
       <c r="R83" t="n">
-        <v>7017441</v>
+        <v>7017366</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10262,7 +10244,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499630</v>
+        <v>135499631</v>
       </c>
       <c r="B84" t="n">
         <v>101403</v>
@@ -10305,10 +10287,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490798</v>
+        <v>490816</v>
       </c>
       <c r="R84" t="n">
-        <v>7017366</v>
+        <v>7017378</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10373,7 +10355,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499631</v>
+        <v>135499632</v>
       </c>
       <c r="B85" t="n">
         <v>101403</v>
@@ -10416,10 +10398,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490816</v>
+        <v>490796</v>
       </c>
       <c r="R85" t="n">
-        <v>7017378</v>
+        <v>7017382</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10484,7 +10466,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499632</v>
+        <v>135499633</v>
       </c>
       <c r="B86" t="n">
         <v>101403</v>
@@ -10527,10 +10509,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490796</v>
+        <v>490782</v>
       </c>
       <c r="R86" t="n">
-        <v>7017382</v>
+        <v>7017407</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10595,7 +10577,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499633</v>
+        <v>135499634</v>
       </c>
       <c r="B87" t="n">
         <v>101403</v>
@@ -10638,10 +10620,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490782</v>
+        <v>490730</v>
       </c>
       <c r="R87" t="n">
-        <v>7017407</v>
+        <v>7017371</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10706,7 +10688,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499634</v>
+        <v>135499635</v>
       </c>
       <c r="B88" t="n">
         <v>101403</v>
@@ -10749,10 +10731,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490730</v>
+        <v>490827</v>
       </c>
       <c r="R88" t="n">
-        <v>7017371</v>
+        <v>7017356</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10817,7 +10799,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499635</v>
+        <v>135499636</v>
       </c>
       <c r="B89" t="n">
         <v>101403</v>
@@ -10860,10 +10842,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490827</v>
+        <v>490844</v>
       </c>
       <c r="R89" t="n">
-        <v>7017356</v>
+        <v>7017345</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10928,7 +10910,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499636</v>
+        <v>135499637</v>
       </c>
       <c r="B90" t="n">
         <v>101403</v>
@@ -10971,10 +10953,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490844</v>
+        <v>490852</v>
       </c>
       <c r="R90" t="n">
-        <v>7017345</v>
+        <v>7017373</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11021,7 +11003,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11039,7 +11021,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499637</v>
+        <v>135499638</v>
       </c>
       <c r="B91" t="n">
         <v>101403</v>
@@ -11082,10 +11064,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490852</v>
+        <v>490882</v>
       </c>
       <c r="R91" t="n">
-        <v>7017373</v>
+        <v>7017368</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11150,7 +11132,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499638</v>
+        <v>135499639</v>
       </c>
       <c r="B92" t="n">
         <v>101403</v>
@@ -11193,10 +11175,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490882</v>
+        <v>490865</v>
       </c>
       <c r="R92" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11243,7 +11225,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11261,7 +11243,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499639</v>
+        <v>135499640</v>
       </c>
       <c r="B93" t="n">
         <v>101403</v>
@@ -11304,10 +11286,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490865</v>
+        <v>490840</v>
       </c>
       <c r="R93" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11372,7 +11354,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499640</v>
+        <v>135499641</v>
       </c>
       <c r="B94" t="n">
         <v>101403</v>
@@ -11415,10 +11397,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490840</v>
+        <v>490880</v>
       </c>
       <c r="R94" t="n">
-        <v>7017433</v>
+        <v>7017422</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11483,10 +11465,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499641</v>
+        <v>135499618</v>
       </c>
       <c r="B95" t="n">
-        <v>101403</v>
+        <v>98214</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11494,21 +11476,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11526,10 +11508,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490880</v>
+        <v>490791</v>
       </c>
       <c r="R95" t="n">
-        <v>7017422</v>
+        <v>7017443</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11562,6 +11544,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11594,7 +11581,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499618</v>
+        <v>135499619</v>
       </c>
       <c r="B96" t="n">
         <v>98214</v>
@@ -11622,8 +11609,16 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -11637,10 +11632,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490791</v>
+        <v>490868</v>
       </c>
       <c r="R96" t="n">
-        <v>7017443</v>
+        <v>7017387</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11677,7 +11672,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11693,6 +11688,11 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11710,10 +11710,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499619</v>
+        <v>135499520</v>
       </c>
       <c r="B97" t="n">
-        <v>98214</v>
+        <v>99001</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11721,33 +11721,25 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -11761,10 +11753,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490868</v>
+        <v>490757</v>
       </c>
       <c r="R97" t="n">
-        <v>7017387</v>
+        <v>7017472</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11799,11 +11791,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11817,11 +11804,6 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11839,7 +11821,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499520</v>
+        <v>135499521</v>
       </c>
       <c r="B98" t="n">
         <v>99001</v>
@@ -11882,10 +11864,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490757</v>
+        <v>490966</v>
       </c>
       <c r="R98" t="n">
-        <v>7017472</v>
+        <v>7017430</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11950,7 +11932,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499521</v>
+        <v>135499522</v>
       </c>
       <c r="B99" t="n">
         <v>99001</v>
@@ -11993,10 +11975,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490966</v>
+        <v>490920</v>
       </c>
       <c r="R99" t="n">
-        <v>7017430</v>
+        <v>7017445</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12061,7 +12043,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499522</v>
+        <v>135499523</v>
       </c>
       <c r="B100" t="n">
         <v>99001</v>
@@ -12104,10 +12086,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490920</v>
+        <v>490912</v>
       </c>
       <c r="R100" t="n">
-        <v>7017445</v>
+        <v>7017466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12172,7 +12154,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499523</v>
+        <v>135499524</v>
       </c>
       <c r="B101" t="n">
         <v>99001</v>
@@ -12215,10 +12197,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490912</v>
+        <v>490858</v>
       </c>
       <c r="R101" t="n">
-        <v>7017466</v>
+        <v>7017493</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12283,7 +12265,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499524</v>
+        <v>135499525</v>
       </c>
       <c r="B102" t="n">
         <v>99001</v>
@@ -12315,7 +12297,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12326,10 +12308,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490858</v>
+        <v>490804</v>
       </c>
       <c r="R102" t="n">
-        <v>7017493</v>
+        <v>7017492</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12394,7 +12376,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499525</v>
+        <v>135499526</v>
       </c>
       <c r="B103" t="n">
         <v>99001</v>
@@ -12426,7 +12408,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12437,10 +12419,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490804</v>
+        <v>490740</v>
       </c>
       <c r="R103" t="n">
-        <v>7017492</v>
+        <v>7017423</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12505,7 +12487,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499526</v>
+        <v>135499527</v>
       </c>
       <c r="B104" t="n">
         <v>99001</v>
@@ -12548,10 +12530,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490740</v>
+        <v>490732</v>
       </c>
       <c r="R104" t="n">
-        <v>7017423</v>
+        <v>7017370</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12616,7 +12598,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499527</v>
+        <v>135499528</v>
       </c>
       <c r="B105" t="n">
         <v>99001</v>
@@ -12659,10 +12641,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490732</v>
+        <v>490867</v>
       </c>
       <c r="R105" t="n">
-        <v>7017370</v>
+        <v>7017386</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12695,6 +12677,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12727,7 +12714,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499528</v>
+        <v>135499529</v>
       </c>
       <c r="B106" t="n">
         <v>99001</v>
@@ -12770,10 +12757,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490867</v>
+        <v>490807</v>
       </c>
       <c r="R106" t="n">
-        <v>7017386</v>
+        <v>7017431</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12806,11 +12793,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12843,7 +12825,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499529</v>
+        <v>135499530</v>
       </c>
       <c r="B107" t="n">
         <v>99001</v>
@@ -12875,7 +12857,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -12886,10 +12868,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490807</v>
+        <v>490932</v>
       </c>
       <c r="R107" t="n">
-        <v>7017431</v>
+        <v>7017369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12954,10 +12936,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499530</v>
+        <v>135499597</v>
       </c>
       <c r="B108" t="n">
-        <v>99001</v>
+        <v>98249</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12965,28 +12947,28 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -12997,10 +12979,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490932</v>
+        <v>490969</v>
       </c>
       <c r="R108" t="n">
-        <v>7017369</v>
+        <v>7017431</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13065,7 +13047,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499597</v>
+        <v>135499598</v>
       </c>
       <c r="B109" t="n">
         <v>98249</v>
@@ -13108,10 +13090,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490969</v>
+        <v>490840</v>
       </c>
       <c r="R109" t="n">
-        <v>7017431</v>
+        <v>7017457</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13176,7 +13158,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499598</v>
+        <v>135499599</v>
       </c>
       <c r="B110" t="n">
         <v>98249</v>
@@ -13219,10 +13201,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490840</v>
+        <v>490831</v>
       </c>
       <c r="R110" t="n">
-        <v>7017457</v>
+        <v>7017486</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13287,7 +13269,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499599</v>
+        <v>135499600</v>
       </c>
       <c r="B111" t="n">
         <v>98249</v>
@@ -13330,10 +13312,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490831</v>
+        <v>490797</v>
       </c>
       <c r="R111" t="n">
-        <v>7017486</v>
+        <v>7017497</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13398,7 +13380,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499600</v>
+        <v>135499601</v>
       </c>
       <c r="B112" t="n">
         <v>98249</v>
@@ -13444,7 +13426,7 @@
         <v>490797</v>
       </c>
       <c r="R112" t="n">
-        <v>7017497</v>
+        <v>7017511</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13509,7 +13491,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499601</v>
+        <v>135499602</v>
       </c>
       <c r="B113" t="n">
         <v>98249</v>
@@ -13552,10 +13534,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490797</v>
+        <v>490737</v>
       </c>
       <c r="R113" t="n">
-        <v>7017511</v>
+        <v>7017473</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13620,10 +13602,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499602</v>
+        <v>135499515</v>
       </c>
       <c r="B114" t="n">
-        <v>98249</v>
+        <v>101940</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13631,21 +13613,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223358</v>
+        <v>223366</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13663,10 +13645,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490737</v>
+        <v>490788</v>
       </c>
       <c r="R114" t="n">
-        <v>7017473</v>
+        <v>7017450</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13731,10 +13713,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499515</v>
+        <v>135499532</v>
       </c>
       <c r="B115" t="n">
-        <v>101940</v>
+        <v>101293</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13742,21 +13724,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>223366</v>
+        <v>224885</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13774,10 +13756,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490788</v>
+        <v>490889</v>
       </c>
       <c r="R115" t="n">
-        <v>7017450</v>
+        <v>7017459</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13842,7 +13824,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499532</v>
+        <v>135499533</v>
       </c>
       <c r="B116" t="n">
         <v>101293</v>
@@ -13885,10 +13867,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490889</v>
+        <v>490743</v>
       </c>
       <c r="R116" t="n">
-        <v>7017459</v>
+        <v>7017495</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13953,7 +13935,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499533</v>
+        <v>135499534</v>
       </c>
       <c r="B117" t="n">
         <v>101293</v>
@@ -13996,10 +13978,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>490743</v>
+        <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017495</v>
+        <v>7017474</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14064,7 +14046,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499534</v>
+        <v>135499535</v>
       </c>
       <c r="B118" t="n">
         <v>101293</v>
@@ -14107,10 +14089,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490737</v>
+        <v>490734</v>
       </c>
       <c r="R118" t="n">
-        <v>7017474</v>
+        <v>7017429</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14175,7 +14157,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499535</v>
+        <v>135499536</v>
       </c>
       <c r="B119" t="n">
         <v>101293</v>
@@ -14218,10 +14200,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490734</v>
+        <v>490780</v>
       </c>
       <c r="R119" t="n">
-        <v>7017429</v>
+        <v>7017405</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14286,7 +14268,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499536</v>
+        <v>135499537</v>
       </c>
       <c r="B120" t="n">
         <v>101293</v>
@@ -14329,10 +14311,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490780</v>
+        <v>490751</v>
       </c>
       <c r="R120" t="n">
-        <v>7017405</v>
+        <v>7017406</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14397,7 +14379,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499537</v>
+        <v>135499538</v>
       </c>
       <c r="B121" t="n">
         <v>101293</v>
@@ -14440,10 +14422,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490751</v>
+        <v>490729</v>
       </c>
       <c r="R121" t="n">
-        <v>7017406</v>
+        <v>7017373</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14508,7 +14490,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499538</v>
+        <v>135499540</v>
       </c>
       <c r="B122" t="n">
         <v>101293</v>
@@ -14551,10 +14533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490729</v>
+        <v>490847</v>
       </c>
       <c r="R122" t="n">
-        <v>7017373</v>
+        <v>7017345</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14619,7 +14601,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499540</v>
+        <v>135499541</v>
       </c>
       <c r="B123" t="n">
         <v>101293</v>
@@ -14662,10 +14644,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490847</v>
+        <v>490856</v>
       </c>
       <c r="R123" t="n">
-        <v>7017345</v>
+        <v>7017358</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14730,7 +14712,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499541</v>
+        <v>135499542</v>
       </c>
       <c r="B124" t="n">
         <v>101293</v>
@@ -14762,7 +14744,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -14773,10 +14755,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490856</v>
+        <v>490840</v>
       </c>
       <c r="R124" t="n">
-        <v>7017358</v>
+        <v>7017433</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14838,117 +14820,6 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>135499542</v>
-      </c>
-      <c r="B125" t="n">
-        <v>101293</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q125" t="n">
-        <v>490840</v>
-      </c>
-      <c r="R125" t="n">
-        <v>7017433</v>
-      </c>
-      <c r="S125" t="n">
-        <v>10</v>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="inlineStr"/>
-      <c r="AG125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT125" t="inlineStr"/>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499608</v>
+        <v>135499607</v>
       </c>
       <c r="B2" t="n">
         <v>99101</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490867</v>
+        <v>490869</v>
       </c>
       <c r="R2" t="n">
-        <v>7017387</v>
+        <v>7017370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
+          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad snitslad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +785,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+          <t>Kalkrikt fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -808,52 +808,65 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499603</v>
+        <v>135499608</v>
       </c>
       <c r="B3" t="n">
-        <v>91970</v>
+        <v>99101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490968</v>
+        <v>490867</v>
       </c>
       <c r="R3" t="n">
-        <v>7017430</v>
+        <v>7017387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +903,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,24 +921,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,7 +941,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499604</v>
+        <v>135499603</v>
       </c>
       <c r="B4" t="n">
         <v>91970</v>
@@ -985,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490893</v>
+        <v>490968</v>
       </c>
       <c r="R4" t="n">
-        <v>7017459</v>
+        <v>7017430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,12 +1053,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1078,7 +1076,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499605</v>
+        <v>135499604</v>
       </c>
       <c r="B5" t="n">
         <v>91970</v>
@@ -1120,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490741</v>
+        <v>490893</v>
       </c>
       <c r="R5" t="n">
-        <v>7017465</v>
+        <v>7017459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,7 +1158,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1213,7 +1211,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499606</v>
+        <v>135499605</v>
       </c>
       <c r="B6" t="n">
         <v>91970</v>
@@ -1255,10 +1253,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490951</v>
+        <v>490741</v>
       </c>
       <c r="R6" t="n">
-        <v>7017411</v>
+        <v>7017465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1293,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,12 +1323,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1348,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75185503</v>
+        <v>135499606</v>
       </c>
       <c r="B7" t="n">
-        <v>87322</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,34 +1357,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1988</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490758</v>
+        <v>490951</v>
       </c>
       <c r="R7" t="n">
-        <v>7017384</v>
+        <v>7017411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,12 +1418,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,68 +1441,85 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135499557</v>
+        <v>75185503</v>
       </c>
       <c r="B8" t="n">
-        <v>96410</v>
+        <v>87322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2812</v>
+        <v>1988</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490738</v>
+        <v>490758</v>
       </c>
       <c r="R8" t="n">
-        <v>7017396</v>
+        <v>7017384</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,12 +1546,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,27 +1564,26 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499558</v>
+        <v>135499557</v>
       </c>
       <c r="B9" t="n">
         <v>96410</v>
@@ -1596,10 +1622,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490991</v>
+        <v>490738</v>
       </c>
       <c r="R9" t="n">
-        <v>7017297</v>
+        <v>7017396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,7 +1690,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499560</v>
+        <v>135499558</v>
       </c>
       <c r="B10" t="n">
         <v>96410</v>
@@ -1703,10 +1729,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490966</v>
+        <v>490991</v>
       </c>
       <c r="R10" t="n">
-        <v>7017426</v>
+        <v>7017297</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1754,11 +1780,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1776,7 +1797,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499561</v>
+        <v>135499560</v>
       </c>
       <c r="B11" t="n">
         <v>96410</v>
@@ -1815,10 +1836,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490929</v>
+        <v>490966</v>
       </c>
       <c r="R11" t="n">
-        <v>7017441</v>
+        <v>7017426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1865,7 +1886,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1883,7 +1909,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499562</v>
+        <v>135499561</v>
       </c>
       <c r="B12" t="n">
         <v>96410</v>
@@ -1922,10 +1948,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490910</v>
+        <v>490929</v>
       </c>
       <c r="R12" t="n">
-        <v>7017467</v>
+        <v>7017441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,7 +2016,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499563</v>
+        <v>135499562</v>
       </c>
       <c r="B13" t="n">
         <v>96410</v>
@@ -2029,10 +2055,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490878</v>
+        <v>490910</v>
       </c>
       <c r="R13" t="n">
-        <v>7017474</v>
+        <v>7017467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,7 +2105,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2097,7 +2123,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499564</v>
+        <v>135499563</v>
       </c>
       <c r="B14" t="n">
         <v>96410</v>
@@ -2136,10 +2162,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490883</v>
+        <v>490878</v>
       </c>
       <c r="R14" t="n">
-        <v>7017462</v>
+        <v>7017474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,7 +2212,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2204,7 +2230,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499565</v>
+        <v>135499564</v>
       </c>
       <c r="B15" t="n">
         <v>96410</v>
@@ -2243,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490756</v>
+        <v>490883</v>
       </c>
       <c r="R15" t="n">
-        <v>7017472</v>
+        <v>7017462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2319,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2311,7 +2337,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499566</v>
+        <v>135499565</v>
       </c>
       <c r="B16" t="n">
         <v>96410</v>
@@ -2350,10 +2376,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490790</v>
+        <v>490756</v>
       </c>
       <c r="R16" t="n">
-        <v>7017441</v>
+        <v>7017472</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2418,7 +2444,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499567</v>
+        <v>135499566</v>
       </c>
       <c r="B17" t="n">
         <v>96410</v>
@@ -2457,10 +2483,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490732</v>
+        <v>490790</v>
       </c>
       <c r="R17" t="n">
-        <v>7017442</v>
+        <v>7017441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,7 +2533,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2525,7 +2551,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499568</v>
+        <v>135499567</v>
       </c>
       <c r="B18" t="n">
         <v>96410</v>
@@ -2564,10 +2590,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490781</v>
+        <v>490732</v>
       </c>
       <c r="R18" t="n">
-        <v>7017407</v>
+        <v>7017442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,7 +2640,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2632,7 +2658,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499569</v>
+        <v>135499568</v>
       </c>
       <c r="B19" t="n">
         <v>96410</v>
@@ -2671,10 +2697,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490731</v>
+        <v>490781</v>
       </c>
       <c r="R19" t="n">
-        <v>7017371</v>
+        <v>7017407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2722,11 +2748,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2744,7 +2765,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499570</v>
+        <v>135499569</v>
       </c>
       <c r="B20" t="n">
         <v>96410</v>
@@ -2783,10 +2804,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490854</v>
+        <v>490731</v>
       </c>
       <c r="R20" t="n">
-        <v>7017345</v>
+        <v>7017371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2834,6 +2855,11 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2851,7 +2877,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499571</v>
+        <v>135499570</v>
       </c>
       <c r="B21" t="n">
         <v>96410</v>
@@ -2890,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490878</v>
+        <v>490854</v>
       </c>
       <c r="R21" t="n">
-        <v>7017366</v>
+        <v>7017345</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2926,11 +2952,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,7 +2984,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499572</v>
+        <v>135499571</v>
       </c>
       <c r="B22" t="n">
         <v>96410</v>
@@ -3002,10 +3023,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490867</v>
+        <v>490878</v>
       </c>
       <c r="R22" t="n">
-        <v>7017386</v>
+        <v>7017366</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3038,6 +3059,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,7 +3096,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499573</v>
+        <v>135499572</v>
       </c>
       <c r="B23" t="n">
         <v>96410</v>
@@ -3109,10 +3135,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490840</v>
+        <v>490867</v>
       </c>
       <c r="R23" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3177,7 +3203,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499574</v>
+        <v>135499573</v>
       </c>
       <c r="B24" t="n">
         <v>96410</v>
@@ -3216,10 +3242,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490844</v>
+        <v>490840</v>
       </c>
       <c r="R24" t="n">
-        <v>7017436</v>
+        <v>7017433</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,7 +3310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499575</v>
+        <v>135499574</v>
       </c>
       <c r="B25" t="n">
         <v>96410</v>
@@ -3323,10 +3349,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490872</v>
+        <v>490844</v>
       </c>
       <c r="R25" t="n">
-        <v>7017426</v>
+        <v>7017436</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3391,7 +3417,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499576</v>
+        <v>135499575</v>
       </c>
       <c r="B26" t="n">
         <v>96410</v>
@@ -3430,10 +3456,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490917</v>
+        <v>490872</v>
       </c>
       <c r="R26" t="n">
-        <v>7017402</v>
+        <v>7017426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3498,7 +3524,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499577</v>
+        <v>135499576</v>
       </c>
       <c r="B27" t="n">
         <v>96410</v>
@@ -3537,10 +3563,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490931</v>
+        <v>490917</v>
       </c>
       <c r="R27" t="n">
-        <v>7017371</v>
+        <v>7017402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3588,11 +3614,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3610,7 +3631,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499578</v>
+        <v>135499577</v>
       </c>
       <c r="B28" t="n">
         <v>96410</v>
@@ -3649,10 +3670,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490951</v>
+        <v>490931</v>
       </c>
       <c r="R28" t="n">
-        <v>7017390</v>
+        <v>7017371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3722,7 +3743,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499579</v>
+        <v>135499578</v>
       </c>
       <c r="B29" t="n">
         <v>96410</v>
@@ -3761,10 +3782,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490976</v>
+        <v>490951</v>
       </c>
       <c r="R29" t="n">
-        <v>7017311</v>
+        <v>7017390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3834,10 +3855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>91488964</v>
+        <v>135499579</v>
       </c>
       <c r="B30" t="n">
-        <v>92632</v>
+        <v>96410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,37 +3866,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>2812</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490939</v>
+        <v>490976</v>
       </c>
       <c r="R30" t="n">
-        <v>7017412</v>
+        <v>7017311</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3899,12 +3924,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3913,54 +3938,61 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>75185505</v>
+        <v>91488964</v>
       </c>
       <c r="B31" t="n">
-        <v>89156</v>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4412</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3970,13 +4002,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490781</v>
+        <v>490939</v>
       </c>
       <c r="R31" t="n">
-        <v>7017384</v>
+        <v>7017412</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4014,19 +4046,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4037,48 +4068,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135499609</v>
+        <v>75185505</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>89156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490849</v>
+        <v>490781</v>
       </c>
       <c r="R32" t="n">
-        <v>7017392</v>
+        <v>7017384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4105,17 +4133,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,47 +4151,26 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499610</v>
+        <v>135499609</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -4206,10 +4208,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490859</v>
+        <v>490849</v>
       </c>
       <c r="R33" t="n">
-        <v>7017416</v>
+        <v>7017392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4244,6 +4246,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4271,12 +4278,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4294,61 +4301,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499531</v>
+        <v>135499610</v>
       </c>
       <c r="B34" t="n">
-        <v>58089</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100090</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490781</v>
+        <v>490859</v>
       </c>
       <c r="R34" t="n">
-        <v>7017369</v>
+        <v>7017416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4383,23 +4377,39 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Synobservation av en individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4417,10 +4427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499510</v>
+        <v>135499531</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>58089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4428,16 +4438,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100090</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4445,12 +4455,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4464,10 +4478,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490891</v>
+        <v>490781</v>
       </c>
       <c r="R35" t="n">
-        <v>7017451</v>
+        <v>7017369</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4504,7 +4518,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Synobservation av en individ med lockläte.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,27 +4532,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4556,7 +4550,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499511</v>
+        <v>135499510</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4589,7 +4583,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4603,10 +4597,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490785</v>
+        <v>490891</v>
       </c>
       <c r="R36" t="n">
-        <v>7017521</v>
+        <v>7017451</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4643,7 +4637,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4657,7 +4651,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -4695,7 +4689,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499512</v>
+        <v>135499511</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4742,10 +4736,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490783</v>
+        <v>490785</v>
       </c>
       <c r="R37" t="n">
-        <v>7017360</v>
+        <v>7017521</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4782,7 +4776,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4797,11 +4791,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4839,27 +4828,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499596</v>
+        <v>135499512</v>
       </c>
       <c r="B38" t="n">
-        <v>58234</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102981</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4867,29 +4856,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490875</v>
+        <v>490783</v>
       </c>
       <c r="R38" t="n">
-        <v>7017470</v>
+        <v>7017360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4926,7 +4915,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4941,6 +4930,31 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4958,10 +4972,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499513</v>
+        <v>135499549</v>
       </c>
       <c r="B39" t="n">
-        <v>58136</v>
+        <v>58231</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4969,21 +4983,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>102980</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4995,7 +5009,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5009,10 +5023,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490763</v>
+        <v>490804</v>
       </c>
       <c r="R39" t="n">
-        <v>7017499</v>
+        <v>7017502</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5049,7 +5063,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Minst 1 överflygande med sång.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5063,12 +5077,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5086,37 +5095,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499514</v>
+        <v>135499596</v>
       </c>
       <c r="B40" t="n">
-        <v>58136</v>
+        <v>58234</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>102981</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5126,11 +5135,7 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
@@ -5140,7 +5145,7 @@
         <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017397</v>
+        <v>7017470</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5177,7 +5182,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5192,11 +5197,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5214,53 +5214,61 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499611</v>
+        <v>135499513</v>
       </c>
       <c r="B41" t="n">
-        <v>99112</v>
+        <v>58136</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490821</v>
+        <v>490763</v>
       </c>
       <c r="R41" t="n">
-        <v>7017504</v>
+        <v>7017499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5297,7 +5305,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5306,13 +5314,17 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5330,53 +5342,61 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499612</v>
+        <v>135499514</v>
       </c>
       <c r="B42" t="n">
-        <v>99112</v>
+        <v>58136</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490848</v>
+        <v>490875</v>
       </c>
       <c r="R42" t="n">
-        <v>7017375</v>
+        <v>7017397</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5411,19 +5431,28 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5441,7 +5470,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499613</v>
+        <v>135499611</v>
       </c>
       <c r="B43" t="n">
         <v>99112</v>
@@ -5484,10 +5513,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490878</v>
+        <v>490821</v>
       </c>
       <c r="R43" t="n">
-        <v>7017368</v>
+        <v>7017504</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5524,7 +5553,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5557,7 +5586,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499614</v>
+        <v>135499612</v>
       </c>
       <c r="B44" t="n">
         <v>99112</v>
@@ -5600,10 +5629,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490867</v>
+        <v>490848</v>
       </c>
       <c r="R44" t="n">
-        <v>7017386</v>
+        <v>7017375</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5636,11 +5665,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5673,7 +5697,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499615</v>
+        <v>135499613</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5716,10 +5740,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490860</v>
+        <v>490878</v>
       </c>
       <c r="R45" t="n">
-        <v>7017386</v>
+        <v>7017368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5789,10 +5813,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499509</v>
+        <v>135499614</v>
       </c>
       <c r="B46" t="n">
-        <v>99219</v>
+        <v>99112</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,28 +5824,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -5832,10 +5856,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490880</v>
+        <v>490867</v>
       </c>
       <c r="R46" t="n">
-        <v>7017365</v>
+        <v>7017386</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5872,7 +5896,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flertalet plantor.</t>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5888,11 +5912,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5910,10 +5929,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499620</v>
+        <v>135499615</v>
       </c>
       <c r="B47" t="n">
-        <v>108205</v>
+        <v>99112</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5921,28 +5940,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220083</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -5953,10 +5972,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490853</v>
+        <v>490860</v>
       </c>
       <c r="R47" t="n">
-        <v>7017483</v>
+        <v>7017386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5989,6 +6008,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6021,10 +6045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499621</v>
+        <v>135499509</v>
       </c>
       <c r="B48" t="n">
-        <v>108205</v>
+        <v>99219</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6032,28 +6056,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6064,10 +6088,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490837</v>
+        <v>490880</v>
       </c>
       <c r="R48" t="n">
-        <v>7017379</v>
+        <v>7017365</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6102,6 +6126,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flertalet plantor.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6115,6 +6144,11 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6132,7 +6166,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499623</v>
+        <v>135499620</v>
       </c>
       <c r="B49" t="n">
         <v>108205</v>
@@ -6164,7 +6198,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6175,10 +6209,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490848</v>
+        <v>490853</v>
       </c>
       <c r="R49" t="n">
-        <v>7017376</v>
+        <v>7017483</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6243,7 +6277,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499624</v>
+        <v>135499621</v>
       </c>
       <c r="B50" t="n">
         <v>108205</v>
@@ -6286,10 +6320,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490861</v>
+        <v>490837</v>
       </c>
       <c r="R50" t="n">
-        <v>7017386</v>
+        <v>7017379</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6354,7 +6388,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499625</v>
+        <v>135499623</v>
       </c>
       <c r="B51" t="n">
         <v>108205</v>
@@ -6386,7 +6420,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6397,10 +6431,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490821</v>
+        <v>490848</v>
       </c>
       <c r="R51" t="n">
-        <v>7017394</v>
+        <v>7017376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6465,7 +6499,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499626</v>
+        <v>135499624</v>
       </c>
       <c r="B52" t="n">
         <v>108205</v>
@@ -6497,7 +6531,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6508,10 +6542,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490841</v>
+        <v>490861</v>
       </c>
       <c r="R52" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6576,10 +6610,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499550</v>
+        <v>135499625</v>
       </c>
       <c r="B53" t="n">
-        <v>108274</v>
+        <v>108205</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6587,28 +6621,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6619,10 +6653,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490929</v>
+        <v>490821</v>
       </c>
       <c r="R53" t="n">
-        <v>7017429</v>
+        <v>7017394</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6687,10 +6721,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499551</v>
+        <v>135499626</v>
       </c>
       <c r="B54" t="n">
-        <v>108274</v>
+        <v>108205</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6698,28 +6732,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -6730,10 +6764,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490853</v>
+        <v>490841</v>
       </c>
       <c r="R54" t="n">
-        <v>7017480</v>
+        <v>7017433</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6766,11 +6800,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6803,7 +6832,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499552</v>
+        <v>135499550</v>
       </c>
       <c r="B55" t="n">
         <v>108274</v>
@@ -6846,10 +6875,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490867</v>
+        <v>490929</v>
       </c>
       <c r="R55" t="n">
-        <v>7017480</v>
+        <v>7017429</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6914,7 +6943,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499553</v>
+        <v>135499551</v>
       </c>
       <c r="B56" t="n">
         <v>108274</v>
@@ -6957,10 +6986,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R56" t="n">
-        <v>7017457</v>
+        <v>7017480</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6993,6 +7022,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7025,7 +7059,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499554</v>
+        <v>135499552</v>
       </c>
       <c r="B57" t="n">
         <v>108274</v>
@@ -7068,10 +7102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490737</v>
+        <v>490867</v>
       </c>
       <c r="R57" t="n">
-        <v>7017474</v>
+        <v>7017480</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7136,7 +7170,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499555</v>
+        <v>135499553</v>
       </c>
       <c r="B58" t="n">
         <v>108274</v>
@@ -7179,10 +7213,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490873</v>
+        <v>490841</v>
       </c>
       <c r="R58" t="n">
-        <v>7017368</v>
+        <v>7017457</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7247,7 +7281,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499556</v>
+        <v>135499554</v>
       </c>
       <c r="B59" t="n">
         <v>108274</v>
@@ -7290,10 +7324,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490863</v>
+        <v>490737</v>
       </c>
       <c r="R59" t="n">
-        <v>7017386</v>
+        <v>7017474</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7341,11 +7375,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7363,10 +7392,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499544</v>
+        <v>135499555</v>
       </c>
       <c r="B60" t="n">
-        <v>111153</v>
+        <v>108274</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,28 +7403,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7406,10 +7435,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490844</v>
+        <v>490873</v>
       </c>
       <c r="R60" t="n">
-        <v>7017468</v>
+        <v>7017368</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7474,10 +7503,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499546</v>
+        <v>135499556</v>
       </c>
       <c r="B61" t="n">
-        <v>111153</v>
+        <v>108274</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7485,28 +7514,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7517,10 +7546,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490780</v>
+        <v>490863</v>
       </c>
       <c r="R61" t="n">
-        <v>7017405</v>
+        <v>7017386</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7568,6 +7597,11 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7585,7 +7619,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499547</v>
+        <v>135499544</v>
       </c>
       <c r="B62" t="n">
         <v>111153</v>
@@ -7617,7 +7651,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7628,10 +7662,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490858</v>
+        <v>490844</v>
       </c>
       <c r="R62" t="n">
-        <v>7017416</v>
+        <v>7017468</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7696,7 +7730,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499548</v>
+        <v>135499546</v>
       </c>
       <c r="B63" t="n">
         <v>111153</v>
@@ -7728,7 +7762,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -7739,10 +7773,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490964</v>
+        <v>490780</v>
       </c>
       <c r="R63" t="n">
-        <v>7017356</v>
+        <v>7017405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7790,11 +7824,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7812,10 +7841,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499617</v>
+        <v>135499547</v>
       </c>
       <c r="B64" t="n">
-        <v>110150</v>
+        <v>111153</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7823,28 +7852,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220294</v>
+        <v>220240</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -7855,10 +7884,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490864</v>
+        <v>490858</v>
       </c>
       <c r="R64" t="n">
-        <v>7017486</v>
+        <v>7017416</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7891,11 +7920,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7928,47 +7952,39 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499580</v>
+        <v>135499548</v>
       </c>
       <c r="B65" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -7979,10 +7995,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490975</v>
+        <v>490964</v>
       </c>
       <c r="R65" t="n">
-        <v>7017304</v>
+        <v>7017356</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,11 +8031,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8057,47 +8068,39 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499583</v>
+        <v>135499617</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>110150</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -8108,10 +8111,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490768</v>
+        <v>490864</v>
       </c>
       <c r="R66" t="n">
-        <v>7017376</v>
+        <v>7017486</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8148,7 +8151,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8164,11 +8167,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8186,7 +8184,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499584</v>
+        <v>135499580</v>
       </c>
       <c r="B67" t="n">
         <v>99195</v>
@@ -8216,7 +8214,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8237,10 +8235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490839</v>
+        <v>490975</v>
       </c>
       <c r="R67" t="n">
-        <v>7017351</v>
+        <v>7017304</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8277,7 +8275,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8292,7 +8290,12 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8310,7 +8313,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499585</v>
+        <v>135499581</v>
       </c>
       <c r="B68" t="n">
         <v>99195</v>
@@ -8340,7 +8343,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8361,10 +8364,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490845</v>
+        <v>490951</v>
       </c>
       <c r="R68" t="n">
-        <v>7017392</v>
+        <v>7017428</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8401,7 +8404,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8416,7 +8419,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8434,7 +8437,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499586</v>
+        <v>135499582</v>
       </c>
       <c r="B69" t="n">
         <v>99195</v>
@@ -8485,10 +8488,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490812</v>
+        <v>490884</v>
       </c>
       <c r="R69" t="n">
-        <v>7017401</v>
+        <v>7017471</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8525,7 +8528,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8540,12 +8543,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8563,7 +8561,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499588</v>
+        <v>135499583</v>
       </c>
       <c r="B70" t="n">
         <v>99195</v>
@@ -8593,7 +8591,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8614,10 +8612,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490843</v>
+        <v>490768</v>
       </c>
       <c r="R70" t="n">
-        <v>7017436</v>
+        <v>7017376</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8654,7 +8652,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8692,7 +8690,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499589</v>
+        <v>135499584</v>
       </c>
       <c r="B71" t="n">
         <v>99195</v>
@@ -8722,7 +8720,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8743,10 +8741,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490967</v>
+        <v>490839</v>
       </c>
       <c r="R71" t="n">
-        <v>7017335</v>
+        <v>7017351</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8783,7 +8781,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8798,12 +8796,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8821,7 +8814,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499590</v>
+        <v>135499585</v>
       </c>
       <c r="B72" t="n">
         <v>99195</v>
@@ -8851,7 +8844,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8872,10 +8865,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490979</v>
+        <v>490845</v>
       </c>
       <c r="R72" t="n">
-        <v>7017360</v>
+        <v>7017392</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8912,7 +8905,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8927,12 +8920,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8950,7 +8938,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499591</v>
+        <v>135499586</v>
       </c>
       <c r="B73" t="n">
         <v>99195</v>
@@ -8980,7 +8968,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9001,10 +8989,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490973</v>
+        <v>490812</v>
       </c>
       <c r="R73" t="n">
-        <v>7017399</v>
+        <v>7017401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9041,7 +9029,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9079,7 +9067,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499592</v>
+        <v>135499588</v>
       </c>
       <c r="B74" t="n">
         <v>99195</v>
@@ -9109,7 +9097,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9130,10 +9118,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490951</v>
+        <v>490843</v>
       </c>
       <c r="R74" t="n">
-        <v>7017408</v>
+        <v>7017436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9170,7 +9158,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9208,7 +9196,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499593</v>
+        <v>135499589</v>
       </c>
       <c r="B75" t="n">
         <v>99195</v>
@@ -9238,7 +9226,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9259,10 +9247,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490951</v>
+        <v>490967</v>
       </c>
       <c r="R75" t="n">
-        <v>7017396</v>
+        <v>7017335</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9299,7 +9287,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9337,7 +9325,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499594</v>
+        <v>135499590</v>
       </c>
       <c r="B76" t="n">
         <v>99195</v>
@@ -9367,7 +9355,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9388,10 +9376,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490957</v>
+        <v>490979</v>
       </c>
       <c r="R76" t="n">
-        <v>7017386</v>
+        <v>7017360</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9428,7 +9416,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9466,37 +9454,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499519</v>
+        <v>135499591</v>
       </c>
       <c r="B77" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490752</v>
+        <v>490973</v>
       </c>
       <c r="R77" t="n">
-        <v>7017499</v>
+        <v>7017399</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9561,6 +9561,11 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9578,39 +9583,47 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499516</v>
+        <v>135499592</v>
       </c>
       <c r="B78" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -9621,10 +9634,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490844</v>
+        <v>490951</v>
       </c>
       <c r="R78" t="n">
-        <v>7017394</v>
+        <v>7017408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9659,6 +9672,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9672,6 +9690,11 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9689,39 +9712,47 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499517</v>
+        <v>135499593</v>
       </c>
       <c r="B79" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -9732,10 +9763,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490814</v>
+        <v>490951</v>
       </c>
       <c r="R79" t="n">
-        <v>7017404</v>
+        <v>7017396</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9770,6 +9801,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9783,6 +9819,11 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9800,39 +9841,47 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499627</v>
+        <v>135499594</v>
       </c>
       <c r="B80" t="n">
-        <v>101403</v>
+        <v>99195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -9843,10 +9892,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490803</v>
+        <v>490957</v>
       </c>
       <c r="R80" t="n">
-        <v>7017492</v>
+        <v>7017386</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9881,6 +9930,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9894,6 +9948,11 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9911,10 +9970,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499628</v>
+        <v>135499519</v>
       </c>
       <c r="B81" t="n">
-        <v>101403</v>
+        <v>98060</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9922,30 +9981,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -9954,10 +10009,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490792</v>
+        <v>490752</v>
       </c>
       <c r="R81" t="n">
-        <v>7017441</v>
+        <v>7017499</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9990,6 +10045,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10022,10 +10082,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499629</v>
+        <v>135499516</v>
       </c>
       <c r="B82" t="n">
-        <v>101403</v>
+        <v>99217</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10033,28 +10093,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10065,10 +10125,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490764</v>
+        <v>490844</v>
       </c>
       <c r="R82" t="n">
-        <v>7017441</v>
+        <v>7017394</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10133,10 +10193,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499630</v>
+        <v>135499517</v>
       </c>
       <c r="B83" t="n">
-        <v>101403</v>
+        <v>99217</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10144,28 +10204,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -10176,10 +10236,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490798</v>
+        <v>490814</v>
       </c>
       <c r="R83" t="n">
-        <v>7017366</v>
+        <v>7017404</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10244,7 +10304,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499631</v>
+        <v>135499627</v>
       </c>
       <c r="B84" t="n">
         <v>101403</v>
@@ -10287,10 +10347,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490816</v>
+        <v>490803</v>
       </c>
       <c r="R84" t="n">
-        <v>7017378</v>
+        <v>7017492</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10355,7 +10415,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499632</v>
+        <v>135499628</v>
       </c>
       <c r="B85" t="n">
         <v>101403</v>
@@ -10398,10 +10458,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490796</v>
+        <v>490792</v>
       </c>
       <c r="R85" t="n">
-        <v>7017382</v>
+        <v>7017441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10466,7 +10526,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499633</v>
+        <v>135499629</v>
       </c>
       <c r="B86" t="n">
         <v>101403</v>
@@ -10509,10 +10569,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490782</v>
+        <v>490764</v>
       </c>
       <c r="R86" t="n">
-        <v>7017407</v>
+        <v>7017441</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10577,7 +10637,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499634</v>
+        <v>135499630</v>
       </c>
       <c r="B87" t="n">
         <v>101403</v>
@@ -10620,10 +10680,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490730</v>
+        <v>490798</v>
       </c>
       <c r="R87" t="n">
-        <v>7017371</v>
+        <v>7017366</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10688,7 +10748,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499635</v>
+        <v>135499631</v>
       </c>
       <c r="B88" t="n">
         <v>101403</v>
@@ -10731,10 +10791,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490827</v>
+        <v>490816</v>
       </c>
       <c r="R88" t="n">
-        <v>7017356</v>
+        <v>7017378</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10799,7 +10859,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499636</v>
+        <v>135499632</v>
       </c>
       <c r="B89" t="n">
         <v>101403</v>
@@ -10842,10 +10902,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490844</v>
+        <v>490796</v>
       </c>
       <c r="R89" t="n">
-        <v>7017345</v>
+        <v>7017382</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10910,7 +10970,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499637</v>
+        <v>135499633</v>
       </c>
       <c r="B90" t="n">
         <v>101403</v>
@@ -10953,10 +11013,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490852</v>
+        <v>490782</v>
       </c>
       <c r="R90" t="n">
-        <v>7017373</v>
+        <v>7017407</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11003,7 +11063,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11021,7 +11081,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499638</v>
+        <v>135499634</v>
       </c>
       <c r="B91" t="n">
         <v>101403</v>
@@ -11064,10 +11124,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490882</v>
+        <v>490730</v>
       </c>
       <c r="R91" t="n">
-        <v>7017368</v>
+        <v>7017371</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11114,7 +11174,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11132,7 +11192,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499639</v>
+        <v>135499635</v>
       </c>
       <c r="B92" t="n">
         <v>101403</v>
@@ -11175,10 +11235,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490865</v>
+        <v>490827</v>
       </c>
       <c r="R92" t="n">
-        <v>7017386</v>
+        <v>7017356</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11243,7 +11303,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499640</v>
+        <v>135499636</v>
       </c>
       <c r="B93" t="n">
         <v>101403</v>
@@ -11286,10 +11346,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490840</v>
+        <v>490844</v>
       </c>
       <c r="R93" t="n">
-        <v>7017433</v>
+        <v>7017345</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11354,7 +11414,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499641</v>
+        <v>135499637</v>
       </c>
       <c r="B94" t="n">
         <v>101403</v>
@@ -11397,10 +11457,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490880</v>
+        <v>490852</v>
       </c>
       <c r="R94" t="n">
-        <v>7017422</v>
+        <v>7017373</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11447,7 +11507,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11465,10 +11525,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499618</v>
+        <v>135499638</v>
       </c>
       <c r="B95" t="n">
-        <v>98214</v>
+        <v>101403</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11476,21 +11536,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11508,10 +11568,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490791</v>
+        <v>490882</v>
       </c>
       <c r="R95" t="n">
-        <v>7017443</v>
+        <v>7017368</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11546,11 +11606,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11563,7 +11618,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11581,10 +11636,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499619</v>
+        <v>135499639</v>
       </c>
       <c r="B96" t="n">
-        <v>98214</v>
+        <v>101403</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11592,33 +11647,25 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -11632,10 +11679,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490868</v>
+        <v>490865</v>
       </c>
       <c r="R96" t="n">
-        <v>7017387</v>
+        <v>7017386</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11670,11 +11717,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11688,11 +11730,6 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11710,10 +11747,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499520</v>
+        <v>135499640</v>
       </c>
       <c r="B97" t="n">
-        <v>99001</v>
+        <v>101403</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11721,21 +11758,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11753,10 +11790,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490757</v>
+        <v>490840</v>
       </c>
       <c r="R97" t="n">
-        <v>7017472</v>
+        <v>7017433</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11821,10 +11858,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499521</v>
+        <v>135499641</v>
       </c>
       <c r="B98" t="n">
-        <v>99001</v>
+        <v>101403</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11832,21 +11869,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11864,10 +11901,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490966</v>
+        <v>490880</v>
       </c>
       <c r="R98" t="n">
-        <v>7017430</v>
+        <v>7017422</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11932,10 +11969,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499522</v>
+        <v>135499618</v>
       </c>
       <c r="B99" t="n">
-        <v>99001</v>
+        <v>98214</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11943,21 +11980,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11975,10 +12012,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490920</v>
+        <v>490791</v>
       </c>
       <c r="R99" t="n">
-        <v>7017445</v>
+        <v>7017443</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12011,6 +12048,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12043,10 +12085,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499523</v>
+        <v>135499619</v>
       </c>
       <c r="B100" t="n">
-        <v>99001</v>
+        <v>98214</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12054,25 +12096,33 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12086,10 +12136,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490912</v>
+        <v>490868</v>
       </c>
       <c r="R100" t="n">
-        <v>7017466</v>
+        <v>7017387</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12124,6 +12174,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12137,6 +12192,11 @@
       <c r="AH100" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12154,7 +12214,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499524</v>
+        <v>135499520</v>
       </c>
       <c r="B101" t="n">
         <v>99001</v>
@@ -12197,10 +12257,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490858</v>
+        <v>490757</v>
       </c>
       <c r="R101" t="n">
-        <v>7017493</v>
+        <v>7017472</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12265,7 +12325,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499525</v>
+        <v>135499521</v>
       </c>
       <c r="B102" t="n">
         <v>99001</v>
@@ -12297,7 +12357,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12308,10 +12368,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490804</v>
+        <v>490966</v>
       </c>
       <c r="R102" t="n">
-        <v>7017492</v>
+        <v>7017430</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12376,7 +12436,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499526</v>
+        <v>135499522</v>
       </c>
       <c r="B103" t="n">
         <v>99001</v>
@@ -12419,10 +12479,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490740</v>
+        <v>490920</v>
       </c>
       <c r="R103" t="n">
-        <v>7017423</v>
+        <v>7017445</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12487,7 +12547,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499527</v>
+        <v>135499523</v>
       </c>
       <c r="B104" t="n">
         <v>99001</v>
@@ -12530,10 +12590,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490732</v>
+        <v>490912</v>
       </c>
       <c r="R104" t="n">
-        <v>7017370</v>
+        <v>7017466</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12598,7 +12658,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499528</v>
+        <v>135499524</v>
       </c>
       <c r="B105" t="n">
         <v>99001</v>
@@ -12641,10 +12701,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490867</v>
+        <v>490858</v>
       </c>
       <c r="R105" t="n">
-        <v>7017386</v>
+        <v>7017493</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12677,11 +12737,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12714,7 +12769,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499529</v>
+        <v>135499525</v>
       </c>
       <c r="B106" t="n">
         <v>99001</v>
@@ -12746,7 +12801,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -12757,10 +12812,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490807</v>
+        <v>490804</v>
       </c>
       <c r="R106" t="n">
-        <v>7017431</v>
+        <v>7017492</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12825,7 +12880,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499530</v>
+        <v>135499526</v>
       </c>
       <c r="B107" t="n">
         <v>99001</v>
@@ -12857,7 +12912,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -12868,10 +12923,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490932</v>
+        <v>490740</v>
       </c>
       <c r="R107" t="n">
-        <v>7017369</v>
+        <v>7017423</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12936,10 +12991,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499597</v>
+        <v>135499527</v>
       </c>
       <c r="B108" t="n">
-        <v>98249</v>
+        <v>99001</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12947,21 +13002,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12979,10 +13034,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490969</v>
+        <v>490732</v>
       </c>
       <c r="R108" t="n">
-        <v>7017431</v>
+        <v>7017370</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13047,10 +13102,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499598</v>
+        <v>135499528</v>
       </c>
       <c r="B109" t="n">
-        <v>98249</v>
+        <v>99001</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13058,21 +13113,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13090,10 +13145,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490840</v>
+        <v>490867</v>
       </c>
       <c r="R109" t="n">
-        <v>7017457</v>
+        <v>7017386</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13126,6 +13181,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13158,10 +13218,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499599</v>
+        <v>135499529</v>
       </c>
       <c r="B110" t="n">
-        <v>98249</v>
+        <v>99001</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13169,21 +13229,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13201,10 +13261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490831</v>
+        <v>490807</v>
       </c>
       <c r="R110" t="n">
-        <v>7017486</v>
+        <v>7017431</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13269,10 +13329,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499600</v>
+        <v>135499530</v>
       </c>
       <c r="B111" t="n">
-        <v>98249</v>
+        <v>99001</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13280,28 +13340,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13312,10 +13372,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490797</v>
+        <v>490932</v>
       </c>
       <c r="R111" t="n">
-        <v>7017497</v>
+        <v>7017369</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13380,7 +13440,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499601</v>
+        <v>135499597</v>
       </c>
       <c r="B112" t="n">
         <v>98249</v>
@@ -13423,10 +13483,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490797</v>
+        <v>490969</v>
       </c>
       <c r="R112" t="n">
-        <v>7017511</v>
+        <v>7017431</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13491,7 +13551,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499602</v>
+        <v>135499598</v>
       </c>
       <c r="B113" t="n">
         <v>98249</v>
@@ -13534,10 +13594,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490737</v>
+        <v>490840</v>
       </c>
       <c r="R113" t="n">
-        <v>7017473</v>
+        <v>7017457</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13602,10 +13662,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499515</v>
+        <v>135499599</v>
       </c>
       <c r="B114" t="n">
-        <v>101940</v>
+        <v>98249</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13613,21 +13673,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223366</v>
+        <v>223358</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13645,10 +13705,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490788</v>
+        <v>490831</v>
       </c>
       <c r="R114" t="n">
-        <v>7017450</v>
+        <v>7017486</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13713,10 +13773,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499532</v>
+        <v>135499600</v>
       </c>
       <c r="B115" t="n">
-        <v>101293</v>
+        <v>98249</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13724,21 +13784,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13756,10 +13816,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490889</v>
+        <v>490797</v>
       </c>
       <c r="R115" t="n">
-        <v>7017459</v>
+        <v>7017497</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13824,10 +13884,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499533</v>
+        <v>135499601</v>
       </c>
       <c r="B116" t="n">
-        <v>101293</v>
+        <v>98249</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13835,21 +13895,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13867,10 +13927,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490743</v>
+        <v>490797</v>
       </c>
       <c r="R116" t="n">
-        <v>7017495</v>
+        <v>7017511</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13935,10 +13995,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499534</v>
+        <v>135499602</v>
       </c>
       <c r="B117" t="n">
-        <v>101293</v>
+        <v>98249</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13946,21 +14006,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13981,7 +14041,7 @@
         <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017474</v>
+        <v>7017473</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14046,10 +14106,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499535</v>
+        <v>135499515</v>
       </c>
       <c r="B118" t="n">
-        <v>101293</v>
+        <v>101940</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14057,21 +14117,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>224885</v>
+        <v>223366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14089,10 +14149,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490734</v>
+        <v>490788</v>
       </c>
       <c r="R118" t="n">
-        <v>7017429</v>
+        <v>7017450</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14157,7 +14217,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499536</v>
+        <v>135499532</v>
       </c>
       <c r="B119" t="n">
         <v>101293</v>
@@ -14200,10 +14260,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490780</v>
+        <v>490889</v>
       </c>
       <c r="R119" t="n">
-        <v>7017405</v>
+        <v>7017459</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14268,7 +14328,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499537</v>
+        <v>135499533</v>
       </c>
       <c r="B120" t="n">
         <v>101293</v>
@@ -14311,10 +14371,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490751</v>
+        <v>490743</v>
       </c>
       <c r="R120" t="n">
-        <v>7017406</v>
+        <v>7017495</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14379,7 +14439,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499538</v>
+        <v>135499534</v>
       </c>
       <c r="B121" t="n">
         <v>101293</v>
@@ -14422,10 +14482,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490729</v>
+        <v>490737</v>
       </c>
       <c r="R121" t="n">
-        <v>7017373</v>
+        <v>7017474</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14490,7 +14550,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499540</v>
+        <v>135499535</v>
       </c>
       <c r="B122" t="n">
         <v>101293</v>
@@ -14533,10 +14593,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490847</v>
+        <v>490734</v>
       </c>
       <c r="R122" t="n">
-        <v>7017345</v>
+        <v>7017429</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14601,7 +14661,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499541</v>
+        <v>135499536</v>
       </c>
       <c r="B123" t="n">
         <v>101293</v>
@@ -14644,10 +14704,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490856</v>
+        <v>490780</v>
       </c>
       <c r="R123" t="n">
-        <v>7017358</v>
+        <v>7017405</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14712,7 +14772,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499542</v>
+        <v>135499537</v>
       </c>
       <c r="B124" t="n">
         <v>101293</v>
@@ -14744,7 +14804,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -14755,10 +14815,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490840</v>
+        <v>490751</v>
       </c>
       <c r="R124" t="n">
-        <v>7017433</v>
+        <v>7017406</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14820,6 +14880,450 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>135499538</v>
+      </c>
+      <c r="B125" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>490729</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7017373</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>135499540</v>
+      </c>
+      <c r="B126" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>490847</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7017345</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>135499541</v>
+      </c>
+      <c r="B127" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>490856</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7017358</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>135499542</v>
+      </c>
+      <c r="B128" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>490840</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7017433</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY128"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499607</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -938,6 +948,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499608</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1073,6 +1088,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499603</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1208,6 +1228,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499604</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1343,6 +1368,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499605</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1478,6 +1508,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499606</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1578,6 +1613,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75185503</t>
         </is>
       </c>
     </row>
@@ -1687,6 +1727,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499557</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1794,6 +1839,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499558</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1906,6 +1956,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499560</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2013,6 +2068,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499561</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2120,6 +2180,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499562</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2227,6 +2292,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499563</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2334,6 +2404,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499564</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2441,6 +2516,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499565</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2548,6 +2628,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499566</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2655,6 +2740,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499567</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2762,6 +2852,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499568</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2874,6 +2969,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499569</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2981,6 +3081,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499570</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3093,6 +3198,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499571</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3200,6 +3310,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499572</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3307,6 +3422,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499573</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3414,6 +3534,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499574</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3521,6 +3646,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499575</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3628,6 +3758,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499576</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3740,6 +3875,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499577</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3852,6 +3992,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499578</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3964,6 +4109,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499579</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4065,6 +4215,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91488964</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4165,6 +4320,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75185505</t>
         </is>
       </c>
     </row>
@@ -4298,6 +4458,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499609</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4424,6 +4589,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499610</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4547,6 +4717,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499531</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4686,6 +4861,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499510</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4825,6 +5005,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499511</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4969,6 +5154,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499512</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5092,6 +5282,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499549</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5211,6 +5406,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499596</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5339,6 +5539,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499513</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5467,6 +5672,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499514</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5583,6 +5793,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499611</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5694,6 +5909,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499612</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5810,6 +6030,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499613</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5926,6 +6151,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499614</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6042,6 +6272,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499615</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6163,6 +6398,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499509</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6274,6 +6514,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499620</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6385,6 +6630,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499621</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6496,6 +6746,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499623</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6607,6 +6862,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499624</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6718,6 +6978,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499625</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6829,6 +7094,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499626</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6940,6 +7210,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499550</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7056,6 +7331,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499551</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7167,6 +7447,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499552</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7278,6 +7563,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499553</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7389,6 +7679,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499554</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7500,6 +7795,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499555</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7616,6 +7916,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499556</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7727,6 +8032,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499544</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7838,6 +8148,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499546</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7949,6 +8264,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499547</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8065,6 +8385,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499548</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8181,6 +8506,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499617</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8310,6 +8640,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499580</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8434,6 +8769,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499581</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8558,6 +8898,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499582</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8687,6 +9032,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499583</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8811,6 +9161,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499584</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8935,6 +9290,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499585</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9064,6 +9424,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499586</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9193,6 +9558,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499588</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9322,6 +9692,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499589</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9451,6 +9826,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499590</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9580,6 +9960,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499591</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9709,6 +10094,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499592</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9838,6 +10228,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499593</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9967,6 +10362,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499594</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10079,6 +10479,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499519</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10190,6 +10595,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499516</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10301,6 +10711,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499517</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10412,6 +10827,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499627</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10523,6 +10943,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499628</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10634,6 +11059,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499629</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10745,6 +11175,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499630</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10856,6 +11291,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499631</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10967,6 +11407,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499632</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11078,6 +11523,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499633</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11189,6 +11639,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499634</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11300,6 +11755,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499635</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11411,6 +11871,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499636</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11522,6 +11987,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499637</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11633,6 +12103,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499638</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11744,6 +12219,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499639</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11855,6 +12335,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499640</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11966,6 +12451,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499641</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12082,6 +12572,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499618</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12211,6 +12706,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499619</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12322,6 +12822,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499520</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12433,6 +12938,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499521</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12544,6 +13054,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499522</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12655,6 +13170,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499523</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12766,6 +13286,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499524</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12877,6 +13402,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499525</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12988,6 +13518,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499526</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13099,6 +13634,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499527</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13215,6 +13755,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499528</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13326,6 +13871,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499529</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13437,6 +13987,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499530</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13548,6 +14103,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499597</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13659,6 +14219,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499598</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13770,6 +14335,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499599</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13881,6 +14451,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499600</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13992,6 +14567,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499601</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14103,6 +14683,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499602</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14214,6 +14799,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499515</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14325,6 +14915,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499532</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14436,6 +15031,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499533</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14547,6 +15147,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499534</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14658,6 +15263,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499535</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14769,6 +15379,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499536</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14880,6 +15495,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499537</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14991,6 +15611,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499538</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15102,6 +15727,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499540</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15213,6 +15843,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499541</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15324,8 +15959,142 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499542</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ128"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499607</v>
+        <v>135499608</v>
       </c>
       <c r="B2" t="n">
-        <v>99101</v>
+        <v>99148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490869</v>
+        <v>490867</v>
       </c>
       <c r="R2" t="n">
-        <v>7017370</v>
+        <v>7017387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad snitslad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +790,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkrikt fuktstråk.</t>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,71 +812,58 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499607</t>
+          <t>https://artportalen.se/Sighting/135499608</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499608</v>
+        <v>135499603</v>
       </c>
       <c r="B3" t="n">
-        <v>99101</v>
+        <v>92012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490867</v>
+        <v>490968</v>
       </c>
       <c r="R3" t="n">
-        <v>7017387</v>
+        <v>7017430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,7 +900,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,9 +918,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,16 +952,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499608</t>
+          <t>https://artportalen.se/Sighting/135499603</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499603</v>
+        <v>135499604</v>
       </c>
       <c r="B4" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,10 +1000,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490968</v>
+        <v>490893</v>
       </c>
       <c r="R4" t="n">
-        <v>7017430</v>
+        <v>7017459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,12 +1070,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,16 +1092,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499603</t>
+          <t>https://artportalen.se/Sighting/135499604</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499604</v>
+        <v>135499605</v>
       </c>
       <c r="B5" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,10 +1140,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490893</v>
+        <v>490741</v>
       </c>
       <c r="R5" t="n">
-        <v>7017459</v>
+        <v>7017465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1178,7 +1180,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,16 +1232,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499604</t>
+          <t>https://artportalen.se/Sighting/135499605</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499605</v>
+        <v>135499606</v>
       </c>
       <c r="B6" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,10 +1280,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490741</v>
+        <v>490951</v>
       </c>
       <c r="R6" t="n">
-        <v>7017465</v>
+        <v>7017411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1320,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1348,12 +1350,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1370,16 +1372,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499605</t>
+          <t>https://artportalen.se/Sighting/135499606</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135499606</v>
+        <v>75185503</v>
       </c>
       <c r="B7" t="n">
-        <v>91970</v>
+        <v>87322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,41 +1389,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1988</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490951</v>
+        <v>490758</v>
       </c>
       <c r="R7" t="n">
-        <v>7017411</v>
+        <v>7017384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1448,17 +1443,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1471,90 +1461,73 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499606</t>
+          <t>https://artportalen.se/Sighting/75185503</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75185503</v>
+        <v>135499557</v>
       </c>
       <c r="B8" t="n">
-        <v>87322</v>
+        <v>96454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1988</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490758</v>
+        <v>490738</v>
       </c>
       <c r="R8" t="n">
-        <v>7017384</v>
+        <v>7017396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1581,12 +1554,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,34 +1572,35 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185503</t>
+          <t>https://artportalen.se/Sighting/135499557</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499557</v>
+        <v>135499558</v>
       </c>
       <c r="B9" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1662,10 +1636,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490738</v>
+        <v>490991</v>
       </c>
       <c r="R9" t="n">
-        <v>7017396</v>
+        <v>7017297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1729,16 +1703,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499557</t>
+          <t>https://artportalen.se/Sighting/135499558</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499558</v>
+        <v>135499560</v>
       </c>
       <c r="B10" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,10 +1748,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490991</v>
+        <v>490966</v>
       </c>
       <c r="R10" t="n">
-        <v>7017297</v>
+        <v>7017426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,6 +1801,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1841,16 +1820,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499558</t>
+          <t>https://artportalen.se/Sighting/135499560</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499560</v>
+        <v>135499561</v>
       </c>
       <c r="B11" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,10 +1865,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490966</v>
+        <v>490929</v>
       </c>
       <c r="R11" t="n">
-        <v>7017426</v>
+        <v>7017441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1936,12 +1915,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1958,16 +1932,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499560</t>
+          <t>https://artportalen.se/Sighting/135499561</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499561</v>
+        <v>135499562</v>
       </c>
       <c r="B12" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,10 +1977,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490929</v>
+        <v>490910</v>
       </c>
       <c r="R12" t="n">
-        <v>7017441</v>
+        <v>7017467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2070,16 +2044,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499561</t>
+          <t>https://artportalen.se/Sighting/135499562</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499562</v>
+        <v>135499563</v>
       </c>
       <c r="B13" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,10 +2089,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490910</v>
+        <v>490878</v>
       </c>
       <c r="R13" t="n">
-        <v>7017467</v>
+        <v>7017474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,7 +2139,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2182,16 +2156,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499562</t>
+          <t>https://artportalen.se/Sighting/135499563</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499563</v>
+        <v>135499564</v>
       </c>
       <c r="B14" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,10 +2201,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490878</v>
+        <v>490883</v>
       </c>
       <c r="R14" t="n">
-        <v>7017474</v>
+        <v>7017462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2277,7 +2251,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2294,16 +2268,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499563</t>
+          <t>https://artportalen.se/Sighting/135499564</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499564</v>
+        <v>135499565</v>
       </c>
       <c r="B15" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2339,10 +2313,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490883</v>
+        <v>490756</v>
       </c>
       <c r="R15" t="n">
-        <v>7017462</v>
+        <v>7017472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2389,7 +2363,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2406,16 +2380,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499564</t>
+          <t>https://artportalen.se/Sighting/135499565</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499565</v>
+        <v>135499566</v>
       </c>
       <c r="B16" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2451,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490756</v>
+        <v>490790</v>
       </c>
       <c r="R16" t="n">
-        <v>7017472</v>
+        <v>7017441</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2518,16 +2492,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499565</t>
+          <t>https://artportalen.se/Sighting/135499566</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499566</v>
+        <v>135499567</v>
       </c>
       <c r="B17" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490790</v>
+        <v>490732</v>
       </c>
       <c r="R17" t="n">
-        <v>7017441</v>
+        <v>7017442</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2613,7 +2587,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2630,16 +2604,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499566</t>
+          <t>https://artportalen.se/Sighting/135499567</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499567</v>
+        <v>135499568</v>
       </c>
       <c r="B18" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,10 +2649,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490732</v>
+        <v>490781</v>
       </c>
       <c r="R18" t="n">
-        <v>7017442</v>
+        <v>7017407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2725,7 +2699,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2742,16 +2716,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499567</t>
+          <t>https://artportalen.se/Sighting/135499568</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499568</v>
+        <v>135499569</v>
       </c>
       <c r="B19" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490781</v>
+        <v>490731</v>
       </c>
       <c r="R19" t="n">
-        <v>7017407</v>
+        <v>7017371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2840,6 +2814,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2854,16 +2833,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499568</t>
+          <t>https://artportalen.se/Sighting/135499569</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499569</v>
+        <v>135499570</v>
       </c>
       <c r="B20" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2899,10 +2878,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490731</v>
+        <v>490854</v>
       </c>
       <c r="R20" t="n">
-        <v>7017371</v>
+        <v>7017345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2952,11 +2931,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2971,16 +2945,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499569</t>
+          <t>https://artportalen.se/Sighting/135499570</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499570</v>
+        <v>135499571</v>
       </c>
       <c r="B21" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,10 +2990,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490854</v>
+        <v>490878</v>
       </c>
       <c r="R21" t="n">
-        <v>7017345</v>
+        <v>7017366</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,6 +3028,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3083,16 +3062,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499570</t>
+          <t>https://artportalen.se/Sighting/135499571</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499571</v>
+        <v>135499572</v>
       </c>
       <c r="B22" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3128,10 +3107,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490878</v>
+        <v>490867</v>
       </c>
       <c r="R22" t="n">
-        <v>7017366</v>
+        <v>7017386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3166,11 +3145,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3200,16 +3174,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499571</t>
+          <t>https://artportalen.se/Sighting/135499572</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499572</v>
+        <v>135499573</v>
       </c>
       <c r="B23" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,10 +3219,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490867</v>
+        <v>490840</v>
       </c>
       <c r="R23" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3312,16 +3286,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499572</t>
+          <t>https://artportalen.se/Sighting/135499573</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499573</v>
+        <v>135499574</v>
       </c>
       <c r="B24" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3357,10 +3331,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490840</v>
+        <v>490844</v>
       </c>
       <c r="R24" t="n">
-        <v>7017433</v>
+        <v>7017436</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,16 +3398,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499573</t>
+          <t>https://artportalen.se/Sighting/135499574</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499574</v>
+        <v>135499575</v>
       </c>
       <c r="B25" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,10 +3443,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490844</v>
+        <v>490872</v>
       </c>
       <c r="R25" t="n">
-        <v>7017436</v>
+        <v>7017426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3536,16 +3510,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499574</t>
+          <t>https://artportalen.se/Sighting/135499575</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499575</v>
+        <v>135499576</v>
       </c>
       <c r="B26" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3581,10 +3555,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490872</v>
+        <v>490917</v>
       </c>
       <c r="R26" t="n">
-        <v>7017426</v>
+        <v>7017402</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3648,16 +3622,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499575</t>
+          <t>https://artportalen.se/Sighting/135499576</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499576</v>
+        <v>135499577</v>
       </c>
       <c r="B27" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3693,10 +3667,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490917</v>
+        <v>490931</v>
       </c>
       <c r="R27" t="n">
-        <v>7017402</v>
+        <v>7017371</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3746,6 +3720,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3760,16 +3739,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499576</t>
+          <t>https://artportalen.se/Sighting/135499577</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499577</v>
+        <v>135499578</v>
       </c>
       <c r="B28" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,10 +3784,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490931</v>
+        <v>490951</v>
       </c>
       <c r="R28" t="n">
-        <v>7017371</v>
+        <v>7017390</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,16 +3856,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499577</t>
+          <t>https://artportalen.se/Sighting/135499578</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499578</v>
+        <v>135499579</v>
       </c>
       <c r="B29" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,10 +3901,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490951</v>
+        <v>490976</v>
       </c>
       <c r="R29" t="n">
-        <v>7017390</v>
+        <v>7017311</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3994,16 +3973,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499578</t>
+          <t>https://artportalen.se/Sighting/135499579</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135499579</v>
+        <v>91488964</v>
       </c>
       <c r="B30" t="n">
-        <v>96410</v>
+        <v>92632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,41 +3990,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2812</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490976</v>
+        <v>490939</v>
       </c>
       <c r="R30" t="n">
-        <v>7017311</v>
+        <v>7017412</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4069,12 +4044,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4083,66 +4058,59 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499579</t>
+          <t>https://artportalen.se/Sighting/91488964</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>91488964</v>
+        <v>75185505</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>89156</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4152,13 +4120,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490939</v>
+        <v>490781</v>
       </c>
       <c r="R31" t="n">
-        <v>7017412</v>
+        <v>7017384</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4196,18 +4164,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4217,51 +4186,54 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91488964</t>
+          <t>https://artportalen.se/Sighting/75185505</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>75185505</v>
+        <v>135499609</v>
       </c>
       <c r="B32" t="n">
-        <v>89156</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490781</v>
+        <v>490849</v>
       </c>
       <c r="R32" t="n">
-        <v>7017384</v>
+        <v>7017392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4288,12 +4260,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4306,34 +4283,55 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185505</t>
+          <t>https://artportalen.se/Sighting/135499609</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499609</v>
+        <v>135499610</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,10 +4366,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490849</v>
+        <v>490859</v>
       </c>
       <c r="R33" t="n">
-        <v>7017392</v>
+        <v>7017416</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,11 +4404,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4438,12 +4431,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4460,54 +4453,67 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499609</t>
+          <t>https://artportalen.se/Sighting/135499610</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499610</v>
+        <v>135499531</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>58094</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100090</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490859</v>
+        <v>490781</v>
       </c>
       <c r="R34" t="n">
-        <v>7017416</v>
+        <v>7017369</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,39 +4548,23 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Synobservation av en individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4591,16 +4581,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499610</t>
+          <t>https://artportalen.se/Sighting/135499531</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499531</v>
+        <v>135499510</v>
       </c>
       <c r="B35" t="n">
-        <v>58089</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4608,16 +4598,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100090</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4625,16 +4615,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4648,10 +4634,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490781</v>
+        <v>490891</v>
       </c>
       <c r="R35" t="n">
-        <v>7017369</v>
+        <v>7017451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,7 +4674,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Synobservation av en individ med lockläte.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4702,7 +4688,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4719,16 +4725,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499531</t>
+          <t>https://artportalen.se/Sighting/135499510</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499510</v>
+        <v>135499511</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4758,7 +4764,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4772,10 +4778,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490891</v>
+        <v>490785</v>
       </c>
       <c r="R36" t="n">
-        <v>7017451</v>
+        <v>7017521</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4812,7 +4818,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4826,7 +4832,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -4863,16 +4869,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499510</t>
+          <t>https://artportalen.se/Sighting/135499511</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499511</v>
+        <v>135499512</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4916,10 +4922,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490785</v>
+        <v>490783</v>
       </c>
       <c r="R37" t="n">
-        <v>7017521</v>
+        <v>7017360</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4956,7 +4962,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4971,6 +4977,11 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5007,33 +5018,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499511</t>
+          <t>https://artportalen.se/Sighting/135499512</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499512</v>
+        <v>135499596</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>58239</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5041,29 +5052,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490783</v>
+        <v>490875</v>
       </c>
       <c r="R38" t="n">
-        <v>7017360</v>
+        <v>7017470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5100,7 +5111,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5115,31 +5126,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5156,16 +5142,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499512</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499549</v>
+        <v>135499513</v>
       </c>
       <c r="B39" t="n">
-        <v>58231</v>
+        <v>58141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,21 +5159,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102980</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5199,7 +5185,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5213,10 +5199,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490804</v>
+        <v>490763</v>
       </c>
       <c r="R39" t="n">
-        <v>7017502</v>
+        <v>7017499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5253,7 +5239,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 1 överflygande med sång.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5267,7 +5253,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5284,43 +5275,43 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499549</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499596</v>
+        <v>135499514</v>
       </c>
       <c r="B40" t="n">
-        <v>58234</v>
+        <v>58141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102981</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5330,7 +5321,11 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
@@ -5340,7 +5335,7 @@
         <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017470</v>
+        <v>7017397</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5377,7 +5372,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5392,6 +5387,11 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5408,67 +5408,59 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499513</v>
+        <v>135499611</v>
       </c>
       <c r="B41" t="n">
-        <v>58136</v>
+        <v>99159</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490763</v>
+        <v>490821</v>
       </c>
       <c r="R41" t="n">
-        <v>7017499</v>
+        <v>7017504</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5505,7 +5497,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5514,17 +5506,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5541,67 +5529,59 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499514</v>
+        <v>135499612</v>
       </c>
       <c r="B42" t="n">
-        <v>58136</v>
+        <v>99159</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490875</v>
+        <v>490848</v>
       </c>
       <c r="R42" t="n">
-        <v>7017397</v>
+        <v>7017375</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5636,28 +5616,19 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5674,16 +5645,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499611</v>
+        <v>135499613</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5723,10 +5694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490821</v>
+        <v>490878</v>
       </c>
       <c r="R43" t="n">
-        <v>7017504</v>
+        <v>7017368</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5763,7 +5734,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk.</t>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5795,16 +5766,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499612</v>
+        <v>135499614</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5844,10 +5815,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490848</v>
+        <v>490867</v>
       </c>
       <c r="R44" t="n">
-        <v>7017375</v>
+        <v>7017386</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5882,6 +5853,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5911,16 +5887,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499613</v>
+        <v>135499615</v>
       </c>
       <c r="B45" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5960,10 +5936,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490878</v>
+        <v>490860</v>
       </c>
       <c r="R45" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6032,16 +6008,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499614</v>
+        <v>135499509</v>
       </c>
       <c r="B46" t="n">
-        <v>99112</v>
+        <v>99266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6049,28 +6025,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6081,10 +6057,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490867</v>
+        <v>490880</v>
       </c>
       <c r="R46" t="n">
-        <v>7017386</v>
+        <v>7017365</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6121,7 +6097,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Flertalet plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6139,6 +6115,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -6153,16 +6134,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499615</v>
+        <v>135499620</v>
       </c>
       <c r="B47" t="n">
-        <v>99112</v>
+        <v>108260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6170,28 +6151,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>220083</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6202,10 +6183,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490860</v>
+        <v>490853</v>
       </c>
       <c r="R47" t="n">
-        <v>7017386</v>
+        <v>7017483</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6240,11 +6221,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6274,16 +6250,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499509</v>
+        <v>135499621</v>
       </c>
       <c r="B48" t="n">
-        <v>99219</v>
+        <v>108260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6291,28 +6267,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6323,10 +6299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490880</v>
+        <v>490837</v>
       </c>
       <c r="R48" t="n">
-        <v>7017365</v>
+        <v>7017379</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6361,11 +6337,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flertalet plantor.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6381,11 +6352,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
@@ -6400,16 +6366,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499620</v>
+        <v>135499623</v>
       </c>
       <c r="B49" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6438,7 +6404,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6449,10 +6415,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490853</v>
+        <v>490848</v>
       </c>
       <c r="R49" t="n">
-        <v>7017483</v>
+        <v>7017376</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6516,16 +6482,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499621</v>
+        <v>135499624</v>
       </c>
       <c r="B50" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6565,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490837</v>
+        <v>490861</v>
       </c>
       <c r="R50" t="n">
-        <v>7017379</v>
+        <v>7017386</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6632,16 +6598,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499623</v>
+        <v>135499625</v>
       </c>
       <c r="B51" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6670,7 +6636,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6681,10 +6647,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490848</v>
+        <v>490821</v>
       </c>
       <c r="R51" t="n">
-        <v>7017376</v>
+        <v>7017394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6748,16 +6714,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499624</v>
+        <v>135499626</v>
       </c>
       <c r="B52" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6786,7 +6752,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6797,10 +6763,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490861</v>
+        <v>490841</v>
       </c>
       <c r="R52" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6864,16 +6830,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499625</v>
+        <v>135499550</v>
       </c>
       <c r="B53" t="n">
-        <v>108205</v>
+        <v>108330</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6881,28 +6847,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6913,10 +6879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490821</v>
+        <v>490929</v>
       </c>
       <c r="R53" t="n">
-        <v>7017394</v>
+        <v>7017429</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6980,16 +6946,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499626</v>
+        <v>135499551</v>
       </c>
       <c r="B54" t="n">
-        <v>108205</v>
+        <v>108330</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6997,28 +6963,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -7029,10 +6995,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R54" t="n">
-        <v>7017433</v>
+        <v>7017480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7067,6 +7033,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7096,16 +7067,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499550</v>
+        <v>135499552</v>
       </c>
       <c r="B55" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7145,10 +7116,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490929</v>
+        <v>490867</v>
       </c>
       <c r="R55" t="n">
-        <v>7017429</v>
+        <v>7017480</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7212,16 +7183,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499551</v>
+        <v>135499553</v>
       </c>
       <c r="B56" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7261,10 +7232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490853</v>
+        <v>490841</v>
       </c>
       <c r="R56" t="n">
-        <v>7017480</v>
+        <v>7017457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7299,11 +7270,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7333,16 +7299,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499552</v>
+        <v>135499554</v>
       </c>
       <c r="B57" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7382,10 +7348,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490867</v>
+        <v>490737</v>
       </c>
       <c r="R57" t="n">
-        <v>7017480</v>
+        <v>7017474</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7449,16 +7415,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499553</v>
+        <v>135499555</v>
       </c>
       <c r="B58" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7498,10 +7464,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490841</v>
+        <v>490873</v>
       </c>
       <c r="R58" t="n">
-        <v>7017457</v>
+        <v>7017368</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7565,16 +7531,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499554</v>
+        <v>135499556</v>
       </c>
       <c r="B59" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7614,10 +7580,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490737</v>
+        <v>490863</v>
       </c>
       <c r="R59" t="n">
-        <v>7017474</v>
+        <v>7017386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7667,6 +7633,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7681,16 +7652,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499555</v>
+        <v>135499544</v>
       </c>
       <c r="B60" t="n">
-        <v>108274</v>
+        <v>111210</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7698,28 +7669,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7730,10 +7701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490873</v>
+        <v>490844</v>
       </c>
       <c r="R60" t="n">
-        <v>7017368</v>
+        <v>7017468</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7797,16 +7768,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499556</v>
+        <v>135499546</v>
       </c>
       <c r="B61" t="n">
-        <v>108274</v>
+        <v>111210</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7814,28 +7785,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7846,10 +7817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490863</v>
+        <v>490780</v>
       </c>
       <c r="R61" t="n">
-        <v>7017386</v>
+        <v>7017405</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7899,11 +7870,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -7918,16 +7884,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499544</v>
+        <v>135499547</v>
       </c>
       <c r="B62" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7956,7 +7922,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7967,10 +7933,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490844</v>
+        <v>490858</v>
       </c>
       <c r="R62" t="n">
-        <v>7017468</v>
+        <v>7017416</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8034,16 +8000,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499546</v>
+        <v>135499548</v>
       </c>
       <c r="B63" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8072,7 +8038,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -8083,10 +8049,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490780</v>
+        <v>490964</v>
       </c>
       <c r="R63" t="n">
-        <v>7017405</v>
+        <v>7017356</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8136,6 +8102,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8150,16 +8121,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499547</v>
+        <v>135499617</v>
       </c>
       <c r="B64" t="n">
-        <v>111153</v>
+        <v>110206</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8167,28 +8138,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220240</v>
+        <v>220294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -8199,10 +8170,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490858</v>
+        <v>490864</v>
       </c>
       <c r="R64" t="n">
-        <v>7017416</v>
+        <v>7017486</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8237,6 +8208,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8266,45 +8242,53 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499548</v>
+        <v>135499580</v>
       </c>
       <c r="B65" t="n">
-        <v>111153</v>
+        <v>99242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -8315,10 +8299,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490964</v>
+        <v>490975</v>
       </c>
       <c r="R65" t="n">
-        <v>7017356</v>
+        <v>7017304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8353,6 +8337,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8387,45 +8376,53 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499617</v>
+        <v>135499583</v>
       </c>
       <c r="B66" t="n">
-        <v>110150</v>
+        <v>99242</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220294</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -8436,10 +8433,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490864</v>
+        <v>490768</v>
       </c>
       <c r="R66" t="n">
-        <v>7017486</v>
+        <v>7017376</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8476,7 +8473,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8494,6 +8491,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
@@ -8508,16 +8510,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499580</v>
+        <v>135499584</v>
       </c>
       <c r="B67" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8544,7 +8546,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8565,10 +8567,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490975</v>
+        <v>490839</v>
       </c>
       <c r="R67" t="n">
-        <v>7017304</v>
+        <v>7017351</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8605,7 +8607,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8620,12 +8622,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8642,16 +8639,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499581</v>
+        <v>135499585</v>
       </c>
       <c r="B68" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8678,7 +8675,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8699,10 +8696,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490951</v>
+        <v>490845</v>
       </c>
       <c r="R68" t="n">
-        <v>7017428</v>
+        <v>7017392</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8739,7 +8736,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8754,7 +8751,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8771,16 +8768,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499581</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499582</v>
+        <v>135499586</v>
       </c>
       <c r="B69" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8828,10 +8825,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490884</v>
+        <v>490812</v>
       </c>
       <c r="R69" t="n">
-        <v>7017471</v>
+        <v>7017401</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8868,7 +8865,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8883,7 +8880,12 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8900,16 +8902,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499582</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499583</v>
+        <v>135499588</v>
       </c>
       <c r="B70" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8936,7 +8938,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8957,10 +8959,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490768</v>
+        <v>490843</v>
       </c>
       <c r="R70" t="n">
-        <v>7017376</v>
+        <v>7017436</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8997,7 +8999,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9034,16 +9036,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499584</v>
+        <v>135499589</v>
       </c>
       <c r="B71" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9070,7 +9072,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9091,10 +9093,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490839</v>
+        <v>490967</v>
       </c>
       <c r="R71" t="n">
-        <v>7017351</v>
+        <v>7017335</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9131,7 +9133,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9146,7 +9148,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9163,16 +9170,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499585</v>
+        <v>135499590</v>
       </c>
       <c r="B72" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9199,7 +9206,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9220,10 +9227,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490845</v>
+        <v>490979</v>
       </c>
       <c r="R72" t="n">
-        <v>7017392</v>
+        <v>7017360</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9260,7 +9267,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9275,7 +9282,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9292,16 +9304,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499586</v>
+        <v>135499591</v>
       </c>
       <c r="B73" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9328,7 +9340,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9349,10 +9361,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490812</v>
+        <v>490973</v>
       </c>
       <c r="R73" t="n">
-        <v>7017401</v>
+        <v>7017399</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9389,7 +9401,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9426,16 +9438,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499588</v>
+        <v>135499592</v>
       </c>
       <c r="B74" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9462,7 +9474,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9483,10 +9495,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490843</v>
+        <v>490951</v>
       </c>
       <c r="R74" t="n">
-        <v>7017436</v>
+        <v>7017408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9523,7 +9535,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9560,16 +9572,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499589</v>
+        <v>135499593</v>
       </c>
       <c r="B75" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9596,7 +9608,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9617,10 +9629,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490967</v>
+        <v>490951</v>
       </c>
       <c r="R75" t="n">
-        <v>7017335</v>
+        <v>7017396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9657,7 +9669,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9694,16 +9706,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499590</v>
+        <v>135499594</v>
       </c>
       <c r="B76" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9730,7 +9742,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9751,10 +9763,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490979</v>
+        <v>490957</v>
       </c>
       <c r="R76" t="n">
-        <v>7017360</v>
+        <v>7017386</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9791,7 +9803,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9828,55 +9840,43 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499591</v>
+        <v>135499519</v>
       </c>
       <c r="B77" t="n">
-        <v>99195</v>
+        <v>98104</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490973</v>
+        <v>490752</v>
       </c>
       <c r="R77" t="n">
-        <v>7017399</v>
+        <v>7017499</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9943,11 +9943,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
@@ -9962,53 +9957,45 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499592</v>
+        <v>135499516</v>
       </c>
       <c r="B78" t="n">
-        <v>99195</v>
+        <v>99264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -10019,10 +10006,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490951</v>
+        <v>490844</v>
       </c>
       <c r="R78" t="n">
-        <v>7017408</v>
+        <v>7017394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10057,11 +10044,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10077,11 +10059,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
@@ -10096,53 +10073,45 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499593</v>
+        <v>135499517</v>
       </c>
       <c r="B79" t="n">
-        <v>99195</v>
+        <v>99264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -10153,10 +10122,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490951</v>
+        <v>490814</v>
       </c>
       <c r="R79" t="n">
-        <v>7017396</v>
+        <v>7017404</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10191,11 +10160,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10211,11 +10175,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
@@ -10230,53 +10189,45 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499594</v>
+        <v>135499627</v>
       </c>
       <c r="B80" t="n">
-        <v>99195</v>
+        <v>101451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10287,10 +10238,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490957</v>
+        <v>490803</v>
       </c>
       <c r="R80" t="n">
-        <v>7017386</v>
+        <v>7017492</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10325,11 +10276,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10345,11 +10291,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
@@ -10364,16 +10305,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499519</v>
+        <v>135499628</v>
       </c>
       <c r="B81" t="n">
-        <v>98060</v>
+        <v>101451</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10381,26 +10322,30 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10409,10 +10354,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490752</v>
+        <v>490792</v>
       </c>
       <c r="R81" t="n">
-        <v>7017499</v>
+        <v>7017441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10447,11 +10392,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10481,16 +10421,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499516</v>
+        <v>135499629</v>
       </c>
       <c r="B82" t="n">
-        <v>99217</v>
+        <v>101451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10498,28 +10438,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10530,10 +10470,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490844</v>
+        <v>490764</v>
       </c>
       <c r="R82" t="n">
-        <v>7017394</v>
+        <v>7017441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10597,16 +10537,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499517</v>
+        <v>135499630</v>
       </c>
       <c r="B83" t="n">
-        <v>99217</v>
+        <v>101451</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10614,28 +10554,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -10646,10 +10586,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490814</v>
+        <v>490798</v>
       </c>
       <c r="R83" t="n">
-        <v>7017404</v>
+        <v>7017366</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10713,16 +10653,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499627</v>
+        <v>135499631</v>
       </c>
       <c r="B84" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10762,10 +10702,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490803</v>
+        <v>490816</v>
       </c>
       <c r="R84" t="n">
-        <v>7017492</v>
+        <v>7017378</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10829,16 +10769,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499628</v>
+        <v>135499632</v>
       </c>
       <c r="B85" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10878,10 +10818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490792</v>
+        <v>490796</v>
       </c>
       <c r="R85" t="n">
-        <v>7017441</v>
+        <v>7017382</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10945,16 +10885,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499629</v>
+        <v>135499633</v>
       </c>
       <c r="B86" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10994,10 +10934,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490764</v>
+        <v>490782</v>
       </c>
       <c r="R86" t="n">
-        <v>7017441</v>
+        <v>7017407</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11061,16 +11001,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499630</v>
+        <v>135499634</v>
       </c>
       <c r="B87" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11110,10 +11050,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490798</v>
+        <v>490730</v>
       </c>
       <c r="R87" t="n">
-        <v>7017366</v>
+        <v>7017371</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11177,16 +11117,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499631</v>
+        <v>135499635</v>
       </c>
       <c r="B88" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11226,10 +11166,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490816</v>
+        <v>490827</v>
       </c>
       <c r="R88" t="n">
-        <v>7017378</v>
+        <v>7017356</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11293,16 +11233,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499632</v>
+        <v>135499636</v>
       </c>
       <c r="B89" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11342,10 +11282,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490796</v>
+        <v>490844</v>
       </c>
       <c r="R89" t="n">
-        <v>7017382</v>
+        <v>7017345</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11409,16 +11349,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499633</v>
+        <v>135499637</v>
       </c>
       <c r="B90" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11458,10 +11398,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490782</v>
+        <v>490852</v>
       </c>
       <c r="R90" t="n">
-        <v>7017407</v>
+        <v>7017373</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11508,7 +11448,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11525,16 +11465,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499634</v>
+        <v>135499638</v>
       </c>
       <c r="B91" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11574,10 +11514,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490730</v>
+        <v>490882</v>
       </c>
       <c r="R91" t="n">
-        <v>7017371</v>
+        <v>7017368</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11624,7 +11564,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11641,16 +11581,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499635</v>
+        <v>135499639</v>
       </c>
       <c r="B92" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11690,10 +11630,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490827</v>
+        <v>490865</v>
       </c>
       <c r="R92" t="n">
-        <v>7017356</v>
+        <v>7017386</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11757,16 +11697,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499636</v>
+        <v>135499640</v>
       </c>
       <c r="B93" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11806,10 +11746,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490844</v>
+        <v>490840</v>
       </c>
       <c r="R93" t="n">
-        <v>7017345</v>
+        <v>7017433</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11873,16 +11813,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499637</v>
+        <v>135499641</v>
       </c>
       <c r="B94" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11922,10 +11862,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490852</v>
+        <v>490880</v>
       </c>
       <c r="R94" t="n">
-        <v>7017373</v>
+        <v>7017422</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11972,7 +11912,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11989,16 +11929,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499638</v>
+        <v>135499618</v>
       </c>
       <c r="B95" t="n">
-        <v>101403</v>
+        <v>98258</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12006,21 +11946,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12038,10 +11978,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490882</v>
+        <v>490791</v>
       </c>
       <c r="R95" t="n">
-        <v>7017368</v>
+        <v>7017443</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12076,6 +12016,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -12088,7 +12033,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12105,16 +12050,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499639</v>
+        <v>135499619</v>
       </c>
       <c r="B96" t="n">
-        <v>101403</v>
+        <v>98258</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12122,25 +12067,33 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12154,10 +12107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490865</v>
+        <v>490868</v>
       </c>
       <c r="R96" t="n">
-        <v>7017386</v>
+        <v>7017387</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12192,6 +12145,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12207,6 +12165,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
@@ -12221,16 +12184,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499640</v>
+        <v>135499520</v>
       </c>
       <c r="B97" t="n">
-        <v>101403</v>
+        <v>99048</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12238,21 +12201,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>223049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12270,10 +12233,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490840</v>
+        <v>490757</v>
       </c>
       <c r="R97" t="n">
-        <v>7017433</v>
+        <v>7017472</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12337,16 +12300,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499641</v>
+        <v>135499521</v>
       </c>
       <c r="B98" t="n">
-        <v>101403</v>
+        <v>99048</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12354,21 +12317,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>223049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12386,10 +12349,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490880</v>
+        <v>490966</v>
       </c>
       <c r="R98" t="n">
-        <v>7017422</v>
+        <v>7017430</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12453,16 +12416,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499618</v>
+        <v>135499522</v>
       </c>
       <c r="B99" t="n">
-        <v>98214</v>
+        <v>99048</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12470,21 +12433,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12502,10 +12465,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490791</v>
+        <v>490920</v>
       </c>
       <c r="R99" t="n">
-        <v>7017443</v>
+        <v>7017445</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12540,11 +12503,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -12574,16 +12532,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499619</v>
+        <v>135499523</v>
       </c>
       <c r="B100" t="n">
-        <v>98214</v>
+        <v>99048</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12591,33 +12549,25 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12631,10 +12581,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490868</v>
+        <v>490912</v>
       </c>
       <c r="R100" t="n">
-        <v>7017387</v>
+        <v>7017466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12669,11 +12619,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12689,11 +12634,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
@@ -12708,16 +12648,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499520</v>
+        <v>135499524</v>
       </c>
       <c r="B101" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12757,10 +12697,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490757</v>
+        <v>490858</v>
       </c>
       <c r="R101" t="n">
-        <v>7017472</v>
+        <v>7017493</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12824,16 +12764,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499521</v>
+        <v>135499525</v>
       </c>
       <c r="B102" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12862,7 +12802,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12873,10 +12813,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490966</v>
+        <v>490804</v>
       </c>
       <c r="R102" t="n">
-        <v>7017430</v>
+        <v>7017492</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12940,16 +12880,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499522</v>
+        <v>135499526</v>
       </c>
       <c r="B103" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12989,10 +12929,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490920</v>
+        <v>490740</v>
       </c>
       <c r="R103" t="n">
-        <v>7017445</v>
+        <v>7017423</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13056,16 +12996,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499523</v>
+        <v>135499527</v>
       </c>
       <c r="B104" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13105,10 +13045,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490912</v>
+        <v>490732</v>
       </c>
       <c r="R104" t="n">
-        <v>7017466</v>
+        <v>7017370</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13172,16 +13112,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499524</v>
+        <v>135499528</v>
       </c>
       <c r="B105" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13221,10 +13161,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490858</v>
+        <v>490867</v>
       </c>
       <c r="R105" t="n">
-        <v>7017493</v>
+        <v>7017386</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13259,6 +13199,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -13288,16 +13233,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499525</v>
+        <v>135499529</v>
       </c>
       <c r="B106" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13326,7 +13271,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -13337,10 +13282,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490804</v>
+        <v>490807</v>
       </c>
       <c r="R106" t="n">
-        <v>7017492</v>
+        <v>7017431</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13404,16 +13349,16 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499526</v>
+        <v>135499530</v>
       </c>
       <c r="B107" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13442,7 +13387,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13453,10 +13398,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490740</v>
+        <v>490932</v>
       </c>
       <c r="R107" t="n">
-        <v>7017423</v>
+        <v>7017369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13520,16 +13465,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499527</v>
+        <v>135499597</v>
       </c>
       <c r="B108" t="n">
-        <v>99001</v>
+        <v>98293</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13537,21 +13482,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13569,10 +13514,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490732</v>
+        <v>490969</v>
       </c>
       <c r="R108" t="n">
-        <v>7017370</v>
+        <v>7017431</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13636,16 +13581,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499528</v>
+        <v>135499598</v>
       </c>
       <c r="B109" t="n">
-        <v>99001</v>
+        <v>98293</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13653,21 +13598,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13685,10 +13630,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490867</v>
+        <v>490840</v>
       </c>
       <c r="R109" t="n">
-        <v>7017386</v>
+        <v>7017457</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13723,11 +13668,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13757,16 +13697,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499529</v>
+        <v>135499599</v>
       </c>
       <c r="B110" t="n">
-        <v>99001</v>
+        <v>98293</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13774,21 +13714,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13806,10 +13746,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490807</v>
+        <v>490831</v>
       </c>
       <c r="R110" t="n">
-        <v>7017431</v>
+        <v>7017486</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13873,16 +13813,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499530</v>
+        <v>135499600</v>
       </c>
       <c r="B111" t="n">
-        <v>99001</v>
+        <v>98293</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13890,28 +13830,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13922,10 +13862,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490932</v>
+        <v>490797</v>
       </c>
       <c r="R111" t="n">
-        <v>7017369</v>
+        <v>7017497</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13989,16 +13929,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499597</v>
+        <v>135499601</v>
       </c>
       <c r="B112" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14038,10 +13978,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490969</v>
+        <v>490797</v>
       </c>
       <c r="R112" t="n">
-        <v>7017431</v>
+        <v>7017511</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14105,16 +14045,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499598</v>
+        <v>135499602</v>
       </c>
       <c r="B113" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14154,10 +14094,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490840</v>
+        <v>490737</v>
       </c>
       <c r="R113" t="n">
-        <v>7017457</v>
+        <v>7017473</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14221,16 +14161,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499599</v>
+        <v>135499515</v>
       </c>
       <c r="B114" t="n">
-        <v>98249</v>
+        <v>101988</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14238,21 +14178,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223358</v>
+        <v>223366</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14270,10 +14210,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490831</v>
+        <v>490788</v>
       </c>
       <c r="R114" t="n">
-        <v>7017486</v>
+        <v>7017450</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14337,16 +14277,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499600</v>
+        <v>135499532</v>
       </c>
       <c r="B115" t="n">
-        <v>98249</v>
+        <v>101341</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14354,21 +14294,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14386,10 +14326,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490797</v>
+        <v>490889</v>
       </c>
       <c r="R115" t="n">
-        <v>7017497</v>
+        <v>7017459</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14453,16 +14393,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499601</v>
+        <v>135499533</v>
       </c>
       <c r="B116" t="n">
-        <v>98249</v>
+        <v>101341</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14470,21 +14410,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14502,10 +14442,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490797</v>
+        <v>490743</v>
       </c>
       <c r="R116" t="n">
-        <v>7017511</v>
+        <v>7017495</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14569,16 +14509,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499602</v>
+        <v>135499534</v>
       </c>
       <c r="B117" t="n">
-        <v>98249</v>
+        <v>101341</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14586,21 +14526,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14621,7 +14561,7 @@
         <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017473</v>
+        <v>7017474</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14685,16 +14625,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499515</v>
+        <v>135499535</v>
       </c>
       <c r="B118" t="n">
-        <v>101940</v>
+        <v>101341</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14702,21 +14642,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>223366</v>
+        <v>224885</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14734,10 +14674,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490788</v>
+        <v>490734</v>
       </c>
       <c r="R118" t="n">
-        <v>7017450</v>
+        <v>7017429</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14801,16 +14741,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499532</v>
+        <v>135499536</v>
       </c>
       <c r="B119" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14850,10 +14790,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490889</v>
+        <v>490780</v>
       </c>
       <c r="R119" t="n">
-        <v>7017459</v>
+        <v>7017405</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14917,16 +14857,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499533</v>
+        <v>135499537</v>
       </c>
       <c r="B120" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14966,10 +14906,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490743</v>
+        <v>490751</v>
       </c>
       <c r="R120" t="n">
-        <v>7017495</v>
+        <v>7017406</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15033,16 +14973,16 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499537</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499534</v>
+        <v>135499538</v>
       </c>
       <c r="B121" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15082,10 +15022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490737</v>
+        <v>490729</v>
       </c>
       <c r="R121" t="n">
-        <v>7017474</v>
+        <v>7017373</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15149,16 +15089,16 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499538</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499535</v>
+        <v>135499540</v>
       </c>
       <c r="B122" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15198,10 +15138,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490734</v>
+        <v>490847</v>
       </c>
       <c r="R122" t="n">
-        <v>7017429</v>
+        <v>7017345</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15265,16 +15205,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499540</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499536</v>
+        <v>135499541</v>
       </c>
       <c r="B123" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15314,10 +15254,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490780</v>
+        <v>490856</v>
       </c>
       <c r="R123" t="n">
-        <v>7017405</v>
+        <v>7017358</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15381,16 +15321,16 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499541</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499537</v>
+        <v>135499542</v>
       </c>
       <c r="B124" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15419,7 +15359,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -15430,10 +15370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490751</v>
+        <v>490840</v>
       </c>
       <c r="R124" t="n">
-        <v>7017406</v>
+        <v>7017433</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15496,470 +15436,6 @@
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>135499538</v>
-      </c>
-      <c r="B125" t="n">
-        <v>101293</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q125" t="n">
-        <v>490729</v>
-      </c>
-      <c r="R125" t="n">
-        <v>7017373</v>
-      </c>
-      <c r="S125" t="n">
-        <v>10</v>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="inlineStr"/>
-      <c r="AG125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT125" t="inlineStr"/>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>135499540</v>
-      </c>
-      <c r="B126" t="n">
-        <v>101293</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q126" t="n">
-        <v>490847</v>
-      </c>
-      <c r="R126" t="n">
-        <v>7017345</v>
-      </c>
-      <c r="S126" t="n">
-        <v>10</v>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="inlineStr"/>
-      <c r="AG126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT126" t="inlineStr"/>
-      <c r="AW126" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>135499541</v>
-      </c>
-      <c r="B127" t="n">
-        <v>101293</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q127" t="n">
-        <v>490856</v>
-      </c>
-      <c r="R127" t="n">
-        <v>7017358</v>
-      </c>
-      <c r="S127" t="n">
-        <v>10</v>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="inlineStr"/>
-      <c r="AG127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT127" t="inlineStr"/>
-      <c r="AW127" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>135499542</v>
-      </c>
-      <c r="B128" t="n">
-        <v>101293</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q128" t="n">
-        <v>490840</v>
-      </c>
-      <c r="R128" t="n">
-        <v>7017433</v>
-      </c>
-      <c r="S128" t="n">
-        <v>10</v>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="inlineStr"/>
-      <c r="AG128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT128" t="inlineStr"/>
-      <c r="AW128" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
-      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -16090,10 +15566,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ124"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499608</v>
+        <v>135499607</v>
       </c>
       <c r="B2" t="n">
-        <v>99148</v>
+        <v>99175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490867</v>
+        <v>490869</v>
       </c>
       <c r="R2" t="n">
-        <v>7017387</v>
+        <v>7017370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
+          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad snitslad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +790,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+          <t>Kalkrikt fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,58 +812,71 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499608</t>
+          <t>https://artportalen.se/Sighting/135499607</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499603</v>
+        <v>135499608</v>
       </c>
       <c r="B3" t="n">
-        <v>92012</v>
+        <v>99175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490968</v>
+        <v>490867</v>
       </c>
       <c r="R3" t="n">
-        <v>7017430</v>
+        <v>7017387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +913,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,24 +931,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -952,16 +950,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499603</t>
+          <t>https://artportalen.se/Sighting/135499608</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499604</v>
+        <v>135499603</v>
       </c>
       <c r="B4" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,10 +998,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490893</v>
+        <v>490968</v>
       </c>
       <c r="R4" t="n">
-        <v>7017459</v>
+        <v>7017430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,7 +1038,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,12 +1068,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,16 +1090,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499604</t>
+          <t>https://artportalen.se/Sighting/135499603</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499605</v>
+        <v>135499604</v>
       </c>
       <c r="B5" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,10 +1138,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490741</v>
+        <v>490893</v>
       </c>
       <c r="R5" t="n">
-        <v>7017465</v>
+        <v>7017459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,7 +1178,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1232,16 +1230,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499605</t>
+          <t>https://artportalen.se/Sighting/135499604</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499606</v>
+        <v>135499605</v>
       </c>
       <c r="B6" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,10 +1278,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490951</v>
+        <v>490741</v>
       </c>
       <c r="R6" t="n">
-        <v>7017411</v>
+        <v>7017465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1320,7 +1318,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,12 +1348,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1372,16 +1370,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499606</t>
+          <t>https://artportalen.se/Sighting/135499605</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75185503</v>
+        <v>135499606</v>
       </c>
       <c r="B7" t="n">
-        <v>87322</v>
+        <v>92039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,34 +1387,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1988</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490758</v>
+        <v>490951</v>
       </c>
       <c r="R7" t="n">
-        <v>7017384</v>
+        <v>7017411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1443,12 +1448,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,73 +1471,90 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185503</t>
+          <t>https://artportalen.se/Sighting/135499606</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135499557</v>
+        <v>75185503</v>
       </c>
       <c r="B8" t="n">
-        <v>96454</v>
+        <v>87322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2812</v>
+        <v>1988</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490738</v>
+        <v>490758</v>
       </c>
       <c r="R8" t="n">
-        <v>7017396</v>
+        <v>7017384</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,12 +1581,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,35 +1599,34 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499557</t>
+          <t>https://artportalen.se/Sighting/75185503</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499558</v>
+        <v>135499557</v>
       </c>
       <c r="B9" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,10 +1662,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490991</v>
+        <v>490738</v>
       </c>
       <c r="R9" t="n">
-        <v>7017297</v>
+        <v>7017396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1703,16 +1729,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499558</t>
+          <t>https://artportalen.se/Sighting/135499557</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499560</v>
+        <v>135499558</v>
       </c>
       <c r="B10" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,10 +1774,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490966</v>
+        <v>490991</v>
       </c>
       <c r="R10" t="n">
-        <v>7017426</v>
+        <v>7017297</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1801,11 +1827,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1820,16 +1841,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499560</t>
+          <t>https://artportalen.se/Sighting/135499558</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499561</v>
+        <v>135499560</v>
       </c>
       <c r="B11" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,10 +1886,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490929</v>
+        <v>490966</v>
       </c>
       <c r="R11" t="n">
-        <v>7017441</v>
+        <v>7017426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1915,7 +1936,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1932,16 +1958,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499561</t>
+          <t>https://artportalen.se/Sighting/135499560</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499562</v>
+        <v>135499561</v>
       </c>
       <c r="B12" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1977,10 +2003,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490910</v>
+        <v>490929</v>
       </c>
       <c r="R12" t="n">
-        <v>7017467</v>
+        <v>7017441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2044,16 +2070,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499562</t>
+          <t>https://artportalen.se/Sighting/135499561</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499563</v>
+        <v>135499562</v>
       </c>
       <c r="B13" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2089,10 +2115,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490878</v>
+        <v>490910</v>
       </c>
       <c r="R13" t="n">
-        <v>7017474</v>
+        <v>7017467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2139,7 +2165,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2156,16 +2182,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499563</t>
+          <t>https://artportalen.se/Sighting/135499562</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499564</v>
+        <v>135499563</v>
       </c>
       <c r="B14" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490883</v>
+        <v>490878</v>
       </c>
       <c r="R14" t="n">
-        <v>7017462</v>
+        <v>7017474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2251,7 +2277,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2268,16 +2294,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499564</t>
+          <t>https://artportalen.se/Sighting/135499563</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499565</v>
+        <v>135499564</v>
       </c>
       <c r="B15" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2313,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490756</v>
+        <v>490883</v>
       </c>
       <c r="R15" t="n">
-        <v>7017472</v>
+        <v>7017462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2363,7 +2389,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2380,16 +2406,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499565</t>
+          <t>https://artportalen.se/Sighting/135499564</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499566</v>
+        <v>135499565</v>
       </c>
       <c r="B16" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,10 +2451,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490790</v>
+        <v>490756</v>
       </c>
       <c r="R16" t="n">
-        <v>7017441</v>
+        <v>7017472</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2492,16 +2518,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499566</t>
+          <t>https://artportalen.se/Sighting/135499565</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499567</v>
+        <v>135499566</v>
       </c>
       <c r="B17" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2537,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490732</v>
+        <v>490790</v>
       </c>
       <c r="R17" t="n">
-        <v>7017442</v>
+        <v>7017441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2587,7 +2613,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2604,16 +2630,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499567</t>
+          <t>https://artportalen.se/Sighting/135499566</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499568</v>
+        <v>135499567</v>
       </c>
       <c r="B18" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,10 +2675,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490781</v>
+        <v>490732</v>
       </c>
       <c r="R18" t="n">
-        <v>7017407</v>
+        <v>7017442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2699,7 +2725,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,16 +2742,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499568</t>
+          <t>https://artportalen.se/Sighting/135499567</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499569</v>
+        <v>135499568</v>
       </c>
       <c r="B19" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,10 +2787,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490731</v>
+        <v>490781</v>
       </c>
       <c r="R19" t="n">
-        <v>7017371</v>
+        <v>7017407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,11 +2840,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2833,16 +2854,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499569</t>
+          <t>https://artportalen.se/Sighting/135499568</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499570</v>
+        <v>135499569</v>
       </c>
       <c r="B20" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2878,10 +2899,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490854</v>
+        <v>490731</v>
       </c>
       <c r="R20" t="n">
-        <v>7017345</v>
+        <v>7017371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,6 +2952,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2945,16 +2971,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499570</t>
+          <t>https://artportalen.se/Sighting/135499569</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499571</v>
+        <v>135499570</v>
       </c>
       <c r="B21" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2990,10 +3016,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490878</v>
+        <v>490854</v>
       </c>
       <c r="R21" t="n">
-        <v>7017366</v>
+        <v>7017345</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3028,11 +3054,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3062,16 +3083,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499571</t>
+          <t>https://artportalen.se/Sighting/135499570</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499572</v>
+        <v>135499571</v>
       </c>
       <c r="B22" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3107,10 +3128,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490867</v>
+        <v>490878</v>
       </c>
       <c r="R22" t="n">
-        <v>7017386</v>
+        <v>7017366</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,6 +3166,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3174,16 +3200,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499572</t>
+          <t>https://artportalen.se/Sighting/135499571</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499573</v>
+        <v>135499572</v>
       </c>
       <c r="B23" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,10 +3245,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490840</v>
+        <v>490867</v>
       </c>
       <c r="R23" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3286,16 +3312,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499573</t>
+          <t>https://artportalen.se/Sighting/135499572</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499574</v>
+        <v>135499573</v>
       </c>
       <c r="B24" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,10 +3357,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490844</v>
+        <v>490840</v>
       </c>
       <c r="R24" t="n">
-        <v>7017436</v>
+        <v>7017433</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3398,16 +3424,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499574</t>
+          <t>https://artportalen.se/Sighting/135499573</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499575</v>
+        <v>135499574</v>
       </c>
       <c r="B25" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,10 +3469,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490872</v>
+        <v>490844</v>
       </c>
       <c r="R25" t="n">
-        <v>7017426</v>
+        <v>7017436</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3510,16 +3536,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499575</t>
+          <t>https://artportalen.se/Sighting/135499574</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499576</v>
+        <v>135499575</v>
       </c>
       <c r="B26" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3555,10 +3581,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490917</v>
+        <v>490872</v>
       </c>
       <c r="R26" t="n">
-        <v>7017402</v>
+        <v>7017426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3622,16 +3648,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499576</t>
+          <t>https://artportalen.se/Sighting/135499575</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499577</v>
+        <v>135499576</v>
       </c>
       <c r="B27" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3667,10 +3693,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490931</v>
+        <v>490917</v>
       </c>
       <c r="R27" t="n">
-        <v>7017371</v>
+        <v>7017402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3720,11 +3746,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3739,16 +3760,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499577</t>
+          <t>https://artportalen.se/Sighting/135499576</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499578</v>
+        <v>135499577</v>
       </c>
       <c r="B28" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,10 +3805,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490951</v>
+        <v>490931</v>
       </c>
       <c r="R28" t="n">
-        <v>7017390</v>
+        <v>7017371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3856,16 +3877,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499578</t>
+          <t>https://artportalen.se/Sighting/135499577</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499579</v>
+        <v>135499578</v>
       </c>
       <c r="B29" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3901,10 +3922,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490976</v>
+        <v>490951</v>
       </c>
       <c r="R29" t="n">
-        <v>7017311</v>
+        <v>7017390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3973,16 +3994,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499579</t>
+          <t>https://artportalen.se/Sighting/135499578</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>91488964</v>
+        <v>135499579</v>
       </c>
       <c r="B30" t="n">
-        <v>92632</v>
+        <v>96481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3990,37 +4011,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>2812</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490939</v>
+        <v>490976</v>
       </c>
       <c r="R30" t="n">
-        <v>7017412</v>
+        <v>7017311</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4044,12 +4069,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4058,59 +4083,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91488964</t>
+          <t>https://artportalen.se/Sighting/135499579</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>75185505</v>
+        <v>91488964</v>
       </c>
       <c r="B31" t="n">
-        <v>89156</v>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4412</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4120,13 +4152,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490781</v>
+        <v>490939</v>
       </c>
       <c r="R31" t="n">
-        <v>7017384</v>
+        <v>7017412</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4164,19 +4196,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4186,54 +4217,51 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185505</t>
+          <t>https://artportalen.se/Sighting/91488964</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135499609</v>
+        <v>75185505</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>89156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490849</v>
+        <v>490781</v>
       </c>
       <c r="R32" t="n">
-        <v>7017392</v>
+        <v>7017384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4260,17 +4288,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4283,55 +4306,34 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499609</t>
+          <t>https://artportalen.se/Sighting/75185505</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499610</v>
+        <v>135499609</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,10 +4368,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490859</v>
+        <v>490849</v>
       </c>
       <c r="R33" t="n">
-        <v>7017416</v>
+        <v>7017392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4404,6 +4406,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4431,12 +4438,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4453,67 +4460,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499610</t>
+          <t>https://artportalen.se/Sighting/135499609</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499531</v>
+        <v>135499610</v>
       </c>
       <c r="B34" t="n">
-        <v>58094</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100090</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490781</v>
+        <v>490859</v>
       </c>
       <c r="R34" t="n">
-        <v>7017369</v>
+        <v>7017416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4548,23 +4542,39 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Synobservation av en individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4581,16 +4591,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499531</t>
+          <t>https://artportalen.se/Sighting/135499610</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499510</v>
+        <v>135499531</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>58094</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4598,16 +4608,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100090</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4615,12 +4625,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4634,10 +4648,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490891</v>
+        <v>490781</v>
       </c>
       <c r="R35" t="n">
-        <v>7017451</v>
+        <v>7017369</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4674,7 +4688,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Synobservation av en individ med lockläte.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4688,27 +4702,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4725,13 +4719,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499510</t>
+          <t>https://artportalen.se/Sighting/135499531</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499511</v>
+        <v>135499510</v>
       </c>
       <c r="B36" t="n">
         <v>57980</v>
@@ -4764,7 +4758,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4778,10 +4772,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490785</v>
+        <v>490891</v>
       </c>
       <c r="R36" t="n">
-        <v>7017521</v>
+        <v>7017451</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4818,7 +4812,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4832,7 +4826,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -4869,13 +4863,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499511</t>
+          <t>https://artportalen.se/Sighting/135499510</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499512</v>
+        <v>135499511</v>
       </c>
       <c r="B37" t="n">
         <v>57980</v>
@@ -4922,10 +4916,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490783</v>
+        <v>490785</v>
       </c>
       <c r="R37" t="n">
-        <v>7017360</v>
+        <v>7017521</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4962,7 +4956,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4977,11 +4971,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5018,33 +5007,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499512</t>
+          <t>https://artportalen.se/Sighting/135499511</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499596</v>
+        <v>135499512</v>
       </c>
       <c r="B38" t="n">
-        <v>58239</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102981</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5052,29 +5041,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490875</v>
+        <v>490783</v>
       </c>
       <c r="R38" t="n">
-        <v>7017470</v>
+        <v>7017360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5111,7 +5100,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5126,6 +5115,31 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5142,16 +5156,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499512</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499513</v>
+        <v>135499549</v>
       </c>
       <c r="B39" t="n">
-        <v>58141</v>
+        <v>58236</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5159,21 +5173,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>102980</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5185,7 +5199,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5199,10 +5213,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490763</v>
+        <v>490804</v>
       </c>
       <c r="R39" t="n">
-        <v>7017499</v>
+        <v>7017502</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5239,7 +5253,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Minst 1 överflygande med sång.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5253,12 +5267,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5275,43 +5284,43 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499549</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499514</v>
+        <v>135499596</v>
       </c>
       <c r="B40" t="n">
-        <v>58141</v>
+        <v>58239</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>102981</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5321,11 +5330,7 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
@@ -5335,7 +5340,7 @@
         <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017397</v>
+        <v>7017470</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5372,7 +5377,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5387,11 +5392,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5408,59 +5408,67 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499611</v>
+        <v>135499513</v>
       </c>
       <c r="B41" t="n">
-        <v>99159</v>
+        <v>58141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490821</v>
+        <v>490763</v>
       </c>
       <c r="R41" t="n">
-        <v>7017504</v>
+        <v>7017499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5497,7 +5505,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5506,13 +5514,17 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5529,59 +5541,67 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499612</v>
+        <v>135499514</v>
       </c>
       <c r="B42" t="n">
-        <v>99159</v>
+        <v>58141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490848</v>
+        <v>490875</v>
       </c>
       <c r="R42" t="n">
-        <v>7017375</v>
+        <v>7017397</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5616,19 +5636,28 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5645,16 +5674,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499613</v>
+        <v>135499611</v>
       </c>
       <c r="B43" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5694,10 +5723,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490878</v>
+        <v>490821</v>
       </c>
       <c r="R43" t="n">
-        <v>7017368</v>
+        <v>7017504</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5734,7 +5763,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5766,16 +5795,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499614</v>
+        <v>135499612</v>
       </c>
       <c r="B44" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5815,10 +5844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490867</v>
+        <v>490848</v>
       </c>
       <c r="R44" t="n">
-        <v>7017386</v>
+        <v>7017375</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5853,11 +5882,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5887,16 +5911,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499615</v>
+        <v>135499613</v>
       </c>
       <c r="B45" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5936,10 +5960,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490860</v>
+        <v>490878</v>
       </c>
       <c r="R45" t="n">
-        <v>7017386</v>
+        <v>7017368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6008,16 +6032,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499509</v>
+        <v>135499614</v>
       </c>
       <c r="B46" t="n">
-        <v>99266</v>
+        <v>99186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6025,28 +6049,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6057,10 +6081,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490880</v>
+        <v>490867</v>
       </c>
       <c r="R46" t="n">
-        <v>7017365</v>
+        <v>7017386</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6097,7 +6121,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flertalet plantor.</t>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6115,11 +6139,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -6134,16 +6153,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499620</v>
+        <v>135499615</v>
       </c>
       <c r="B47" t="n">
-        <v>108260</v>
+        <v>99186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6151,28 +6170,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220083</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6183,10 +6202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490853</v>
+        <v>490860</v>
       </c>
       <c r="R47" t="n">
-        <v>7017483</v>
+        <v>7017386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6221,6 +6240,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6250,16 +6274,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499621</v>
+        <v>135499509</v>
       </c>
       <c r="B48" t="n">
-        <v>108260</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6267,28 +6291,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6299,10 +6323,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490837</v>
+        <v>490880</v>
       </c>
       <c r="R48" t="n">
-        <v>7017379</v>
+        <v>7017365</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6337,6 +6361,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flertalet plantor.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6352,6 +6381,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
@@ -6366,16 +6400,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499623</v>
+        <v>135499620</v>
       </c>
       <c r="B49" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6404,7 +6438,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6415,10 +6449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490848</v>
+        <v>490853</v>
       </c>
       <c r="R49" t="n">
-        <v>7017376</v>
+        <v>7017483</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6482,16 +6516,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499624</v>
+        <v>135499621</v>
       </c>
       <c r="B50" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6531,10 +6565,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490861</v>
+        <v>490837</v>
       </c>
       <c r="R50" t="n">
-        <v>7017386</v>
+        <v>7017379</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6598,16 +6632,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499625</v>
+        <v>135499623</v>
       </c>
       <c r="B51" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6636,7 +6670,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6647,10 +6681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490821</v>
+        <v>490848</v>
       </c>
       <c r="R51" t="n">
-        <v>7017394</v>
+        <v>7017376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6714,16 +6748,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499626</v>
+        <v>135499624</v>
       </c>
       <c r="B52" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6752,7 +6786,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6763,10 +6797,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490841</v>
+        <v>490861</v>
       </c>
       <c r="R52" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6830,16 +6864,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499550</v>
+        <v>135499625</v>
       </c>
       <c r="B53" t="n">
-        <v>108330</v>
+        <v>108287</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6847,28 +6881,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6879,10 +6913,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490929</v>
+        <v>490821</v>
       </c>
       <c r="R53" t="n">
-        <v>7017429</v>
+        <v>7017394</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6946,16 +6980,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499551</v>
+        <v>135499626</v>
       </c>
       <c r="B54" t="n">
-        <v>108330</v>
+        <v>108287</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6963,28 +6997,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -6995,10 +7029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490853</v>
+        <v>490841</v>
       </c>
       <c r="R54" t="n">
-        <v>7017480</v>
+        <v>7017433</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7033,11 +7067,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7067,16 +7096,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499552</v>
+        <v>135499550</v>
       </c>
       <c r="B55" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7116,10 +7145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490867</v>
+        <v>490929</v>
       </c>
       <c r="R55" t="n">
-        <v>7017480</v>
+        <v>7017429</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7183,16 +7212,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499553</v>
+        <v>135499551</v>
       </c>
       <c r="B56" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7232,10 +7261,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R56" t="n">
-        <v>7017457</v>
+        <v>7017480</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7270,6 +7299,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7299,16 +7333,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499554</v>
+        <v>135499552</v>
       </c>
       <c r="B57" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7348,10 +7382,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490737</v>
+        <v>490867</v>
       </c>
       <c r="R57" t="n">
-        <v>7017474</v>
+        <v>7017480</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7415,16 +7449,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499555</v>
+        <v>135499553</v>
       </c>
       <c r="B58" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7464,10 +7498,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490873</v>
+        <v>490841</v>
       </c>
       <c r="R58" t="n">
-        <v>7017368</v>
+        <v>7017457</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7531,16 +7565,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499556</v>
+        <v>135499554</v>
       </c>
       <c r="B59" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7580,10 +7614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490863</v>
+        <v>490737</v>
       </c>
       <c r="R59" t="n">
-        <v>7017386</v>
+        <v>7017474</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7633,11 +7667,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7652,16 +7681,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499544</v>
+        <v>135499555</v>
       </c>
       <c r="B60" t="n">
-        <v>111210</v>
+        <v>108357</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7669,28 +7698,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7701,10 +7730,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490844</v>
+        <v>490873</v>
       </c>
       <c r="R60" t="n">
-        <v>7017468</v>
+        <v>7017368</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7768,16 +7797,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499546</v>
+        <v>135499556</v>
       </c>
       <c r="B61" t="n">
-        <v>111210</v>
+        <v>108357</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7785,28 +7814,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7817,10 +7846,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490780</v>
+        <v>490863</v>
       </c>
       <c r="R61" t="n">
-        <v>7017405</v>
+        <v>7017386</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7870,6 +7899,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -7884,16 +7918,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499547</v>
+        <v>135499544</v>
       </c>
       <c r="B62" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7922,7 +7956,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7933,10 +7967,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490858</v>
+        <v>490844</v>
       </c>
       <c r="R62" t="n">
-        <v>7017416</v>
+        <v>7017468</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8000,16 +8034,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499548</v>
+        <v>135499546</v>
       </c>
       <c r="B63" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8038,7 +8072,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -8049,10 +8083,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490964</v>
+        <v>490780</v>
       </c>
       <c r="R63" t="n">
-        <v>7017356</v>
+        <v>7017405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8102,11 +8136,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8121,16 +8150,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499617</v>
+        <v>135499547</v>
       </c>
       <c r="B64" t="n">
-        <v>110206</v>
+        <v>111237</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8138,28 +8167,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220294</v>
+        <v>220240</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -8170,10 +8199,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490864</v>
+        <v>490858</v>
       </c>
       <c r="R64" t="n">
-        <v>7017486</v>
+        <v>7017416</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8208,11 +8237,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8242,53 +8266,45 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499580</v>
+        <v>135499548</v>
       </c>
       <c r="B65" t="n">
-        <v>99242</v>
+        <v>111237</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -8299,10 +8315,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490975</v>
+        <v>490964</v>
       </c>
       <c r="R65" t="n">
-        <v>7017304</v>
+        <v>7017356</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8337,11 +8353,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8376,53 +8387,45 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499583</v>
+        <v>135499617</v>
       </c>
       <c r="B66" t="n">
-        <v>99242</v>
+        <v>110233</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -8433,10 +8436,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490768</v>
+        <v>490864</v>
       </c>
       <c r="R66" t="n">
-        <v>7017376</v>
+        <v>7017486</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8473,7 +8476,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8491,11 +8494,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
@@ -8510,16 +8508,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499584</v>
+        <v>135499580</v>
       </c>
       <c r="B67" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8546,7 +8544,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8567,10 +8565,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490839</v>
+        <v>490975</v>
       </c>
       <c r="R67" t="n">
-        <v>7017351</v>
+        <v>7017304</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8607,7 +8605,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8622,7 +8620,12 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8639,16 +8642,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499585</v>
+        <v>135499581</v>
       </c>
       <c r="B68" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8675,7 +8678,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8696,10 +8699,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490845</v>
+        <v>490951</v>
       </c>
       <c r="R68" t="n">
-        <v>7017392</v>
+        <v>7017428</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8736,7 +8739,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8751,7 +8754,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8768,16 +8771,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499581</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499586</v>
+        <v>135499582</v>
       </c>
       <c r="B69" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8825,10 +8828,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490812</v>
+        <v>490884</v>
       </c>
       <c r="R69" t="n">
-        <v>7017401</v>
+        <v>7017471</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8865,7 +8868,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8880,12 +8883,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8902,16 +8900,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499582</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499588</v>
+        <v>135499583</v>
       </c>
       <c r="B70" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8938,7 +8936,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8959,10 +8957,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490843</v>
+        <v>490768</v>
       </c>
       <c r="R70" t="n">
-        <v>7017436</v>
+        <v>7017376</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8999,7 +8997,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9036,16 +9034,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499589</v>
+        <v>135499584</v>
       </c>
       <c r="B71" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9072,7 +9070,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9093,10 +9091,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490967</v>
+        <v>490839</v>
       </c>
       <c r="R71" t="n">
-        <v>7017335</v>
+        <v>7017351</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9133,7 +9131,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9148,12 +9146,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9170,16 +9163,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499590</v>
+        <v>135499585</v>
       </c>
       <c r="B72" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9206,7 +9199,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9227,10 +9220,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490979</v>
+        <v>490845</v>
       </c>
       <c r="R72" t="n">
-        <v>7017360</v>
+        <v>7017392</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9267,7 +9260,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9282,12 +9275,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9304,16 +9292,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499591</v>
+        <v>135499586</v>
       </c>
       <c r="B73" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9340,7 +9328,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9361,10 +9349,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490973</v>
+        <v>490812</v>
       </c>
       <c r="R73" t="n">
-        <v>7017399</v>
+        <v>7017401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9401,7 +9389,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9438,16 +9426,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499592</v>
+        <v>135499588</v>
       </c>
       <c r="B74" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9474,7 +9462,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9495,10 +9483,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490951</v>
+        <v>490843</v>
       </c>
       <c r="R74" t="n">
-        <v>7017408</v>
+        <v>7017436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9535,7 +9523,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9572,16 +9560,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499593</v>
+        <v>135499589</v>
       </c>
       <c r="B75" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9608,7 +9596,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9629,10 +9617,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490951</v>
+        <v>490967</v>
       </c>
       <c r="R75" t="n">
-        <v>7017396</v>
+        <v>7017335</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9669,7 +9657,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9706,16 +9694,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499594</v>
+        <v>135499590</v>
       </c>
       <c r="B76" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9742,7 +9730,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9763,10 +9751,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490957</v>
+        <v>490979</v>
       </c>
       <c r="R76" t="n">
-        <v>7017386</v>
+        <v>7017360</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9803,7 +9791,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9840,43 +9828,55 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499519</v>
+        <v>135499591</v>
       </c>
       <c r="B77" t="n">
-        <v>98104</v>
+        <v>99269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490752</v>
+        <v>490973</v>
       </c>
       <c r="R77" t="n">
-        <v>7017499</v>
+        <v>7017399</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9943,6 +9943,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
@@ -9957,45 +9962,53 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499516</v>
+        <v>135499592</v>
       </c>
       <c r="B78" t="n">
-        <v>99264</v>
+        <v>99269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -10006,10 +10019,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490844</v>
+        <v>490951</v>
       </c>
       <c r="R78" t="n">
-        <v>7017394</v>
+        <v>7017408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10044,6 +10057,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10059,6 +10077,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
@@ -10073,45 +10096,53 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499517</v>
+        <v>135499593</v>
       </c>
       <c r="B79" t="n">
-        <v>99264</v>
+        <v>99269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -10122,10 +10153,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490814</v>
+        <v>490951</v>
       </c>
       <c r="R79" t="n">
-        <v>7017404</v>
+        <v>7017396</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10160,6 +10191,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10175,6 +10211,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
@@ -10189,45 +10230,53 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499627</v>
+        <v>135499594</v>
       </c>
       <c r="B80" t="n">
-        <v>101451</v>
+        <v>99269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10238,10 +10287,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490803</v>
+        <v>490957</v>
       </c>
       <c r="R80" t="n">
-        <v>7017492</v>
+        <v>7017386</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10276,6 +10325,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10291,6 +10345,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
@@ -10305,16 +10364,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499628</v>
+        <v>135499519</v>
       </c>
       <c r="B81" t="n">
-        <v>101451</v>
+        <v>98131</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10322,30 +10381,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10354,10 +10409,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490792</v>
+        <v>490752</v>
       </c>
       <c r="R81" t="n">
-        <v>7017441</v>
+        <v>7017499</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10392,6 +10447,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10421,16 +10481,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499629</v>
+        <v>135499516</v>
       </c>
       <c r="B82" t="n">
-        <v>101451</v>
+        <v>99291</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10438,28 +10498,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10470,10 +10530,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490764</v>
+        <v>490844</v>
       </c>
       <c r="R82" t="n">
-        <v>7017441</v>
+        <v>7017394</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10537,16 +10597,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499630</v>
+        <v>135499517</v>
       </c>
       <c r="B83" t="n">
-        <v>101451</v>
+        <v>99291</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10554,28 +10614,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -10586,10 +10646,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490798</v>
+        <v>490814</v>
       </c>
       <c r="R83" t="n">
-        <v>7017366</v>
+        <v>7017404</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10653,16 +10713,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499631</v>
+        <v>135499627</v>
       </c>
       <c r="B84" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10702,10 +10762,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490816</v>
+        <v>490803</v>
       </c>
       <c r="R84" t="n">
-        <v>7017378</v>
+        <v>7017492</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10769,16 +10829,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499632</v>
+        <v>135499628</v>
       </c>
       <c r="B85" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10818,10 +10878,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490796</v>
+        <v>490792</v>
       </c>
       <c r="R85" t="n">
-        <v>7017382</v>
+        <v>7017441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10885,16 +10945,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499633</v>
+        <v>135499629</v>
       </c>
       <c r="B86" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10934,10 +10994,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490782</v>
+        <v>490764</v>
       </c>
       <c r="R86" t="n">
-        <v>7017407</v>
+        <v>7017441</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11001,16 +11061,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499634</v>
+        <v>135499630</v>
       </c>
       <c r="B87" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11050,10 +11110,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490730</v>
+        <v>490798</v>
       </c>
       <c r="R87" t="n">
-        <v>7017371</v>
+        <v>7017366</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11117,16 +11177,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499635</v>
+        <v>135499631</v>
       </c>
       <c r="B88" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11166,10 +11226,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490827</v>
+        <v>490816</v>
       </c>
       <c r="R88" t="n">
-        <v>7017356</v>
+        <v>7017378</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11233,16 +11293,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499636</v>
+        <v>135499632</v>
       </c>
       <c r="B89" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11282,10 +11342,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490844</v>
+        <v>490796</v>
       </c>
       <c r="R89" t="n">
-        <v>7017345</v>
+        <v>7017382</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11349,16 +11409,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499637</v>
+        <v>135499633</v>
       </c>
       <c r="B90" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11398,10 +11458,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490852</v>
+        <v>490782</v>
       </c>
       <c r="R90" t="n">
-        <v>7017373</v>
+        <v>7017407</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11448,7 +11508,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11465,16 +11525,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499638</v>
+        <v>135499634</v>
       </c>
       <c r="B91" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11514,10 +11574,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490882</v>
+        <v>490730</v>
       </c>
       <c r="R91" t="n">
-        <v>7017368</v>
+        <v>7017371</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11564,7 +11624,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11581,16 +11641,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499639</v>
+        <v>135499635</v>
       </c>
       <c r="B92" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11630,10 +11690,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490865</v>
+        <v>490827</v>
       </c>
       <c r="R92" t="n">
-        <v>7017386</v>
+        <v>7017356</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11697,16 +11757,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499640</v>
+        <v>135499636</v>
       </c>
       <c r="B93" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11746,10 +11806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490840</v>
+        <v>490844</v>
       </c>
       <c r="R93" t="n">
-        <v>7017433</v>
+        <v>7017345</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11813,16 +11873,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499641</v>
+        <v>135499637</v>
       </c>
       <c r="B94" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11862,10 +11922,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490880</v>
+        <v>490852</v>
       </c>
       <c r="R94" t="n">
-        <v>7017422</v>
+        <v>7017373</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11912,7 +11972,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11929,16 +11989,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499618</v>
+        <v>135499638</v>
       </c>
       <c r="B95" t="n">
-        <v>98258</v>
+        <v>101478</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11946,21 +12006,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11978,10 +12038,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490791</v>
+        <v>490882</v>
       </c>
       <c r="R95" t="n">
-        <v>7017443</v>
+        <v>7017368</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12016,11 +12076,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -12033,7 +12088,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12050,16 +12105,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499619</v>
+        <v>135499639</v>
       </c>
       <c r="B96" t="n">
-        <v>98258</v>
+        <v>101478</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12067,33 +12122,25 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12107,10 +12154,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490868</v>
+        <v>490865</v>
       </c>
       <c r="R96" t="n">
-        <v>7017387</v>
+        <v>7017386</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12145,11 +12192,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12165,11 +12207,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
@@ -12184,16 +12221,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499520</v>
+        <v>135499640</v>
       </c>
       <c r="B97" t="n">
-        <v>99048</v>
+        <v>101478</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12201,21 +12238,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12233,10 +12270,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490757</v>
+        <v>490840</v>
       </c>
       <c r="R97" t="n">
-        <v>7017472</v>
+        <v>7017433</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12300,16 +12337,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499521</v>
+        <v>135499641</v>
       </c>
       <c r="B98" t="n">
-        <v>99048</v>
+        <v>101478</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12317,21 +12354,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12349,10 +12386,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490966</v>
+        <v>490880</v>
       </c>
       <c r="R98" t="n">
-        <v>7017430</v>
+        <v>7017422</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12416,16 +12453,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499522</v>
+        <v>135499618</v>
       </c>
       <c r="B99" t="n">
-        <v>99048</v>
+        <v>98285</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12433,21 +12470,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12465,10 +12502,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490920</v>
+        <v>490791</v>
       </c>
       <c r="R99" t="n">
-        <v>7017445</v>
+        <v>7017443</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12503,6 +12540,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -12532,16 +12574,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499523</v>
+        <v>135499619</v>
       </c>
       <c r="B100" t="n">
-        <v>99048</v>
+        <v>98285</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12549,25 +12591,33 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12581,10 +12631,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490912</v>
+        <v>490868</v>
       </c>
       <c r="R100" t="n">
-        <v>7017466</v>
+        <v>7017387</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12619,6 +12669,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12634,6 +12689,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
@@ -12648,16 +12708,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499524</v>
+        <v>135499520</v>
       </c>
       <c r="B101" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12697,10 +12757,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490858</v>
+        <v>490757</v>
       </c>
       <c r="R101" t="n">
-        <v>7017493</v>
+        <v>7017472</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12764,16 +12824,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499525</v>
+        <v>135499521</v>
       </c>
       <c r="B102" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12802,7 +12862,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12813,10 +12873,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490804</v>
+        <v>490966</v>
       </c>
       <c r="R102" t="n">
-        <v>7017492</v>
+        <v>7017430</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12880,16 +12940,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499526</v>
+        <v>135499522</v>
       </c>
       <c r="B103" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12929,10 +12989,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490740</v>
+        <v>490920</v>
       </c>
       <c r="R103" t="n">
-        <v>7017423</v>
+        <v>7017445</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12996,16 +13056,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499527</v>
+        <v>135499523</v>
       </c>
       <c r="B104" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13045,10 +13105,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490732</v>
+        <v>490912</v>
       </c>
       <c r="R104" t="n">
-        <v>7017370</v>
+        <v>7017466</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13112,16 +13172,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499528</v>
+        <v>135499524</v>
       </c>
       <c r="B105" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13161,10 +13221,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490867</v>
+        <v>490858</v>
       </c>
       <c r="R105" t="n">
-        <v>7017386</v>
+        <v>7017493</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13199,11 +13259,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -13233,16 +13288,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499529</v>
+        <v>135499525</v>
       </c>
       <c r="B106" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13271,7 +13326,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -13282,10 +13337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490807</v>
+        <v>490804</v>
       </c>
       <c r="R106" t="n">
-        <v>7017431</v>
+        <v>7017492</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13349,16 +13404,16 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499530</v>
+        <v>135499526</v>
       </c>
       <c r="B107" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13387,7 +13442,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13398,10 +13453,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490932</v>
+        <v>490740</v>
       </c>
       <c r="R107" t="n">
-        <v>7017369</v>
+        <v>7017423</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13465,16 +13520,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499597</v>
+        <v>135499527</v>
       </c>
       <c r="B108" t="n">
-        <v>98293</v>
+        <v>99075</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13482,21 +13537,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13514,10 +13569,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490969</v>
+        <v>490732</v>
       </c>
       <c r="R108" t="n">
-        <v>7017431</v>
+        <v>7017370</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13581,16 +13636,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499598</v>
+        <v>135499528</v>
       </c>
       <c r="B109" t="n">
-        <v>98293</v>
+        <v>99075</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13598,21 +13653,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13630,10 +13685,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490840</v>
+        <v>490867</v>
       </c>
       <c r="R109" t="n">
-        <v>7017457</v>
+        <v>7017386</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13668,6 +13723,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13697,16 +13757,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499599</v>
+        <v>135499529</v>
       </c>
       <c r="B110" t="n">
-        <v>98293</v>
+        <v>99075</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13714,21 +13774,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13746,10 +13806,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490831</v>
+        <v>490807</v>
       </c>
       <c r="R110" t="n">
-        <v>7017486</v>
+        <v>7017431</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13813,16 +13873,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499600</v>
+        <v>135499530</v>
       </c>
       <c r="B111" t="n">
-        <v>98293</v>
+        <v>99075</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13830,28 +13890,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13862,10 +13922,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490797</v>
+        <v>490932</v>
       </c>
       <c r="R111" t="n">
-        <v>7017497</v>
+        <v>7017369</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13929,16 +13989,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499601</v>
+        <v>135499597</v>
       </c>
       <c r="B112" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13978,10 +14038,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490797</v>
+        <v>490969</v>
       </c>
       <c r="R112" t="n">
-        <v>7017511</v>
+        <v>7017431</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14045,16 +14105,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499602</v>
+        <v>135499598</v>
       </c>
       <c r="B113" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14094,10 +14154,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490737</v>
+        <v>490840</v>
       </c>
       <c r="R113" t="n">
-        <v>7017473</v>
+        <v>7017457</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14161,16 +14221,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499515</v>
+        <v>135499599</v>
       </c>
       <c r="B114" t="n">
-        <v>101988</v>
+        <v>98320</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14178,21 +14238,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223366</v>
+        <v>223358</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14210,10 +14270,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490788</v>
+        <v>490831</v>
       </c>
       <c r="R114" t="n">
-        <v>7017450</v>
+        <v>7017486</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14277,16 +14337,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499532</v>
+        <v>135499600</v>
       </c>
       <c r="B115" t="n">
-        <v>101341</v>
+        <v>98320</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14294,21 +14354,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14326,10 +14386,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490889</v>
+        <v>490797</v>
       </c>
       <c r="R115" t="n">
-        <v>7017459</v>
+        <v>7017497</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14393,16 +14453,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499533</v>
+        <v>135499601</v>
       </c>
       <c r="B116" t="n">
-        <v>101341</v>
+        <v>98320</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14410,21 +14470,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14442,10 +14502,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490743</v>
+        <v>490797</v>
       </c>
       <c r="R116" t="n">
-        <v>7017495</v>
+        <v>7017511</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14509,16 +14569,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499534</v>
+        <v>135499602</v>
       </c>
       <c r="B117" t="n">
-        <v>101341</v>
+        <v>98320</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14526,21 +14586,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14561,7 +14621,7 @@
         <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017474</v>
+        <v>7017473</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14625,16 +14685,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499535</v>
+        <v>135499515</v>
       </c>
       <c r="B118" t="n">
-        <v>101341</v>
+        <v>102015</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14642,21 +14702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>224885</v>
+        <v>223366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14674,10 +14734,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490734</v>
+        <v>490788</v>
       </c>
       <c r="R118" t="n">
-        <v>7017429</v>
+        <v>7017450</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14741,16 +14801,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499536</v>
+        <v>135499532</v>
       </c>
       <c r="B119" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14790,10 +14850,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490780</v>
+        <v>490889</v>
       </c>
       <c r="R119" t="n">
-        <v>7017405</v>
+        <v>7017459</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14857,16 +14917,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499537</v>
+        <v>135499533</v>
       </c>
       <c r="B120" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14906,10 +14966,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490751</v>
+        <v>490743</v>
       </c>
       <c r="R120" t="n">
-        <v>7017406</v>
+        <v>7017495</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14973,16 +15033,16 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499538</v>
+        <v>135499534</v>
       </c>
       <c r="B121" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15022,10 +15082,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490729</v>
+        <v>490737</v>
       </c>
       <c r="R121" t="n">
-        <v>7017373</v>
+        <v>7017474</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15089,16 +15149,16 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499540</v>
+        <v>135499535</v>
       </c>
       <c r="B122" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15138,10 +15198,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490847</v>
+        <v>490734</v>
       </c>
       <c r="R122" t="n">
-        <v>7017345</v>
+        <v>7017429</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15205,16 +15265,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499541</v>
+        <v>135499536</v>
       </c>
       <c r="B123" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15254,10 +15314,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490856</v>
+        <v>490780</v>
       </c>
       <c r="R123" t="n">
-        <v>7017358</v>
+        <v>7017405</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15321,16 +15381,16 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499542</v>
+        <v>135499537</v>
       </c>
       <c r="B124" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15359,7 +15419,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -15370,10 +15430,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490840</v>
+        <v>490751</v>
       </c>
       <c r="R124" t="n">
-        <v>7017433</v>
+        <v>7017406</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15436,6 +15496,470 @@
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499537</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>135499538</v>
+      </c>
+      <c r="B125" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>490729</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7017373</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499538</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>135499540</v>
+      </c>
+      <c r="B126" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>490847</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7017345</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499540</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>135499541</v>
+      </c>
+      <c r="B127" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>490856</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7017358</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499541</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>135499542</v>
+      </c>
+      <c r="B128" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>490840</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7017433</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -15566,6 +16090,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ128"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499607</v>
+        <v>135499608</v>
       </c>
       <c r="B2" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490869</v>
+        <v>490867</v>
       </c>
       <c r="R2" t="n">
-        <v>7017370</v>
+        <v>7017387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad snitslad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +790,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkrikt fuktstråk.</t>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,71 +812,58 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499607</t>
+          <t>https://artportalen.se/Sighting/135499608</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499608</v>
+        <v>135499603</v>
       </c>
       <c r="B3" t="n">
-        <v>99180</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490867</v>
+        <v>490968</v>
       </c>
       <c r="R3" t="n">
-        <v>7017387</v>
+        <v>7017430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,7 +900,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,9 +918,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,16 +952,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499608</t>
+          <t>https://artportalen.se/Sighting/135499603</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499603</v>
+        <v>135499604</v>
       </c>
       <c r="B4" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,10 +1000,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490968</v>
+        <v>490893</v>
       </c>
       <c r="R4" t="n">
-        <v>7017430</v>
+        <v>7017459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,12 +1070,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,16 +1092,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499603</t>
+          <t>https://artportalen.se/Sighting/135499604</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499604</v>
+        <v>135499605</v>
       </c>
       <c r="B5" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,10 +1140,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490893</v>
+        <v>490741</v>
       </c>
       <c r="R5" t="n">
-        <v>7017459</v>
+        <v>7017465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1178,7 +1180,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,16 +1232,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499604</t>
+          <t>https://artportalen.se/Sighting/135499605</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499605</v>
+        <v>135499606</v>
       </c>
       <c r="B6" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,10 +1280,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490741</v>
+        <v>490951</v>
       </c>
       <c r="R6" t="n">
-        <v>7017465</v>
+        <v>7017411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1320,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1348,12 +1350,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1370,16 +1372,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499605</t>
+          <t>https://artportalen.se/Sighting/135499606</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135499606</v>
+        <v>75185503</v>
       </c>
       <c r="B7" t="n">
-        <v>92044</v>
+        <v>87322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,41 +1389,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1988</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490951</v>
+        <v>490758</v>
       </c>
       <c r="R7" t="n">
-        <v>7017411</v>
+        <v>7017384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1448,17 +1443,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1471,90 +1461,73 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499606</t>
+          <t>https://artportalen.se/Sighting/75185503</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75185503</v>
+        <v>135499557</v>
       </c>
       <c r="B8" t="n">
-        <v>87322</v>
+        <v>96488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1988</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490758</v>
+        <v>490738</v>
       </c>
       <c r="R8" t="n">
-        <v>7017384</v>
+        <v>7017396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1581,12 +1554,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,34 +1572,35 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185503</t>
+          <t>https://artportalen.se/Sighting/135499557</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499557</v>
+        <v>135499558</v>
       </c>
       <c r="B9" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1662,10 +1636,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490738</v>
+        <v>490991</v>
       </c>
       <c r="R9" t="n">
-        <v>7017396</v>
+        <v>7017297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1729,16 +1703,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499557</t>
+          <t>https://artportalen.se/Sighting/135499558</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499558</v>
+        <v>135499560</v>
       </c>
       <c r="B10" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,10 +1748,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490991</v>
+        <v>490966</v>
       </c>
       <c r="R10" t="n">
-        <v>7017297</v>
+        <v>7017426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,6 +1801,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1841,16 +1820,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499558</t>
+          <t>https://artportalen.se/Sighting/135499560</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499560</v>
+        <v>135499561</v>
       </c>
       <c r="B11" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,10 +1865,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490966</v>
+        <v>490929</v>
       </c>
       <c r="R11" t="n">
-        <v>7017426</v>
+        <v>7017441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1936,12 +1915,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1958,16 +1932,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499560</t>
+          <t>https://artportalen.se/Sighting/135499561</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499561</v>
+        <v>135499562</v>
       </c>
       <c r="B12" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,10 +1977,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490929</v>
+        <v>490910</v>
       </c>
       <c r="R12" t="n">
-        <v>7017441</v>
+        <v>7017467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2070,16 +2044,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499561</t>
+          <t>https://artportalen.se/Sighting/135499562</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499562</v>
+        <v>135499563</v>
       </c>
       <c r="B13" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,10 +2089,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490910</v>
+        <v>490878</v>
       </c>
       <c r="R13" t="n">
-        <v>7017467</v>
+        <v>7017474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,7 +2139,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2182,16 +2156,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499562</t>
+          <t>https://artportalen.se/Sighting/135499563</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499563</v>
+        <v>135499564</v>
       </c>
       <c r="B14" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,10 +2201,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490878</v>
+        <v>490883</v>
       </c>
       <c r="R14" t="n">
-        <v>7017474</v>
+        <v>7017462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2277,7 +2251,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2294,16 +2268,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499563</t>
+          <t>https://artportalen.se/Sighting/135499564</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499564</v>
+        <v>135499565</v>
       </c>
       <c r="B15" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2339,10 +2313,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490883</v>
+        <v>490756</v>
       </c>
       <c r="R15" t="n">
-        <v>7017462</v>
+        <v>7017472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2389,7 +2363,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2406,16 +2380,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499564</t>
+          <t>https://artportalen.se/Sighting/135499565</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499565</v>
+        <v>135499566</v>
       </c>
       <c r="B16" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2451,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490756</v>
+        <v>490790</v>
       </c>
       <c r="R16" t="n">
-        <v>7017472</v>
+        <v>7017441</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2518,16 +2492,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499565</t>
+          <t>https://artportalen.se/Sighting/135499566</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499566</v>
+        <v>135499567</v>
       </c>
       <c r="B17" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490790</v>
+        <v>490732</v>
       </c>
       <c r="R17" t="n">
-        <v>7017441</v>
+        <v>7017442</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2613,7 +2587,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2630,16 +2604,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499566</t>
+          <t>https://artportalen.se/Sighting/135499567</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499567</v>
+        <v>135499568</v>
       </c>
       <c r="B18" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,10 +2649,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490732</v>
+        <v>490781</v>
       </c>
       <c r="R18" t="n">
-        <v>7017442</v>
+        <v>7017407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2725,7 +2699,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2742,16 +2716,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499567</t>
+          <t>https://artportalen.se/Sighting/135499568</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499568</v>
+        <v>135499569</v>
       </c>
       <c r="B19" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490781</v>
+        <v>490731</v>
       </c>
       <c r="R19" t="n">
-        <v>7017407</v>
+        <v>7017371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2840,6 +2814,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2854,16 +2833,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499568</t>
+          <t>https://artportalen.se/Sighting/135499569</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499569</v>
+        <v>135499570</v>
       </c>
       <c r="B20" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2899,10 +2878,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490731</v>
+        <v>490854</v>
       </c>
       <c r="R20" t="n">
-        <v>7017371</v>
+        <v>7017345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2952,11 +2931,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2971,16 +2945,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499569</t>
+          <t>https://artportalen.se/Sighting/135499570</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499570</v>
+        <v>135499571</v>
       </c>
       <c r="B21" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,10 +2990,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490854</v>
+        <v>490878</v>
       </c>
       <c r="R21" t="n">
-        <v>7017345</v>
+        <v>7017366</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,6 +3028,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3083,16 +3062,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499570</t>
+          <t>https://artportalen.se/Sighting/135499571</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499571</v>
+        <v>135499572</v>
       </c>
       <c r="B22" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3128,10 +3107,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490878</v>
+        <v>490867</v>
       </c>
       <c r="R22" t="n">
-        <v>7017366</v>
+        <v>7017386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3166,11 +3145,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3200,16 +3174,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499571</t>
+          <t>https://artportalen.se/Sighting/135499572</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499572</v>
+        <v>135499573</v>
       </c>
       <c r="B23" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,10 +3219,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490867</v>
+        <v>490840</v>
       </c>
       <c r="R23" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3312,16 +3286,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499572</t>
+          <t>https://artportalen.se/Sighting/135499573</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499573</v>
+        <v>135499574</v>
       </c>
       <c r="B24" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3357,10 +3331,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490840</v>
+        <v>490844</v>
       </c>
       <c r="R24" t="n">
-        <v>7017433</v>
+        <v>7017436</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,16 +3398,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499573</t>
+          <t>https://artportalen.se/Sighting/135499574</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499574</v>
+        <v>135499575</v>
       </c>
       <c r="B25" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,10 +3443,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490844</v>
+        <v>490872</v>
       </c>
       <c r="R25" t="n">
-        <v>7017436</v>
+        <v>7017426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3536,16 +3510,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499574</t>
+          <t>https://artportalen.se/Sighting/135499575</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499575</v>
+        <v>135499576</v>
       </c>
       <c r="B26" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3581,10 +3555,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490872</v>
+        <v>490917</v>
       </c>
       <c r="R26" t="n">
-        <v>7017426</v>
+        <v>7017402</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3648,16 +3622,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499575</t>
+          <t>https://artportalen.se/Sighting/135499576</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499576</v>
+        <v>135499577</v>
       </c>
       <c r="B27" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3693,10 +3667,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490917</v>
+        <v>490931</v>
       </c>
       <c r="R27" t="n">
-        <v>7017402</v>
+        <v>7017371</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3746,6 +3720,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3760,16 +3739,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499576</t>
+          <t>https://artportalen.se/Sighting/135499577</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499577</v>
+        <v>135499578</v>
       </c>
       <c r="B28" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,10 +3784,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490931</v>
+        <v>490951</v>
       </c>
       <c r="R28" t="n">
-        <v>7017371</v>
+        <v>7017390</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,16 +3856,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499577</t>
+          <t>https://artportalen.se/Sighting/135499578</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499578</v>
+        <v>135499579</v>
       </c>
       <c r="B29" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,10 +3901,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490951</v>
+        <v>490976</v>
       </c>
       <c r="R29" t="n">
-        <v>7017390</v>
+        <v>7017311</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3994,16 +3973,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499578</t>
+          <t>https://artportalen.se/Sighting/135499579</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135499579</v>
+        <v>91488964</v>
       </c>
       <c r="B30" t="n">
-        <v>96486</v>
+        <v>92632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,41 +3990,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2812</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490976</v>
+        <v>490939</v>
       </c>
       <c r="R30" t="n">
-        <v>7017311</v>
+        <v>7017412</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4069,12 +4044,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4083,66 +4058,59 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499579</t>
+          <t>https://artportalen.se/Sighting/91488964</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>91488964</v>
+        <v>75185505</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>89156</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4152,13 +4120,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490939</v>
+        <v>490781</v>
       </c>
       <c r="R31" t="n">
-        <v>7017412</v>
+        <v>7017384</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4196,18 +4164,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4217,51 +4186,54 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91488964</t>
+          <t>https://artportalen.se/Sighting/75185505</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>75185505</v>
+        <v>135499609</v>
       </c>
       <c r="B32" t="n">
-        <v>89156</v>
+        <v>79441</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490781</v>
+        <v>490849</v>
       </c>
       <c r="R32" t="n">
-        <v>7017384</v>
+        <v>7017392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4288,12 +4260,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4306,31 +4283,52 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185505</t>
+          <t>https://artportalen.se/Sighting/135499609</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499609</v>
+        <v>135499610</v>
       </c>
       <c r="B33" t="n">
         <v>79441</v>
@@ -4368,10 +4366,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490849</v>
+        <v>490859</v>
       </c>
       <c r="R33" t="n">
-        <v>7017392</v>
+        <v>7017416</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,11 +4404,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4438,12 +4431,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4460,54 +4453,67 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499609</t>
+          <t>https://artportalen.se/Sighting/135499610</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499610</v>
+        <v>135499531</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>58094</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100090</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490859</v>
+        <v>490781</v>
       </c>
       <c r="R34" t="n">
-        <v>7017416</v>
+        <v>7017369</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,39 +4548,23 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Synobservation av en individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4591,16 +4581,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499610</t>
+          <t>https://artportalen.se/Sighting/135499531</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499531</v>
+        <v>135499510</v>
       </c>
       <c r="B35" t="n">
-        <v>58094</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4608,16 +4598,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100090</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4625,16 +4615,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4648,10 +4634,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490781</v>
+        <v>490891</v>
       </c>
       <c r="R35" t="n">
-        <v>7017369</v>
+        <v>7017451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,7 +4674,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Synobservation av en individ med lockläte.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4702,7 +4688,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4719,13 +4725,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499531</t>
+          <t>https://artportalen.se/Sighting/135499510</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499510</v>
+        <v>135499511</v>
       </c>
       <c r="B36" t="n">
         <v>57980</v>
@@ -4758,7 +4764,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4772,10 +4778,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490891</v>
+        <v>490785</v>
       </c>
       <c r="R36" t="n">
-        <v>7017451</v>
+        <v>7017521</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4812,7 +4818,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4826,7 +4832,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -4863,13 +4869,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499510</t>
+          <t>https://artportalen.se/Sighting/135499511</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499511</v>
+        <v>135499512</v>
       </c>
       <c r="B37" t="n">
         <v>57980</v>
@@ -4916,10 +4922,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490785</v>
+        <v>490783</v>
       </c>
       <c r="R37" t="n">
-        <v>7017521</v>
+        <v>7017360</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4956,7 +4962,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4971,6 +4977,11 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5007,33 +5018,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499511</t>
+          <t>https://artportalen.se/Sighting/135499512</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499512</v>
+        <v>135499596</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>58239</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5041,29 +5052,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490783</v>
+        <v>490875</v>
       </c>
       <c r="R38" t="n">
-        <v>7017360</v>
+        <v>7017470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5100,7 +5111,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5115,31 +5126,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5156,16 +5142,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499512</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499549</v>
+        <v>135499513</v>
       </c>
       <c r="B39" t="n">
-        <v>58236</v>
+        <v>58141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,21 +5159,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102980</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5199,7 +5185,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5213,10 +5199,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490804</v>
+        <v>490763</v>
       </c>
       <c r="R39" t="n">
-        <v>7017502</v>
+        <v>7017499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5253,7 +5239,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 1 överflygande med sång.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5267,7 +5253,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5284,43 +5275,43 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499549</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499596</v>
+        <v>135499514</v>
       </c>
       <c r="B40" t="n">
-        <v>58239</v>
+        <v>58141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102981</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5330,7 +5321,11 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
@@ -5340,7 +5335,7 @@
         <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017470</v>
+        <v>7017397</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5377,7 +5372,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5392,6 +5387,11 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5408,67 +5408,59 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499513</v>
+        <v>135499611</v>
       </c>
       <c r="B41" t="n">
-        <v>58141</v>
+        <v>99193</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490763</v>
+        <v>490821</v>
       </c>
       <c r="R41" t="n">
-        <v>7017499</v>
+        <v>7017504</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5505,7 +5497,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5514,17 +5506,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5541,67 +5529,59 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499514</v>
+        <v>135499612</v>
       </c>
       <c r="B42" t="n">
-        <v>58141</v>
+        <v>99193</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490875</v>
+        <v>490848</v>
       </c>
       <c r="R42" t="n">
-        <v>7017397</v>
+        <v>7017375</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5636,28 +5616,19 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5674,16 +5645,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499611</v>
+        <v>135499613</v>
       </c>
       <c r="B43" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5723,10 +5694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490821</v>
+        <v>490878</v>
       </c>
       <c r="R43" t="n">
-        <v>7017504</v>
+        <v>7017368</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5763,7 +5734,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk.</t>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5795,16 +5766,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499612</v>
+        <v>135499614</v>
       </c>
       <c r="B44" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5844,10 +5815,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490848</v>
+        <v>490867</v>
       </c>
       <c r="R44" t="n">
-        <v>7017375</v>
+        <v>7017386</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5882,6 +5853,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5911,16 +5887,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499613</v>
+        <v>135499615</v>
       </c>
       <c r="B45" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5960,10 +5936,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490878</v>
+        <v>490860</v>
       </c>
       <c r="R45" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6032,16 +6008,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499614</v>
+        <v>135499509</v>
       </c>
       <c r="B46" t="n">
-        <v>99191</v>
+        <v>99300</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6049,28 +6025,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6081,10 +6057,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490867</v>
+        <v>490880</v>
       </c>
       <c r="R46" t="n">
-        <v>7017386</v>
+        <v>7017365</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6121,7 +6097,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Flertalet plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6139,6 +6115,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -6153,16 +6134,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499615</v>
+        <v>135499620</v>
       </c>
       <c r="B47" t="n">
-        <v>99191</v>
+        <v>108294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6170,28 +6151,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>220083</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6202,10 +6183,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490860</v>
+        <v>490853</v>
       </c>
       <c r="R47" t="n">
-        <v>7017386</v>
+        <v>7017483</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6240,11 +6221,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6274,16 +6250,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499509</v>
+        <v>135499621</v>
       </c>
       <c r="B48" t="n">
-        <v>99298</v>
+        <v>108294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6291,28 +6267,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6323,10 +6299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490880</v>
+        <v>490837</v>
       </c>
       <c r="R48" t="n">
-        <v>7017365</v>
+        <v>7017379</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6361,11 +6337,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flertalet plantor.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6381,11 +6352,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
@@ -6400,16 +6366,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499620</v>
+        <v>135499623</v>
       </c>
       <c r="B49" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6438,7 +6404,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6449,10 +6415,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490853</v>
+        <v>490848</v>
       </c>
       <c r="R49" t="n">
-        <v>7017483</v>
+        <v>7017376</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6516,16 +6482,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499621</v>
+        <v>135499624</v>
       </c>
       <c r="B50" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6565,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490837</v>
+        <v>490861</v>
       </c>
       <c r="R50" t="n">
-        <v>7017379</v>
+        <v>7017386</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6632,16 +6598,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499623</v>
+        <v>135499625</v>
       </c>
       <c r="B51" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6670,7 +6636,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6681,10 +6647,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490848</v>
+        <v>490821</v>
       </c>
       <c r="R51" t="n">
-        <v>7017376</v>
+        <v>7017394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6748,16 +6714,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499624</v>
+        <v>135499626</v>
       </c>
       <c r="B52" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6786,7 +6752,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6797,10 +6763,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490861</v>
+        <v>490841</v>
       </c>
       <c r="R52" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6864,16 +6830,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499625</v>
+        <v>135499550</v>
       </c>
       <c r="B53" t="n">
-        <v>108292</v>
+        <v>108364</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6881,28 +6847,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6913,10 +6879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490821</v>
+        <v>490929</v>
       </c>
       <c r="R53" t="n">
-        <v>7017394</v>
+        <v>7017429</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6980,16 +6946,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499626</v>
+        <v>135499551</v>
       </c>
       <c r="B54" t="n">
-        <v>108292</v>
+        <v>108364</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6997,28 +6963,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -7029,10 +6995,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R54" t="n">
-        <v>7017433</v>
+        <v>7017480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7067,6 +7033,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7096,16 +7067,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499550</v>
+        <v>135499552</v>
       </c>
       <c r="B55" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7145,10 +7116,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490929</v>
+        <v>490867</v>
       </c>
       <c r="R55" t="n">
-        <v>7017429</v>
+        <v>7017480</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7212,16 +7183,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499551</v>
+        <v>135499553</v>
       </c>
       <c r="B56" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7261,10 +7232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490853</v>
+        <v>490841</v>
       </c>
       <c r="R56" t="n">
-        <v>7017480</v>
+        <v>7017457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7299,11 +7270,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7333,16 +7299,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499552</v>
+        <v>135499554</v>
       </c>
       <c r="B57" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7382,10 +7348,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490867</v>
+        <v>490737</v>
       </c>
       <c r="R57" t="n">
-        <v>7017480</v>
+        <v>7017474</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7449,16 +7415,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499553</v>
+        <v>135499555</v>
       </c>
       <c r="B58" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7498,10 +7464,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490841</v>
+        <v>490873</v>
       </c>
       <c r="R58" t="n">
-        <v>7017457</v>
+        <v>7017368</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7565,16 +7531,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499554</v>
+        <v>135499556</v>
       </c>
       <c r="B59" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7614,10 +7580,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490737</v>
+        <v>490863</v>
       </c>
       <c r="R59" t="n">
-        <v>7017474</v>
+        <v>7017386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7667,6 +7633,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7681,16 +7652,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499555</v>
+        <v>135499544</v>
       </c>
       <c r="B60" t="n">
-        <v>108362</v>
+        <v>111244</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7698,28 +7669,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7730,10 +7701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490873</v>
+        <v>490844</v>
       </c>
       <c r="R60" t="n">
-        <v>7017368</v>
+        <v>7017468</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7797,16 +7768,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499556</v>
+        <v>135499546</v>
       </c>
       <c r="B61" t="n">
-        <v>108362</v>
+        <v>111244</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7814,28 +7785,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7846,10 +7817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490863</v>
+        <v>490780</v>
       </c>
       <c r="R61" t="n">
-        <v>7017386</v>
+        <v>7017405</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7899,11 +7870,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -7918,16 +7884,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499544</v>
+        <v>135499547</v>
       </c>
       <c r="B62" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7956,7 +7922,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7967,10 +7933,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490844</v>
+        <v>490858</v>
       </c>
       <c r="R62" t="n">
-        <v>7017468</v>
+        <v>7017416</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8034,16 +8000,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499546</v>
+        <v>135499548</v>
       </c>
       <c r="B63" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8072,7 +8038,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -8083,10 +8049,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490780</v>
+        <v>490964</v>
       </c>
       <c r="R63" t="n">
-        <v>7017405</v>
+        <v>7017356</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8136,6 +8102,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8150,16 +8121,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499547</v>
+        <v>135499617</v>
       </c>
       <c r="B64" t="n">
-        <v>111242</v>
+        <v>110240</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8167,28 +8138,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220240</v>
+        <v>220294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -8199,10 +8170,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490858</v>
+        <v>490864</v>
       </c>
       <c r="R64" t="n">
-        <v>7017416</v>
+        <v>7017486</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8237,6 +8208,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8266,45 +8242,53 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499548</v>
+        <v>135499580</v>
       </c>
       <c r="B65" t="n">
-        <v>111242</v>
+        <v>99276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -8315,10 +8299,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490964</v>
+        <v>490975</v>
       </c>
       <c r="R65" t="n">
-        <v>7017356</v>
+        <v>7017304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8353,6 +8337,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8387,45 +8376,53 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499617</v>
+        <v>135499583</v>
       </c>
       <c r="B66" t="n">
-        <v>110238</v>
+        <v>99276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220294</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -8436,10 +8433,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490864</v>
+        <v>490768</v>
       </c>
       <c r="R66" t="n">
-        <v>7017486</v>
+        <v>7017376</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8476,7 +8473,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8494,6 +8491,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
@@ -8508,16 +8510,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499580</v>
+        <v>135499584</v>
       </c>
       <c r="B67" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8544,7 +8546,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8565,10 +8567,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490975</v>
+        <v>490839</v>
       </c>
       <c r="R67" t="n">
-        <v>7017304</v>
+        <v>7017351</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8605,7 +8607,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8620,12 +8622,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8642,16 +8639,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499581</v>
+        <v>135499585</v>
       </c>
       <c r="B68" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8678,7 +8675,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8699,10 +8696,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490951</v>
+        <v>490845</v>
       </c>
       <c r="R68" t="n">
-        <v>7017428</v>
+        <v>7017392</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8739,7 +8736,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8754,7 +8751,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8771,16 +8768,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499581</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499582</v>
+        <v>135499586</v>
       </c>
       <c r="B69" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8828,10 +8825,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490884</v>
+        <v>490812</v>
       </c>
       <c r="R69" t="n">
-        <v>7017471</v>
+        <v>7017401</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8868,7 +8865,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8883,7 +8880,12 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8900,16 +8902,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499582</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499583</v>
+        <v>135499588</v>
       </c>
       <c r="B70" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8936,7 +8938,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8957,10 +8959,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490768</v>
+        <v>490843</v>
       </c>
       <c r="R70" t="n">
-        <v>7017376</v>
+        <v>7017436</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8997,7 +8999,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9034,16 +9036,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499584</v>
+        <v>135499589</v>
       </c>
       <c r="B71" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9070,7 +9072,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9091,10 +9093,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490839</v>
+        <v>490967</v>
       </c>
       <c r="R71" t="n">
-        <v>7017351</v>
+        <v>7017335</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9131,7 +9133,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9146,7 +9148,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9163,16 +9170,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499585</v>
+        <v>135499590</v>
       </c>
       <c r="B72" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9199,7 +9206,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9220,10 +9227,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490845</v>
+        <v>490979</v>
       </c>
       <c r="R72" t="n">
-        <v>7017392</v>
+        <v>7017360</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9260,7 +9267,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9275,7 +9282,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9292,16 +9304,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499586</v>
+        <v>135499591</v>
       </c>
       <c r="B73" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9328,7 +9340,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9349,10 +9361,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490812</v>
+        <v>490973</v>
       </c>
       <c r="R73" t="n">
-        <v>7017401</v>
+        <v>7017399</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9389,7 +9401,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9426,16 +9438,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499588</v>
+        <v>135499592</v>
       </c>
       <c r="B74" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9462,7 +9474,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9483,10 +9495,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490843</v>
+        <v>490951</v>
       </c>
       <c r="R74" t="n">
-        <v>7017436</v>
+        <v>7017408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9523,7 +9535,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9560,16 +9572,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499589</v>
+        <v>135499593</v>
       </c>
       <c r="B75" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9596,7 +9608,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9617,10 +9629,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490967</v>
+        <v>490951</v>
       </c>
       <c r="R75" t="n">
-        <v>7017335</v>
+        <v>7017396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9657,7 +9669,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9694,16 +9706,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499590</v>
+        <v>135499594</v>
       </c>
       <c r="B76" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9730,7 +9742,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9751,10 +9763,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490979</v>
+        <v>490957</v>
       </c>
       <c r="R76" t="n">
-        <v>7017360</v>
+        <v>7017386</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9791,7 +9803,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9828,55 +9840,43 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499591</v>
+        <v>135499519</v>
       </c>
       <c r="B77" t="n">
-        <v>99274</v>
+        <v>98138</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490973</v>
+        <v>490752</v>
       </c>
       <c r="R77" t="n">
-        <v>7017399</v>
+        <v>7017499</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9943,11 +9943,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
@@ -9962,53 +9957,45 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499592</v>
+        <v>135499516</v>
       </c>
       <c r="B78" t="n">
-        <v>99274</v>
+        <v>99298</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -10019,10 +10006,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490951</v>
+        <v>490844</v>
       </c>
       <c r="R78" t="n">
-        <v>7017408</v>
+        <v>7017394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10057,11 +10044,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10077,11 +10059,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
@@ -10096,53 +10073,45 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499593</v>
+        <v>135499517</v>
       </c>
       <c r="B79" t="n">
-        <v>99274</v>
+        <v>99298</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -10153,10 +10122,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490951</v>
+        <v>490814</v>
       </c>
       <c r="R79" t="n">
-        <v>7017396</v>
+        <v>7017404</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10191,11 +10160,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10211,11 +10175,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
@@ -10230,53 +10189,45 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499594</v>
+        <v>135499627</v>
       </c>
       <c r="B80" t="n">
-        <v>99274</v>
+        <v>101485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10287,10 +10238,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490957</v>
+        <v>490803</v>
       </c>
       <c r="R80" t="n">
-        <v>7017386</v>
+        <v>7017492</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10325,11 +10276,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10345,11 +10291,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
@@ -10364,16 +10305,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499519</v>
+        <v>135499628</v>
       </c>
       <c r="B81" t="n">
-        <v>98136</v>
+        <v>101485</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10381,26 +10322,30 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10409,10 +10354,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490752</v>
+        <v>490792</v>
       </c>
       <c r="R81" t="n">
-        <v>7017499</v>
+        <v>7017441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10447,11 +10392,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10481,16 +10421,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499516</v>
+        <v>135499629</v>
       </c>
       <c r="B82" t="n">
-        <v>99296</v>
+        <v>101485</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10498,28 +10438,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10530,10 +10470,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490844</v>
+        <v>490764</v>
       </c>
       <c r="R82" t="n">
-        <v>7017394</v>
+        <v>7017441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10597,16 +10537,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499517</v>
+        <v>135499630</v>
       </c>
       <c r="B83" t="n">
-        <v>99296</v>
+        <v>101485</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10614,28 +10554,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -10646,10 +10586,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490814</v>
+        <v>490798</v>
       </c>
       <c r="R83" t="n">
-        <v>7017404</v>
+        <v>7017366</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10713,16 +10653,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499627</v>
+        <v>135499631</v>
       </c>
       <c r="B84" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10762,10 +10702,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490803</v>
+        <v>490816</v>
       </c>
       <c r="R84" t="n">
-        <v>7017492</v>
+        <v>7017378</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10829,16 +10769,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499628</v>
+        <v>135499632</v>
       </c>
       <c r="B85" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10878,10 +10818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490792</v>
+        <v>490796</v>
       </c>
       <c r="R85" t="n">
-        <v>7017441</v>
+        <v>7017382</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10945,16 +10885,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499629</v>
+        <v>135499633</v>
       </c>
       <c r="B86" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10994,10 +10934,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490764</v>
+        <v>490782</v>
       </c>
       <c r="R86" t="n">
-        <v>7017441</v>
+        <v>7017407</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11061,16 +11001,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499630</v>
+        <v>135499634</v>
       </c>
       <c r="B87" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11110,10 +11050,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490798</v>
+        <v>490730</v>
       </c>
       <c r="R87" t="n">
-        <v>7017366</v>
+        <v>7017371</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11177,16 +11117,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499631</v>
+        <v>135499635</v>
       </c>
       <c r="B88" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11226,10 +11166,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490816</v>
+        <v>490827</v>
       </c>
       <c r="R88" t="n">
-        <v>7017378</v>
+        <v>7017356</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11293,16 +11233,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499632</v>
+        <v>135499636</v>
       </c>
       <c r="B89" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11342,10 +11282,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490796</v>
+        <v>490844</v>
       </c>
       <c r="R89" t="n">
-        <v>7017382</v>
+        <v>7017345</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11409,16 +11349,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499633</v>
+        <v>135499637</v>
       </c>
       <c r="B90" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11458,10 +11398,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490782</v>
+        <v>490852</v>
       </c>
       <c r="R90" t="n">
-        <v>7017407</v>
+        <v>7017373</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11508,7 +11448,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11525,16 +11465,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499634</v>
+        <v>135499638</v>
       </c>
       <c r="B91" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11574,10 +11514,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490730</v>
+        <v>490882</v>
       </c>
       <c r="R91" t="n">
-        <v>7017371</v>
+        <v>7017368</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11624,7 +11564,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11641,16 +11581,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499635</v>
+        <v>135499639</v>
       </c>
       <c r="B92" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11690,10 +11630,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490827</v>
+        <v>490865</v>
       </c>
       <c r="R92" t="n">
-        <v>7017356</v>
+        <v>7017386</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11757,16 +11697,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499636</v>
+        <v>135499640</v>
       </c>
       <c r="B93" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11806,10 +11746,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490844</v>
+        <v>490840</v>
       </c>
       <c r="R93" t="n">
-        <v>7017345</v>
+        <v>7017433</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11873,16 +11813,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499637</v>
+        <v>135499641</v>
       </c>
       <c r="B94" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11922,10 +11862,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490852</v>
+        <v>490880</v>
       </c>
       <c r="R94" t="n">
-        <v>7017373</v>
+        <v>7017422</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11972,7 +11912,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11989,16 +11929,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499638</v>
+        <v>135499618</v>
       </c>
       <c r="B95" t="n">
-        <v>101483</v>
+        <v>98292</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12006,21 +11946,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12038,10 +11978,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490882</v>
+        <v>490791</v>
       </c>
       <c r="R95" t="n">
-        <v>7017368</v>
+        <v>7017443</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12076,6 +12016,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -12088,7 +12033,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12105,16 +12050,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499639</v>
+        <v>135499619</v>
       </c>
       <c r="B96" t="n">
-        <v>101483</v>
+        <v>98292</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12122,25 +12067,33 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12154,10 +12107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490865</v>
+        <v>490868</v>
       </c>
       <c r="R96" t="n">
-        <v>7017386</v>
+        <v>7017387</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12192,6 +12145,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12207,6 +12165,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
@@ -12221,16 +12184,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499640</v>
+        <v>135499520</v>
       </c>
       <c r="B97" t="n">
-        <v>101483</v>
+        <v>99082</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12238,21 +12201,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>223049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12270,10 +12233,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490840</v>
+        <v>490757</v>
       </c>
       <c r="R97" t="n">
-        <v>7017433</v>
+        <v>7017472</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12337,16 +12300,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499641</v>
+        <v>135499521</v>
       </c>
       <c r="B98" t="n">
-        <v>101483</v>
+        <v>99082</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12354,21 +12317,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>223049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12386,10 +12349,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490880</v>
+        <v>490966</v>
       </c>
       <c r="R98" t="n">
-        <v>7017422</v>
+        <v>7017430</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12453,16 +12416,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499618</v>
+        <v>135499522</v>
       </c>
       <c r="B99" t="n">
-        <v>98290</v>
+        <v>99082</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12470,21 +12433,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12502,10 +12465,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490791</v>
+        <v>490920</v>
       </c>
       <c r="R99" t="n">
-        <v>7017443</v>
+        <v>7017445</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12540,11 +12503,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -12574,16 +12532,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499619</v>
+        <v>135499523</v>
       </c>
       <c r="B100" t="n">
-        <v>98290</v>
+        <v>99082</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12591,33 +12549,25 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12631,10 +12581,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490868</v>
+        <v>490912</v>
       </c>
       <c r="R100" t="n">
-        <v>7017387</v>
+        <v>7017466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12669,11 +12619,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12689,11 +12634,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
@@ -12708,16 +12648,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499520</v>
+        <v>135499524</v>
       </c>
       <c r="B101" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12757,10 +12697,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490757</v>
+        <v>490858</v>
       </c>
       <c r="R101" t="n">
-        <v>7017472</v>
+        <v>7017493</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12824,16 +12764,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499521</v>
+        <v>135499525</v>
       </c>
       <c r="B102" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12862,7 +12802,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12873,10 +12813,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490966</v>
+        <v>490804</v>
       </c>
       <c r="R102" t="n">
-        <v>7017430</v>
+        <v>7017492</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12940,16 +12880,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499522</v>
+        <v>135499526</v>
       </c>
       <c r="B103" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12989,10 +12929,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490920</v>
+        <v>490740</v>
       </c>
       <c r="R103" t="n">
-        <v>7017445</v>
+        <v>7017423</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13056,16 +12996,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499523</v>
+        <v>135499527</v>
       </c>
       <c r="B104" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13105,10 +13045,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490912</v>
+        <v>490732</v>
       </c>
       <c r="R104" t="n">
-        <v>7017466</v>
+        <v>7017370</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13172,16 +13112,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499524</v>
+        <v>135499528</v>
       </c>
       <c r="B105" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13221,10 +13161,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490858</v>
+        <v>490867</v>
       </c>
       <c r="R105" t="n">
-        <v>7017493</v>
+        <v>7017386</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13259,6 +13199,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -13288,16 +13233,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499525</v>
+        <v>135499529</v>
       </c>
       <c r="B106" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13326,7 +13271,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -13337,10 +13282,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490804</v>
+        <v>490807</v>
       </c>
       <c r="R106" t="n">
-        <v>7017492</v>
+        <v>7017431</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13404,16 +13349,16 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499526</v>
+        <v>135499530</v>
       </c>
       <c r="B107" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13442,7 +13387,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13453,10 +13398,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490740</v>
+        <v>490932</v>
       </c>
       <c r="R107" t="n">
-        <v>7017423</v>
+        <v>7017369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13520,16 +13465,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499527</v>
+        <v>135499597</v>
       </c>
       <c r="B108" t="n">
-        <v>99080</v>
+        <v>98327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13537,21 +13482,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13569,10 +13514,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490732</v>
+        <v>490969</v>
       </c>
       <c r="R108" t="n">
-        <v>7017370</v>
+        <v>7017431</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13636,16 +13581,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499528</v>
+        <v>135499598</v>
       </c>
       <c r="B109" t="n">
-        <v>99080</v>
+        <v>98327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13653,21 +13598,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13685,10 +13630,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490867</v>
+        <v>490840</v>
       </c>
       <c r="R109" t="n">
-        <v>7017386</v>
+        <v>7017457</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13723,11 +13668,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13757,16 +13697,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499529</v>
+        <v>135499599</v>
       </c>
       <c r="B110" t="n">
-        <v>99080</v>
+        <v>98327</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13774,21 +13714,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13806,10 +13746,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490807</v>
+        <v>490831</v>
       </c>
       <c r="R110" t="n">
-        <v>7017431</v>
+        <v>7017486</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13873,16 +13813,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499530</v>
+        <v>135499600</v>
       </c>
       <c r="B111" t="n">
-        <v>99080</v>
+        <v>98327</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13890,28 +13830,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13922,10 +13862,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490932</v>
+        <v>490797</v>
       </c>
       <c r="R111" t="n">
-        <v>7017369</v>
+        <v>7017497</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13989,16 +13929,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499597</v>
+        <v>135499601</v>
       </c>
       <c r="B112" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14038,10 +13978,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490969</v>
+        <v>490797</v>
       </c>
       <c r="R112" t="n">
-        <v>7017431</v>
+        <v>7017511</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14105,16 +14045,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499598</v>
+        <v>135499602</v>
       </c>
       <c r="B113" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14154,10 +14094,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490840</v>
+        <v>490737</v>
       </c>
       <c r="R113" t="n">
-        <v>7017457</v>
+        <v>7017473</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14221,16 +14161,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499599</v>
+        <v>135499515</v>
       </c>
       <c r="B114" t="n">
-        <v>98325</v>
+        <v>102022</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14238,21 +14178,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223358</v>
+        <v>223366</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14270,10 +14210,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490831</v>
+        <v>490788</v>
       </c>
       <c r="R114" t="n">
-        <v>7017486</v>
+        <v>7017450</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14337,16 +14277,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499600</v>
+        <v>135499532</v>
       </c>
       <c r="B115" t="n">
-        <v>98325</v>
+        <v>101375</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14354,21 +14294,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14386,10 +14326,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490797</v>
+        <v>490889</v>
       </c>
       <c r="R115" t="n">
-        <v>7017497</v>
+        <v>7017459</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14453,16 +14393,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499601</v>
+        <v>135499533</v>
       </c>
       <c r="B116" t="n">
-        <v>98325</v>
+        <v>101375</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14470,21 +14410,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14502,10 +14442,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490797</v>
+        <v>490743</v>
       </c>
       <c r="R116" t="n">
-        <v>7017511</v>
+        <v>7017495</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14569,16 +14509,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499602</v>
+        <v>135499534</v>
       </c>
       <c r="B117" t="n">
-        <v>98325</v>
+        <v>101375</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14586,21 +14526,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14621,7 +14561,7 @@
         <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017473</v>
+        <v>7017474</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14685,16 +14625,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499515</v>
+        <v>135499535</v>
       </c>
       <c r="B118" t="n">
-        <v>102020</v>
+        <v>101375</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14702,21 +14642,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>223366</v>
+        <v>224885</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14734,10 +14674,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490788</v>
+        <v>490734</v>
       </c>
       <c r="R118" t="n">
-        <v>7017450</v>
+        <v>7017429</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14801,16 +14741,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499532</v>
+        <v>135499536</v>
       </c>
       <c r="B119" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14850,10 +14790,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490889</v>
+        <v>490780</v>
       </c>
       <c r="R119" t="n">
-        <v>7017459</v>
+        <v>7017405</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14917,16 +14857,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499533</v>
+        <v>135499537</v>
       </c>
       <c r="B120" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14966,10 +14906,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490743</v>
+        <v>490751</v>
       </c>
       <c r="R120" t="n">
-        <v>7017495</v>
+        <v>7017406</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15033,16 +14973,16 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499537</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499534</v>
+        <v>135499538</v>
       </c>
       <c r="B121" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15082,10 +15022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490737</v>
+        <v>490729</v>
       </c>
       <c r="R121" t="n">
-        <v>7017474</v>
+        <v>7017373</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15149,16 +15089,16 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499538</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499535</v>
+        <v>135499540</v>
       </c>
       <c r="B122" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15198,10 +15138,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490734</v>
+        <v>490847</v>
       </c>
       <c r="R122" t="n">
-        <v>7017429</v>
+        <v>7017345</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15265,16 +15205,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499540</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499536</v>
+        <v>135499541</v>
       </c>
       <c r="B123" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15314,10 +15254,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490780</v>
+        <v>490856</v>
       </c>
       <c r="R123" t="n">
-        <v>7017405</v>
+        <v>7017358</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15381,16 +15321,16 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499541</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499537</v>
+        <v>135499542</v>
       </c>
       <c r="B124" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15419,7 +15359,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -15430,10 +15370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490751</v>
+        <v>490840</v>
       </c>
       <c r="R124" t="n">
-        <v>7017406</v>
+        <v>7017433</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15496,470 +15436,6 @@
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>135499538</v>
-      </c>
-      <c r="B125" t="n">
-        <v>101373</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q125" t="n">
-        <v>490729</v>
-      </c>
-      <c r="R125" t="n">
-        <v>7017373</v>
-      </c>
-      <c r="S125" t="n">
-        <v>10</v>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="inlineStr"/>
-      <c r="AG125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT125" t="inlineStr"/>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>135499540</v>
-      </c>
-      <c r="B126" t="n">
-        <v>101373</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q126" t="n">
-        <v>490847</v>
-      </c>
-      <c r="R126" t="n">
-        <v>7017345</v>
-      </c>
-      <c r="S126" t="n">
-        <v>10</v>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="inlineStr"/>
-      <c r="AG126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT126" t="inlineStr"/>
-      <c r="AW126" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>135499541</v>
-      </c>
-      <c r="B127" t="n">
-        <v>101373</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q127" t="n">
-        <v>490856</v>
-      </c>
-      <c r="R127" t="n">
-        <v>7017358</v>
-      </c>
-      <c r="S127" t="n">
-        <v>10</v>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="inlineStr"/>
-      <c r="AG127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT127" t="inlineStr"/>
-      <c r="AW127" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>135499542</v>
-      </c>
-      <c r="B128" t="n">
-        <v>101373</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q128" t="n">
-        <v>490840</v>
-      </c>
-      <c r="R128" t="n">
-        <v>7017433</v>
-      </c>
-      <c r="S128" t="n">
-        <v>10</v>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="inlineStr"/>
-      <c r="AG128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT128" t="inlineStr"/>
-      <c r="AW128" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
-      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -16090,10 +15566,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ124"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499608</v>
+        <v>135499607</v>
       </c>
       <c r="B2" t="n">
         <v>99182</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490867</v>
+        <v>490869</v>
       </c>
       <c r="R2" t="n">
-        <v>7017387</v>
+        <v>7017370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
+          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad snitslad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +790,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+          <t>Kalkrikt fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,58 +812,71 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499608</t>
+          <t>https://artportalen.se/Sighting/135499607</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499603</v>
+        <v>135499608</v>
       </c>
       <c r="B3" t="n">
-        <v>92046</v>
+        <v>99182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490968</v>
+        <v>490867</v>
       </c>
       <c r="R3" t="n">
-        <v>7017430</v>
+        <v>7017387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +913,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,24 +931,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -952,13 +950,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499603</t>
+          <t>https://artportalen.se/Sighting/135499608</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499604</v>
+        <v>135499603</v>
       </c>
       <c r="B4" t="n">
         <v>92046</v>
@@ -1000,10 +998,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490893</v>
+        <v>490968</v>
       </c>
       <c r="R4" t="n">
-        <v>7017459</v>
+        <v>7017430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,7 +1038,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,12 +1068,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,13 +1090,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499604</t>
+          <t>https://artportalen.se/Sighting/135499603</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499605</v>
+        <v>135499604</v>
       </c>
       <c r="B5" t="n">
         <v>92046</v>
@@ -1140,10 +1138,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490741</v>
+        <v>490893</v>
       </c>
       <c r="R5" t="n">
-        <v>7017465</v>
+        <v>7017459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,7 +1178,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1232,13 +1230,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499605</t>
+          <t>https://artportalen.se/Sighting/135499604</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499606</v>
+        <v>135499605</v>
       </c>
       <c r="B6" t="n">
         <v>92046</v>
@@ -1280,10 +1278,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490951</v>
+        <v>490741</v>
       </c>
       <c r="R6" t="n">
-        <v>7017411</v>
+        <v>7017465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1320,7 +1318,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,12 +1348,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1372,16 +1370,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499606</t>
+          <t>https://artportalen.se/Sighting/135499605</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75185503</v>
+        <v>135499606</v>
       </c>
       <c r="B7" t="n">
-        <v>87322</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,34 +1387,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1988</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490758</v>
+        <v>490951</v>
       </c>
       <c r="R7" t="n">
-        <v>7017384</v>
+        <v>7017411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1443,12 +1448,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,73 +1471,90 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185503</t>
+          <t>https://artportalen.se/Sighting/135499606</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135499557</v>
+        <v>75185503</v>
       </c>
       <c r="B8" t="n">
-        <v>96488</v>
+        <v>87322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2812</v>
+        <v>1988</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490738</v>
+        <v>490758</v>
       </c>
       <c r="R8" t="n">
-        <v>7017396</v>
+        <v>7017384</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,12 +1581,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,32 +1599,31 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499557</t>
+          <t>https://artportalen.se/Sighting/75185503</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499558</v>
+        <v>135499557</v>
       </c>
       <c r="B9" t="n">
         <v>96488</v>
@@ -1636,10 +1662,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490991</v>
+        <v>490738</v>
       </c>
       <c r="R9" t="n">
-        <v>7017297</v>
+        <v>7017396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1703,13 +1729,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499558</t>
+          <t>https://artportalen.se/Sighting/135499557</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499560</v>
+        <v>135499558</v>
       </c>
       <c r="B10" t="n">
         <v>96488</v>
@@ -1748,10 +1774,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490966</v>
+        <v>490991</v>
       </c>
       <c r="R10" t="n">
-        <v>7017426</v>
+        <v>7017297</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1801,11 +1827,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1820,13 +1841,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499560</t>
+          <t>https://artportalen.se/Sighting/135499558</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499561</v>
+        <v>135499560</v>
       </c>
       <c r="B11" t="n">
         <v>96488</v>
@@ -1865,10 +1886,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490929</v>
+        <v>490966</v>
       </c>
       <c r="R11" t="n">
-        <v>7017441</v>
+        <v>7017426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1915,7 +1936,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1932,13 +1958,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499561</t>
+          <t>https://artportalen.se/Sighting/135499560</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499562</v>
+        <v>135499561</v>
       </c>
       <c r="B12" t="n">
         <v>96488</v>
@@ -1977,10 +2003,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490910</v>
+        <v>490929</v>
       </c>
       <c r="R12" t="n">
-        <v>7017467</v>
+        <v>7017441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2044,13 +2070,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499562</t>
+          <t>https://artportalen.se/Sighting/135499561</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499563</v>
+        <v>135499562</v>
       </c>
       <c r="B13" t="n">
         <v>96488</v>
@@ -2089,10 +2115,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490878</v>
+        <v>490910</v>
       </c>
       <c r="R13" t="n">
-        <v>7017474</v>
+        <v>7017467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2139,7 +2165,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2156,13 +2182,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499563</t>
+          <t>https://artportalen.se/Sighting/135499562</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499564</v>
+        <v>135499563</v>
       </c>
       <c r="B14" t="n">
         <v>96488</v>
@@ -2201,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490883</v>
+        <v>490878</v>
       </c>
       <c r="R14" t="n">
-        <v>7017462</v>
+        <v>7017474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2251,7 +2277,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2268,13 +2294,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499564</t>
+          <t>https://artportalen.se/Sighting/135499563</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499565</v>
+        <v>135499564</v>
       </c>
       <c r="B15" t="n">
         <v>96488</v>
@@ -2313,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490756</v>
+        <v>490883</v>
       </c>
       <c r="R15" t="n">
-        <v>7017472</v>
+        <v>7017462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2363,7 +2389,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2380,13 +2406,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499565</t>
+          <t>https://artportalen.se/Sighting/135499564</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499566</v>
+        <v>135499565</v>
       </c>
       <c r="B16" t="n">
         <v>96488</v>
@@ -2425,10 +2451,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490790</v>
+        <v>490756</v>
       </c>
       <c r="R16" t="n">
-        <v>7017441</v>
+        <v>7017472</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2492,13 +2518,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499566</t>
+          <t>https://artportalen.se/Sighting/135499565</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499567</v>
+        <v>135499566</v>
       </c>
       <c r="B17" t="n">
         <v>96488</v>
@@ -2537,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490732</v>
+        <v>490790</v>
       </c>
       <c r="R17" t="n">
-        <v>7017442</v>
+        <v>7017441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2587,7 +2613,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2604,13 +2630,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499567</t>
+          <t>https://artportalen.se/Sighting/135499566</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499568</v>
+        <v>135499567</v>
       </c>
       <c r="B18" t="n">
         <v>96488</v>
@@ -2649,10 +2675,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490781</v>
+        <v>490732</v>
       </c>
       <c r="R18" t="n">
-        <v>7017407</v>
+        <v>7017442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2699,7 +2725,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,13 +2742,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499568</t>
+          <t>https://artportalen.se/Sighting/135499567</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499569</v>
+        <v>135499568</v>
       </c>
       <c r="B19" t="n">
         <v>96488</v>
@@ -2761,10 +2787,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490731</v>
+        <v>490781</v>
       </c>
       <c r="R19" t="n">
-        <v>7017371</v>
+        <v>7017407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,11 +2840,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2833,13 +2854,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499569</t>
+          <t>https://artportalen.se/Sighting/135499568</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499570</v>
+        <v>135499569</v>
       </c>
       <c r="B20" t="n">
         <v>96488</v>
@@ -2878,10 +2899,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490854</v>
+        <v>490731</v>
       </c>
       <c r="R20" t="n">
-        <v>7017345</v>
+        <v>7017371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,6 +2952,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2945,13 +2971,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499570</t>
+          <t>https://artportalen.se/Sighting/135499569</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499571</v>
+        <v>135499570</v>
       </c>
       <c r="B21" t="n">
         <v>96488</v>
@@ -2990,10 +3016,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490878</v>
+        <v>490854</v>
       </c>
       <c r="R21" t="n">
-        <v>7017366</v>
+        <v>7017345</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3028,11 +3054,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3062,13 +3083,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499571</t>
+          <t>https://artportalen.se/Sighting/135499570</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499572</v>
+        <v>135499571</v>
       </c>
       <c r="B22" t="n">
         <v>96488</v>
@@ -3107,10 +3128,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490867</v>
+        <v>490878</v>
       </c>
       <c r="R22" t="n">
-        <v>7017386</v>
+        <v>7017366</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,6 +3166,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3174,13 +3200,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499572</t>
+          <t>https://artportalen.se/Sighting/135499571</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499573</v>
+        <v>135499572</v>
       </c>
       <c r="B23" t="n">
         <v>96488</v>
@@ -3219,10 +3245,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490840</v>
+        <v>490867</v>
       </c>
       <c r="R23" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3286,13 +3312,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499573</t>
+          <t>https://artportalen.se/Sighting/135499572</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499574</v>
+        <v>135499573</v>
       </c>
       <c r="B24" t="n">
         <v>96488</v>
@@ -3331,10 +3357,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490844</v>
+        <v>490840</v>
       </c>
       <c r="R24" t="n">
-        <v>7017436</v>
+        <v>7017433</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3398,13 +3424,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499574</t>
+          <t>https://artportalen.se/Sighting/135499573</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499575</v>
+        <v>135499574</v>
       </c>
       <c r="B25" t="n">
         <v>96488</v>
@@ -3443,10 +3469,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490872</v>
+        <v>490844</v>
       </c>
       <c r="R25" t="n">
-        <v>7017426</v>
+        <v>7017436</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3510,13 +3536,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499575</t>
+          <t>https://artportalen.se/Sighting/135499574</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499576</v>
+        <v>135499575</v>
       </c>
       <c r="B26" t="n">
         <v>96488</v>
@@ -3555,10 +3581,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490917</v>
+        <v>490872</v>
       </c>
       <c r="R26" t="n">
-        <v>7017402</v>
+        <v>7017426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3622,13 +3648,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499576</t>
+          <t>https://artportalen.se/Sighting/135499575</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499577</v>
+        <v>135499576</v>
       </c>
       <c r="B27" t="n">
         <v>96488</v>
@@ -3667,10 +3693,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490931</v>
+        <v>490917</v>
       </c>
       <c r="R27" t="n">
-        <v>7017371</v>
+        <v>7017402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3720,11 +3746,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3739,13 +3760,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499577</t>
+          <t>https://artportalen.se/Sighting/135499576</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499578</v>
+        <v>135499577</v>
       </c>
       <c r="B28" t="n">
         <v>96488</v>
@@ -3784,10 +3805,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490951</v>
+        <v>490931</v>
       </c>
       <c r="R28" t="n">
-        <v>7017390</v>
+        <v>7017371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3856,13 +3877,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499578</t>
+          <t>https://artportalen.se/Sighting/135499577</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499579</v>
+        <v>135499578</v>
       </c>
       <c r="B29" t="n">
         <v>96488</v>
@@ -3901,10 +3922,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490976</v>
+        <v>490951</v>
       </c>
       <c r="R29" t="n">
-        <v>7017311</v>
+        <v>7017390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3973,16 +3994,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499579</t>
+          <t>https://artportalen.se/Sighting/135499578</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>91488964</v>
+        <v>135499579</v>
       </c>
       <c r="B30" t="n">
-        <v>92632</v>
+        <v>96488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3990,37 +4011,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>2812</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490939</v>
+        <v>490976</v>
       </c>
       <c r="R30" t="n">
-        <v>7017412</v>
+        <v>7017311</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4044,12 +4069,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4058,59 +4083,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91488964</t>
+          <t>https://artportalen.se/Sighting/135499579</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>75185505</v>
+        <v>91488964</v>
       </c>
       <c r="B31" t="n">
-        <v>89156</v>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4412</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4120,13 +4152,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490781</v>
+        <v>490939</v>
       </c>
       <c r="R31" t="n">
-        <v>7017384</v>
+        <v>7017412</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4164,19 +4196,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4186,54 +4217,51 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185505</t>
+          <t>https://artportalen.se/Sighting/91488964</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135499609</v>
+        <v>75185505</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>89156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490849</v>
+        <v>490781</v>
       </c>
       <c r="R32" t="n">
-        <v>7017392</v>
+        <v>7017384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4260,17 +4288,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4283,52 +4306,31 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499609</t>
+          <t>https://artportalen.se/Sighting/75185505</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499610</v>
+        <v>135499609</v>
       </c>
       <c r="B33" t="n">
         <v>79441</v>
@@ -4366,10 +4368,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490859</v>
+        <v>490849</v>
       </c>
       <c r="R33" t="n">
-        <v>7017416</v>
+        <v>7017392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4404,6 +4406,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4431,12 +4438,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4453,67 +4460,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499610</t>
+          <t>https://artportalen.se/Sighting/135499609</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499531</v>
+        <v>135499610</v>
       </c>
       <c r="B34" t="n">
-        <v>58094</v>
+        <v>79441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100090</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490781</v>
+        <v>490859</v>
       </c>
       <c r="R34" t="n">
-        <v>7017369</v>
+        <v>7017416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4548,23 +4542,39 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Synobservation av en individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4581,16 +4591,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499531</t>
+          <t>https://artportalen.se/Sighting/135499610</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499510</v>
+        <v>135499531</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>58094</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4598,16 +4608,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100090</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4615,12 +4625,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4634,10 +4648,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490891</v>
+        <v>490781</v>
       </c>
       <c r="R35" t="n">
-        <v>7017451</v>
+        <v>7017369</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4674,7 +4688,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Synobservation av en individ med lockläte.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4688,27 +4702,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4725,13 +4719,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499510</t>
+          <t>https://artportalen.se/Sighting/135499531</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499511</v>
+        <v>135499510</v>
       </c>
       <c r="B36" t="n">
         <v>57980</v>
@@ -4764,7 +4758,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4778,10 +4772,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490785</v>
+        <v>490891</v>
       </c>
       <c r="R36" t="n">
-        <v>7017521</v>
+        <v>7017451</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4818,7 +4812,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4832,7 +4826,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -4869,13 +4863,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499511</t>
+          <t>https://artportalen.se/Sighting/135499510</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499512</v>
+        <v>135499511</v>
       </c>
       <c r="B37" t="n">
         <v>57980</v>
@@ -4922,10 +4916,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490783</v>
+        <v>490785</v>
       </c>
       <c r="R37" t="n">
-        <v>7017360</v>
+        <v>7017521</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4962,7 +4956,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4977,11 +4971,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5018,33 +5007,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499512</t>
+          <t>https://artportalen.se/Sighting/135499511</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499596</v>
+        <v>135499512</v>
       </c>
       <c r="B38" t="n">
-        <v>58239</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102981</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5052,29 +5041,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490875</v>
+        <v>490783</v>
       </c>
       <c r="R38" t="n">
-        <v>7017470</v>
+        <v>7017360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5111,7 +5100,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5126,6 +5115,31 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5142,16 +5156,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499512</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499513</v>
+        <v>135499549</v>
       </c>
       <c r="B39" t="n">
-        <v>58141</v>
+        <v>58236</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5159,21 +5173,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>102980</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5185,7 +5199,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5199,10 +5213,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490763</v>
+        <v>490804</v>
       </c>
       <c r="R39" t="n">
-        <v>7017499</v>
+        <v>7017502</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5239,7 +5253,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Minst 1 överflygande med sång.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5253,12 +5267,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5275,43 +5284,43 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499549</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499514</v>
+        <v>135499596</v>
       </c>
       <c r="B40" t="n">
-        <v>58141</v>
+        <v>58239</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>102981</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5321,11 +5330,7 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
@@ -5335,7 +5340,7 @@
         <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017397</v>
+        <v>7017470</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5372,7 +5377,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5387,11 +5392,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5408,59 +5408,67 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499611</v>
+        <v>135499513</v>
       </c>
       <c r="B41" t="n">
-        <v>99193</v>
+        <v>58141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490821</v>
+        <v>490763</v>
       </c>
       <c r="R41" t="n">
-        <v>7017504</v>
+        <v>7017499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5497,7 +5505,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5506,13 +5514,17 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5529,59 +5541,67 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499612</v>
+        <v>135499514</v>
       </c>
       <c r="B42" t="n">
-        <v>99193</v>
+        <v>58141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490848</v>
+        <v>490875</v>
       </c>
       <c r="R42" t="n">
-        <v>7017375</v>
+        <v>7017397</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5616,19 +5636,28 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5645,13 +5674,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499613</v>
+        <v>135499611</v>
       </c>
       <c r="B43" t="n">
         <v>99193</v>
@@ -5694,10 +5723,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490878</v>
+        <v>490821</v>
       </c>
       <c r="R43" t="n">
-        <v>7017368</v>
+        <v>7017504</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5734,7 +5763,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5766,13 +5795,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499614</v>
+        <v>135499612</v>
       </c>
       <c r="B44" t="n">
         <v>99193</v>
@@ -5815,10 +5844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490867</v>
+        <v>490848</v>
       </c>
       <c r="R44" t="n">
-        <v>7017386</v>
+        <v>7017375</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5853,11 +5882,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5887,13 +5911,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499615</v>
+        <v>135499613</v>
       </c>
       <c r="B45" t="n">
         <v>99193</v>
@@ -5936,10 +5960,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490860</v>
+        <v>490878</v>
       </c>
       <c r="R45" t="n">
-        <v>7017386</v>
+        <v>7017368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6008,16 +6032,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499509</v>
+        <v>135499614</v>
       </c>
       <c r="B46" t="n">
-        <v>99300</v>
+        <v>99193</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6025,28 +6049,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6057,10 +6081,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490880</v>
+        <v>490867</v>
       </c>
       <c r="R46" t="n">
-        <v>7017365</v>
+        <v>7017386</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6097,7 +6121,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flertalet plantor.</t>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6115,11 +6139,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -6134,16 +6153,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499620</v>
+        <v>135499615</v>
       </c>
       <c r="B47" t="n">
-        <v>108294</v>
+        <v>99193</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6151,28 +6170,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220083</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6183,10 +6202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490853</v>
+        <v>490860</v>
       </c>
       <c r="R47" t="n">
-        <v>7017483</v>
+        <v>7017386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6221,6 +6240,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6250,16 +6274,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499621</v>
+        <v>135499509</v>
       </c>
       <c r="B48" t="n">
-        <v>108294</v>
+        <v>99300</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6267,28 +6291,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6299,10 +6323,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490837</v>
+        <v>490880</v>
       </c>
       <c r="R48" t="n">
-        <v>7017379</v>
+        <v>7017365</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6337,6 +6361,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flertalet plantor.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6352,6 +6381,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
@@ -6366,13 +6400,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499623</v>
+        <v>135499620</v>
       </c>
       <c r="B49" t="n">
         <v>108294</v>
@@ -6404,7 +6438,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6415,10 +6449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490848</v>
+        <v>490853</v>
       </c>
       <c r="R49" t="n">
-        <v>7017376</v>
+        <v>7017483</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6482,13 +6516,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499624</v>
+        <v>135499621</v>
       </c>
       <c r="B50" t="n">
         <v>108294</v>
@@ -6531,10 +6565,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490861</v>
+        <v>490837</v>
       </c>
       <c r="R50" t="n">
-        <v>7017386</v>
+        <v>7017379</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6598,13 +6632,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499625</v>
+        <v>135499623</v>
       </c>
       <c r="B51" t="n">
         <v>108294</v>
@@ -6636,7 +6670,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6647,10 +6681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490821</v>
+        <v>490848</v>
       </c>
       <c r="R51" t="n">
-        <v>7017394</v>
+        <v>7017376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6714,13 +6748,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499626</v>
+        <v>135499624</v>
       </c>
       <c r="B52" t="n">
         <v>108294</v>
@@ -6752,7 +6786,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6763,10 +6797,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490841</v>
+        <v>490861</v>
       </c>
       <c r="R52" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6830,16 +6864,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499550</v>
+        <v>135499625</v>
       </c>
       <c r="B53" t="n">
-        <v>108364</v>
+        <v>108294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6847,28 +6881,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6879,10 +6913,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490929</v>
+        <v>490821</v>
       </c>
       <c r="R53" t="n">
-        <v>7017429</v>
+        <v>7017394</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6946,16 +6980,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499551</v>
+        <v>135499626</v>
       </c>
       <c r="B54" t="n">
-        <v>108364</v>
+        <v>108294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6963,28 +6997,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -6995,10 +7029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490853</v>
+        <v>490841</v>
       </c>
       <c r="R54" t="n">
-        <v>7017480</v>
+        <v>7017433</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7033,11 +7067,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7067,13 +7096,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499552</v>
+        <v>135499550</v>
       </c>
       <c r="B55" t="n">
         <v>108364</v>
@@ -7116,10 +7145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490867</v>
+        <v>490929</v>
       </c>
       <c r="R55" t="n">
-        <v>7017480</v>
+        <v>7017429</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7183,13 +7212,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499553</v>
+        <v>135499551</v>
       </c>
       <c r="B56" t="n">
         <v>108364</v>
@@ -7232,10 +7261,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R56" t="n">
-        <v>7017457</v>
+        <v>7017480</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7270,6 +7299,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7299,13 +7333,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499554</v>
+        <v>135499552</v>
       </c>
       <c r="B57" t="n">
         <v>108364</v>
@@ -7348,10 +7382,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490737</v>
+        <v>490867</v>
       </c>
       <c r="R57" t="n">
-        <v>7017474</v>
+        <v>7017480</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7415,13 +7449,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499555</v>
+        <v>135499553</v>
       </c>
       <c r="B58" t="n">
         <v>108364</v>
@@ -7464,10 +7498,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490873</v>
+        <v>490841</v>
       </c>
       <c r="R58" t="n">
-        <v>7017368</v>
+        <v>7017457</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7531,13 +7565,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499556</v>
+        <v>135499554</v>
       </c>
       <c r="B59" t="n">
         <v>108364</v>
@@ -7580,10 +7614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490863</v>
+        <v>490737</v>
       </c>
       <c r="R59" t="n">
-        <v>7017386</v>
+        <v>7017474</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7633,11 +7667,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7652,16 +7681,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499544</v>
+        <v>135499555</v>
       </c>
       <c r="B60" t="n">
-        <v>111244</v>
+        <v>108364</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7669,28 +7698,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7701,10 +7730,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490844</v>
+        <v>490873</v>
       </c>
       <c r="R60" t="n">
-        <v>7017468</v>
+        <v>7017368</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7768,16 +7797,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499546</v>
+        <v>135499556</v>
       </c>
       <c r="B61" t="n">
-        <v>111244</v>
+        <v>108364</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7785,28 +7814,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7817,10 +7846,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490780</v>
+        <v>490863</v>
       </c>
       <c r="R61" t="n">
-        <v>7017405</v>
+        <v>7017386</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7870,6 +7899,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -7884,13 +7918,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499547</v>
+        <v>135499544</v>
       </c>
       <c r="B62" t="n">
         <v>111244</v>
@@ -7922,7 +7956,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7933,10 +7967,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490858</v>
+        <v>490844</v>
       </c>
       <c r="R62" t="n">
-        <v>7017416</v>
+        <v>7017468</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8000,13 +8034,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499548</v>
+        <v>135499546</v>
       </c>
       <c r="B63" t="n">
         <v>111244</v>
@@ -8038,7 +8072,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -8049,10 +8083,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490964</v>
+        <v>490780</v>
       </c>
       <c r="R63" t="n">
-        <v>7017356</v>
+        <v>7017405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8102,11 +8136,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8121,16 +8150,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499617</v>
+        <v>135499547</v>
       </c>
       <c r="B64" t="n">
-        <v>110240</v>
+        <v>111244</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8138,28 +8167,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220294</v>
+        <v>220240</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -8170,10 +8199,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490864</v>
+        <v>490858</v>
       </c>
       <c r="R64" t="n">
-        <v>7017486</v>
+        <v>7017416</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8208,11 +8237,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8242,53 +8266,45 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499580</v>
+        <v>135499548</v>
       </c>
       <c r="B65" t="n">
-        <v>99276</v>
+        <v>111244</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -8299,10 +8315,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490975</v>
+        <v>490964</v>
       </c>
       <c r="R65" t="n">
-        <v>7017304</v>
+        <v>7017356</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8337,11 +8353,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8376,53 +8387,45 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499583</v>
+        <v>135499617</v>
       </c>
       <c r="B66" t="n">
-        <v>99276</v>
+        <v>110240</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -8433,10 +8436,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490768</v>
+        <v>490864</v>
       </c>
       <c r="R66" t="n">
-        <v>7017376</v>
+        <v>7017486</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8473,7 +8476,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8491,11 +8494,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
@@ -8510,13 +8508,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499584</v>
+        <v>135499580</v>
       </c>
       <c r="B67" t="n">
         <v>99276</v>
@@ -8546,7 +8544,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8567,10 +8565,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490839</v>
+        <v>490975</v>
       </c>
       <c r="R67" t="n">
-        <v>7017351</v>
+        <v>7017304</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8607,7 +8605,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8622,7 +8620,12 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8639,13 +8642,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499585</v>
+        <v>135499581</v>
       </c>
       <c r="B68" t="n">
         <v>99276</v>
@@ -8675,7 +8678,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8696,10 +8699,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490845</v>
+        <v>490951</v>
       </c>
       <c r="R68" t="n">
-        <v>7017392</v>
+        <v>7017428</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8736,7 +8739,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8751,7 +8754,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8768,13 +8771,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499581</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499586</v>
+        <v>135499582</v>
       </c>
       <c r="B69" t="n">
         <v>99276</v>
@@ -8825,10 +8828,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490812</v>
+        <v>490884</v>
       </c>
       <c r="R69" t="n">
-        <v>7017401</v>
+        <v>7017471</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8865,7 +8868,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8880,12 +8883,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8902,13 +8900,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499582</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499588</v>
+        <v>135499583</v>
       </c>
       <c r="B70" t="n">
         <v>99276</v>
@@ -8938,7 +8936,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8959,10 +8957,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490843</v>
+        <v>490768</v>
       </c>
       <c r="R70" t="n">
-        <v>7017436</v>
+        <v>7017376</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8999,7 +8997,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9036,13 +9034,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499589</v>
+        <v>135499584</v>
       </c>
       <c r="B71" t="n">
         <v>99276</v>
@@ -9072,7 +9070,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9093,10 +9091,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490967</v>
+        <v>490839</v>
       </c>
       <c r="R71" t="n">
-        <v>7017335</v>
+        <v>7017351</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9133,7 +9131,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9148,12 +9146,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9170,13 +9163,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499590</v>
+        <v>135499585</v>
       </c>
       <c r="B72" t="n">
         <v>99276</v>
@@ -9206,7 +9199,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9227,10 +9220,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490979</v>
+        <v>490845</v>
       </c>
       <c r="R72" t="n">
-        <v>7017360</v>
+        <v>7017392</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9267,7 +9260,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9282,12 +9275,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9304,13 +9292,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499591</v>
+        <v>135499586</v>
       </c>
       <c r="B73" t="n">
         <v>99276</v>
@@ -9340,7 +9328,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9361,10 +9349,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490973</v>
+        <v>490812</v>
       </c>
       <c r="R73" t="n">
-        <v>7017399</v>
+        <v>7017401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9401,7 +9389,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9438,13 +9426,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499592</v>
+        <v>135499588</v>
       </c>
       <c r="B74" t="n">
         <v>99276</v>
@@ -9474,7 +9462,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9495,10 +9483,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490951</v>
+        <v>490843</v>
       </c>
       <c r="R74" t="n">
-        <v>7017408</v>
+        <v>7017436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9535,7 +9523,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9572,13 +9560,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499593</v>
+        <v>135499589</v>
       </c>
       <c r="B75" t="n">
         <v>99276</v>
@@ -9608,7 +9596,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9629,10 +9617,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490951</v>
+        <v>490967</v>
       </c>
       <c r="R75" t="n">
-        <v>7017396</v>
+        <v>7017335</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9669,7 +9657,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9706,13 +9694,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499594</v>
+        <v>135499590</v>
       </c>
       <c r="B76" t="n">
         <v>99276</v>
@@ -9742,7 +9730,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9763,10 +9751,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490957</v>
+        <v>490979</v>
       </c>
       <c r="R76" t="n">
-        <v>7017386</v>
+        <v>7017360</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9803,7 +9791,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9840,43 +9828,55 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499519</v>
+        <v>135499591</v>
       </c>
       <c r="B77" t="n">
-        <v>98138</v>
+        <v>99276</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490752</v>
+        <v>490973</v>
       </c>
       <c r="R77" t="n">
-        <v>7017499</v>
+        <v>7017399</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9943,6 +9943,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
@@ -9957,45 +9962,53 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499516</v>
+        <v>135499592</v>
       </c>
       <c r="B78" t="n">
-        <v>99298</v>
+        <v>99276</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -10006,10 +10019,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490844</v>
+        <v>490951</v>
       </c>
       <c r="R78" t="n">
-        <v>7017394</v>
+        <v>7017408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10044,6 +10057,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10059,6 +10077,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
@@ -10073,45 +10096,53 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499517</v>
+        <v>135499593</v>
       </c>
       <c r="B79" t="n">
-        <v>99298</v>
+        <v>99276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -10122,10 +10153,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490814</v>
+        <v>490951</v>
       </c>
       <c r="R79" t="n">
-        <v>7017404</v>
+        <v>7017396</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10160,6 +10191,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10175,6 +10211,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
@@ -10189,45 +10230,53 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499627</v>
+        <v>135499594</v>
       </c>
       <c r="B80" t="n">
-        <v>101485</v>
+        <v>99276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10238,10 +10287,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490803</v>
+        <v>490957</v>
       </c>
       <c r="R80" t="n">
-        <v>7017492</v>
+        <v>7017386</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10276,6 +10325,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10291,6 +10345,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
@@ -10305,16 +10364,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499628</v>
+        <v>135499519</v>
       </c>
       <c r="B81" t="n">
-        <v>101485</v>
+        <v>98138</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10322,30 +10381,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10354,10 +10409,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490792</v>
+        <v>490752</v>
       </c>
       <c r="R81" t="n">
-        <v>7017441</v>
+        <v>7017499</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10392,6 +10447,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10421,16 +10481,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499629</v>
+        <v>135499516</v>
       </c>
       <c r="B82" t="n">
-        <v>101485</v>
+        <v>99298</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10438,28 +10498,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10470,10 +10530,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490764</v>
+        <v>490844</v>
       </c>
       <c r="R82" t="n">
-        <v>7017441</v>
+        <v>7017394</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10537,16 +10597,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499630</v>
+        <v>135499517</v>
       </c>
       <c r="B83" t="n">
-        <v>101485</v>
+        <v>99298</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10554,28 +10614,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -10586,10 +10646,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490798</v>
+        <v>490814</v>
       </c>
       <c r="R83" t="n">
-        <v>7017366</v>
+        <v>7017404</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10653,13 +10713,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499631</v>
+        <v>135499627</v>
       </c>
       <c r="B84" t="n">
         <v>101485</v>
@@ -10702,10 +10762,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490816</v>
+        <v>490803</v>
       </c>
       <c r="R84" t="n">
-        <v>7017378</v>
+        <v>7017492</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10769,13 +10829,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499632</v>
+        <v>135499628</v>
       </c>
       <c r="B85" t="n">
         <v>101485</v>
@@ -10818,10 +10878,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490796</v>
+        <v>490792</v>
       </c>
       <c r="R85" t="n">
-        <v>7017382</v>
+        <v>7017441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10885,13 +10945,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499633</v>
+        <v>135499629</v>
       </c>
       <c r="B86" t="n">
         <v>101485</v>
@@ -10934,10 +10994,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490782</v>
+        <v>490764</v>
       </c>
       <c r="R86" t="n">
-        <v>7017407</v>
+        <v>7017441</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11001,13 +11061,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499634</v>
+        <v>135499630</v>
       </c>
       <c r="B87" t="n">
         <v>101485</v>
@@ -11050,10 +11110,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490730</v>
+        <v>490798</v>
       </c>
       <c r="R87" t="n">
-        <v>7017371</v>
+        <v>7017366</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11117,13 +11177,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499635</v>
+        <v>135499631</v>
       </c>
       <c r="B88" t="n">
         <v>101485</v>
@@ -11166,10 +11226,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490827</v>
+        <v>490816</v>
       </c>
       <c r="R88" t="n">
-        <v>7017356</v>
+        <v>7017378</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11233,13 +11293,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499636</v>
+        <v>135499632</v>
       </c>
       <c r="B89" t="n">
         <v>101485</v>
@@ -11282,10 +11342,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490844</v>
+        <v>490796</v>
       </c>
       <c r="R89" t="n">
-        <v>7017345</v>
+        <v>7017382</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11349,13 +11409,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499637</v>
+        <v>135499633</v>
       </c>
       <c r="B90" t="n">
         <v>101485</v>
@@ -11398,10 +11458,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490852</v>
+        <v>490782</v>
       </c>
       <c r="R90" t="n">
-        <v>7017373</v>
+        <v>7017407</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11448,7 +11508,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11465,13 +11525,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499638</v>
+        <v>135499634</v>
       </c>
       <c r="B91" t="n">
         <v>101485</v>
@@ -11514,10 +11574,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490882</v>
+        <v>490730</v>
       </c>
       <c r="R91" t="n">
-        <v>7017368</v>
+        <v>7017371</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11564,7 +11624,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11581,13 +11641,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499639</v>
+        <v>135499635</v>
       </c>
       <c r="B92" t="n">
         <v>101485</v>
@@ -11630,10 +11690,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490865</v>
+        <v>490827</v>
       </c>
       <c r="R92" t="n">
-        <v>7017386</v>
+        <v>7017356</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11697,13 +11757,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499640</v>
+        <v>135499636</v>
       </c>
       <c r="B93" t="n">
         <v>101485</v>
@@ -11746,10 +11806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490840</v>
+        <v>490844</v>
       </c>
       <c r="R93" t="n">
-        <v>7017433</v>
+        <v>7017345</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11813,13 +11873,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499641</v>
+        <v>135499637</v>
       </c>
       <c r="B94" t="n">
         <v>101485</v>
@@ -11862,10 +11922,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490880</v>
+        <v>490852</v>
       </c>
       <c r="R94" t="n">
-        <v>7017422</v>
+        <v>7017373</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11912,7 +11972,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11929,16 +11989,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499618</v>
+        <v>135499638</v>
       </c>
       <c r="B95" t="n">
-        <v>98292</v>
+        <v>101485</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11946,21 +12006,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11978,10 +12038,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490791</v>
+        <v>490882</v>
       </c>
       <c r="R95" t="n">
-        <v>7017443</v>
+        <v>7017368</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12016,11 +12076,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -12033,7 +12088,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12050,16 +12105,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499619</v>
+        <v>135499639</v>
       </c>
       <c r="B96" t="n">
-        <v>98292</v>
+        <v>101485</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12067,33 +12122,25 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12107,10 +12154,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490868</v>
+        <v>490865</v>
       </c>
       <c r="R96" t="n">
-        <v>7017387</v>
+        <v>7017386</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12145,11 +12192,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12165,11 +12207,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
@@ -12184,16 +12221,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499520</v>
+        <v>135499640</v>
       </c>
       <c r="B97" t="n">
-        <v>99082</v>
+        <v>101485</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12201,21 +12238,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12233,10 +12270,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490757</v>
+        <v>490840</v>
       </c>
       <c r="R97" t="n">
-        <v>7017472</v>
+        <v>7017433</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12300,16 +12337,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499521</v>
+        <v>135499641</v>
       </c>
       <c r="B98" t="n">
-        <v>99082</v>
+        <v>101485</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12317,21 +12354,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12349,10 +12386,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490966</v>
+        <v>490880</v>
       </c>
       <c r="R98" t="n">
-        <v>7017430</v>
+        <v>7017422</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12416,16 +12453,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499522</v>
+        <v>135499618</v>
       </c>
       <c r="B99" t="n">
-        <v>99082</v>
+        <v>98292</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12433,21 +12470,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12465,10 +12502,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490920</v>
+        <v>490791</v>
       </c>
       <c r="R99" t="n">
-        <v>7017445</v>
+        <v>7017443</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12503,6 +12540,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -12532,16 +12574,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499523</v>
+        <v>135499619</v>
       </c>
       <c r="B100" t="n">
-        <v>99082</v>
+        <v>98292</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12549,25 +12591,33 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12581,10 +12631,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490912</v>
+        <v>490868</v>
       </c>
       <c r="R100" t="n">
-        <v>7017466</v>
+        <v>7017387</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12619,6 +12669,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12634,6 +12689,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
@@ -12648,13 +12708,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499524</v>
+        <v>135499520</v>
       </c>
       <c r="B101" t="n">
         <v>99082</v>
@@ -12697,10 +12757,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490858</v>
+        <v>490757</v>
       </c>
       <c r="R101" t="n">
-        <v>7017493</v>
+        <v>7017472</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12764,13 +12824,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499525</v>
+        <v>135499521</v>
       </c>
       <c r="B102" t="n">
         <v>99082</v>
@@ -12802,7 +12862,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12813,10 +12873,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490804</v>
+        <v>490966</v>
       </c>
       <c r="R102" t="n">
-        <v>7017492</v>
+        <v>7017430</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12880,13 +12940,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499526</v>
+        <v>135499522</v>
       </c>
       <c r="B103" t="n">
         <v>99082</v>
@@ -12929,10 +12989,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490740</v>
+        <v>490920</v>
       </c>
       <c r="R103" t="n">
-        <v>7017423</v>
+        <v>7017445</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12996,13 +13056,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499527</v>
+        <v>135499523</v>
       </c>
       <c r="B104" t="n">
         <v>99082</v>
@@ -13045,10 +13105,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490732</v>
+        <v>490912</v>
       </c>
       <c r="R104" t="n">
-        <v>7017370</v>
+        <v>7017466</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13112,13 +13172,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499528</v>
+        <v>135499524</v>
       </c>
       <c r="B105" t="n">
         <v>99082</v>
@@ -13161,10 +13221,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490867</v>
+        <v>490858</v>
       </c>
       <c r="R105" t="n">
-        <v>7017386</v>
+        <v>7017493</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13199,11 +13259,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -13233,13 +13288,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499529</v>
+        <v>135499525</v>
       </c>
       <c r="B106" t="n">
         <v>99082</v>
@@ -13271,7 +13326,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -13282,10 +13337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490807</v>
+        <v>490804</v>
       </c>
       <c r="R106" t="n">
-        <v>7017431</v>
+        <v>7017492</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13349,13 +13404,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499530</v>
+        <v>135499526</v>
       </c>
       <c r="B107" t="n">
         <v>99082</v>
@@ -13387,7 +13442,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13398,10 +13453,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490932</v>
+        <v>490740</v>
       </c>
       <c r="R107" t="n">
-        <v>7017369</v>
+        <v>7017423</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13465,16 +13520,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499597</v>
+        <v>135499527</v>
       </c>
       <c r="B108" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13482,21 +13537,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13514,10 +13569,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490969</v>
+        <v>490732</v>
       </c>
       <c r="R108" t="n">
-        <v>7017431</v>
+        <v>7017370</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13581,16 +13636,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499598</v>
+        <v>135499528</v>
       </c>
       <c r="B109" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13598,21 +13653,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13630,10 +13685,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490840</v>
+        <v>490867</v>
       </c>
       <c r="R109" t="n">
-        <v>7017457</v>
+        <v>7017386</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13668,6 +13723,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13697,16 +13757,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499599</v>
+        <v>135499529</v>
       </c>
       <c r="B110" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13714,21 +13774,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13746,10 +13806,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490831</v>
+        <v>490807</v>
       </c>
       <c r="R110" t="n">
-        <v>7017486</v>
+        <v>7017431</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13813,16 +13873,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499600</v>
+        <v>135499530</v>
       </c>
       <c r="B111" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13830,28 +13890,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13862,10 +13922,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490797</v>
+        <v>490932</v>
       </c>
       <c r="R111" t="n">
-        <v>7017497</v>
+        <v>7017369</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13929,13 +13989,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499601</v>
+        <v>135499597</v>
       </c>
       <c r="B112" t="n">
         <v>98327</v>
@@ -13978,10 +14038,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490797</v>
+        <v>490969</v>
       </c>
       <c r="R112" t="n">
-        <v>7017511</v>
+        <v>7017431</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14045,13 +14105,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499602</v>
+        <v>135499598</v>
       </c>
       <c r="B113" t="n">
         <v>98327</v>
@@ -14094,10 +14154,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490737</v>
+        <v>490840</v>
       </c>
       <c r="R113" t="n">
-        <v>7017473</v>
+        <v>7017457</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14161,16 +14221,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499515</v>
+        <v>135499599</v>
       </c>
       <c r="B114" t="n">
-        <v>102022</v>
+        <v>98327</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14178,21 +14238,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223366</v>
+        <v>223358</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14210,10 +14270,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490788</v>
+        <v>490831</v>
       </c>
       <c r="R114" t="n">
-        <v>7017450</v>
+        <v>7017486</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14277,16 +14337,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499532</v>
+        <v>135499600</v>
       </c>
       <c r="B115" t="n">
-        <v>101375</v>
+        <v>98327</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14294,21 +14354,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14326,10 +14386,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490889</v>
+        <v>490797</v>
       </c>
       <c r="R115" t="n">
-        <v>7017459</v>
+        <v>7017497</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14393,16 +14453,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499533</v>
+        <v>135499601</v>
       </c>
       <c r="B116" t="n">
-        <v>101375</v>
+        <v>98327</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14410,21 +14470,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14442,10 +14502,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490743</v>
+        <v>490797</v>
       </c>
       <c r="R116" t="n">
-        <v>7017495</v>
+        <v>7017511</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14509,16 +14569,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499534</v>
+        <v>135499602</v>
       </c>
       <c r="B117" t="n">
-        <v>101375</v>
+        <v>98327</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14526,21 +14586,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14561,7 +14621,7 @@
         <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017474</v>
+        <v>7017473</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14625,16 +14685,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499535</v>
+        <v>135499515</v>
       </c>
       <c r="B118" t="n">
-        <v>101375</v>
+        <v>102022</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14642,21 +14702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>224885</v>
+        <v>223366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14674,10 +14734,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490734</v>
+        <v>490788</v>
       </c>
       <c r="R118" t="n">
-        <v>7017429</v>
+        <v>7017450</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14741,13 +14801,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499536</v>
+        <v>135499532</v>
       </c>
       <c r="B119" t="n">
         <v>101375</v>
@@ -14790,10 +14850,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490780</v>
+        <v>490889</v>
       </c>
       <c r="R119" t="n">
-        <v>7017405</v>
+        <v>7017459</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14857,13 +14917,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499537</v>
+        <v>135499533</v>
       </c>
       <c r="B120" t="n">
         <v>101375</v>
@@ -14906,10 +14966,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490751</v>
+        <v>490743</v>
       </c>
       <c r="R120" t="n">
-        <v>7017406</v>
+        <v>7017495</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14973,13 +15033,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499538</v>
+        <v>135499534</v>
       </c>
       <c r="B121" t="n">
         <v>101375</v>
@@ -15022,10 +15082,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490729</v>
+        <v>490737</v>
       </c>
       <c r="R121" t="n">
-        <v>7017373</v>
+        <v>7017474</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15089,13 +15149,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499540</v>
+        <v>135499535</v>
       </c>
       <c r="B122" t="n">
         <v>101375</v>
@@ -15138,10 +15198,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490847</v>
+        <v>490734</v>
       </c>
       <c r="R122" t="n">
-        <v>7017345</v>
+        <v>7017429</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15205,13 +15265,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499541</v>
+        <v>135499536</v>
       </c>
       <c r="B123" t="n">
         <v>101375</v>
@@ -15254,10 +15314,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490856</v>
+        <v>490780</v>
       </c>
       <c r="R123" t="n">
-        <v>7017358</v>
+        <v>7017405</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15321,13 +15381,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499542</v>
+        <v>135499537</v>
       </c>
       <c r="B124" t="n">
         <v>101375</v>
@@ -15359,7 +15419,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -15370,10 +15430,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490840</v>
+        <v>490751</v>
       </c>
       <c r="R124" t="n">
-        <v>7017433</v>
+        <v>7017406</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15436,6 +15496,470 @@
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499537</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>135499538</v>
+      </c>
+      <c r="B125" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>490729</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7017373</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499538</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>135499540</v>
+      </c>
+      <c r="B126" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>490847</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7017345</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499540</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>135499541</v>
+      </c>
+      <c r="B127" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>490856</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7017358</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499541</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>135499542</v>
+      </c>
+      <c r="B128" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>490840</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7017433</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -15566,6 +16090,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ128"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499607</v>
+        <v>135499608</v>
       </c>
       <c r="B2" t="n">
         <v>99182</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490869</v>
+        <v>490867</v>
       </c>
       <c r="R2" t="n">
-        <v>7017370</v>
+        <v>7017387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad snitslad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +790,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkrikt fuktstråk.</t>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,71 +812,58 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499607</t>
+          <t>https://artportalen.se/Sighting/135499608</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499608</v>
+        <v>135499603</v>
       </c>
       <c r="B3" t="n">
-        <v>99182</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490867</v>
+        <v>490968</v>
       </c>
       <c r="R3" t="n">
-        <v>7017387</v>
+        <v>7017430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,7 +900,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,9 +918,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,13 +952,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499608</t>
+          <t>https://artportalen.se/Sighting/135499603</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499603</v>
+        <v>135499604</v>
       </c>
       <c r="B4" t="n">
         <v>92046</v>
@@ -998,10 +1000,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490968</v>
+        <v>490893</v>
       </c>
       <c r="R4" t="n">
-        <v>7017430</v>
+        <v>7017459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,12 +1070,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,13 +1092,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499603</t>
+          <t>https://artportalen.se/Sighting/135499604</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499604</v>
+        <v>135499605</v>
       </c>
       <c r="B5" t="n">
         <v>92046</v>
@@ -1138,10 +1140,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490893</v>
+        <v>490741</v>
       </c>
       <c r="R5" t="n">
-        <v>7017459</v>
+        <v>7017465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1178,7 +1180,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,13 +1232,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499604</t>
+          <t>https://artportalen.se/Sighting/135499605</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499605</v>
+        <v>135499606</v>
       </c>
       <c r="B6" t="n">
         <v>92046</v>
@@ -1278,10 +1280,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490741</v>
+        <v>490951</v>
       </c>
       <c r="R6" t="n">
-        <v>7017465</v>
+        <v>7017411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1320,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1348,12 +1350,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1370,16 +1372,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499605</t>
+          <t>https://artportalen.se/Sighting/135499606</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135499606</v>
+        <v>75185503</v>
       </c>
       <c r="B7" t="n">
-        <v>92046</v>
+        <v>87322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,41 +1389,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1988</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490951</v>
+        <v>490758</v>
       </c>
       <c r="R7" t="n">
-        <v>7017411</v>
+        <v>7017384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1448,17 +1443,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1471,90 +1461,73 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499606</t>
+          <t>https://artportalen.se/Sighting/75185503</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75185503</v>
+        <v>135499557</v>
       </c>
       <c r="B8" t="n">
-        <v>87322</v>
+        <v>96488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1988</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490758</v>
+        <v>490738</v>
       </c>
       <c r="R8" t="n">
-        <v>7017384</v>
+        <v>7017396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1581,12 +1554,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,31 +1572,32 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185503</t>
+          <t>https://artportalen.se/Sighting/135499557</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499557</v>
+        <v>135499558</v>
       </c>
       <c r="B9" t="n">
         <v>96488</v>
@@ -1662,10 +1636,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490738</v>
+        <v>490991</v>
       </c>
       <c r="R9" t="n">
-        <v>7017396</v>
+        <v>7017297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1729,13 +1703,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499557</t>
+          <t>https://artportalen.se/Sighting/135499558</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499558</v>
+        <v>135499560</v>
       </c>
       <c r="B10" t="n">
         <v>96488</v>
@@ -1774,10 +1748,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490991</v>
+        <v>490966</v>
       </c>
       <c r="R10" t="n">
-        <v>7017297</v>
+        <v>7017426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,6 +1801,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1841,13 +1820,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499558</t>
+          <t>https://artportalen.se/Sighting/135499560</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499560</v>
+        <v>135499561</v>
       </c>
       <c r="B11" t="n">
         <v>96488</v>
@@ -1886,10 +1865,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490966</v>
+        <v>490929</v>
       </c>
       <c r="R11" t="n">
-        <v>7017426</v>
+        <v>7017441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1936,12 +1915,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1958,13 +1932,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499560</t>
+          <t>https://artportalen.se/Sighting/135499561</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499561</v>
+        <v>135499562</v>
       </c>
       <c r="B12" t="n">
         <v>96488</v>
@@ -2003,10 +1977,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490929</v>
+        <v>490910</v>
       </c>
       <c r="R12" t="n">
-        <v>7017441</v>
+        <v>7017467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2070,13 +2044,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499561</t>
+          <t>https://artportalen.se/Sighting/135499562</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499562</v>
+        <v>135499563</v>
       </c>
       <c r="B13" t="n">
         <v>96488</v>
@@ -2115,10 +2089,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490910</v>
+        <v>490878</v>
       </c>
       <c r="R13" t="n">
-        <v>7017467</v>
+        <v>7017474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,7 +2139,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2182,13 +2156,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499562</t>
+          <t>https://artportalen.se/Sighting/135499563</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499563</v>
+        <v>135499564</v>
       </c>
       <c r="B14" t="n">
         <v>96488</v>
@@ -2227,10 +2201,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490878</v>
+        <v>490883</v>
       </c>
       <c r="R14" t="n">
-        <v>7017474</v>
+        <v>7017462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2277,7 +2251,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2294,13 +2268,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499563</t>
+          <t>https://artportalen.se/Sighting/135499564</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499564</v>
+        <v>135499565</v>
       </c>
       <c r="B15" t="n">
         <v>96488</v>
@@ -2339,10 +2313,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490883</v>
+        <v>490756</v>
       </c>
       <c r="R15" t="n">
-        <v>7017462</v>
+        <v>7017472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2389,7 +2363,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2406,13 +2380,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499564</t>
+          <t>https://artportalen.se/Sighting/135499565</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499565</v>
+        <v>135499566</v>
       </c>
       <c r="B16" t="n">
         <v>96488</v>
@@ -2451,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490756</v>
+        <v>490790</v>
       </c>
       <c r="R16" t="n">
-        <v>7017472</v>
+        <v>7017441</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2518,13 +2492,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499565</t>
+          <t>https://artportalen.se/Sighting/135499566</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499566</v>
+        <v>135499567</v>
       </c>
       <c r="B17" t="n">
         <v>96488</v>
@@ -2563,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490790</v>
+        <v>490732</v>
       </c>
       <c r="R17" t="n">
-        <v>7017441</v>
+        <v>7017442</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2613,7 +2587,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2630,13 +2604,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499566</t>
+          <t>https://artportalen.se/Sighting/135499567</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499567</v>
+        <v>135499568</v>
       </c>
       <c r="B18" t="n">
         <v>96488</v>
@@ -2675,10 +2649,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490732</v>
+        <v>490781</v>
       </c>
       <c r="R18" t="n">
-        <v>7017442</v>
+        <v>7017407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2725,7 +2699,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2742,13 +2716,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499567</t>
+          <t>https://artportalen.se/Sighting/135499568</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499568</v>
+        <v>135499569</v>
       </c>
       <c r="B19" t="n">
         <v>96488</v>
@@ -2787,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490781</v>
+        <v>490731</v>
       </c>
       <c r="R19" t="n">
-        <v>7017407</v>
+        <v>7017371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2840,6 +2814,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2854,13 +2833,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499568</t>
+          <t>https://artportalen.se/Sighting/135499569</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499569</v>
+        <v>135499570</v>
       </c>
       <c r="B20" t="n">
         <v>96488</v>
@@ -2899,10 +2878,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490731</v>
+        <v>490854</v>
       </c>
       <c r="R20" t="n">
-        <v>7017371</v>
+        <v>7017345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2952,11 +2931,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2971,13 +2945,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499569</t>
+          <t>https://artportalen.se/Sighting/135499570</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499570</v>
+        <v>135499571</v>
       </c>
       <c r="B21" t="n">
         <v>96488</v>
@@ -3016,10 +2990,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490854</v>
+        <v>490878</v>
       </c>
       <c r="R21" t="n">
-        <v>7017345</v>
+        <v>7017366</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,6 +3028,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3083,13 +3062,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499570</t>
+          <t>https://artportalen.se/Sighting/135499571</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499571</v>
+        <v>135499572</v>
       </c>
       <c r="B22" t="n">
         <v>96488</v>
@@ -3128,10 +3107,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490878</v>
+        <v>490867</v>
       </c>
       <c r="R22" t="n">
-        <v>7017366</v>
+        <v>7017386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3166,11 +3145,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3200,13 +3174,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499571</t>
+          <t>https://artportalen.se/Sighting/135499572</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499572</v>
+        <v>135499573</v>
       </c>
       <c r="B23" t="n">
         <v>96488</v>
@@ -3245,10 +3219,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490867</v>
+        <v>490840</v>
       </c>
       <c r="R23" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3312,13 +3286,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499572</t>
+          <t>https://artportalen.se/Sighting/135499573</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499573</v>
+        <v>135499574</v>
       </c>
       <c r="B24" t="n">
         <v>96488</v>
@@ -3357,10 +3331,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490840</v>
+        <v>490844</v>
       </c>
       <c r="R24" t="n">
-        <v>7017433</v>
+        <v>7017436</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,13 +3398,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499573</t>
+          <t>https://artportalen.se/Sighting/135499574</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499574</v>
+        <v>135499575</v>
       </c>
       <c r="B25" t="n">
         <v>96488</v>
@@ -3469,10 +3443,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490844</v>
+        <v>490872</v>
       </c>
       <c r="R25" t="n">
-        <v>7017436</v>
+        <v>7017426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3536,13 +3510,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499574</t>
+          <t>https://artportalen.se/Sighting/135499575</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499575</v>
+        <v>135499576</v>
       </c>
       <c r="B26" t="n">
         <v>96488</v>
@@ -3581,10 +3555,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490872</v>
+        <v>490917</v>
       </c>
       <c r="R26" t="n">
-        <v>7017426</v>
+        <v>7017402</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3648,13 +3622,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499575</t>
+          <t>https://artportalen.se/Sighting/135499576</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499576</v>
+        <v>135499577</v>
       </c>
       <c r="B27" t="n">
         <v>96488</v>
@@ -3693,10 +3667,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490917</v>
+        <v>490931</v>
       </c>
       <c r="R27" t="n">
-        <v>7017402</v>
+        <v>7017371</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3746,6 +3720,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3760,13 +3739,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499576</t>
+          <t>https://artportalen.se/Sighting/135499577</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499577</v>
+        <v>135499578</v>
       </c>
       <c r="B28" t="n">
         <v>96488</v>
@@ -3805,10 +3784,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490931</v>
+        <v>490951</v>
       </c>
       <c r="R28" t="n">
-        <v>7017371</v>
+        <v>7017390</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,13 +3856,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499577</t>
+          <t>https://artportalen.se/Sighting/135499578</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499578</v>
+        <v>135499579</v>
       </c>
       <c r="B29" t="n">
         <v>96488</v>
@@ -3922,10 +3901,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490951</v>
+        <v>490976</v>
       </c>
       <c r="R29" t="n">
-        <v>7017390</v>
+        <v>7017311</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3994,16 +3973,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499578</t>
+          <t>https://artportalen.se/Sighting/135499579</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135499579</v>
+        <v>91488964</v>
       </c>
       <c r="B30" t="n">
-        <v>96488</v>
+        <v>92632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,41 +3990,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2812</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490976</v>
+        <v>490939</v>
       </c>
       <c r="R30" t="n">
-        <v>7017311</v>
+        <v>7017412</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4069,12 +4044,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4083,66 +4058,59 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499579</t>
+          <t>https://artportalen.se/Sighting/91488964</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>91488964</v>
+        <v>75185505</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>89156</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4152,13 +4120,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490939</v>
+        <v>490781</v>
       </c>
       <c r="R31" t="n">
-        <v>7017412</v>
+        <v>7017384</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4196,18 +4164,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4217,51 +4186,54 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91488964</t>
+          <t>https://artportalen.se/Sighting/75185505</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>75185505</v>
+        <v>135499609</v>
       </c>
       <c r="B32" t="n">
-        <v>89156</v>
+        <v>79441</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490781</v>
+        <v>490849</v>
       </c>
       <c r="R32" t="n">
-        <v>7017384</v>
+        <v>7017392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4288,12 +4260,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4306,31 +4283,52 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185505</t>
+          <t>https://artportalen.se/Sighting/135499609</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499609</v>
+        <v>135499610</v>
       </c>
       <c r="B33" t="n">
         <v>79441</v>
@@ -4368,10 +4366,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490849</v>
+        <v>490859</v>
       </c>
       <c r="R33" t="n">
-        <v>7017392</v>
+        <v>7017416</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,11 +4404,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4438,12 +4431,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4460,54 +4453,67 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499609</t>
+          <t>https://artportalen.se/Sighting/135499610</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499610</v>
+        <v>135499531</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>58094</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100090</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490859</v>
+        <v>490781</v>
       </c>
       <c r="R34" t="n">
-        <v>7017416</v>
+        <v>7017369</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,39 +4548,23 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Synobservation av en individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4591,16 +4581,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499610</t>
+          <t>https://artportalen.se/Sighting/135499531</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499531</v>
+        <v>135499510</v>
       </c>
       <c r="B35" t="n">
-        <v>58094</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4608,16 +4598,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100090</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4625,16 +4615,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4648,10 +4634,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490781</v>
+        <v>490891</v>
       </c>
       <c r="R35" t="n">
-        <v>7017369</v>
+        <v>7017451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,7 +4674,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Synobservation av en individ med lockläte.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4702,7 +4688,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4719,13 +4725,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499531</t>
+          <t>https://artportalen.se/Sighting/135499510</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499510</v>
+        <v>135499511</v>
       </c>
       <c r="B36" t="n">
         <v>57980</v>
@@ -4758,7 +4764,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4772,10 +4778,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490891</v>
+        <v>490785</v>
       </c>
       <c r="R36" t="n">
-        <v>7017451</v>
+        <v>7017521</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4812,7 +4818,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4826,7 +4832,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -4863,13 +4869,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499510</t>
+          <t>https://artportalen.se/Sighting/135499511</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499511</v>
+        <v>135499512</v>
       </c>
       <c r="B37" t="n">
         <v>57980</v>
@@ -4916,10 +4922,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490785</v>
+        <v>490783</v>
       </c>
       <c r="R37" t="n">
-        <v>7017521</v>
+        <v>7017360</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4956,7 +4962,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4971,6 +4977,11 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5007,33 +5018,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499511</t>
+          <t>https://artportalen.se/Sighting/135499512</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499512</v>
+        <v>135499596</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>58239</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5041,29 +5052,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490783</v>
+        <v>490875</v>
       </c>
       <c r="R38" t="n">
-        <v>7017360</v>
+        <v>7017470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5100,7 +5111,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5115,31 +5126,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5156,16 +5142,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499512</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499549</v>
+        <v>135499513</v>
       </c>
       <c r="B39" t="n">
-        <v>58236</v>
+        <v>58141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,21 +5159,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102980</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5199,7 +5185,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5213,10 +5199,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490804</v>
+        <v>490763</v>
       </c>
       <c r="R39" t="n">
-        <v>7017502</v>
+        <v>7017499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5253,7 +5239,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 1 överflygande med sång.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5267,7 +5253,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5284,43 +5275,43 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499549</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499596</v>
+        <v>135499514</v>
       </c>
       <c r="B40" t="n">
-        <v>58239</v>
+        <v>58141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102981</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5330,7 +5321,11 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
@@ -5340,7 +5335,7 @@
         <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017470</v>
+        <v>7017397</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5377,7 +5372,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5392,6 +5387,11 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5408,67 +5408,59 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499513</v>
+        <v>135499611</v>
       </c>
       <c r="B41" t="n">
-        <v>58141</v>
+        <v>99193</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490763</v>
+        <v>490821</v>
       </c>
       <c r="R41" t="n">
-        <v>7017499</v>
+        <v>7017504</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5505,7 +5497,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5514,17 +5506,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5541,67 +5529,59 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499514</v>
+        <v>135499612</v>
       </c>
       <c r="B42" t="n">
-        <v>58141</v>
+        <v>99193</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490875</v>
+        <v>490848</v>
       </c>
       <c r="R42" t="n">
-        <v>7017397</v>
+        <v>7017375</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5636,28 +5616,19 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5674,13 +5645,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499611</v>
+        <v>135499613</v>
       </c>
       <c r="B43" t="n">
         <v>99193</v>
@@ -5723,10 +5694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490821</v>
+        <v>490878</v>
       </c>
       <c r="R43" t="n">
-        <v>7017504</v>
+        <v>7017368</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5763,7 +5734,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk.</t>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5795,13 +5766,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499612</v>
+        <v>135499614</v>
       </c>
       <c r="B44" t="n">
         <v>99193</v>
@@ -5844,10 +5815,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490848</v>
+        <v>490867</v>
       </c>
       <c r="R44" t="n">
-        <v>7017375</v>
+        <v>7017386</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5882,6 +5853,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5911,13 +5887,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499613</v>
+        <v>135499615</v>
       </c>
       <c r="B45" t="n">
         <v>99193</v>
@@ -5960,10 +5936,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490878</v>
+        <v>490860</v>
       </c>
       <c r="R45" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6032,16 +6008,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499614</v>
+        <v>135499509</v>
       </c>
       <c r="B46" t="n">
-        <v>99193</v>
+        <v>99300</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6049,28 +6025,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6081,10 +6057,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490867</v>
+        <v>490880</v>
       </c>
       <c r="R46" t="n">
-        <v>7017386</v>
+        <v>7017365</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6121,7 +6097,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Flertalet plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6139,6 +6115,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -6153,16 +6134,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499615</v>
+        <v>135499620</v>
       </c>
       <c r="B47" t="n">
-        <v>99193</v>
+        <v>108294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6170,28 +6151,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>220083</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6202,10 +6183,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490860</v>
+        <v>490853</v>
       </c>
       <c r="R47" t="n">
-        <v>7017386</v>
+        <v>7017483</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6240,11 +6221,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6274,16 +6250,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499509</v>
+        <v>135499621</v>
       </c>
       <c r="B48" t="n">
-        <v>99300</v>
+        <v>108294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6291,28 +6267,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6323,10 +6299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490880</v>
+        <v>490837</v>
       </c>
       <c r="R48" t="n">
-        <v>7017365</v>
+        <v>7017379</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6361,11 +6337,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flertalet plantor.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6381,11 +6352,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
@@ -6400,13 +6366,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499620</v>
+        <v>135499623</v>
       </c>
       <c r="B49" t="n">
         <v>108294</v>
@@ -6438,7 +6404,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6449,10 +6415,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490853</v>
+        <v>490848</v>
       </c>
       <c r="R49" t="n">
-        <v>7017483</v>
+        <v>7017376</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6516,13 +6482,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499621</v>
+        <v>135499624</v>
       </c>
       <c r="B50" t="n">
         <v>108294</v>
@@ -6565,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490837</v>
+        <v>490861</v>
       </c>
       <c r="R50" t="n">
-        <v>7017379</v>
+        <v>7017386</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6632,13 +6598,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499623</v>
+        <v>135499625</v>
       </c>
       <c r="B51" t="n">
         <v>108294</v>
@@ -6670,7 +6636,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6681,10 +6647,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490848</v>
+        <v>490821</v>
       </c>
       <c r="R51" t="n">
-        <v>7017376</v>
+        <v>7017394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6748,13 +6714,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499624</v>
+        <v>135499626</v>
       </c>
       <c r="B52" t="n">
         <v>108294</v>
@@ -6786,7 +6752,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6797,10 +6763,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490861</v>
+        <v>490841</v>
       </c>
       <c r="R52" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6864,16 +6830,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499625</v>
+        <v>135499550</v>
       </c>
       <c r="B53" t="n">
-        <v>108294</v>
+        <v>108364</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6881,28 +6847,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6913,10 +6879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490821</v>
+        <v>490929</v>
       </c>
       <c r="R53" t="n">
-        <v>7017394</v>
+        <v>7017429</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6980,16 +6946,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499626</v>
+        <v>135499551</v>
       </c>
       <c r="B54" t="n">
-        <v>108294</v>
+        <v>108364</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6997,28 +6963,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -7029,10 +6995,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R54" t="n">
-        <v>7017433</v>
+        <v>7017480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7067,6 +7033,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7096,13 +7067,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499550</v>
+        <v>135499552</v>
       </c>
       <c r="B55" t="n">
         <v>108364</v>
@@ -7145,10 +7116,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490929</v>
+        <v>490867</v>
       </c>
       <c r="R55" t="n">
-        <v>7017429</v>
+        <v>7017480</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7212,13 +7183,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499551</v>
+        <v>135499553</v>
       </c>
       <c r="B56" t="n">
         <v>108364</v>
@@ -7261,10 +7232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490853</v>
+        <v>490841</v>
       </c>
       <c r="R56" t="n">
-        <v>7017480</v>
+        <v>7017457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7299,11 +7270,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7333,13 +7299,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499552</v>
+        <v>135499554</v>
       </c>
       <c r="B57" t="n">
         <v>108364</v>
@@ -7382,10 +7348,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490867</v>
+        <v>490737</v>
       </c>
       <c r="R57" t="n">
-        <v>7017480</v>
+        <v>7017474</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7449,13 +7415,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499553</v>
+        <v>135499555</v>
       </c>
       <c r="B58" t="n">
         <v>108364</v>
@@ -7498,10 +7464,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490841</v>
+        <v>490873</v>
       </c>
       <c r="R58" t="n">
-        <v>7017457</v>
+        <v>7017368</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7565,13 +7531,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499554</v>
+        <v>135499556</v>
       </c>
       <c r="B59" t="n">
         <v>108364</v>
@@ -7614,10 +7580,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490737</v>
+        <v>490863</v>
       </c>
       <c r="R59" t="n">
-        <v>7017474</v>
+        <v>7017386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7667,6 +7633,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7681,16 +7652,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499555</v>
+        <v>135499544</v>
       </c>
       <c r="B60" t="n">
-        <v>108364</v>
+        <v>111244</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7698,28 +7669,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7730,10 +7701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490873</v>
+        <v>490844</v>
       </c>
       <c r="R60" t="n">
-        <v>7017368</v>
+        <v>7017468</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7797,16 +7768,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499556</v>
+        <v>135499546</v>
       </c>
       <c r="B61" t="n">
-        <v>108364</v>
+        <v>111244</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7814,28 +7785,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7846,10 +7817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490863</v>
+        <v>490780</v>
       </c>
       <c r="R61" t="n">
-        <v>7017386</v>
+        <v>7017405</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7899,11 +7870,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -7918,13 +7884,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499544</v>
+        <v>135499547</v>
       </c>
       <c r="B62" t="n">
         <v>111244</v>
@@ -7956,7 +7922,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7967,10 +7933,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490844</v>
+        <v>490858</v>
       </c>
       <c r="R62" t="n">
-        <v>7017468</v>
+        <v>7017416</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8034,13 +8000,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499546</v>
+        <v>135499548</v>
       </c>
       <c r="B63" t="n">
         <v>111244</v>
@@ -8072,7 +8038,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -8083,10 +8049,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490780</v>
+        <v>490964</v>
       </c>
       <c r="R63" t="n">
-        <v>7017405</v>
+        <v>7017356</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8136,6 +8102,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8150,16 +8121,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499547</v>
+        <v>135499617</v>
       </c>
       <c r="B64" t="n">
-        <v>111244</v>
+        <v>110240</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8167,28 +8138,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220240</v>
+        <v>220294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -8199,10 +8170,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490858</v>
+        <v>490864</v>
       </c>
       <c r="R64" t="n">
-        <v>7017416</v>
+        <v>7017486</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8237,6 +8208,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8266,45 +8242,53 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499548</v>
+        <v>135499580</v>
       </c>
       <c r="B65" t="n">
-        <v>111244</v>
+        <v>99276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -8315,10 +8299,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490964</v>
+        <v>490975</v>
       </c>
       <c r="R65" t="n">
-        <v>7017356</v>
+        <v>7017304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8353,6 +8337,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8387,45 +8376,53 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499617</v>
+        <v>135499583</v>
       </c>
       <c r="B66" t="n">
-        <v>110240</v>
+        <v>99276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220294</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -8436,10 +8433,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490864</v>
+        <v>490768</v>
       </c>
       <c r="R66" t="n">
-        <v>7017486</v>
+        <v>7017376</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8476,7 +8473,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8494,6 +8491,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
@@ -8508,13 +8510,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499580</v>
+        <v>135499584</v>
       </c>
       <c r="B67" t="n">
         <v>99276</v>
@@ -8544,7 +8546,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8565,10 +8567,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490975</v>
+        <v>490839</v>
       </c>
       <c r="R67" t="n">
-        <v>7017304</v>
+        <v>7017351</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8605,7 +8607,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8620,12 +8622,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8642,13 +8639,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499581</v>
+        <v>135499585</v>
       </c>
       <c r="B68" t="n">
         <v>99276</v>
@@ -8678,7 +8675,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8699,10 +8696,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490951</v>
+        <v>490845</v>
       </c>
       <c r="R68" t="n">
-        <v>7017428</v>
+        <v>7017392</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8739,7 +8736,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8754,7 +8751,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8771,13 +8768,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499581</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499582</v>
+        <v>135499586</v>
       </c>
       <c r="B69" t="n">
         <v>99276</v>
@@ -8828,10 +8825,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490884</v>
+        <v>490812</v>
       </c>
       <c r="R69" t="n">
-        <v>7017471</v>
+        <v>7017401</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8868,7 +8865,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8883,7 +8880,12 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8900,13 +8902,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499582</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499583</v>
+        <v>135499588</v>
       </c>
       <c r="B70" t="n">
         <v>99276</v>
@@ -8936,7 +8938,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8957,10 +8959,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490768</v>
+        <v>490843</v>
       </c>
       <c r="R70" t="n">
-        <v>7017376</v>
+        <v>7017436</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8997,7 +8999,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9034,13 +9036,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499584</v>
+        <v>135499589</v>
       </c>
       <c r="B71" t="n">
         <v>99276</v>
@@ -9070,7 +9072,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9091,10 +9093,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490839</v>
+        <v>490967</v>
       </c>
       <c r="R71" t="n">
-        <v>7017351</v>
+        <v>7017335</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9131,7 +9133,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9146,7 +9148,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9163,13 +9170,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499585</v>
+        <v>135499590</v>
       </c>
       <c r="B72" t="n">
         <v>99276</v>
@@ -9199,7 +9206,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9220,10 +9227,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490845</v>
+        <v>490979</v>
       </c>
       <c r="R72" t="n">
-        <v>7017392</v>
+        <v>7017360</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9260,7 +9267,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9275,7 +9282,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9292,13 +9304,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499586</v>
+        <v>135499591</v>
       </c>
       <c r="B73" t="n">
         <v>99276</v>
@@ -9328,7 +9340,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9349,10 +9361,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490812</v>
+        <v>490973</v>
       </c>
       <c r="R73" t="n">
-        <v>7017401</v>
+        <v>7017399</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9389,7 +9401,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9426,13 +9438,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499588</v>
+        <v>135499592</v>
       </c>
       <c r="B74" t="n">
         <v>99276</v>
@@ -9462,7 +9474,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9483,10 +9495,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490843</v>
+        <v>490951</v>
       </c>
       <c r="R74" t="n">
-        <v>7017436</v>
+        <v>7017408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9523,7 +9535,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9560,13 +9572,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499589</v>
+        <v>135499593</v>
       </c>
       <c r="B75" t="n">
         <v>99276</v>
@@ -9596,7 +9608,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9617,10 +9629,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490967</v>
+        <v>490951</v>
       </c>
       <c r="R75" t="n">
-        <v>7017335</v>
+        <v>7017396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9657,7 +9669,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9694,13 +9706,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499590</v>
+        <v>135499594</v>
       </c>
       <c r="B76" t="n">
         <v>99276</v>
@@ -9730,7 +9742,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9751,10 +9763,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490979</v>
+        <v>490957</v>
       </c>
       <c r="R76" t="n">
-        <v>7017360</v>
+        <v>7017386</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9791,7 +9803,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9828,55 +9840,43 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499591</v>
+        <v>135499519</v>
       </c>
       <c r="B77" t="n">
-        <v>99276</v>
+        <v>98138</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490973</v>
+        <v>490752</v>
       </c>
       <c r="R77" t="n">
-        <v>7017399</v>
+        <v>7017499</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9943,11 +9943,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
@@ -9962,53 +9957,45 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499592</v>
+        <v>135499516</v>
       </c>
       <c r="B78" t="n">
-        <v>99276</v>
+        <v>99298</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -10019,10 +10006,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490951</v>
+        <v>490844</v>
       </c>
       <c r="R78" t="n">
-        <v>7017408</v>
+        <v>7017394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10057,11 +10044,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10077,11 +10059,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
@@ -10096,53 +10073,45 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499593</v>
+        <v>135499517</v>
       </c>
       <c r="B79" t="n">
-        <v>99276</v>
+        <v>99298</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -10153,10 +10122,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490951</v>
+        <v>490814</v>
       </c>
       <c r="R79" t="n">
-        <v>7017396</v>
+        <v>7017404</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10191,11 +10160,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10211,11 +10175,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
@@ -10230,53 +10189,45 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499594</v>
+        <v>135499627</v>
       </c>
       <c r="B80" t="n">
-        <v>99276</v>
+        <v>101485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10287,10 +10238,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490957</v>
+        <v>490803</v>
       </c>
       <c r="R80" t="n">
-        <v>7017386</v>
+        <v>7017492</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10325,11 +10276,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10345,11 +10291,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
@@ -10364,16 +10305,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499519</v>
+        <v>135499628</v>
       </c>
       <c r="B81" t="n">
-        <v>98138</v>
+        <v>101485</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10381,26 +10322,30 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10409,10 +10354,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490752</v>
+        <v>490792</v>
       </c>
       <c r="R81" t="n">
-        <v>7017499</v>
+        <v>7017441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10447,11 +10392,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10481,16 +10421,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499516</v>
+        <v>135499629</v>
       </c>
       <c r="B82" t="n">
-        <v>99298</v>
+        <v>101485</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10498,28 +10438,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10530,10 +10470,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490844</v>
+        <v>490764</v>
       </c>
       <c r="R82" t="n">
-        <v>7017394</v>
+        <v>7017441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10597,16 +10537,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499517</v>
+        <v>135499630</v>
       </c>
       <c r="B83" t="n">
-        <v>99298</v>
+        <v>101485</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10614,28 +10554,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -10646,10 +10586,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490814</v>
+        <v>490798</v>
       </c>
       <c r="R83" t="n">
-        <v>7017404</v>
+        <v>7017366</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10713,13 +10653,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499627</v>
+        <v>135499631</v>
       </c>
       <c r="B84" t="n">
         <v>101485</v>
@@ -10762,10 +10702,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490803</v>
+        <v>490816</v>
       </c>
       <c r="R84" t="n">
-        <v>7017492</v>
+        <v>7017378</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10829,13 +10769,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499628</v>
+        <v>135499632</v>
       </c>
       <c r="B85" t="n">
         <v>101485</v>
@@ -10878,10 +10818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490792</v>
+        <v>490796</v>
       </c>
       <c r="R85" t="n">
-        <v>7017441</v>
+        <v>7017382</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10945,13 +10885,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499629</v>
+        <v>135499633</v>
       </c>
       <c r="B86" t="n">
         <v>101485</v>
@@ -10994,10 +10934,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490764</v>
+        <v>490782</v>
       </c>
       <c r="R86" t="n">
-        <v>7017441</v>
+        <v>7017407</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11061,13 +11001,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499630</v>
+        <v>135499634</v>
       </c>
       <c r="B87" t="n">
         <v>101485</v>
@@ -11110,10 +11050,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490798</v>
+        <v>490730</v>
       </c>
       <c r="R87" t="n">
-        <v>7017366</v>
+        <v>7017371</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11177,13 +11117,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499631</v>
+        <v>135499635</v>
       </c>
       <c r="B88" t="n">
         <v>101485</v>
@@ -11226,10 +11166,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490816</v>
+        <v>490827</v>
       </c>
       <c r="R88" t="n">
-        <v>7017378</v>
+        <v>7017356</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11293,13 +11233,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499632</v>
+        <v>135499636</v>
       </c>
       <c r="B89" t="n">
         <v>101485</v>
@@ -11342,10 +11282,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490796</v>
+        <v>490844</v>
       </c>
       <c r="R89" t="n">
-        <v>7017382</v>
+        <v>7017345</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11409,13 +11349,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499633</v>
+        <v>135499637</v>
       </c>
       <c r="B90" t="n">
         <v>101485</v>
@@ -11458,10 +11398,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490782</v>
+        <v>490852</v>
       </c>
       <c r="R90" t="n">
-        <v>7017407</v>
+        <v>7017373</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11508,7 +11448,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11525,13 +11465,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499634</v>
+        <v>135499638</v>
       </c>
       <c r="B91" t="n">
         <v>101485</v>
@@ -11574,10 +11514,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490730</v>
+        <v>490882</v>
       </c>
       <c r="R91" t="n">
-        <v>7017371</v>
+        <v>7017368</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11624,7 +11564,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11641,13 +11581,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499635</v>
+        <v>135499639</v>
       </c>
       <c r="B92" t="n">
         <v>101485</v>
@@ -11690,10 +11630,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490827</v>
+        <v>490865</v>
       </c>
       <c r="R92" t="n">
-        <v>7017356</v>
+        <v>7017386</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11757,13 +11697,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499636</v>
+        <v>135499640</v>
       </c>
       <c r="B93" t="n">
         <v>101485</v>
@@ -11806,10 +11746,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490844</v>
+        <v>490840</v>
       </c>
       <c r="R93" t="n">
-        <v>7017345</v>
+        <v>7017433</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11873,13 +11813,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499637</v>
+        <v>135499641</v>
       </c>
       <c r="B94" t="n">
         <v>101485</v>
@@ -11922,10 +11862,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490852</v>
+        <v>490880</v>
       </c>
       <c r="R94" t="n">
-        <v>7017373</v>
+        <v>7017422</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11972,7 +11912,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11989,16 +11929,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499638</v>
+        <v>135499618</v>
       </c>
       <c r="B95" t="n">
-        <v>101485</v>
+        <v>98292</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12006,21 +11946,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12038,10 +11978,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490882</v>
+        <v>490791</v>
       </c>
       <c r="R95" t="n">
-        <v>7017368</v>
+        <v>7017443</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12076,6 +12016,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -12088,7 +12033,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12105,16 +12050,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499639</v>
+        <v>135499619</v>
       </c>
       <c r="B96" t="n">
-        <v>101485</v>
+        <v>98292</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12122,25 +12067,33 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12154,10 +12107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490865</v>
+        <v>490868</v>
       </c>
       <c r="R96" t="n">
-        <v>7017386</v>
+        <v>7017387</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12192,6 +12145,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12207,6 +12165,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
@@ -12221,16 +12184,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499640</v>
+        <v>135499520</v>
       </c>
       <c r="B97" t="n">
-        <v>101485</v>
+        <v>99082</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12238,21 +12201,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>223049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12270,10 +12233,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490840</v>
+        <v>490757</v>
       </c>
       <c r="R97" t="n">
-        <v>7017433</v>
+        <v>7017472</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12337,16 +12300,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499641</v>
+        <v>135499521</v>
       </c>
       <c r="B98" t="n">
-        <v>101485</v>
+        <v>99082</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12354,21 +12317,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>223049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12386,10 +12349,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490880</v>
+        <v>490966</v>
       </c>
       <c r="R98" t="n">
-        <v>7017422</v>
+        <v>7017430</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12453,16 +12416,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499618</v>
+        <v>135499522</v>
       </c>
       <c r="B99" t="n">
-        <v>98292</v>
+        <v>99082</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12470,21 +12433,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12502,10 +12465,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490791</v>
+        <v>490920</v>
       </c>
       <c r="R99" t="n">
-        <v>7017443</v>
+        <v>7017445</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12540,11 +12503,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -12574,16 +12532,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499619</v>
+        <v>135499523</v>
       </c>
       <c r="B100" t="n">
-        <v>98292</v>
+        <v>99082</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12591,33 +12549,25 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12631,10 +12581,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490868</v>
+        <v>490912</v>
       </c>
       <c r="R100" t="n">
-        <v>7017387</v>
+        <v>7017466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12669,11 +12619,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12689,11 +12634,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
@@ -12708,13 +12648,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499520</v>
+        <v>135499524</v>
       </c>
       <c r="B101" t="n">
         <v>99082</v>
@@ -12757,10 +12697,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490757</v>
+        <v>490858</v>
       </c>
       <c r="R101" t="n">
-        <v>7017472</v>
+        <v>7017493</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12824,13 +12764,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499521</v>
+        <v>135499525</v>
       </c>
       <c r="B102" t="n">
         <v>99082</v>
@@ -12862,7 +12802,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12873,10 +12813,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490966</v>
+        <v>490804</v>
       </c>
       <c r="R102" t="n">
-        <v>7017430</v>
+        <v>7017492</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12940,13 +12880,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499522</v>
+        <v>135499526</v>
       </c>
       <c r="B103" t="n">
         <v>99082</v>
@@ -12989,10 +12929,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490920</v>
+        <v>490740</v>
       </c>
       <c r="R103" t="n">
-        <v>7017445</v>
+        <v>7017423</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13056,13 +12996,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499523</v>
+        <v>135499527</v>
       </c>
       <c r="B104" t="n">
         <v>99082</v>
@@ -13105,10 +13045,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490912</v>
+        <v>490732</v>
       </c>
       <c r="R104" t="n">
-        <v>7017466</v>
+        <v>7017370</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13172,13 +13112,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499524</v>
+        <v>135499528</v>
       </c>
       <c r="B105" t="n">
         <v>99082</v>
@@ -13221,10 +13161,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490858</v>
+        <v>490867</v>
       </c>
       <c r="R105" t="n">
-        <v>7017493</v>
+        <v>7017386</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13259,6 +13199,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -13288,13 +13233,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499525</v>
+        <v>135499529</v>
       </c>
       <c r="B106" t="n">
         <v>99082</v>
@@ -13326,7 +13271,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -13337,10 +13282,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490804</v>
+        <v>490807</v>
       </c>
       <c r="R106" t="n">
-        <v>7017492</v>
+        <v>7017431</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13404,13 +13349,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499526</v>
+        <v>135499530</v>
       </c>
       <c r="B107" t="n">
         <v>99082</v>
@@ -13442,7 +13387,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13453,10 +13398,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490740</v>
+        <v>490932</v>
       </c>
       <c r="R107" t="n">
-        <v>7017423</v>
+        <v>7017369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13520,16 +13465,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499527</v>
+        <v>135499597</v>
       </c>
       <c r="B108" t="n">
-        <v>99082</v>
+        <v>98327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13537,21 +13482,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13569,10 +13514,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490732</v>
+        <v>490969</v>
       </c>
       <c r="R108" t="n">
-        <v>7017370</v>
+        <v>7017431</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13636,16 +13581,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499528</v>
+        <v>135499598</v>
       </c>
       <c r="B109" t="n">
-        <v>99082</v>
+        <v>98327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13653,21 +13598,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13685,10 +13630,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490867</v>
+        <v>490840</v>
       </c>
       <c r="R109" t="n">
-        <v>7017386</v>
+        <v>7017457</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13723,11 +13668,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13757,16 +13697,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499529</v>
+        <v>135499599</v>
       </c>
       <c r="B110" t="n">
-        <v>99082</v>
+        <v>98327</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13774,21 +13714,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13806,10 +13746,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490807</v>
+        <v>490831</v>
       </c>
       <c r="R110" t="n">
-        <v>7017431</v>
+        <v>7017486</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13873,16 +13813,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499530</v>
+        <v>135499600</v>
       </c>
       <c r="B111" t="n">
-        <v>99082</v>
+        <v>98327</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13890,28 +13830,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13922,10 +13862,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490932</v>
+        <v>490797</v>
       </c>
       <c r="R111" t="n">
-        <v>7017369</v>
+        <v>7017497</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13989,13 +13929,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499597</v>
+        <v>135499601</v>
       </c>
       <c r="B112" t="n">
         <v>98327</v>
@@ -14038,10 +13978,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490969</v>
+        <v>490797</v>
       </c>
       <c r="R112" t="n">
-        <v>7017431</v>
+        <v>7017511</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14105,13 +14045,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499598</v>
+        <v>135499602</v>
       </c>
       <c r="B113" t="n">
         <v>98327</v>
@@ -14154,10 +14094,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490840</v>
+        <v>490737</v>
       </c>
       <c r="R113" t="n">
-        <v>7017457</v>
+        <v>7017473</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14221,16 +14161,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499599</v>
+        <v>135499515</v>
       </c>
       <c r="B114" t="n">
-        <v>98327</v>
+        <v>102022</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14238,21 +14178,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223358</v>
+        <v>223366</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14270,10 +14210,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490831</v>
+        <v>490788</v>
       </c>
       <c r="R114" t="n">
-        <v>7017486</v>
+        <v>7017450</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14337,16 +14277,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499600</v>
+        <v>135499532</v>
       </c>
       <c r="B115" t="n">
-        <v>98327</v>
+        <v>101375</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14354,21 +14294,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14386,10 +14326,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490797</v>
+        <v>490889</v>
       </c>
       <c r="R115" t="n">
-        <v>7017497</v>
+        <v>7017459</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14453,16 +14393,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499601</v>
+        <v>135499533</v>
       </c>
       <c r="B116" t="n">
-        <v>98327</v>
+        <v>101375</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14470,21 +14410,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14502,10 +14442,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490797</v>
+        <v>490743</v>
       </c>
       <c r="R116" t="n">
-        <v>7017511</v>
+        <v>7017495</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14569,16 +14509,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499602</v>
+        <v>135499534</v>
       </c>
       <c r="B117" t="n">
-        <v>98327</v>
+        <v>101375</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14586,21 +14526,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14621,7 +14561,7 @@
         <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017473</v>
+        <v>7017474</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14685,16 +14625,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499515</v>
+        <v>135499535</v>
       </c>
       <c r="B118" t="n">
-        <v>102022</v>
+        <v>101375</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14702,21 +14642,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>223366</v>
+        <v>224885</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14734,10 +14674,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490788</v>
+        <v>490734</v>
       </c>
       <c r="R118" t="n">
-        <v>7017450</v>
+        <v>7017429</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14801,13 +14741,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499532</v>
+        <v>135499536</v>
       </c>
       <c r="B119" t="n">
         <v>101375</v>
@@ -14850,10 +14790,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490889</v>
+        <v>490780</v>
       </c>
       <c r="R119" t="n">
-        <v>7017459</v>
+        <v>7017405</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14917,13 +14857,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499533</v>
+        <v>135499537</v>
       </c>
       <c r="B120" t="n">
         <v>101375</v>
@@ -14966,10 +14906,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490743</v>
+        <v>490751</v>
       </c>
       <c r="R120" t="n">
-        <v>7017495</v>
+        <v>7017406</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15033,13 +14973,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499537</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499534</v>
+        <v>135499538</v>
       </c>
       <c r="B121" t="n">
         <v>101375</v>
@@ -15082,10 +15022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490737</v>
+        <v>490729</v>
       </c>
       <c r="R121" t="n">
-        <v>7017474</v>
+        <v>7017373</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15149,13 +15089,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499538</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499535</v>
+        <v>135499540</v>
       </c>
       <c r="B122" t="n">
         <v>101375</v>
@@ -15198,10 +15138,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490734</v>
+        <v>490847</v>
       </c>
       <c r="R122" t="n">
-        <v>7017429</v>
+        <v>7017345</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15265,13 +15205,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499540</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499536</v>
+        <v>135499541</v>
       </c>
       <c r="B123" t="n">
         <v>101375</v>
@@ -15314,10 +15254,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490780</v>
+        <v>490856</v>
       </c>
       <c r="R123" t="n">
-        <v>7017405</v>
+        <v>7017358</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15381,13 +15321,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499541</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499537</v>
+        <v>135499542</v>
       </c>
       <c r="B124" t="n">
         <v>101375</v>
@@ -15419,7 +15359,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -15430,10 +15370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490751</v>
+        <v>490840</v>
       </c>
       <c r="R124" t="n">
-        <v>7017406</v>
+        <v>7017433</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15496,470 +15436,6 @@
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>135499538</v>
-      </c>
-      <c r="B125" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q125" t="n">
-        <v>490729</v>
-      </c>
-      <c r="R125" t="n">
-        <v>7017373</v>
-      </c>
-      <c r="S125" t="n">
-        <v>10</v>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="inlineStr"/>
-      <c r="AG125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT125" t="inlineStr"/>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>135499540</v>
-      </c>
-      <c r="B126" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q126" t="n">
-        <v>490847</v>
-      </c>
-      <c r="R126" t="n">
-        <v>7017345</v>
-      </c>
-      <c r="S126" t="n">
-        <v>10</v>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="inlineStr"/>
-      <c r="AG126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT126" t="inlineStr"/>
-      <c r="AW126" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>135499541</v>
-      </c>
-      <c r="B127" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q127" t="n">
-        <v>490856</v>
-      </c>
-      <c r="R127" t="n">
-        <v>7017358</v>
-      </c>
-      <c r="S127" t="n">
-        <v>10</v>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="inlineStr"/>
-      <c r="AG127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT127" t="inlineStr"/>
-      <c r="AW127" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>135499542</v>
-      </c>
-      <c r="B128" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q128" t="n">
-        <v>490840</v>
-      </c>
-      <c r="R128" t="n">
-        <v>7017433</v>
-      </c>
-      <c r="S128" t="n">
-        <v>10</v>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="inlineStr"/>
-      <c r="AG128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT128" t="inlineStr"/>
-      <c r="AW128" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
-      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -16090,10 +15566,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ124"/>
+  <dimension ref="A1:AZ125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499608</v>
+        <v>135499607</v>
       </c>
       <c r="B2" t="n">
         <v>99182</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490867</v>
+        <v>490869</v>
       </c>
       <c r="R2" t="n">
-        <v>7017387</v>
+        <v>7017370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
+          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad snitslad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +790,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+          <t>Kalkrikt fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,58 +812,71 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499608</t>
+          <t>https://artportalen.se/Sighting/135499607</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499603</v>
+        <v>135499608</v>
       </c>
       <c r="B3" t="n">
-        <v>92046</v>
+        <v>99182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490968</v>
+        <v>490867</v>
       </c>
       <c r="R3" t="n">
-        <v>7017430</v>
+        <v>7017387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +913,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,24 +931,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -952,13 +950,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499603</t>
+          <t>https://artportalen.se/Sighting/135499608</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499604</v>
+        <v>135499603</v>
       </c>
       <c r="B4" t="n">
         <v>92046</v>
@@ -1000,10 +998,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490893</v>
+        <v>490968</v>
       </c>
       <c r="R4" t="n">
-        <v>7017459</v>
+        <v>7017430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,7 +1038,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,12 +1068,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,13 +1090,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499604</t>
+          <t>https://artportalen.se/Sighting/135499603</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499605</v>
+        <v>135499604</v>
       </c>
       <c r="B5" t="n">
         <v>92046</v>
@@ -1140,10 +1138,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490741</v>
+        <v>490893</v>
       </c>
       <c r="R5" t="n">
-        <v>7017465</v>
+        <v>7017459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,7 +1178,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1232,13 +1230,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499605</t>
+          <t>https://artportalen.se/Sighting/135499604</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499606</v>
+        <v>135499605</v>
       </c>
       <c r="B6" t="n">
         <v>92046</v>
@@ -1280,10 +1278,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490951</v>
+        <v>490741</v>
       </c>
       <c r="R6" t="n">
-        <v>7017411</v>
+        <v>7017465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1320,7 +1318,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,12 +1348,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1372,16 +1370,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499606</t>
+          <t>https://artportalen.se/Sighting/135499605</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75185503</v>
+        <v>135499606</v>
       </c>
       <c r="B7" t="n">
-        <v>87322</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,34 +1387,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1988</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490758</v>
+        <v>490951</v>
       </c>
       <c r="R7" t="n">
-        <v>7017384</v>
+        <v>7017411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1443,12 +1448,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,73 +1471,90 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185503</t>
+          <t>https://artportalen.se/Sighting/135499606</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135499557</v>
+        <v>75185503</v>
       </c>
       <c r="B8" t="n">
-        <v>96488</v>
+        <v>87322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2812</v>
+        <v>1988</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490738</v>
+        <v>490758</v>
       </c>
       <c r="R8" t="n">
-        <v>7017396</v>
+        <v>7017384</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,12 +1581,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,32 +1599,31 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499557</t>
+          <t>https://artportalen.se/Sighting/75185503</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499558</v>
+        <v>135499557</v>
       </c>
       <c r="B9" t="n">
         <v>96488</v>
@@ -1636,10 +1662,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490991</v>
+        <v>490738</v>
       </c>
       <c r="R9" t="n">
-        <v>7017297</v>
+        <v>7017396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1703,13 +1729,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499558</t>
+          <t>https://artportalen.se/Sighting/135499557</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499560</v>
+        <v>135499558</v>
       </c>
       <c r="B10" t="n">
         <v>96488</v>
@@ -1748,10 +1774,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490966</v>
+        <v>490991</v>
       </c>
       <c r="R10" t="n">
-        <v>7017426</v>
+        <v>7017297</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1801,11 +1827,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1820,13 +1841,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499560</t>
+          <t>https://artportalen.se/Sighting/135499558</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499561</v>
+        <v>135499560</v>
       </c>
       <c r="B11" t="n">
         <v>96488</v>
@@ -1865,10 +1886,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490929</v>
+        <v>490966</v>
       </c>
       <c r="R11" t="n">
-        <v>7017441</v>
+        <v>7017426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1915,7 +1936,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1932,13 +1958,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499561</t>
+          <t>https://artportalen.se/Sighting/135499560</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499562</v>
+        <v>135499561</v>
       </c>
       <c r="B12" t="n">
         <v>96488</v>
@@ -1977,10 +2003,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490910</v>
+        <v>490929</v>
       </c>
       <c r="R12" t="n">
-        <v>7017467</v>
+        <v>7017441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2044,13 +2070,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499562</t>
+          <t>https://artportalen.se/Sighting/135499561</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499563</v>
+        <v>135499562</v>
       </c>
       <c r="B13" t="n">
         <v>96488</v>
@@ -2089,10 +2115,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490878</v>
+        <v>490910</v>
       </c>
       <c r="R13" t="n">
-        <v>7017474</v>
+        <v>7017467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2139,7 +2165,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2156,13 +2182,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499563</t>
+          <t>https://artportalen.se/Sighting/135499562</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499564</v>
+        <v>135499563</v>
       </c>
       <c r="B14" t="n">
         <v>96488</v>
@@ -2201,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490883</v>
+        <v>490878</v>
       </c>
       <c r="R14" t="n">
-        <v>7017462</v>
+        <v>7017474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2251,7 +2277,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2268,13 +2294,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499564</t>
+          <t>https://artportalen.se/Sighting/135499563</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499565</v>
+        <v>135499564</v>
       </c>
       <c r="B15" t="n">
         <v>96488</v>
@@ -2313,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490756</v>
+        <v>490883</v>
       </c>
       <c r="R15" t="n">
-        <v>7017472</v>
+        <v>7017462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2363,7 +2389,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2380,13 +2406,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499565</t>
+          <t>https://artportalen.se/Sighting/135499564</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499566</v>
+        <v>135499565</v>
       </c>
       <c r="B16" t="n">
         <v>96488</v>
@@ -2425,10 +2451,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490790</v>
+        <v>490756</v>
       </c>
       <c r="R16" t="n">
-        <v>7017441</v>
+        <v>7017472</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2492,13 +2518,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499566</t>
+          <t>https://artportalen.se/Sighting/135499565</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499567</v>
+        <v>135499566</v>
       </c>
       <c r="B17" t="n">
         <v>96488</v>
@@ -2537,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490732</v>
+        <v>490790</v>
       </c>
       <c r="R17" t="n">
-        <v>7017442</v>
+        <v>7017441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2587,7 +2613,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2604,13 +2630,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499567</t>
+          <t>https://artportalen.se/Sighting/135499566</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499568</v>
+        <v>135499567</v>
       </c>
       <c r="B18" t="n">
         <v>96488</v>
@@ -2649,10 +2675,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490781</v>
+        <v>490732</v>
       </c>
       <c r="R18" t="n">
-        <v>7017407</v>
+        <v>7017442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2699,7 +2725,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,13 +2742,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499568</t>
+          <t>https://artportalen.se/Sighting/135499567</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499569</v>
+        <v>135499568</v>
       </c>
       <c r="B19" t="n">
         <v>96488</v>
@@ -2761,10 +2787,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490731</v>
+        <v>490781</v>
       </c>
       <c r="R19" t="n">
-        <v>7017371</v>
+        <v>7017407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,11 +2840,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2833,13 +2854,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499569</t>
+          <t>https://artportalen.se/Sighting/135499568</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499570</v>
+        <v>135499569</v>
       </c>
       <c r="B20" t="n">
         <v>96488</v>
@@ -2878,10 +2899,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490854</v>
+        <v>490731</v>
       </c>
       <c r="R20" t="n">
-        <v>7017345</v>
+        <v>7017371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,6 +2952,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2945,13 +2971,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499570</t>
+          <t>https://artportalen.se/Sighting/135499569</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499571</v>
+        <v>135499570</v>
       </c>
       <c r="B21" t="n">
         <v>96488</v>
@@ -2990,10 +3016,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490878</v>
+        <v>490854</v>
       </c>
       <c r="R21" t="n">
-        <v>7017366</v>
+        <v>7017345</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3028,11 +3054,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3062,13 +3083,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499571</t>
+          <t>https://artportalen.se/Sighting/135499570</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499572</v>
+        <v>135499571</v>
       </c>
       <c r="B22" t="n">
         <v>96488</v>
@@ -3107,10 +3128,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490867</v>
+        <v>490878</v>
       </c>
       <c r="R22" t="n">
-        <v>7017386</v>
+        <v>7017366</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,6 +3166,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3174,13 +3200,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499572</t>
+          <t>https://artportalen.se/Sighting/135499571</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499573</v>
+        <v>135499572</v>
       </c>
       <c r="B23" t="n">
         <v>96488</v>
@@ -3219,10 +3245,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490840</v>
+        <v>490867</v>
       </c>
       <c r="R23" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3286,13 +3312,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499573</t>
+          <t>https://artportalen.se/Sighting/135499572</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499574</v>
+        <v>135499573</v>
       </c>
       <c r="B24" t="n">
         <v>96488</v>
@@ -3331,10 +3357,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490844</v>
+        <v>490840</v>
       </c>
       <c r="R24" t="n">
-        <v>7017436</v>
+        <v>7017433</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3398,13 +3424,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499574</t>
+          <t>https://artportalen.se/Sighting/135499573</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499575</v>
+        <v>135499574</v>
       </c>
       <c r="B25" t="n">
         <v>96488</v>
@@ -3443,10 +3469,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490872</v>
+        <v>490844</v>
       </c>
       <c r="R25" t="n">
-        <v>7017426</v>
+        <v>7017436</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3510,13 +3536,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499575</t>
+          <t>https://artportalen.se/Sighting/135499574</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499576</v>
+        <v>135499575</v>
       </c>
       <c r="B26" t="n">
         <v>96488</v>
@@ -3555,10 +3581,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490917</v>
+        <v>490872</v>
       </c>
       <c r="R26" t="n">
-        <v>7017402</v>
+        <v>7017426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3622,13 +3648,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499576</t>
+          <t>https://artportalen.se/Sighting/135499575</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499577</v>
+        <v>135499576</v>
       </c>
       <c r="B27" t="n">
         <v>96488</v>
@@ -3667,10 +3693,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490931</v>
+        <v>490917</v>
       </c>
       <c r="R27" t="n">
-        <v>7017371</v>
+        <v>7017402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3720,11 +3746,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3739,13 +3760,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499577</t>
+          <t>https://artportalen.se/Sighting/135499576</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499578</v>
+        <v>135499577</v>
       </c>
       <c r="B28" t="n">
         <v>96488</v>
@@ -3784,10 +3805,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490951</v>
+        <v>490931</v>
       </c>
       <c r="R28" t="n">
-        <v>7017390</v>
+        <v>7017371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3856,13 +3877,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499578</t>
+          <t>https://artportalen.se/Sighting/135499577</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499579</v>
+        <v>135499578</v>
       </c>
       <c r="B29" t="n">
         <v>96488</v>
@@ -3901,10 +3922,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490976</v>
+        <v>490951</v>
       </c>
       <c r="R29" t="n">
-        <v>7017311</v>
+        <v>7017390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3973,16 +3994,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499579</t>
+          <t>https://artportalen.se/Sighting/135499578</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>91488964</v>
+        <v>135499579</v>
       </c>
       <c r="B30" t="n">
-        <v>92632</v>
+        <v>96488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3990,37 +4011,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>2812</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490939</v>
+        <v>490976</v>
       </c>
       <c r="R30" t="n">
-        <v>7017412</v>
+        <v>7017311</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4044,12 +4069,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4058,59 +4083,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91488964</t>
+          <t>https://artportalen.se/Sighting/135499579</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>75185505</v>
+        <v>91488964</v>
       </c>
       <c r="B31" t="n">
-        <v>89156</v>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4412</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4120,13 +4152,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490781</v>
+        <v>490939</v>
       </c>
       <c r="R31" t="n">
-        <v>7017384</v>
+        <v>7017412</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4164,19 +4196,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4186,54 +4217,51 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185505</t>
+          <t>https://artportalen.se/Sighting/91488964</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135499609</v>
+        <v>75185505</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>89156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490849</v>
+        <v>490781</v>
       </c>
       <c r="R32" t="n">
-        <v>7017392</v>
+        <v>7017384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4260,17 +4288,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4283,52 +4306,31 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499609</t>
+          <t>https://artportalen.se/Sighting/75185505</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499610</v>
+        <v>135499609</v>
       </c>
       <c r="B33" t="n">
         <v>79441</v>
@@ -4366,10 +4368,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490859</v>
+        <v>490849</v>
       </c>
       <c r="R33" t="n">
-        <v>7017416</v>
+        <v>7017392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4404,6 +4406,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4431,12 +4438,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4453,67 +4460,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499610</t>
+          <t>https://artportalen.se/Sighting/135499609</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499531</v>
+        <v>135499610</v>
       </c>
       <c r="B34" t="n">
-        <v>58094</v>
+        <v>79441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100090</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490781</v>
+        <v>490859</v>
       </c>
       <c r="R34" t="n">
-        <v>7017369</v>
+        <v>7017416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4548,23 +4542,39 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Synobservation av en individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4581,16 +4591,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499531</t>
+          <t>https://artportalen.se/Sighting/135499610</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499510</v>
+        <v>135499531</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>58094</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4598,16 +4608,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100090</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4615,12 +4625,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4634,10 +4648,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490891</v>
+        <v>490781</v>
       </c>
       <c r="R35" t="n">
-        <v>7017451</v>
+        <v>7017369</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4674,7 +4688,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Synobservation av en individ med lockläte.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4688,27 +4702,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4725,16 +4719,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499510</t>
+          <t>https://artportalen.se/Sighting/135499531</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499511</v>
+        <v>135499549</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>58236</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,29 +4736,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102980</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4778,10 +4776,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490785</v>
+        <v>490804</v>
       </c>
       <c r="R36" t="n">
-        <v>7017521</v>
+        <v>7017502</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4818,7 +4816,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Minst 1 överflygande med sång.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4833,26 +4831,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4869,33 +4847,33 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499511</t>
+          <t>https://artportalen.se/Sighting/135499549</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499512</v>
+        <v>135499596</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>58239</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4903,29 +4881,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490783</v>
+        <v>490875</v>
       </c>
       <c r="R37" t="n">
-        <v>7017360</v>
+        <v>7017470</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4962,7 +4940,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4977,31 +4955,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5018,43 +4971,43 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499512</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499596</v>
+        <v>135499513</v>
       </c>
       <c r="B38" t="n">
-        <v>58239</v>
+        <v>58141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102981</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5064,17 +5017,21 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490875</v>
+        <v>490763</v>
       </c>
       <c r="R38" t="n">
-        <v>7017470</v>
+        <v>7017499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5111,7 +5068,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5125,7 +5082,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5142,13 +5104,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499513</v>
+        <v>135499514</v>
       </c>
       <c r="B39" t="n">
         <v>58141</v>
@@ -5178,7 +5140,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5199,10 +5161,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490763</v>
+        <v>490875</v>
       </c>
       <c r="R39" t="n">
-        <v>7017499</v>
+        <v>7017397</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5239,7 +5201,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5253,12 +5215,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5275,67 +5237,59 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499514</v>
+        <v>135499611</v>
       </c>
       <c r="B40" t="n">
-        <v>58141</v>
+        <v>99193</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490875</v>
+        <v>490821</v>
       </c>
       <c r="R40" t="n">
-        <v>7017397</v>
+        <v>7017504</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5372,7 +5326,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5381,17 +5335,13 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5408,13 +5358,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499611</v>
+        <v>135499612</v>
       </c>
       <c r="B41" t="n">
         <v>99193</v>
@@ -5446,7 +5396,7 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5457,10 +5407,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490821</v>
+        <v>490848</v>
       </c>
       <c r="R41" t="n">
-        <v>7017504</v>
+        <v>7017375</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5495,11 +5445,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5529,13 +5474,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499612</v>
+        <v>135499613</v>
       </c>
       <c r="B42" t="n">
         <v>99193</v>
@@ -5567,7 +5512,7 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5578,10 +5523,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490848</v>
+        <v>490878</v>
       </c>
       <c r="R42" t="n">
-        <v>7017375</v>
+        <v>7017368</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5616,6 +5561,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5645,13 +5595,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499613</v>
+        <v>135499614</v>
       </c>
       <c r="B43" t="n">
         <v>99193</v>
@@ -5683,7 +5633,7 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5694,10 +5644,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490878</v>
+        <v>490867</v>
       </c>
       <c r="R43" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5766,13 +5716,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499614</v>
+        <v>135499615</v>
       </c>
       <c r="B44" t="n">
         <v>99193</v>
@@ -5804,7 +5754,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5815,7 +5765,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490867</v>
+        <v>490860</v>
       </c>
       <c r="R44" t="n">
         <v>7017386</v>
@@ -5887,16 +5837,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499615</v>
+        <v>135499509</v>
       </c>
       <c r="B45" t="n">
-        <v>99193</v>
+        <v>99300</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5904,28 +5854,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -5936,10 +5886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490860</v>
+        <v>490880</v>
       </c>
       <c r="R45" t="n">
-        <v>7017386</v>
+        <v>7017365</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5976,7 +5926,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Flertalet plantor.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5994,6 +5944,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
@@ -6008,16 +5963,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499509</v>
+        <v>135499620</v>
       </c>
       <c r="B46" t="n">
-        <v>99300</v>
+        <v>108294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6025,28 +5980,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6057,10 +6012,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490880</v>
+        <v>490853</v>
       </c>
       <c r="R46" t="n">
-        <v>7017365</v>
+        <v>7017483</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6095,11 +6050,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Flertalet plantor.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6115,11 +6065,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -6134,13 +6079,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499620</v>
+        <v>135499621</v>
       </c>
       <c r="B47" t="n">
         <v>108294</v>
@@ -6172,7 +6117,7 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6183,10 +6128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490853</v>
+        <v>490837</v>
       </c>
       <c r="R47" t="n">
-        <v>7017483</v>
+        <v>7017379</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,13 +6195,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499621</v>
+        <v>135499623</v>
       </c>
       <c r="B48" t="n">
         <v>108294</v>
@@ -6299,10 +6244,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490837</v>
+        <v>490848</v>
       </c>
       <c r="R48" t="n">
-        <v>7017379</v>
+        <v>7017376</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6366,13 +6311,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499623</v>
+        <v>135499624</v>
       </c>
       <c r="B49" t="n">
         <v>108294</v>
@@ -6415,10 +6360,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490848</v>
+        <v>490861</v>
       </c>
       <c r="R49" t="n">
-        <v>7017376</v>
+        <v>7017386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6482,13 +6427,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499624</v>
+        <v>135499625</v>
       </c>
       <c r="B50" t="n">
         <v>108294</v>
@@ -6520,7 +6465,7 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -6531,10 +6476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490861</v>
+        <v>490821</v>
       </c>
       <c r="R50" t="n">
-        <v>7017386</v>
+        <v>7017394</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6598,13 +6543,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499625</v>
+        <v>135499626</v>
       </c>
       <c r="B51" t="n">
         <v>108294</v>
@@ -6647,10 +6592,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490821</v>
+        <v>490841</v>
       </c>
       <c r="R51" t="n">
-        <v>7017394</v>
+        <v>7017433</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6714,16 +6659,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499626</v>
+        <v>135499550</v>
       </c>
       <c r="B52" t="n">
-        <v>108294</v>
+        <v>108364</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6731,28 +6676,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6763,10 +6708,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490841</v>
+        <v>490929</v>
       </c>
       <c r="R52" t="n">
-        <v>7017433</v>
+        <v>7017429</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6830,13 +6775,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499550</v>
+        <v>135499551</v>
       </c>
       <c r="B53" t="n">
         <v>108364</v>
@@ -6879,10 +6824,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490929</v>
+        <v>490853</v>
       </c>
       <c r="R53" t="n">
-        <v>7017429</v>
+        <v>7017480</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6917,6 +6862,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6946,13 +6896,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499551</v>
+        <v>135499552</v>
       </c>
       <c r="B54" t="n">
         <v>108364</v>
@@ -6995,7 +6945,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490853</v>
+        <v>490867</v>
       </c>
       <c r="R54" t="n">
         <v>7017480</v>
@@ -7033,11 +6983,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7067,13 +7012,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499552</v>
+        <v>135499553</v>
       </c>
       <c r="B55" t="n">
         <v>108364</v>
@@ -7116,10 +7061,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490867</v>
+        <v>490841</v>
       </c>
       <c r="R55" t="n">
-        <v>7017480</v>
+        <v>7017457</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7183,13 +7128,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499553</v>
+        <v>135499554</v>
       </c>
       <c r="B56" t="n">
         <v>108364</v>
@@ -7232,10 +7177,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490841</v>
+        <v>490737</v>
       </c>
       <c r="R56" t="n">
-        <v>7017457</v>
+        <v>7017474</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7299,13 +7244,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499554</v>
+        <v>135499555</v>
       </c>
       <c r="B57" t="n">
         <v>108364</v>
@@ -7348,10 +7293,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490737</v>
+        <v>490873</v>
       </c>
       <c r="R57" t="n">
-        <v>7017474</v>
+        <v>7017368</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7415,13 +7360,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499555</v>
+        <v>135499556</v>
       </c>
       <c r="B58" t="n">
         <v>108364</v>
@@ -7464,10 +7409,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490873</v>
+        <v>490863</v>
       </c>
       <c r="R58" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7517,6 +7462,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
@@ -7531,16 +7481,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499556</v>
+        <v>135499544</v>
       </c>
       <c r="B59" t="n">
-        <v>108364</v>
+        <v>111244</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7548,28 +7498,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -7580,10 +7530,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490863</v>
+        <v>490844</v>
       </c>
       <c r="R59" t="n">
-        <v>7017386</v>
+        <v>7017468</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7633,11 +7583,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7652,13 +7597,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499544</v>
+        <v>135499546</v>
       </c>
       <c r="B60" t="n">
         <v>111244</v>
@@ -7701,10 +7646,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490844</v>
+        <v>490780</v>
       </c>
       <c r="R60" t="n">
-        <v>7017468</v>
+        <v>7017405</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7768,13 +7713,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499546</v>
+        <v>135499547</v>
       </c>
       <c r="B61" t="n">
         <v>111244</v>
@@ -7806,7 +7751,7 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7817,10 +7762,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490780</v>
+        <v>490858</v>
       </c>
       <c r="R61" t="n">
-        <v>7017405</v>
+        <v>7017416</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7884,13 +7829,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499547</v>
+        <v>135499548</v>
       </c>
       <c r="B62" t="n">
         <v>111244</v>
@@ -7922,7 +7867,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7933,10 +7878,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490858</v>
+        <v>490964</v>
       </c>
       <c r="R62" t="n">
-        <v>7017416</v>
+        <v>7017356</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7986,6 +7931,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -8000,16 +7950,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499548</v>
+        <v>135499617</v>
       </c>
       <c r="B63" t="n">
-        <v>111244</v>
+        <v>110240</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8017,28 +7967,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220240</v>
+        <v>220294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -8049,10 +7999,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490964</v>
+        <v>490864</v>
       </c>
       <c r="R63" t="n">
-        <v>7017356</v>
+        <v>7017486</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8087,6 +8037,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8102,11 +8057,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8121,45 +8071,53 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499617</v>
+        <v>135499580</v>
       </c>
       <c r="B64" t="n">
-        <v>110240</v>
+        <v>99276</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220294</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -8170,10 +8128,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490864</v>
+        <v>490975</v>
       </c>
       <c r="R64" t="n">
-        <v>7017486</v>
+        <v>7017304</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8210,7 +8168,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8228,6 +8186,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
@@ -8242,13 +8205,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499580</v>
+        <v>135499581</v>
       </c>
       <c r="B65" t="n">
         <v>99276</v>
@@ -8278,7 +8241,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8299,10 +8262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490975</v>
+        <v>490951</v>
       </c>
       <c r="R65" t="n">
-        <v>7017304</v>
+        <v>7017428</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8339,7 +8302,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8357,11 +8320,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
@@ -8376,13 +8334,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499581</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499583</v>
+        <v>135499582</v>
       </c>
       <c r="B66" t="n">
         <v>99276</v>
@@ -8412,7 +8370,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8433,10 +8391,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490768</v>
+        <v>490884</v>
       </c>
       <c r="R66" t="n">
-        <v>7017376</v>
+        <v>7017471</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8473,7 +8431,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8488,12 +8446,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8510,13 +8463,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499582</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499584</v>
+        <v>135499583</v>
       </c>
       <c r="B67" t="n">
         <v>99276</v>
@@ -8546,7 +8499,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8567,10 +8520,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490839</v>
+        <v>490768</v>
       </c>
       <c r="R67" t="n">
-        <v>7017351</v>
+        <v>7017376</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8607,7 +8560,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8622,7 +8575,12 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8639,13 +8597,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499585</v>
+        <v>135499584</v>
       </c>
       <c r="B68" t="n">
         <v>99276</v>
@@ -8675,7 +8633,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8696,10 +8654,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490845</v>
+        <v>490839</v>
       </c>
       <c r="R68" t="n">
-        <v>7017392</v>
+        <v>7017351</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8736,7 +8694,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8768,13 +8726,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499586</v>
+        <v>135499585</v>
       </c>
       <c r="B69" t="n">
         <v>99276</v>
@@ -8804,7 +8762,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8825,10 +8783,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490812</v>
+        <v>490845</v>
       </c>
       <c r="R69" t="n">
-        <v>7017401</v>
+        <v>7017392</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8865,7 +8823,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8880,12 +8838,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8902,13 +8855,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499588</v>
+        <v>135499586</v>
       </c>
       <c r="B70" t="n">
         <v>99276</v>
@@ -8938,7 +8891,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8959,10 +8912,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490843</v>
+        <v>490812</v>
       </c>
       <c r="R70" t="n">
-        <v>7017436</v>
+        <v>7017401</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8999,7 +8952,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9036,13 +8989,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499589</v>
+        <v>135499588</v>
       </c>
       <c r="B71" t="n">
         <v>99276</v>
@@ -9072,7 +9025,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9093,10 +9046,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490967</v>
+        <v>490843</v>
       </c>
       <c r="R71" t="n">
-        <v>7017335</v>
+        <v>7017436</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9133,7 +9086,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9170,13 +9123,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499590</v>
+        <v>135499589</v>
       </c>
       <c r="B72" t="n">
         <v>99276</v>
@@ -9206,7 +9159,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9227,10 +9180,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490979</v>
+        <v>490967</v>
       </c>
       <c r="R72" t="n">
-        <v>7017360</v>
+        <v>7017335</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9267,7 +9220,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9304,13 +9257,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499591</v>
+        <v>135499590</v>
       </c>
       <c r="B73" t="n">
         <v>99276</v>
@@ -9340,7 +9293,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9361,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490973</v>
+        <v>490979</v>
       </c>
       <c r="R73" t="n">
-        <v>7017399</v>
+        <v>7017360</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9401,7 +9354,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9438,13 +9391,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499592</v>
+        <v>135499591</v>
       </c>
       <c r="B74" t="n">
         <v>99276</v>
@@ -9474,7 +9427,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9495,10 +9448,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490951</v>
+        <v>490973</v>
       </c>
       <c r="R74" t="n">
-        <v>7017408</v>
+        <v>7017399</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9535,7 +9488,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9572,13 +9525,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499593</v>
+        <v>135499592</v>
       </c>
       <c r="B75" t="n">
         <v>99276</v>
@@ -9608,7 +9561,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9632,7 +9585,7 @@
         <v>490951</v>
       </c>
       <c r="R75" t="n">
-        <v>7017396</v>
+        <v>7017408</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9669,7 +9622,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9706,13 +9659,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499594</v>
+        <v>135499593</v>
       </c>
       <c r="B76" t="n">
         <v>99276</v>
@@ -9742,7 +9695,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9763,10 +9716,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490957</v>
+        <v>490951</v>
       </c>
       <c r="R76" t="n">
-        <v>7017386</v>
+        <v>7017396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9803,7 +9756,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9840,43 +9793,55 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499519</v>
+        <v>135499594</v>
       </c>
       <c r="B77" t="n">
-        <v>98138</v>
+        <v>99276</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9885,10 +9850,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490752</v>
+        <v>490957</v>
       </c>
       <c r="R77" t="n">
-        <v>7017499</v>
+        <v>7017386</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9925,7 +9890,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9943,6 +9908,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
@@ -9957,16 +9927,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499516</v>
+        <v>135499519</v>
       </c>
       <c r="B78" t="n">
-        <v>99298</v>
+        <v>98138</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9974,30 +9944,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -10006,10 +9972,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490844</v>
+        <v>490752</v>
       </c>
       <c r="R78" t="n">
-        <v>7017394</v>
+        <v>7017499</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10044,6 +10010,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10073,13 +10044,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499517</v>
+        <v>135499516</v>
       </c>
       <c r="B79" t="n">
         <v>99298</v>
@@ -10122,10 +10093,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490814</v>
+        <v>490844</v>
       </c>
       <c r="R79" t="n">
-        <v>7017404</v>
+        <v>7017394</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10189,16 +10160,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499627</v>
+        <v>135499517</v>
       </c>
       <c r="B80" t="n">
-        <v>101485</v>
+        <v>99298</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10206,28 +10177,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10238,10 +10209,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490803</v>
+        <v>490814</v>
       </c>
       <c r="R80" t="n">
-        <v>7017492</v>
+        <v>7017404</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10305,13 +10276,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499628</v>
+        <v>135499627</v>
       </c>
       <c r="B81" t="n">
         <v>101485</v>
@@ -10354,10 +10325,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490792</v>
+        <v>490803</v>
       </c>
       <c r="R81" t="n">
-        <v>7017441</v>
+        <v>7017492</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10421,13 +10392,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499629</v>
+        <v>135499628</v>
       </c>
       <c r="B82" t="n">
         <v>101485</v>
@@ -10470,7 +10441,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490764</v>
+        <v>490792</v>
       </c>
       <c r="R82" t="n">
         <v>7017441</v>
@@ -10537,13 +10508,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499630</v>
+        <v>135499629</v>
       </c>
       <c r="B83" t="n">
         <v>101485</v>
@@ -10586,10 +10557,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490798</v>
+        <v>490764</v>
       </c>
       <c r="R83" t="n">
-        <v>7017366</v>
+        <v>7017441</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10653,13 +10624,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499631</v>
+        <v>135499630</v>
       </c>
       <c r="B84" t="n">
         <v>101485</v>
@@ -10702,10 +10673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490816</v>
+        <v>490798</v>
       </c>
       <c r="R84" t="n">
-        <v>7017378</v>
+        <v>7017366</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10769,13 +10740,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499632</v>
+        <v>135499631</v>
       </c>
       <c r="B85" t="n">
         <v>101485</v>
@@ -10818,10 +10789,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490796</v>
+        <v>490816</v>
       </c>
       <c r="R85" t="n">
-        <v>7017382</v>
+        <v>7017378</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10885,13 +10856,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499633</v>
+        <v>135499632</v>
       </c>
       <c r="B86" t="n">
         <v>101485</v>
@@ -10934,10 +10905,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490782</v>
+        <v>490796</v>
       </c>
       <c r="R86" t="n">
-        <v>7017407</v>
+        <v>7017382</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11001,13 +10972,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499634</v>
+        <v>135499633</v>
       </c>
       <c r="B87" t="n">
         <v>101485</v>
@@ -11050,10 +11021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490730</v>
+        <v>490782</v>
       </c>
       <c r="R87" t="n">
-        <v>7017371</v>
+        <v>7017407</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11117,13 +11088,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499635</v>
+        <v>135499634</v>
       </c>
       <c r="B88" t="n">
         <v>101485</v>
@@ -11166,10 +11137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490827</v>
+        <v>490730</v>
       </c>
       <c r="R88" t="n">
-        <v>7017356</v>
+        <v>7017371</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11233,13 +11204,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499636</v>
+        <v>135499635</v>
       </c>
       <c r="B89" t="n">
         <v>101485</v>
@@ -11282,10 +11253,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490844</v>
+        <v>490827</v>
       </c>
       <c r="R89" t="n">
-        <v>7017345</v>
+        <v>7017356</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11349,13 +11320,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499637</v>
+        <v>135499636</v>
       </c>
       <c r="B90" t="n">
         <v>101485</v>
@@ -11398,10 +11369,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490852</v>
+        <v>490844</v>
       </c>
       <c r="R90" t="n">
-        <v>7017373</v>
+        <v>7017345</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11448,7 +11419,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11465,13 +11436,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499638</v>
+        <v>135499637</v>
       </c>
       <c r="B91" t="n">
         <v>101485</v>
@@ -11514,10 +11485,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490882</v>
+        <v>490852</v>
       </c>
       <c r="R91" t="n">
-        <v>7017368</v>
+        <v>7017373</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11581,13 +11552,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499639</v>
+        <v>135499638</v>
       </c>
       <c r="B92" t="n">
         <v>101485</v>
@@ -11630,10 +11601,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490865</v>
+        <v>490882</v>
       </c>
       <c r="R92" t="n">
-        <v>7017386</v>
+        <v>7017368</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11680,7 +11651,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11697,13 +11668,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499640</v>
+        <v>135499639</v>
       </c>
       <c r="B93" t="n">
         <v>101485</v>
@@ -11746,10 +11717,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490840</v>
+        <v>490865</v>
       </c>
       <c r="R93" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11813,13 +11784,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499641</v>
+        <v>135499640</v>
       </c>
       <c r="B94" t="n">
         <v>101485</v>
@@ -11862,10 +11833,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490880</v>
+        <v>490840</v>
       </c>
       <c r="R94" t="n">
-        <v>7017422</v>
+        <v>7017433</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11929,16 +11900,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499618</v>
+        <v>135499641</v>
       </c>
       <c r="B95" t="n">
-        <v>98292</v>
+        <v>101485</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11946,21 +11917,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11978,10 +11949,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490791</v>
+        <v>490880</v>
       </c>
       <c r="R95" t="n">
-        <v>7017443</v>
+        <v>7017422</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12016,11 +11987,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -12050,13 +12016,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499619</v>
+        <v>135499618</v>
       </c>
       <c r="B96" t="n">
         <v>98292</v>
@@ -12084,16 +12050,8 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12107,10 +12065,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490868</v>
+        <v>490791</v>
       </c>
       <c r="R96" t="n">
-        <v>7017387</v>
+        <v>7017443</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12147,7 +12105,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+          <t>Relativt rikligt i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12165,11 +12123,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
@@ -12184,16 +12137,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499520</v>
+        <v>135499619</v>
       </c>
       <c r="B97" t="n">
-        <v>99082</v>
+        <v>98292</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12201,25 +12154,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12233,10 +12194,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490757</v>
+        <v>490868</v>
       </c>
       <c r="R97" t="n">
-        <v>7017472</v>
+        <v>7017387</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12271,6 +12232,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12286,6 +12252,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
@@ -12300,13 +12271,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499521</v>
+        <v>135499520</v>
       </c>
       <c r="B98" t="n">
         <v>99082</v>
@@ -12349,10 +12320,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490966</v>
+        <v>490757</v>
       </c>
       <c r="R98" t="n">
-        <v>7017430</v>
+        <v>7017472</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12416,13 +12387,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499522</v>
+        <v>135499521</v>
       </c>
       <c r="B99" t="n">
         <v>99082</v>
@@ -12465,10 +12436,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490920</v>
+        <v>490966</v>
       </c>
       <c r="R99" t="n">
-        <v>7017445</v>
+        <v>7017430</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12532,13 +12503,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499523</v>
+        <v>135499522</v>
       </c>
       <c r="B100" t="n">
         <v>99082</v>
@@ -12581,10 +12552,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490912</v>
+        <v>490920</v>
       </c>
       <c r="R100" t="n">
-        <v>7017466</v>
+        <v>7017445</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12648,13 +12619,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499524</v>
+        <v>135499523</v>
       </c>
       <c r="B101" t="n">
         <v>99082</v>
@@ -12697,10 +12668,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490858</v>
+        <v>490912</v>
       </c>
       <c r="R101" t="n">
-        <v>7017493</v>
+        <v>7017466</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12764,13 +12735,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499525</v>
+        <v>135499524</v>
       </c>
       <c r="B102" t="n">
         <v>99082</v>
@@ -12802,7 +12773,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12813,10 +12784,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490804</v>
+        <v>490858</v>
       </c>
       <c r="R102" t="n">
-        <v>7017492</v>
+        <v>7017493</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12880,13 +12851,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499526</v>
+        <v>135499525</v>
       </c>
       <c r="B103" t="n">
         <v>99082</v>
@@ -12918,7 +12889,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12929,10 +12900,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490740</v>
+        <v>490804</v>
       </c>
       <c r="R103" t="n">
-        <v>7017423</v>
+        <v>7017492</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12996,13 +12967,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499527</v>
+        <v>135499526</v>
       </c>
       <c r="B104" t="n">
         <v>99082</v>
@@ -13045,10 +13016,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490732</v>
+        <v>490740</v>
       </c>
       <c r="R104" t="n">
-        <v>7017370</v>
+        <v>7017423</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13112,13 +13083,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499528</v>
+        <v>135499527</v>
       </c>
       <c r="B105" t="n">
         <v>99082</v>
@@ -13161,10 +13132,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490867</v>
+        <v>490732</v>
       </c>
       <c r="R105" t="n">
-        <v>7017386</v>
+        <v>7017370</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13199,11 +13170,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -13233,13 +13199,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499529</v>
+        <v>135499528</v>
       </c>
       <c r="B106" t="n">
         <v>99082</v>
@@ -13282,10 +13248,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490807</v>
+        <v>490867</v>
       </c>
       <c r="R106" t="n">
-        <v>7017431</v>
+        <v>7017386</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13320,6 +13286,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -13349,13 +13320,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499530</v>
+        <v>135499529</v>
       </c>
       <c r="B107" t="n">
         <v>99082</v>
@@ -13387,7 +13358,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13398,10 +13369,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490932</v>
+        <v>490807</v>
       </c>
       <c r="R107" t="n">
-        <v>7017369</v>
+        <v>7017431</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13465,16 +13436,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499597</v>
+        <v>135499530</v>
       </c>
       <c r="B108" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13482,28 +13453,28 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -13514,10 +13485,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490969</v>
+        <v>490932</v>
       </c>
       <c r="R108" t="n">
-        <v>7017431</v>
+        <v>7017369</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13581,13 +13552,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499598</v>
+        <v>135499597</v>
       </c>
       <c r="B109" t="n">
         <v>98327</v>
@@ -13630,10 +13601,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490840</v>
+        <v>490969</v>
       </c>
       <c r="R109" t="n">
-        <v>7017457</v>
+        <v>7017431</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13697,13 +13668,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499599</v>
+        <v>135499598</v>
       </c>
       <c r="B110" t="n">
         <v>98327</v>
@@ -13746,10 +13717,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490831</v>
+        <v>490840</v>
       </c>
       <c r="R110" t="n">
-        <v>7017486</v>
+        <v>7017457</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13813,13 +13784,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499600</v>
+        <v>135499599</v>
       </c>
       <c r="B111" t="n">
         <v>98327</v>
@@ -13862,10 +13833,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490797</v>
+        <v>490831</v>
       </c>
       <c r="R111" t="n">
-        <v>7017497</v>
+        <v>7017486</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13929,13 +13900,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499601</v>
+        <v>135499600</v>
       </c>
       <c r="B112" t="n">
         <v>98327</v>
@@ -13981,7 +13952,7 @@
         <v>490797</v>
       </c>
       <c r="R112" t="n">
-        <v>7017511</v>
+        <v>7017497</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14045,13 +14016,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499602</v>
+        <v>135499601</v>
       </c>
       <c r="B113" t="n">
         <v>98327</v>
@@ -14094,10 +14065,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490737</v>
+        <v>490797</v>
       </c>
       <c r="R113" t="n">
-        <v>7017473</v>
+        <v>7017511</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14161,16 +14132,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499515</v>
+        <v>135499602</v>
       </c>
       <c r="B114" t="n">
-        <v>102022</v>
+        <v>98327</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14178,21 +14149,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223366</v>
+        <v>223358</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14210,10 +14181,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490788</v>
+        <v>490737</v>
       </c>
       <c r="R114" t="n">
-        <v>7017450</v>
+        <v>7017473</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14277,16 +14248,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499532</v>
+        <v>135499515</v>
       </c>
       <c r="B115" t="n">
-        <v>101375</v>
+        <v>102022</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14294,21 +14265,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>224885</v>
+        <v>223366</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14326,10 +14297,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490889</v>
+        <v>490788</v>
       </c>
       <c r="R115" t="n">
-        <v>7017459</v>
+        <v>7017450</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14393,13 +14364,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499533</v>
+        <v>135499532</v>
       </c>
       <c r="B116" t="n">
         <v>101375</v>
@@ -14442,10 +14413,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490743</v>
+        <v>490889</v>
       </c>
       <c r="R116" t="n">
-        <v>7017495</v>
+        <v>7017459</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14509,13 +14480,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499534</v>
+        <v>135499533</v>
       </c>
       <c r="B117" t="n">
         <v>101375</v>
@@ -14558,10 +14529,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>490737</v>
+        <v>490743</v>
       </c>
       <c r="R117" t="n">
-        <v>7017474</v>
+        <v>7017495</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14625,13 +14596,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499535</v>
+        <v>135499534</v>
       </c>
       <c r="B118" t="n">
         <v>101375</v>
@@ -14674,10 +14645,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490734</v>
+        <v>490737</v>
       </c>
       <c r="R118" t="n">
-        <v>7017429</v>
+        <v>7017474</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14741,13 +14712,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499536</v>
+        <v>135499535</v>
       </c>
       <c r="B119" t="n">
         <v>101375</v>
@@ -14790,10 +14761,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490780</v>
+        <v>490734</v>
       </c>
       <c r="R119" t="n">
-        <v>7017405</v>
+        <v>7017429</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14857,13 +14828,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499537</v>
+        <v>135499536</v>
       </c>
       <c r="B120" t="n">
         <v>101375</v>
@@ -14906,10 +14877,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490751</v>
+        <v>490780</v>
       </c>
       <c r="R120" t="n">
-        <v>7017406</v>
+        <v>7017405</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14973,13 +14944,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499538</v>
+        <v>135499537</v>
       </c>
       <c r="B121" t="n">
         <v>101375</v>
@@ -15022,10 +14993,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490729</v>
+        <v>490751</v>
       </c>
       <c r="R121" t="n">
-        <v>7017373</v>
+        <v>7017406</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15089,13 +15060,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
+          <t>https://artportalen.se/Sighting/135499537</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499540</v>
+        <v>135499538</v>
       </c>
       <c r="B122" t="n">
         <v>101375</v>
@@ -15138,10 +15109,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490847</v>
+        <v>490729</v>
       </c>
       <c r="R122" t="n">
-        <v>7017345</v>
+        <v>7017373</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15205,13 +15176,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
+          <t>https://artportalen.se/Sighting/135499538</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499541</v>
+        <v>135499540</v>
       </c>
       <c r="B123" t="n">
         <v>101375</v>
@@ -15254,10 +15225,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490856</v>
+        <v>490847</v>
       </c>
       <c r="R123" t="n">
-        <v>7017358</v>
+        <v>7017345</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15321,13 +15292,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
+          <t>https://artportalen.se/Sighting/135499540</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499542</v>
+        <v>135499541</v>
       </c>
       <c r="B124" t="n">
         <v>101375</v>
@@ -15359,7 +15330,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -15370,10 +15341,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490840</v>
+        <v>490856</v>
       </c>
       <c r="R124" t="n">
-        <v>7017433</v>
+        <v>7017358</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15436,6 +15407,122 @@
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499541</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>135499542</v>
+      </c>
+      <c r="B125" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>490840</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7017433</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -15566,6 +15653,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ125"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4725,10 +4725,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499549</v>
+        <v>135499510</v>
       </c>
       <c r="B36" t="n">
-        <v>58236</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,33 +4736,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102980</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4776,10 +4772,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490804</v>
+        <v>490891</v>
       </c>
       <c r="R36" t="n">
-        <v>7017502</v>
+        <v>7017451</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4816,7 +4812,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 1 överflygande med sång.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4830,7 +4826,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4847,33 +4863,33 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499549</t>
+          <t>https://artportalen.se/Sighting/135499510</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499596</v>
+        <v>135499511</v>
       </c>
       <c r="B37" t="n">
-        <v>58239</v>
+        <v>57980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102981</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4881,29 +4897,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490875</v>
+        <v>490785</v>
       </c>
       <c r="R37" t="n">
-        <v>7017470</v>
+        <v>7017521</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4940,7 +4956,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4955,6 +4971,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4971,16 +5007,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499511</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499513</v>
+        <v>135499512</v>
       </c>
       <c r="B38" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4988,33 +5024,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5028,10 +5060,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490763</v>
+        <v>490783</v>
       </c>
       <c r="R38" t="n">
-        <v>7017499</v>
+        <v>7017360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5068,7 +5100,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5082,12 +5114,32 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5104,16 +5156,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499512</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499514</v>
+        <v>135499549</v>
       </c>
       <c r="B39" t="n">
-        <v>58141</v>
+        <v>58236</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5121,33 +5173,33 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>102980</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5161,10 +5213,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490875</v>
+        <v>490804</v>
       </c>
       <c r="R39" t="n">
-        <v>7017397</v>
+        <v>7017502</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5201,7 +5253,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+          <t>Minst 1 överflygande med sång.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5216,11 +5268,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5237,48 +5284,52 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499549</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499611</v>
+        <v>135499596</v>
       </c>
       <c r="B40" t="n">
-        <v>99193</v>
+        <v>58239</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>102981</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5286,10 +5337,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490821</v>
+        <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017504</v>
+        <v>7017470</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5326,7 +5377,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5335,7 +5386,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5358,59 +5408,67 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499612</v>
+        <v>135499513</v>
       </c>
       <c r="B41" t="n">
-        <v>99193</v>
+        <v>58141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490848</v>
+        <v>490763</v>
       </c>
       <c r="R41" t="n">
-        <v>7017375</v>
+        <v>7017499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5445,19 +5503,28 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5474,59 +5541,67 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499613</v>
+        <v>135499514</v>
       </c>
       <c r="B42" t="n">
-        <v>99193</v>
+        <v>58141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490878</v>
+        <v>490875</v>
       </c>
       <c r="R42" t="n">
-        <v>7017368</v>
+        <v>7017397</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5563,7 +5638,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5572,13 +5647,17 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5595,13 +5674,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499614</v>
+        <v>135499611</v>
       </c>
       <c r="B43" t="n">
         <v>99193</v>
@@ -5633,7 +5712,7 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5644,10 +5723,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490867</v>
+        <v>490821</v>
       </c>
       <c r="R43" t="n">
-        <v>7017386</v>
+        <v>7017504</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5684,7 +5763,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5716,13 +5795,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499615</v>
+        <v>135499612</v>
       </c>
       <c r="B44" t="n">
         <v>99193</v>
@@ -5754,7 +5833,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5765,10 +5844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490860</v>
+        <v>490848</v>
       </c>
       <c r="R44" t="n">
-        <v>7017386</v>
+        <v>7017375</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5803,11 +5882,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5837,16 +5911,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499509</v>
+        <v>135499613</v>
       </c>
       <c r="B45" t="n">
-        <v>99300</v>
+        <v>99193</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5854,28 +5928,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -5886,10 +5960,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490880</v>
+        <v>490878</v>
       </c>
       <c r="R45" t="n">
-        <v>7017365</v>
+        <v>7017368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5926,7 +6000,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flertalet plantor.</t>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5944,11 +6018,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
@@ -5963,16 +6032,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499620</v>
+        <v>135499614</v>
       </c>
       <c r="B46" t="n">
-        <v>108294</v>
+        <v>99193</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5980,21 +6049,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220083</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6012,10 +6081,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490853</v>
+        <v>490867</v>
       </c>
       <c r="R46" t="n">
-        <v>7017483</v>
+        <v>7017386</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6050,6 +6119,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6079,16 +6153,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499621</v>
+        <v>135499615</v>
       </c>
       <c r="B47" t="n">
-        <v>108294</v>
+        <v>99193</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6096,28 +6170,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220083</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6128,10 +6202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490837</v>
+        <v>490860</v>
       </c>
       <c r="R47" t="n">
-        <v>7017379</v>
+        <v>7017386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6166,6 +6240,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6195,16 +6274,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499623</v>
+        <v>135499509</v>
       </c>
       <c r="B48" t="n">
-        <v>108294</v>
+        <v>99300</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6212,28 +6291,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6244,10 +6323,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490848</v>
+        <v>490880</v>
       </c>
       <c r="R48" t="n">
-        <v>7017376</v>
+        <v>7017365</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6282,6 +6361,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flertalet plantor.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6297,6 +6381,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
@@ -6311,13 +6400,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499624</v>
+        <v>135499620</v>
       </c>
       <c r="B49" t="n">
         <v>108294</v>
@@ -6349,7 +6438,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6360,10 +6449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490861</v>
+        <v>490853</v>
       </c>
       <c r="R49" t="n">
-        <v>7017386</v>
+        <v>7017483</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6427,13 +6516,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499625</v>
+        <v>135499621</v>
       </c>
       <c r="B50" t="n">
         <v>108294</v>
@@ -6465,7 +6554,7 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -6476,10 +6565,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490821</v>
+        <v>490837</v>
       </c>
       <c r="R50" t="n">
-        <v>7017394</v>
+        <v>7017379</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6543,13 +6632,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499626</v>
+        <v>135499623</v>
       </c>
       <c r="B51" t="n">
         <v>108294</v>
@@ -6581,7 +6670,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6592,10 +6681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490841</v>
+        <v>490848</v>
       </c>
       <c r="R51" t="n">
-        <v>7017433</v>
+        <v>7017376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6659,16 +6748,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499550</v>
+        <v>135499624</v>
       </c>
       <c r="B52" t="n">
-        <v>108364</v>
+        <v>108294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6676,28 +6765,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6708,10 +6797,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490929</v>
+        <v>490861</v>
       </c>
       <c r="R52" t="n">
-        <v>7017429</v>
+        <v>7017386</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6775,16 +6864,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499551</v>
+        <v>135499625</v>
       </c>
       <c r="B53" t="n">
-        <v>108364</v>
+        <v>108294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6792,28 +6881,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6824,10 +6913,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490853</v>
+        <v>490821</v>
       </c>
       <c r="R53" t="n">
-        <v>7017480</v>
+        <v>7017394</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6862,11 +6951,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6896,16 +6980,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499552</v>
+        <v>135499626</v>
       </c>
       <c r="B54" t="n">
-        <v>108364</v>
+        <v>108294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6913,28 +6997,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -6945,10 +7029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490867</v>
+        <v>490841</v>
       </c>
       <c r="R54" t="n">
-        <v>7017480</v>
+        <v>7017433</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7012,13 +7096,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499553</v>
+        <v>135499550</v>
       </c>
       <c r="B55" t="n">
         <v>108364</v>
@@ -7061,10 +7145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490841</v>
+        <v>490929</v>
       </c>
       <c r="R55" t="n">
-        <v>7017457</v>
+        <v>7017429</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7128,13 +7212,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499554</v>
+        <v>135499551</v>
       </c>
       <c r="B56" t="n">
         <v>108364</v>
@@ -7177,10 +7261,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490737</v>
+        <v>490853</v>
       </c>
       <c r="R56" t="n">
-        <v>7017474</v>
+        <v>7017480</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7215,6 +7299,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7244,13 +7333,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499555</v>
+        <v>135499552</v>
       </c>
       <c r="B57" t="n">
         <v>108364</v>
@@ -7293,10 +7382,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490873</v>
+        <v>490867</v>
       </c>
       <c r="R57" t="n">
-        <v>7017368</v>
+        <v>7017480</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7360,13 +7449,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499556</v>
+        <v>135499553</v>
       </c>
       <c r="B58" t="n">
         <v>108364</v>
@@ -7409,10 +7498,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490863</v>
+        <v>490841</v>
       </c>
       <c r="R58" t="n">
-        <v>7017386</v>
+        <v>7017457</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7462,11 +7551,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
@@ -7481,16 +7565,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499544</v>
+        <v>135499554</v>
       </c>
       <c r="B59" t="n">
-        <v>111244</v>
+        <v>108364</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7498,28 +7582,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -7530,10 +7614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490844</v>
+        <v>490737</v>
       </c>
       <c r="R59" t="n">
-        <v>7017468</v>
+        <v>7017474</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7597,16 +7681,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499546</v>
+        <v>135499555</v>
       </c>
       <c r="B60" t="n">
-        <v>111244</v>
+        <v>108364</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7614,28 +7698,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7646,10 +7730,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490780</v>
+        <v>490873</v>
       </c>
       <c r="R60" t="n">
-        <v>7017405</v>
+        <v>7017368</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7713,16 +7797,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499547</v>
+        <v>135499556</v>
       </c>
       <c r="B61" t="n">
-        <v>111244</v>
+        <v>108364</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7730,21 +7814,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7762,10 +7846,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490858</v>
+        <v>490863</v>
       </c>
       <c r="R61" t="n">
-        <v>7017416</v>
+        <v>7017386</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7815,6 +7899,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -7829,13 +7918,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499548</v>
+        <v>135499544</v>
       </c>
       <c r="B62" t="n">
         <v>111244</v>
@@ -7867,7 +7956,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7878,10 +7967,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490964</v>
+        <v>490844</v>
       </c>
       <c r="R62" t="n">
-        <v>7017356</v>
+        <v>7017468</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7931,11 +8020,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7950,16 +8034,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499617</v>
+        <v>135499546</v>
       </c>
       <c r="B63" t="n">
-        <v>110240</v>
+        <v>111244</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7967,28 +8051,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220294</v>
+        <v>220240</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -7999,10 +8083,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490864</v>
+        <v>490780</v>
       </c>
       <c r="R63" t="n">
-        <v>7017486</v>
+        <v>7017405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8037,11 +8121,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8071,50 +8150,42 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499580</v>
+        <v>135499547</v>
       </c>
       <c r="B64" t="n">
-        <v>99276</v>
+        <v>111244</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -8128,10 +8199,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490975</v>
+        <v>490858</v>
       </c>
       <c r="R64" t="n">
-        <v>7017304</v>
+        <v>7017416</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8166,11 +8237,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8186,11 +8252,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
@@ -8205,53 +8266,45 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499581</v>
+        <v>135499548</v>
       </c>
       <c r="B65" t="n">
-        <v>99276</v>
+        <v>111244</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -8262,10 +8315,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490951</v>
+        <v>490964</v>
       </c>
       <c r="R65" t="n">
-        <v>7017428</v>
+        <v>7017356</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8300,11 +8353,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8320,6 +8368,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
@@ -8334,53 +8387,45 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499581</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499582</v>
+        <v>135499617</v>
       </c>
       <c r="B66" t="n">
-        <v>99276</v>
+        <v>110240</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -8391,10 +8436,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490884</v>
+        <v>490864</v>
       </c>
       <c r="R66" t="n">
-        <v>7017471</v>
+        <v>7017486</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8431,7 +8476,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8446,7 +8491,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8463,13 +8508,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499582</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499583</v>
+        <v>135499580</v>
       </c>
       <c r="B67" t="n">
         <v>99276</v>
@@ -8499,7 +8544,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8520,10 +8565,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490768</v>
+        <v>490975</v>
       </c>
       <c r="R67" t="n">
-        <v>7017376</v>
+        <v>7017304</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8560,7 +8605,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8597,13 +8642,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499584</v>
+        <v>135499581</v>
       </c>
       <c r="B68" t="n">
         <v>99276</v>
@@ -8633,7 +8678,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8654,10 +8699,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490839</v>
+        <v>490951</v>
       </c>
       <c r="R68" t="n">
-        <v>7017351</v>
+        <v>7017428</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8694,7 +8739,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8709,7 +8754,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8726,13 +8771,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499581</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499585</v>
+        <v>135499582</v>
       </c>
       <c r="B69" t="n">
         <v>99276</v>
@@ -8762,7 +8807,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8783,10 +8828,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490845</v>
+        <v>490884</v>
       </c>
       <c r="R69" t="n">
-        <v>7017392</v>
+        <v>7017471</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8823,7 +8868,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8855,13 +8900,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499582</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499586</v>
+        <v>135499583</v>
       </c>
       <c r="B70" t="n">
         <v>99276</v>
@@ -8891,7 +8936,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8912,10 +8957,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490812</v>
+        <v>490768</v>
       </c>
       <c r="R70" t="n">
-        <v>7017401</v>
+        <v>7017376</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8952,7 +8997,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8989,13 +9034,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499588</v>
+        <v>135499584</v>
       </c>
       <c r="B71" t="n">
         <v>99276</v>
@@ -9025,7 +9070,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9046,10 +9091,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490843</v>
+        <v>490839</v>
       </c>
       <c r="R71" t="n">
-        <v>7017436</v>
+        <v>7017351</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9086,7 +9131,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9101,12 +9146,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9123,13 +9163,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499589</v>
+        <v>135499585</v>
       </c>
       <c r="B72" t="n">
         <v>99276</v>
@@ -9159,7 +9199,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9180,10 +9220,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490967</v>
+        <v>490845</v>
       </c>
       <c r="R72" t="n">
-        <v>7017335</v>
+        <v>7017392</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9220,7 +9260,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9235,12 +9275,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9257,13 +9292,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499590</v>
+        <v>135499586</v>
       </c>
       <c r="B73" t="n">
         <v>99276</v>
@@ -9293,7 +9328,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9314,10 +9349,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490979</v>
+        <v>490812</v>
       </c>
       <c r="R73" t="n">
-        <v>7017360</v>
+        <v>7017401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9354,7 +9389,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9391,13 +9426,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499591</v>
+        <v>135499588</v>
       </c>
       <c r="B74" t="n">
         <v>99276</v>
@@ -9427,7 +9462,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9448,10 +9483,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490973</v>
+        <v>490843</v>
       </c>
       <c r="R74" t="n">
-        <v>7017399</v>
+        <v>7017436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9488,7 +9523,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9525,13 +9560,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499592</v>
+        <v>135499589</v>
       </c>
       <c r="B75" t="n">
         <v>99276</v>
@@ -9561,7 +9596,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9582,10 +9617,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490951</v>
+        <v>490967</v>
       </c>
       <c r="R75" t="n">
-        <v>7017408</v>
+        <v>7017335</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9622,7 +9657,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9659,13 +9694,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499593</v>
+        <v>135499590</v>
       </c>
       <c r="B76" t="n">
         <v>99276</v>
@@ -9695,7 +9730,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9716,10 +9751,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490951</v>
+        <v>490979</v>
       </c>
       <c r="R76" t="n">
-        <v>7017396</v>
+        <v>7017360</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9756,7 +9791,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9793,13 +9828,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499594</v>
+        <v>135499591</v>
       </c>
       <c r="B77" t="n">
         <v>99276</v>
@@ -9829,7 +9864,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9850,10 +9885,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490957</v>
+        <v>490973</v>
       </c>
       <c r="R77" t="n">
-        <v>7017386</v>
+        <v>7017399</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9890,7 +9925,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9927,43 +9962,55 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499519</v>
+        <v>135499592</v>
       </c>
       <c r="B78" t="n">
-        <v>98138</v>
+        <v>99276</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -9972,10 +10019,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490752</v>
+        <v>490951</v>
       </c>
       <c r="R78" t="n">
-        <v>7017499</v>
+        <v>7017408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10012,7 +10059,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10030,6 +10077,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
@@ -10044,45 +10096,53 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499516</v>
+        <v>135499593</v>
       </c>
       <c r="B79" t="n">
-        <v>99298</v>
+        <v>99276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -10093,10 +10153,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490844</v>
+        <v>490951</v>
       </c>
       <c r="R79" t="n">
-        <v>7017394</v>
+        <v>7017396</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10131,6 +10191,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10146,6 +10211,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
@@ -10160,45 +10230,53 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499517</v>
+        <v>135499594</v>
       </c>
       <c r="B80" t="n">
-        <v>99298</v>
+        <v>99276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10209,10 +10287,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490814</v>
+        <v>490957</v>
       </c>
       <c r="R80" t="n">
-        <v>7017404</v>
+        <v>7017386</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10247,6 +10325,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10262,6 +10345,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
@@ -10276,16 +10364,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499627</v>
+        <v>135499519</v>
       </c>
       <c r="B81" t="n">
-        <v>101485</v>
+        <v>98138</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10293,30 +10381,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10325,10 +10409,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490803</v>
+        <v>490752</v>
       </c>
       <c r="R81" t="n">
-        <v>7017492</v>
+        <v>7017499</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10363,6 +10447,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10392,16 +10481,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499628</v>
+        <v>135499516</v>
       </c>
       <c r="B82" t="n">
-        <v>101485</v>
+        <v>99298</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10409,28 +10498,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10441,10 +10530,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490792</v>
+        <v>490844</v>
       </c>
       <c r="R82" t="n">
-        <v>7017441</v>
+        <v>7017394</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10508,16 +10597,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499629</v>
+        <v>135499517</v>
       </c>
       <c r="B83" t="n">
-        <v>101485</v>
+        <v>99298</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10525,28 +10614,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -10557,10 +10646,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490764</v>
+        <v>490814</v>
       </c>
       <c r="R83" t="n">
-        <v>7017441</v>
+        <v>7017404</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10624,13 +10713,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499630</v>
+        <v>135499627</v>
       </c>
       <c r="B84" t="n">
         <v>101485</v>
@@ -10673,10 +10762,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490798</v>
+        <v>490803</v>
       </c>
       <c r="R84" t="n">
-        <v>7017366</v>
+        <v>7017492</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10740,13 +10829,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499631</v>
+        <v>135499628</v>
       </c>
       <c r="B85" t="n">
         <v>101485</v>
@@ -10789,10 +10878,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490816</v>
+        <v>490792</v>
       </c>
       <c r="R85" t="n">
-        <v>7017378</v>
+        <v>7017441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10856,13 +10945,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499632</v>
+        <v>135499629</v>
       </c>
       <c r="B86" t="n">
         <v>101485</v>
@@ -10905,10 +10994,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490796</v>
+        <v>490764</v>
       </c>
       <c r="R86" t="n">
-        <v>7017382</v>
+        <v>7017441</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10972,13 +11061,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499633</v>
+        <v>135499630</v>
       </c>
       <c r="B87" t="n">
         <v>101485</v>
@@ -11021,10 +11110,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490782</v>
+        <v>490798</v>
       </c>
       <c r="R87" t="n">
-        <v>7017407</v>
+        <v>7017366</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11088,13 +11177,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499634</v>
+        <v>135499631</v>
       </c>
       <c r="B88" t="n">
         <v>101485</v>
@@ -11137,10 +11226,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490730</v>
+        <v>490816</v>
       </c>
       <c r="R88" t="n">
-        <v>7017371</v>
+        <v>7017378</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11204,13 +11293,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499635</v>
+        <v>135499632</v>
       </c>
       <c r="B89" t="n">
         <v>101485</v>
@@ -11253,10 +11342,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490827</v>
+        <v>490796</v>
       </c>
       <c r="R89" t="n">
-        <v>7017356</v>
+        <v>7017382</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11320,13 +11409,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499636</v>
+        <v>135499633</v>
       </c>
       <c r="B90" t="n">
         <v>101485</v>
@@ -11369,10 +11458,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490844</v>
+        <v>490782</v>
       </c>
       <c r="R90" t="n">
-        <v>7017345</v>
+        <v>7017407</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11436,13 +11525,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499637</v>
+        <v>135499634</v>
       </c>
       <c r="B91" t="n">
         <v>101485</v>
@@ -11485,10 +11574,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490852</v>
+        <v>490730</v>
       </c>
       <c r="R91" t="n">
-        <v>7017373</v>
+        <v>7017371</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11535,7 +11624,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11552,13 +11641,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499638</v>
+        <v>135499635</v>
       </c>
       <c r="B92" t="n">
         <v>101485</v>
@@ -11601,10 +11690,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490882</v>
+        <v>490827</v>
       </c>
       <c r="R92" t="n">
-        <v>7017368</v>
+        <v>7017356</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11651,7 +11740,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11668,13 +11757,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499639</v>
+        <v>135499636</v>
       </c>
       <c r="B93" t="n">
         <v>101485</v>
@@ -11717,10 +11806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490865</v>
+        <v>490844</v>
       </c>
       <c r="R93" t="n">
-        <v>7017386</v>
+        <v>7017345</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11784,13 +11873,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499640</v>
+        <v>135499637</v>
       </c>
       <c r="B94" t="n">
         <v>101485</v>
@@ -11833,10 +11922,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490840</v>
+        <v>490852</v>
       </c>
       <c r="R94" t="n">
-        <v>7017433</v>
+        <v>7017373</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11883,7 +11972,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11900,13 +11989,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499641</v>
+        <v>135499638</v>
       </c>
       <c r="B95" t="n">
         <v>101485</v>
@@ -11949,10 +12038,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490880</v>
+        <v>490882</v>
       </c>
       <c r="R95" t="n">
-        <v>7017422</v>
+        <v>7017368</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11999,7 +12088,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12016,16 +12105,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499618</v>
+        <v>135499639</v>
       </c>
       <c r="B96" t="n">
-        <v>98292</v>
+        <v>101485</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12033,21 +12122,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -12065,10 +12154,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490791</v>
+        <v>490865</v>
       </c>
       <c r="R96" t="n">
-        <v>7017443</v>
+        <v>7017386</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12103,11 +12192,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12137,16 +12221,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499619</v>
+        <v>135499640</v>
       </c>
       <c r="B97" t="n">
-        <v>98292</v>
+        <v>101485</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12154,33 +12238,25 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12194,10 +12270,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490868</v>
+        <v>490840</v>
       </c>
       <c r="R97" t="n">
-        <v>7017387</v>
+        <v>7017433</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12232,11 +12308,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12252,11 +12323,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
@@ -12271,16 +12337,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499520</v>
+        <v>135499641</v>
       </c>
       <c r="B98" t="n">
-        <v>99082</v>
+        <v>101485</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12288,21 +12354,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12320,10 +12386,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490757</v>
+        <v>490880</v>
       </c>
       <c r="R98" t="n">
-        <v>7017472</v>
+        <v>7017422</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12387,16 +12453,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499521</v>
+        <v>135499618</v>
       </c>
       <c r="B99" t="n">
-        <v>99082</v>
+        <v>98292</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12404,21 +12470,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12436,10 +12502,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490966</v>
+        <v>490791</v>
       </c>
       <c r="R99" t="n">
-        <v>7017430</v>
+        <v>7017443</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12474,6 +12540,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -12503,16 +12574,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499522</v>
+        <v>135499619</v>
       </c>
       <c r="B100" t="n">
-        <v>99082</v>
+        <v>98292</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12520,25 +12591,33 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12552,10 +12631,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490920</v>
+        <v>490868</v>
       </c>
       <c r="R100" t="n">
-        <v>7017445</v>
+        <v>7017387</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12590,6 +12669,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12605,6 +12689,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
@@ -12619,13 +12708,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499523</v>
+        <v>135499520</v>
       </c>
       <c r="B101" t="n">
         <v>99082</v>
@@ -12668,10 +12757,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490912</v>
+        <v>490757</v>
       </c>
       <c r="R101" t="n">
-        <v>7017466</v>
+        <v>7017472</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12735,13 +12824,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499524</v>
+        <v>135499521</v>
       </c>
       <c r="B102" t="n">
         <v>99082</v>
@@ -12784,10 +12873,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490858</v>
+        <v>490966</v>
       </c>
       <c r="R102" t="n">
-        <v>7017493</v>
+        <v>7017430</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12851,13 +12940,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499525</v>
+        <v>135499522</v>
       </c>
       <c r="B103" t="n">
         <v>99082</v>
@@ -12889,7 +12978,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12900,10 +12989,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490804</v>
+        <v>490920</v>
       </c>
       <c r="R103" t="n">
-        <v>7017492</v>
+        <v>7017445</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12967,13 +13056,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499526</v>
+        <v>135499523</v>
       </c>
       <c r="B104" t="n">
         <v>99082</v>
@@ -13016,10 +13105,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490740</v>
+        <v>490912</v>
       </c>
       <c r="R104" t="n">
-        <v>7017423</v>
+        <v>7017466</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13083,13 +13172,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499527</v>
+        <v>135499524</v>
       </c>
       <c r="B105" t="n">
         <v>99082</v>
@@ -13132,10 +13221,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490732</v>
+        <v>490858</v>
       </c>
       <c r="R105" t="n">
-        <v>7017370</v>
+        <v>7017493</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13199,13 +13288,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499528</v>
+        <v>135499525</v>
       </c>
       <c r="B106" t="n">
         <v>99082</v>
@@ -13237,7 +13326,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -13248,10 +13337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490867</v>
+        <v>490804</v>
       </c>
       <c r="R106" t="n">
-        <v>7017386</v>
+        <v>7017492</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13286,11 +13375,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -13320,13 +13404,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499529</v>
+        <v>135499526</v>
       </c>
       <c r="B107" t="n">
         <v>99082</v>
@@ -13369,10 +13453,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490807</v>
+        <v>490740</v>
       </c>
       <c r="R107" t="n">
-        <v>7017431</v>
+        <v>7017423</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13436,13 +13520,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499530</v>
+        <v>135499527</v>
       </c>
       <c r="B108" t="n">
         <v>99082</v>
@@ -13474,7 +13558,7 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -13485,10 +13569,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490932</v>
+        <v>490732</v>
       </c>
       <c r="R108" t="n">
-        <v>7017369</v>
+        <v>7017370</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13552,16 +13636,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499597</v>
+        <v>135499528</v>
       </c>
       <c r="B109" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13569,21 +13653,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13601,10 +13685,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490969</v>
+        <v>490867</v>
       </c>
       <c r="R109" t="n">
-        <v>7017431</v>
+        <v>7017386</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13639,6 +13723,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13668,16 +13757,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499598</v>
+        <v>135499529</v>
       </c>
       <c r="B110" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13685,21 +13774,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13717,10 +13806,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490840</v>
+        <v>490807</v>
       </c>
       <c r="R110" t="n">
-        <v>7017457</v>
+        <v>7017431</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13784,16 +13873,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499599</v>
+        <v>135499530</v>
       </c>
       <c r="B111" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13801,28 +13890,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13833,10 +13922,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490831</v>
+        <v>490932</v>
       </c>
       <c r="R111" t="n">
-        <v>7017486</v>
+        <v>7017369</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13900,13 +13989,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499600</v>
+        <v>135499597</v>
       </c>
       <c r="B112" t="n">
         <v>98327</v>
@@ -13949,10 +14038,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490797</v>
+        <v>490969</v>
       </c>
       <c r="R112" t="n">
-        <v>7017497</v>
+        <v>7017431</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14016,13 +14105,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499601</v>
+        <v>135499598</v>
       </c>
       <c r="B113" t="n">
         <v>98327</v>
@@ -14065,10 +14154,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490797</v>
+        <v>490840</v>
       </c>
       <c r="R113" t="n">
-        <v>7017511</v>
+        <v>7017457</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14132,13 +14221,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499602</v>
+        <v>135499599</v>
       </c>
       <c r="B114" t="n">
         <v>98327</v>
@@ -14181,10 +14270,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490737</v>
+        <v>490831</v>
       </c>
       <c r="R114" t="n">
-        <v>7017473</v>
+        <v>7017486</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14248,16 +14337,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499515</v>
+        <v>135499600</v>
       </c>
       <c r="B115" t="n">
-        <v>102022</v>
+        <v>98327</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14265,21 +14354,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>223366</v>
+        <v>223358</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14297,10 +14386,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490788</v>
+        <v>490797</v>
       </c>
       <c r="R115" t="n">
-        <v>7017450</v>
+        <v>7017497</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14364,16 +14453,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499532</v>
+        <v>135499601</v>
       </c>
       <c r="B116" t="n">
-        <v>101375</v>
+        <v>98327</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14381,21 +14470,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14413,10 +14502,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490889</v>
+        <v>490797</v>
       </c>
       <c r="R116" t="n">
-        <v>7017459</v>
+        <v>7017511</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14480,16 +14569,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499533</v>
+        <v>135499602</v>
       </c>
       <c r="B117" t="n">
-        <v>101375</v>
+        <v>98327</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14497,21 +14586,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14529,10 +14618,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>490743</v>
+        <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017495</v>
+        <v>7017473</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14596,16 +14685,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499534</v>
+        <v>135499515</v>
       </c>
       <c r="B118" t="n">
-        <v>101375</v>
+        <v>102022</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14613,21 +14702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>224885</v>
+        <v>223366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14645,10 +14734,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490737</v>
+        <v>490788</v>
       </c>
       <c r="R118" t="n">
-        <v>7017474</v>
+        <v>7017450</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14712,13 +14801,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499535</v>
+        <v>135499532</v>
       </c>
       <c r="B119" t="n">
         <v>101375</v>
@@ -14761,10 +14850,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490734</v>
+        <v>490889</v>
       </c>
       <c r="R119" t="n">
-        <v>7017429</v>
+        <v>7017459</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14828,13 +14917,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499536</v>
+        <v>135499533</v>
       </c>
       <c r="B120" t="n">
         <v>101375</v>
@@ -14877,10 +14966,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490780</v>
+        <v>490743</v>
       </c>
       <c r="R120" t="n">
-        <v>7017405</v>
+        <v>7017495</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14944,13 +15033,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499537</v>
+        <v>135499534</v>
       </c>
       <c r="B121" t="n">
         <v>101375</v>
@@ -14993,10 +15082,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490751</v>
+        <v>490737</v>
       </c>
       <c r="R121" t="n">
-        <v>7017406</v>
+        <v>7017474</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15060,13 +15149,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499538</v>
+        <v>135499535</v>
       </c>
       <c r="B122" t="n">
         <v>101375</v>
@@ -15109,10 +15198,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490729</v>
+        <v>490734</v>
       </c>
       <c r="R122" t="n">
-        <v>7017373</v>
+        <v>7017429</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15176,13 +15265,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499540</v>
+        <v>135499536</v>
       </c>
       <c r="B123" t="n">
         <v>101375</v>
@@ -15225,10 +15314,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490847</v>
+        <v>490780</v>
       </c>
       <c r="R123" t="n">
-        <v>7017345</v>
+        <v>7017405</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15292,13 +15381,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499541</v>
+        <v>135499537</v>
       </c>
       <c r="B124" t="n">
         <v>101375</v>
@@ -15341,10 +15430,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490856</v>
+        <v>490751</v>
       </c>
       <c r="R124" t="n">
-        <v>7017358</v>
+        <v>7017406</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15408,13 +15497,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
+          <t>https://artportalen.se/Sighting/135499537</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135499542</v>
+        <v>135499538</v>
       </c>
       <c r="B125" t="n">
         <v>101375</v>
@@ -15446,7 +15535,7 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -15457,10 +15546,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>490840</v>
+        <v>490729</v>
       </c>
       <c r="R125" t="n">
-        <v>7017433</v>
+        <v>7017373</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15523,6 +15612,354 @@
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499538</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>135499540</v>
+      </c>
+      <c r="B126" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>490847</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7017345</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499540</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>135499541</v>
+      </c>
+      <c r="B127" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>490856</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7017358</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499541</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>135499542</v>
+      </c>
+      <c r="B128" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>490840</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7017433</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -15654,6 +16091,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135499607</v>
       </c>
       <c r="B2" t="n">
-        <v>99182</v>
+        <v>99199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>135499608</v>
       </c>
       <c r="B3" t="n">
-        <v>99182</v>
+        <v>99199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>135499603</v>
       </c>
       <c r="B4" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135499604</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135499605</v>
       </c>
       <c r="B6" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135499606</v>
       </c>
       <c r="B7" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135499557</v>
       </c>
       <c r="B9" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>135499558</v>
       </c>
       <c r="B10" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>135499560</v>
       </c>
       <c r="B11" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135499561</v>
       </c>
       <c r="B12" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>135499562</v>
       </c>
       <c r="B13" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135499563</v>
       </c>
       <c r="B14" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135499564</v>
       </c>
       <c r="B15" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>135499565</v>
       </c>
       <c r="B16" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>135499566</v>
       </c>
       <c r="B17" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>135499567</v>
       </c>
       <c r="B18" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135499568</v>
       </c>
       <c r="B19" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>135499569</v>
       </c>
       <c r="B20" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>135499570</v>
       </c>
       <c r="B21" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>135499571</v>
       </c>
       <c r="B22" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>135499572</v>
       </c>
       <c r="B23" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>135499573</v>
       </c>
       <c r="B24" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>135499574</v>
       </c>
       <c r="B25" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>135499575</v>
       </c>
       <c r="B26" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>135499576</v>
       </c>
       <c r="B27" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>135499577</v>
       </c>
       <c r="B28" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>135499578</v>
       </c>
       <c r="B29" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>135499579</v>
       </c>
       <c r="B30" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>135499609</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>135499610</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>135499531</v>
       </c>
       <c r="B35" t="n">
-        <v>58094</v>
+        <v>58096</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>135499510</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>135499511</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>135499512</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>135499549</v>
       </c>
       <c r="B39" t="n">
-        <v>58236</v>
+        <v>58238</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>135499596</v>
       </c>
       <c r="B40" t="n">
-        <v>58239</v>
+        <v>58241</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135499513</v>
       </c>
       <c r="B41" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>135499514</v>
       </c>
       <c r="B42" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>135499611</v>
       </c>
       <c r="B43" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>135499612</v>
       </c>
       <c r="B44" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>135499613</v>
       </c>
       <c r="B45" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135499614</v>
       </c>
       <c r="B46" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>135499615</v>
       </c>
       <c r="B47" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>135499509</v>
       </c>
       <c r="B48" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>135499620</v>
       </c>
       <c r="B49" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>135499621</v>
       </c>
       <c r="B50" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>135499623</v>
       </c>
       <c r="B51" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>135499624</v>
       </c>
       <c r="B52" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>135499625</v>
       </c>
       <c r="B53" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>135499626</v>
       </c>
       <c r="B54" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>135499550</v>
       </c>
       <c r="B55" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>135499551</v>
       </c>
       <c r="B56" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>135499552</v>
       </c>
       <c r="B57" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>135499553</v>
       </c>
       <c r="B58" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>135499554</v>
       </c>
       <c r="B59" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>135499555</v>
       </c>
       <c r="B60" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>135499556</v>
       </c>
       <c r="B61" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135499544</v>
       </c>
       <c r="B62" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>135499546</v>
       </c>
       <c r="B63" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>135499547</v>
       </c>
       <c r="B64" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>135499548</v>
       </c>
       <c r="B65" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>135499617</v>
       </c>
       <c r="B66" t="n">
-        <v>110240</v>
+        <v>110263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>135499580</v>
       </c>
       <c r="B67" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>135499581</v>
       </c>
       <c r="B68" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135499582</v>
       </c>
       <c r="B69" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>135499583</v>
       </c>
       <c r="B70" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>135499584</v>
       </c>
       <c r="B71" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135499585</v>
       </c>
       <c r="B72" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>135499586</v>
       </c>
       <c r="B73" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>135499588</v>
       </c>
       <c r="B74" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>135499589</v>
       </c>
       <c r="B75" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>135499590</v>
       </c>
       <c r="B76" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>135499591</v>
       </c>
       <c r="B77" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>135499592</v>
       </c>
       <c r="B78" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>135499593</v>
       </c>
       <c r="B79" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>135499594</v>
       </c>
       <c r="B80" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>135499519</v>
       </c>
       <c r="B81" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>135499516</v>
       </c>
       <c r="B82" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>135499517</v>
       </c>
       <c r="B83" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>135499627</v>
       </c>
       <c r="B84" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>135499628</v>
       </c>
       <c r="B85" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>135499629</v>
       </c>
       <c r="B86" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>135499630</v>
       </c>
       <c r="B87" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>135499631</v>
       </c>
       <c r="B88" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>135499632</v>
       </c>
       <c r="B89" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>135499633</v>
       </c>
       <c r="B90" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>135499634</v>
       </c>
       <c r="B91" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>135499635</v>
       </c>
       <c r="B92" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>135499636</v>
       </c>
       <c r="B93" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>135499637</v>
       </c>
       <c r="B94" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>135499638</v>
       </c>
       <c r="B95" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>135499639</v>
       </c>
       <c r="B96" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>135499640</v>
       </c>
       <c r="B97" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>135499641</v>
       </c>
       <c r="B98" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>135499618</v>
       </c>
       <c r="B99" t="n">
-        <v>98292</v>
+        <v>98309</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>135499619</v>
       </c>
       <c r="B100" t="n">
-        <v>98292</v>
+        <v>98309</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>135499520</v>
       </c>
       <c r="B101" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>135499521</v>
       </c>
       <c r="B102" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>135499522</v>
       </c>
       <c r="B103" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>135499523</v>
       </c>
       <c r="B104" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>135499524</v>
       </c>
       <c r="B105" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>135499525</v>
       </c>
       <c r="B106" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>135499526</v>
       </c>
       <c r="B107" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>135499527</v>
       </c>
       <c r="B108" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>135499528</v>
       </c>
       <c r="B109" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>135499529</v>
       </c>
       <c r="B110" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>135499530</v>
       </c>
       <c r="B111" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>135499597</v>
       </c>
       <c r="B112" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>135499598</v>
       </c>
       <c r="B113" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>135499599</v>
       </c>
       <c r="B114" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135499600</v>
       </c>
       <c r="B115" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135499601</v>
       </c>
       <c r="B116" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135499602</v>
       </c>
       <c r="B117" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>135499515</v>
       </c>
       <c r="B118" t="n">
-        <v>102022</v>
+        <v>102039</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>135499532</v>
       </c>
       <c r="B119" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>135499533</v>
       </c>
       <c r="B120" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>135499534</v>
       </c>
       <c r="B121" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>135499535</v>
       </c>
       <c r="B122" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>135499536</v>
       </c>
       <c r="B123" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>135499537</v>
       </c>
       <c r="B124" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>135499538</v>
       </c>
       <c r="B125" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>135499540</v>
       </c>
       <c r="B126" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>135499541</v>
       </c>
       <c r="B127" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>135499542</v>
       </c>
       <c r="B128" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ128"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499607</v>
+        <v>135499608</v>
       </c>
       <c r="B2" t="n">
         <v>99199</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490869</v>
+        <v>490867</v>
       </c>
       <c r="R2" t="n">
-        <v>7017370</v>
+        <v>7017387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad snitslad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +790,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkrikt fuktstråk.</t>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,71 +812,58 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499607</t>
+          <t>https://artportalen.se/Sighting/135499608</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499608</v>
+        <v>135499603</v>
       </c>
       <c r="B3" t="n">
-        <v>99199</v>
+        <v>92060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490867</v>
+        <v>490968</v>
       </c>
       <c r="R3" t="n">
-        <v>7017387</v>
+        <v>7017430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,7 +900,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,9 +918,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,13 +952,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499608</t>
+          <t>https://artportalen.se/Sighting/135499603</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499603</v>
+        <v>135499604</v>
       </c>
       <c r="B4" t="n">
         <v>92060</v>
@@ -998,10 +1000,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490968</v>
+        <v>490893</v>
       </c>
       <c r="R4" t="n">
-        <v>7017430</v>
+        <v>7017459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,12 +1070,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,13 +1092,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499603</t>
+          <t>https://artportalen.se/Sighting/135499604</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499604</v>
+        <v>135499605</v>
       </c>
       <c r="B5" t="n">
         <v>92060</v>
@@ -1138,10 +1140,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490893</v>
+        <v>490741</v>
       </c>
       <c r="R5" t="n">
-        <v>7017459</v>
+        <v>7017465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1178,7 +1180,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,13 +1232,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499604</t>
+          <t>https://artportalen.se/Sighting/135499605</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499605</v>
+        <v>135499606</v>
       </c>
       <c r="B6" t="n">
         <v>92060</v>
@@ -1278,10 +1280,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490741</v>
+        <v>490951</v>
       </c>
       <c r="R6" t="n">
-        <v>7017465</v>
+        <v>7017411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1320,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1348,12 +1350,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1370,16 +1372,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499605</t>
+          <t>https://artportalen.se/Sighting/135499606</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135499606</v>
+        <v>75185503</v>
       </c>
       <c r="B7" t="n">
-        <v>92060</v>
+        <v>87322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,41 +1389,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1988</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490951</v>
+        <v>490758</v>
       </c>
       <c r="R7" t="n">
-        <v>7017411</v>
+        <v>7017384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1448,17 +1443,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1471,90 +1461,73 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499606</t>
+          <t>https://artportalen.se/Sighting/75185503</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75185503</v>
+        <v>135499557</v>
       </c>
       <c r="B8" t="n">
-        <v>87322</v>
+        <v>96505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1988</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490758</v>
+        <v>490738</v>
       </c>
       <c r="R8" t="n">
-        <v>7017384</v>
+        <v>7017396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1581,12 +1554,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,31 +1572,32 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185503</t>
+          <t>https://artportalen.se/Sighting/135499557</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499557</v>
+        <v>135499558</v>
       </c>
       <c r="B9" t="n">
         <v>96505</v>
@@ -1662,10 +1636,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490738</v>
+        <v>490991</v>
       </c>
       <c r="R9" t="n">
-        <v>7017396</v>
+        <v>7017297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1729,13 +1703,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499557</t>
+          <t>https://artportalen.se/Sighting/135499558</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499558</v>
+        <v>135499560</v>
       </c>
       <c r="B10" t="n">
         <v>96505</v>
@@ -1774,10 +1748,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490991</v>
+        <v>490966</v>
       </c>
       <c r="R10" t="n">
-        <v>7017297</v>
+        <v>7017426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,6 +1801,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1841,13 +1820,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499558</t>
+          <t>https://artportalen.se/Sighting/135499560</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499560</v>
+        <v>135499561</v>
       </c>
       <c r="B11" t="n">
         <v>96505</v>
@@ -1886,10 +1865,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490966</v>
+        <v>490929</v>
       </c>
       <c r="R11" t="n">
-        <v>7017426</v>
+        <v>7017441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1936,12 +1915,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1958,13 +1932,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499560</t>
+          <t>https://artportalen.se/Sighting/135499561</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499561</v>
+        <v>135499562</v>
       </c>
       <c r="B12" t="n">
         <v>96505</v>
@@ -2003,10 +1977,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490929</v>
+        <v>490910</v>
       </c>
       <c r="R12" t="n">
-        <v>7017441</v>
+        <v>7017467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2070,13 +2044,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499561</t>
+          <t>https://artportalen.se/Sighting/135499562</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499562</v>
+        <v>135499563</v>
       </c>
       <c r="B13" t="n">
         <v>96505</v>
@@ -2115,10 +2089,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490910</v>
+        <v>490878</v>
       </c>
       <c r="R13" t="n">
-        <v>7017467</v>
+        <v>7017474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,7 +2139,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2182,13 +2156,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499562</t>
+          <t>https://artportalen.se/Sighting/135499563</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499563</v>
+        <v>135499564</v>
       </c>
       <c r="B14" t="n">
         <v>96505</v>
@@ -2227,10 +2201,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490878</v>
+        <v>490883</v>
       </c>
       <c r="R14" t="n">
-        <v>7017474</v>
+        <v>7017462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2277,7 +2251,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2294,13 +2268,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499563</t>
+          <t>https://artportalen.se/Sighting/135499564</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499564</v>
+        <v>135499565</v>
       </c>
       <c r="B15" t="n">
         <v>96505</v>
@@ -2339,10 +2313,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490883</v>
+        <v>490756</v>
       </c>
       <c r="R15" t="n">
-        <v>7017462</v>
+        <v>7017472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2389,7 +2363,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2406,13 +2380,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499564</t>
+          <t>https://artportalen.se/Sighting/135499565</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499565</v>
+        <v>135499566</v>
       </c>
       <c r="B16" t="n">
         <v>96505</v>
@@ -2451,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490756</v>
+        <v>490790</v>
       </c>
       <c r="R16" t="n">
-        <v>7017472</v>
+        <v>7017441</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2518,13 +2492,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499565</t>
+          <t>https://artportalen.se/Sighting/135499566</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499566</v>
+        <v>135499567</v>
       </c>
       <c r="B17" t="n">
         <v>96505</v>
@@ -2563,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490790</v>
+        <v>490732</v>
       </c>
       <c r="R17" t="n">
-        <v>7017441</v>
+        <v>7017442</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2613,7 +2587,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2630,13 +2604,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499566</t>
+          <t>https://artportalen.se/Sighting/135499567</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499567</v>
+        <v>135499568</v>
       </c>
       <c r="B18" t="n">
         <v>96505</v>
@@ -2675,10 +2649,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490732</v>
+        <v>490781</v>
       </c>
       <c r="R18" t="n">
-        <v>7017442</v>
+        <v>7017407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2725,7 +2699,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2742,13 +2716,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499567</t>
+          <t>https://artportalen.se/Sighting/135499568</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499568</v>
+        <v>135499569</v>
       </c>
       <c r="B19" t="n">
         <v>96505</v>
@@ -2787,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490781</v>
+        <v>490731</v>
       </c>
       <c r="R19" t="n">
-        <v>7017407</v>
+        <v>7017371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2840,6 +2814,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2854,13 +2833,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499568</t>
+          <t>https://artportalen.se/Sighting/135499569</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499569</v>
+        <v>135499570</v>
       </c>
       <c r="B20" t="n">
         <v>96505</v>
@@ -2899,10 +2878,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490731</v>
+        <v>490854</v>
       </c>
       <c r="R20" t="n">
-        <v>7017371</v>
+        <v>7017345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2952,11 +2931,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2971,13 +2945,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499569</t>
+          <t>https://artportalen.se/Sighting/135499570</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499570</v>
+        <v>135499571</v>
       </c>
       <c r="B21" t="n">
         <v>96505</v>
@@ -3016,10 +2990,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490854</v>
+        <v>490878</v>
       </c>
       <c r="R21" t="n">
-        <v>7017345</v>
+        <v>7017366</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,6 +3028,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3083,13 +3062,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499570</t>
+          <t>https://artportalen.se/Sighting/135499571</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499571</v>
+        <v>135499572</v>
       </c>
       <c r="B22" t="n">
         <v>96505</v>
@@ -3128,10 +3107,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490878</v>
+        <v>490867</v>
       </c>
       <c r="R22" t="n">
-        <v>7017366</v>
+        <v>7017386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3166,11 +3145,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3200,13 +3174,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499571</t>
+          <t>https://artportalen.se/Sighting/135499572</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499572</v>
+        <v>135499573</v>
       </c>
       <c r="B23" t="n">
         <v>96505</v>
@@ -3245,10 +3219,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490867</v>
+        <v>490840</v>
       </c>
       <c r="R23" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3312,13 +3286,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499572</t>
+          <t>https://artportalen.se/Sighting/135499573</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499573</v>
+        <v>135499574</v>
       </c>
       <c r="B24" t="n">
         <v>96505</v>
@@ -3357,10 +3331,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490840</v>
+        <v>490844</v>
       </c>
       <c r="R24" t="n">
-        <v>7017433</v>
+        <v>7017436</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,13 +3398,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499573</t>
+          <t>https://artportalen.se/Sighting/135499574</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499574</v>
+        <v>135499575</v>
       </c>
       <c r="B25" t="n">
         <v>96505</v>
@@ -3469,10 +3443,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490844</v>
+        <v>490872</v>
       </c>
       <c r="R25" t="n">
-        <v>7017436</v>
+        <v>7017426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3536,13 +3510,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499574</t>
+          <t>https://artportalen.se/Sighting/135499575</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499575</v>
+        <v>135499576</v>
       </c>
       <c r="B26" t="n">
         <v>96505</v>
@@ -3581,10 +3555,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490872</v>
+        <v>490917</v>
       </c>
       <c r="R26" t="n">
-        <v>7017426</v>
+        <v>7017402</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3648,13 +3622,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499575</t>
+          <t>https://artportalen.se/Sighting/135499576</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499576</v>
+        <v>135499577</v>
       </c>
       <c r="B27" t="n">
         <v>96505</v>
@@ -3693,10 +3667,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490917</v>
+        <v>490931</v>
       </c>
       <c r="R27" t="n">
-        <v>7017402</v>
+        <v>7017371</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3746,6 +3720,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3760,13 +3739,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499576</t>
+          <t>https://artportalen.se/Sighting/135499577</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499577</v>
+        <v>135499578</v>
       </c>
       <c r="B28" t="n">
         <v>96505</v>
@@ -3805,10 +3784,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490931</v>
+        <v>490951</v>
       </c>
       <c r="R28" t="n">
-        <v>7017371</v>
+        <v>7017390</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,13 +3856,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499577</t>
+          <t>https://artportalen.se/Sighting/135499578</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499578</v>
+        <v>135499579</v>
       </c>
       <c r="B29" t="n">
         <v>96505</v>
@@ -3922,10 +3901,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490951</v>
+        <v>490976</v>
       </c>
       <c r="R29" t="n">
-        <v>7017390</v>
+        <v>7017311</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3994,16 +3973,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499578</t>
+          <t>https://artportalen.se/Sighting/135499579</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135499579</v>
+        <v>91488964</v>
       </c>
       <c r="B30" t="n">
-        <v>96505</v>
+        <v>92632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,41 +3990,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2812</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490976</v>
+        <v>490939</v>
       </c>
       <c r="R30" t="n">
-        <v>7017311</v>
+        <v>7017412</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4069,12 +4044,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4083,66 +4058,59 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499579</t>
+          <t>https://artportalen.se/Sighting/91488964</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>91488964</v>
+        <v>75185505</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>89156</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4152,13 +4120,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490939</v>
+        <v>490781</v>
       </c>
       <c r="R31" t="n">
-        <v>7017412</v>
+        <v>7017384</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4196,18 +4164,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4217,51 +4186,54 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91488964</t>
+          <t>https://artportalen.se/Sighting/75185505</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>75185505</v>
+        <v>135499609</v>
       </c>
       <c r="B32" t="n">
-        <v>89156</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490781</v>
+        <v>490849</v>
       </c>
       <c r="R32" t="n">
-        <v>7017384</v>
+        <v>7017392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4288,12 +4260,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4306,31 +4283,52 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185505</t>
+          <t>https://artportalen.se/Sighting/135499609</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499609</v>
+        <v>135499610</v>
       </c>
       <c r="B33" t="n">
         <v>79443</v>
@@ -4368,10 +4366,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490849</v>
+        <v>490859</v>
       </c>
       <c r="R33" t="n">
-        <v>7017392</v>
+        <v>7017416</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,11 +4404,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4438,12 +4431,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4460,54 +4453,67 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499609</t>
+          <t>https://artportalen.se/Sighting/135499610</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499610</v>
+        <v>135499531</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>58096</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100090</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490859</v>
+        <v>490781</v>
       </c>
       <c r="R34" t="n">
-        <v>7017416</v>
+        <v>7017369</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,39 +4548,23 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Synobservation av en individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4591,16 +4581,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499610</t>
+          <t>https://artportalen.se/Sighting/135499531</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499531</v>
+        <v>135499510</v>
       </c>
       <c r="B35" t="n">
-        <v>58096</v>
+        <v>57982</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4608,16 +4598,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100090</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4625,16 +4615,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4648,10 +4634,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490781</v>
+        <v>490891</v>
       </c>
       <c r="R35" t="n">
-        <v>7017369</v>
+        <v>7017451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,7 +4674,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Synobservation av en individ med lockläte.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4702,7 +4688,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4719,13 +4725,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499531</t>
+          <t>https://artportalen.se/Sighting/135499510</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499510</v>
+        <v>135499511</v>
       </c>
       <c r="B36" t="n">
         <v>57982</v>
@@ -4758,7 +4764,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4772,10 +4778,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490891</v>
+        <v>490785</v>
       </c>
       <c r="R36" t="n">
-        <v>7017451</v>
+        <v>7017521</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4812,7 +4818,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4826,7 +4832,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -4863,13 +4869,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499510</t>
+          <t>https://artportalen.se/Sighting/135499511</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499511</v>
+        <v>135499512</v>
       </c>
       <c r="B37" t="n">
         <v>57982</v>
@@ -4916,10 +4922,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490785</v>
+        <v>490783</v>
       </c>
       <c r="R37" t="n">
-        <v>7017521</v>
+        <v>7017360</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4956,7 +4962,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4971,6 +4977,11 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5007,33 +5018,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499511</t>
+          <t>https://artportalen.se/Sighting/135499512</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499512</v>
+        <v>135499596</v>
       </c>
       <c r="B38" t="n">
-        <v>57982</v>
+        <v>58241</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5041,29 +5052,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490783</v>
+        <v>490875</v>
       </c>
       <c r="R38" t="n">
-        <v>7017360</v>
+        <v>7017470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5100,7 +5111,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5115,31 +5126,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5156,16 +5142,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499512</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499549</v>
+        <v>135499513</v>
       </c>
       <c r="B39" t="n">
-        <v>58238</v>
+        <v>58143</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,21 +5159,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102980</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5199,7 +5185,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5213,10 +5199,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490804</v>
+        <v>490763</v>
       </c>
       <c r="R39" t="n">
-        <v>7017502</v>
+        <v>7017499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5253,7 +5239,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 1 överflygande med sång.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5267,7 +5253,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5284,43 +5275,43 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499549</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499596</v>
+        <v>135499514</v>
       </c>
       <c r="B40" t="n">
-        <v>58241</v>
+        <v>58143</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102981</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5330,7 +5321,11 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
@@ -5340,7 +5335,7 @@
         <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017470</v>
+        <v>7017397</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5377,7 +5372,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5392,6 +5387,11 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5408,67 +5408,59 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499513</v>
+        <v>135499611</v>
       </c>
       <c r="B41" t="n">
-        <v>58143</v>
+        <v>99210</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490763</v>
+        <v>490821</v>
       </c>
       <c r="R41" t="n">
-        <v>7017499</v>
+        <v>7017504</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5505,7 +5497,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5514,17 +5506,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5541,67 +5529,59 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499514</v>
+        <v>135499612</v>
       </c>
       <c r="B42" t="n">
-        <v>58143</v>
+        <v>99210</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490875</v>
+        <v>490848</v>
       </c>
       <c r="R42" t="n">
-        <v>7017397</v>
+        <v>7017375</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5636,28 +5616,19 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5674,13 +5645,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499611</v>
+        <v>135499613</v>
       </c>
       <c r="B43" t="n">
         <v>99210</v>
@@ -5723,10 +5694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490821</v>
+        <v>490878</v>
       </c>
       <c r="R43" t="n">
-        <v>7017504</v>
+        <v>7017368</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5763,7 +5734,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk.</t>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5795,13 +5766,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499612</v>
+        <v>135499614</v>
       </c>
       <c r="B44" t="n">
         <v>99210</v>
@@ -5844,10 +5815,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490848</v>
+        <v>490867</v>
       </c>
       <c r="R44" t="n">
-        <v>7017375</v>
+        <v>7017386</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5882,6 +5853,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5911,13 +5887,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499613</v>
+        <v>135499615</v>
       </c>
       <c r="B45" t="n">
         <v>99210</v>
@@ -5960,10 +5936,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490878</v>
+        <v>490860</v>
       </c>
       <c r="R45" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6032,16 +6008,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499614</v>
+        <v>135499509</v>
       </c>
       <c r="B46" t="n">
-        <v>99210</v>
+        <v>99317</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6049,28 +6025,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6081,10 +6057,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490867</v>
+        <v>490880</v>
       </c>
       <c r="R46" t="n">
-        <v>7017386</v>
+        <v>7017365</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6121,7 +6097,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Flertalet plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6139,6 +6115,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -6153,16 +6134,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499615</v>
+        <v>135499620</v>
       </c>
       <c r="B47" t="n">
-        <v>99210</v>
+        <v>108317</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6170,28 +6151,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>220083</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6202,10 +6183,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490860</v>
+        <v>490853</v>
       </c>
       <c r="R47" t="n">
-        <v>7017386</v>
+        <v>7017483</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6240,11 +6221,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6274,16 +6250,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499509</v>
+        <v>135499621</v>
       </c>
       <c r="B48" t="n">
-        <v>99317</v>
+        <v>108317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6291,28 +6267,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6323,10 +6299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490880</v>
+        <v>490837</v>
       </c>
       <c r="R48" t="n">
-        <v>7017365</v>
+        <v>7017379</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6361,11 +6337,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flertalet plantor.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6381,11 +6352,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
@@ -6400,13 +6366,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499620</v>
+        <v>135499623</v>
       </c>
       <c r="B49" t="n">
         <v>108317</v>
@@ -6438,7 +6404,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6449,10 +6415,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490853</v>
+        <v>490848</v>
       </c>
       <c r="R49" t="n">
-        <v>7017483</v>
+        <v>7017376</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6516,13 +6482,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499621</v>
+        <v>135499624</v>
       </c>
       <c r="B50" t="n">
         <v>108317</v>
@@ -6565,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490837</v>
+        <v>490861</v>
       </c>
       <c r="R50" t="n">
-        <v>7017379</v>
+        <v>7017386</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6632,13 +6598,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499623</v>
+        <v>135499625</v>
       </c>
       <c r="B51" t="n">
         <v>108317</v>
@@ -6670,7 +6636,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6681,10 +6647,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490848</v>
+        <v>490821</v>
       </c>
       <c r="R51" t="n">
-        <v>7017376</v>
+        <v>7017394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6748,13 +6714,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499624</v>
+        <v>135499626</v>
       </c>
       <c r="B52" t="n">
         <v>108317</v>
@@ -6786,7 +6752,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6797,10 +6763,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490861</v>
+        <v>490841</v>
       </c>
       <c r="R52" t="n">
-        <v>7017386</v>
+        <v>7017433</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6864,16 +6830,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499625</v>
+        <v>135499550</v>
       </c>
       <c r="B53" t="n">
-        <v>108317</v>
+        <v>108387</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6881,28 +6847,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6913,10 +6879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490821</v>
+        <v>490929</v>
       </c>
       <c r="R53" t="n">
-        <v>7017394</v>
+        <v>7017429</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6980,16 +6946,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499626</v>
+        <v>135499551</v>
       </c>
       <c r="B54" t="n">
-        <v>108317</v>
+        <v>108387</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6997,28 +6963,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -7029,10 +6995,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R54" t="n">
-        <v>7017433</v>
+        <v>7017480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7067,6 +7033,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7096,13 +7067,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499550</v>
+        <v>135499552</v>
       </c>
       <c r="B55" t="n">
         <v>108387</v>
@@ -7145,10 +7116,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490929</v>
+        <v>490867</v>
       </c>
       <c r="R55" t="n">
-        <v>7017429</v>
+        <v>7017480</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7212,13 +7183,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499551</v>
+        <v>135499553</v>
       </c>
       <c r="B56" t="n">
         <v>108387</v>
@@ -7261,10 +7232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490853</v>
+        <v>490841</v>
       </c>
       <c r="R56" t="n">
-        <v>7017480</v>
+        <v>7017457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7299,11 +7270,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7333,13 +7299,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499552</v>
+        <v>135499554</v>
       </c>
       <c r="B57" t="n">
         <v>108387</v>
@@ -7382,10 +7348,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490867</v>
+        <v>490737</v>
       </c>
       <c r="R57" t="n">
-        <v>7017480</v>
+        <v>7017474</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7449,13 +7415,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499553</v>
+        <v>135499555</v>
       </c>
       <c r="B58" t="n">
         <v>108387</v>
@@ -7498,10 +7464,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490841</v>
+        <v>490873</v>
       </c>
       <c r="R58" t="n">
-        <v>7017457</v>
+        <v>7017368</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7565,13 +7531,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499554</v>
+        <v>135499556</v>
       </c>
       <c r="B59" t="n">
         <v>108387</v>
@@ -7614,10 +7580,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490737</v>
+        <v>490863</v>
       </c>
       <c r="R59" t="n">
-        <v>7017474</v>
+        <v>7017386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7667,6 +7633,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7681,16 +7652,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499555</v>
+        <v>135499544</v>
       </c>
       <c r="B60" t="n">
-        <v>108387</v>
+        <v>111267</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7698,28 +7669,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7730,10 +7701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490873</v>
+        <v>490844</v>
       </c>
       <c r="R60" t="n">
-        <v>7017368</v>
+        <v>7017468</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7797,16 +7768,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499556</v>
+        <v>135499546</v>
       </c>
       <c r="B61" t="n">
-        <v>108387</v>
+        <v>111267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7814,28 +7785,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7846,10 +7817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490863</v>
+        <v>490780</v>
       </c>
       <c r="R61" t="n">
-        <v>7017386</v>
+        <v>7017405</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7899,11 +7870,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -7918,13 +7884,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499544</v>
+        <v>135499547</v>
       </c>
       <c r="B62" t="n">
         <v>111267</v>
@@ -7956,7 +7922,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7967,10 +7933,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490844</v>
+        <v>490858</v>
       </c>
       <c r="R62" t="n">
-        <v>7017468</v>
+        <v>7017416</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8034,13 +8000,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499546</v>
+        <v>135499548</v>
       </c>
       <c r="B63" t="n">
         <v>111267</v>
@@ -8072,7 +8038,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -8083,10 +8049,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490780</v>
+        <v>490964</v>
       </c>
       <c r="R63" t="n">
-        <v>7017405</v>
+        <v>7017356</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8136,6 +8102,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8150,16 +8121,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499547</v>
+        <v>135499617</v>
       </c>
       <c r="B64" t="n">
-        <v>111267</v>
+        <v>110263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8167,28 +8138,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220240</v>
+        <v>220294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -8199,10 +8170,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490858</v>
+        <v>490864</v>
       </c>
       <c r="R64" t="n">
-        <v>7017416</v>
+        <v>7017486</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8237,6 +8208,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8266,45 +8242,53 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499548</v>
+        <v>135499580</v>
       </c>
       <c r="B65" t="n">
-        <v>111267</v>
+        <v>99293</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -8315,10 +8299,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490964</v>
+        <v>490975</v>
       </c>
       <c r="R65" t="n">
-        <v>7017356</v>
+        <v>7017304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8353,6 +8337,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8387,45 +8376,53 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499617</v>
+        <v>135499583</v>
       </c>
       <c r="B66" t="n">
-        <v>110263</v>
+        <v>99293</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220294</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -8436,10 +8433,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490864</v>
+        <v>490768</v>
       </c>
       <c r="R66" t="n">
-        <v>7017486</v>
+        <v>7017376</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8476,7 +8473,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8494,6 +8491,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
@@ -8508,13 +8510,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499580</v>
+        <v>135499584</v>
       </c>
       <c r="B67" t="n">
         <v>99293</v>
@@ -8544,7 +8546,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8565,10 +8567,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490975</v>
+        <v>490839</v>
       </c>
       <c r="R67" t="n">
-        <v>7017304</v>
+        <v>7017351</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8605,7 +8607,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8620,12 +8622,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8642,13 +8639,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499581</v>
+        <v>135499585</v>
       </c>
       <c r="B68" t="n">
         <v>99293</v>
@@ -8678,7 +8675,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8699,10 +8696,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490951</v>
+        <v>490845</v>
       </c>
       <c r="R68" t="n">
-        <v>7017428</v>
+        <v>7017392</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8739,7 +8736,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8754,7 +8751,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8771,13 +8768,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499581</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499582</v>
+        <v>135499586</v>
       </c>
       <c r="B69" t="n">
         <v>99293</v>
@@ -8828,10 +8825,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490884</v>
+        <v>490812</v>
       </c>
       <c r="R69" t="n">
-        <v>7017471</v>
+        <v>7017401</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8868,7 +8865,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8883,7 +8880,12 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8900,13 +8902,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499582</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499583</v>
+        <v>135499588</v>
       </c>
       <c r="B70" t="n">
         <v>99293</v>
@@ -8936,7 +8938,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8957,10 +8959,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490768</v>
+        <v>490843</v>
       </c>
       <c r="R70" t="n">
-        <v>7017376</v>
+        <v>7017436</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8997,7 +8999,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9034,13 +9036,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499584</v>
+        <v>135499589</v>
       </c>
       <c r="B71" t="n">
         <v>99293</v>
@@ -9070,7 +9072,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9091,10 +9093,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490839</v>
+        <v>490967</v>
       </c>
       <c r="R71" t="n">
-        <v>7017351</v>
+        <v>7017335</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9131,7 +9133,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9146,7 +9148,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9163,13 +9170,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499585</v>
+        <v>135499590</v>
       </c>
       <c r="B72" t="n">
         <v>99293</v>
@@ -9199,7 +9206,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9220,10 +9227,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490845</v>
+        <v>490979</v>
       </c>
       <c r="R72" t="n">
-        <v>7017392</v>
+        <v>7017360</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9260,7 +9267,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9275,7 +9282,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9292,13 +9304,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499586</v>
+        <v>135499591</v>
       </c>
       <c r="B73" t="n">
         <v>99293</v>
@@ -9328,7 +9340,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9349,10 +9361,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490812</v>
+        <v>490973</v>
       </c>
       <c r="R73" t="n">
-        <v>7017401</v>
+        <v>7017399</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9389,7 +9401,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9426,13 +9438,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499588</v>
+        <v>135499592</v>
       </c>
       <c r="B74" t="n">
         <v>99293</v>
@@ -9462,7 +9474,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9483,10 +9495,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490843</v>
+        <v>490951</v>
       </c>
       <c r="R74" t="n">
-        <v>7017436</v>
+        <v>7017408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9523,7 +9535,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9560,13 +9572,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499589</v>
+        <v>135499593</v>
       </c>
       <c r="B75" t="n">
         <v>99293</v>
@@ -9596,7 +9608,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9617,10 +9629,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490967</v>
+        <v>490951</v>
       </c>
       <c r="R75" t="n">
-        <v>7017335</v>
+        <v>7017396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9657,7 +9669,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9694,13 +9706,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499590</v>
+        <v>135499594</v>
       </c>
       <c r="B76" t="n">
         <v>99293</v>
@@ -9730,7 +9742,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9751,10 +9763,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490979</v>
+        <v>490957</v>
       </c>
       <c r="R76" t="n">
-        <v>7017360</v>
+        <v>7017386</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9791,7 +9803,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9828,55 +9840,43 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499591</v>
+        <v>135499519</v>
       </c>
       <c r="B77" t="n">
-        <v>99293</v>
+        <v>98155</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490973</v>
+        <v>490752</v>
       </c>
       <c r="R77" t="n">
-        <v>7017399</v>
+        <v>7017499</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9943,11 +9943,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
@@ -9962,53 +9957,45 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499592</v>
+        <v>135499516</v>
       </c>
       <c r="B78" t="n">
-        <v>99293</v>
+        <v>99315</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -10019,10 +10006,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490951</v>
+        <v>490844</v>
       </c>
       <c r="R78" t="n">
-        <v>7017408</v>
+        <v>7017394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10057,11 +10044,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10077,11 +10059,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
@@ -10096,53 +10073,45 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499593</v>
+        <v>135499517</v>
       </c>
       <c r="B79" t="n">
-        <v>99293</v>
+        <v>99315</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -10153,10 +10122,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490951</v>
+        <v>490814</v>
       </c>
       <c r="R79" t="n">
-        <v>7017396</v>
+        <v>7017404</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10191,11 +10160,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10211,11 +10175,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
@@ -10230,53 +10189,45 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499594</v>
+        <v>135499627</v>
       </c>
       <c r="B80" t="n">
-        <v>99293</v>
+        <v>101502</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10287,10 +10238,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490957</v>
+        <v>490803</v>
       </c>
       <c r="R80" t="n">
-        <v>7017386</v>
+        <v>7017492</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10325,11 +10276,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10345,11 +10291,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
@@ -10364,16 +10305,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499519</v>
+        <v>135499628</v>
       </c>
       <c r="B81" t="n">
-        <v>98155</v>
+        <v>101502</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10381,26 +10322,30 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10409,10 +10354,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490752</v>
+        <v>490792</v>
       </c>
       <c r="R81" t="n">
-        <v>7017499</v>
+        <v>7017441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10447,11 +10392,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10481,16 +10421,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499516</v>
+        <v>135499629</v>
       </c>
       <c r="B82" t="n">
-        <v>99315</v>
+        <v>101502</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10498,28 +10438,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10530,10 +10470,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490844</v>
+        <v>490764</v>
       </c>
       <c r="R82" t="n">
-        <v>7017394</v>
+        <v>7017441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10597,16 +10537,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499517</v>
+        <v>135499630</v>
       </c>
       <c r="B83" t="n">
-        <v>99315</v>
+        <v>101502</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10614,28 +10554,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -10646,10 +10586,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490814</v>
+        <v>490798</v>
       </c>
       <c r="R83" t="n">
-        <v>7017404</v>
+        <v>7017366</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10713,13 +10653,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499627</v>
+        <v>135499631</v>
       </c>
       <c r="B84" t="n">
         <v>101502</v>
@@ -10762,10 +10702,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490803</v>
+        <v>490816</v>
       </c>
       <c r="R84" t="n">
-        <v>7017492</v>
+        <v>7017378</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10829,13 +10769,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499628</v>
+        <v>135499632</v>
       </c>
       <c r="B85" t="n">
         <v>101502</v>
@@ -10878,10 +10818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490792</v>
+        <v>490796</v>
       </c>
       <c r="R85" t="n">
-        <v>7017441</v>
+        <v>7017382</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10945,13 +10885,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499629</v>
+        <v>135499633</v>
       </c>
       <c r="B86" t="n">
         <v>101502</v>
@@ -10994,10 +10934,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490764</v>
+        <v>490782</v>
       </c>
       <c r="R86" t="n">
-        <v>7017441</v>
+        <v>7017407</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11061,13 +11001,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499630</v>
+        <v>135499634</v>
       </c>
       <c r="B87" t="n">
         <v>101502</v>
@@ -11110,10 +11050,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490798</v>
+        <v>490730</v>
       </c>
       <c r="R87" t="n">
-        <v>7017366</v>
+        <v>7017371</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11177,13 +11117,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499631</v>
+        <v>135499635</v>
       </c>
       <c r="B88" t="n">
         <v>101502</v>
@@ -11226,10 +11166,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490816</v>
+        <v>490827</v>
       </c>
       <c r="R88" t="n">
-        <v>7017378</v>
+        <v>7017356</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11293,13 +11233,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499632</v>
+        <v>135499636</v>
       </c>
       <c r="B89" t="n">
         <v>101502</v>
@@ -11342,10 +11282,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490796</v>
+        <v>490844</v>
       </c>
       <c r="R89" t="n">
-        <v>7017382</v>
+        <v>7017345</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11409,13 +11349,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499633</v>
+        <v>135499637</v>
       </c>
       <c r="B90" t="n">
         <v>101502</v>
@@ -11458,10 +11398,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490782</v>
+        <v>490852</v>
       </c>
       <c r="R90" t="n">
-        <v>7017407</v>
+        <v>7017373</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11508,7 +11448,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11525,13 +11465,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499634</v>
+        <v>135499638</v>
       </c>
       <c r="B91" t="n">
         <v>101502</v>
@@ -11574,10 +11514,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490730</v>
+        <v>490882</v>
       </c>
       <c r="R91" t="n">
-        <v>7017371</v>
+        <v>7017368</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11624,7 +11564,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11641,13 +11581,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499635</v>
+        <v>135499639</v>
       </c>
       <c r="B92" t="n">
         <v>101502</v>
@@ -11690,10 +11630,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490827</v>
+        <v>490865</v>
       </c>
       <c r="R92" t="n">
-        <v>7017356</v>
+        <v>7017386</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11757,13 +11697,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499636</v>
+        <v>135499640</v>
       </c>
       <c r="B93" t="n">
         <v>101502</v>
@@ -11806,10 +11746,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490844</v>
+        <v>490840</v>
       </c>
       <c r="R93" t="n">
-        <v>7017345</v>
+        <v>7017433</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11873,13 +11813,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499637</v>
+        <v>135499641</v>
       </c>
       <c r="B94" t="n">
         <v>101502</v>
@@ -11922,10 +11862,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490852</v>
+        <v>490880</v>
       </c>
       <c r="R94" t="n">
-        <v>7017373</v>
+        <v>7017422</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11972,7 +11912,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11989,16 +11929,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499638</v>
+        <v>135499618</v>
       </c>
       <c r="B95" t="n">
-        <v>101502</v>
+        <v>98309</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12006,21 +11946,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12038,10 +11978,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490882</v>
+        <v>490791</v>
       </c>
       <c r="R95" t="n">
-        <v>7017368</v>
+        <v>7017443</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12076,6 +12016,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -12088,7 +12033,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12105,16 +12050,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499639</v>
+        <v>135499619</v>
       </c>
       <c r="B96" t="n">
-        <v>101502</v>
+        <v>98309</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12122,25 +12067,33 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12154,10 +12107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490865</v>
+        <v>490868</v>
       </c>
       <c r="R96" t="n">
-        <v>7017386</v>
+        <v>7017387</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12192,6 +12145,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12207,6 +12165,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
@@ -12221,16 +12184,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499640</v>
+        <v>135499520</v>
       </c>
       <c r="B97" t="n">
-        <v>101502</v>
+        <v>99099</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12238,21 +12201,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>223049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12270,10 +12233,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490840</v>
+        <v>490757</v>
       </c>
       <c r="R97" t="n">
-        <v>7017433</v>
+        <v>7017472</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12337,16 +12300,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499641</v>
+        <v>135499521</v>
       </c>
       <c r="B98" t="n">
-        <v>101502</v>
+        <v>99099</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12354,21 +12317,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>223049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12386,10 +12349,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490880</v>
+        <v>490966</v>
       </c>
       <c r="R98" t="n">
-        <v>7017422</v>
+        <v>7017430</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12453,16 +12416,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499618</v>
+        <v>135499522</v>
       </c>
       <c r="B99" t="n">
-        <v>98309</v>
+        <v>99099</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12470,21 +12433,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12502,10 +12465,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490791</v>
+        <v>490920</v>
       </c>
       <c r="R99" t="n">
-        <v>7017443</v>
+        <v>7017445</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12540,11 +12503,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -12574,16 +12532,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499619</v>
+        <v>135499523</v>
       </c>
       <c r="B100" t="n">
-        <v>98309</v>
+        <v>99099</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12591,33 +12549,25 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12631,10 +12581,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490868</v>
+        <v>490912</v>
       </c>
       <c r="R100" t="n">
-        <v>7017387</v>
+        <v>7017466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12669,11 +12619,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12689,11 +12634,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
@@ -12708,13 +12648,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499520</v>
+        <v>135499524</v>
       </c>
       <c r="B101" t="n">
         <v>99099</v>
@@ -12757,10 +12697,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490757</v>
+        <v>490858</v>
       </c>
       <c r="R101" t="n">
-        <v>7017472</v>
+        <v>7017493</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12824,13 +12764,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499521</v>
+        <v>135499525</v>
       </c>
       <c r="B102" t="n">
         <v>99099</v>
@@ -12862,7 +12802,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12873,10 +12813,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490966</v>
+        <v>490804</v>
       </c>
       <c r="R102" t="n">
-        <v>7017430</v>
+        <v>7017492</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12940,13 +12880,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499522</v>
+        <v>135499526</v>
       </c>
       <c r="B103" t="n">
         <v>99099</v>
@@ -12989,10 +12929,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490920</v>
+        <v>490740</v>
       </c>
       <c r="R103" t="n">
-        <v>7017445</v>
+        <v>7017423</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13056,13 +12996,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499523</v>
+        <v>135499527</v>
       </c>
       <c r="B104" t="n">
         <v>99099</v>
@@ -13105,10 +13045,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490912</v>
+        <v>490732</v>
       </c>
       <c r="R104" t="n">
-        <v>7017466</v>
+        <v>7017370</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13172,13 +13112,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499524</v>
+        <v>135499528</v>
       </c>
       <c r="B105" t="n">
         <v>99099</v>
@@ -13221,10 +13161,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490858</v>
+        <v>490867</v>
       </c>
       <c r="R105" t="n">
-        <v>7017493</v>
+        <v>7017386</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13259,6 +13199,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -13288,13 +13233,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499525</v>
+        <v>135499529</v>
       </c>
       <c r="B106" t="n">
         <v>99099</v>
@@ -13326,7 +13271,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -13337,10 +13282,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490804</v>
+        <v>490807</v>
       </c>
       <c r="R106" t="n">
-        <v>7017492</v>
+        <v>7017431</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13404,13 +13349,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499526</v>
+        <v>135499530</v>
       </c>
       <c r="B107" t="n">
         <v>99099</v>
@@ -13442,7 +13387,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13453,10 +13398,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490740</v>
+        <v>490932</v>
       </c>
       <c r="R107" t="n">
-        <v>7017423</v>
+        <v>7017369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13520,16 +13465,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499527</v>
+        <v>135499597</v>
       </c>
       <c r="B108" t="n">
-        <v>99099</v>
+        <v>98344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13537,21 +13482,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13569,10 +13514,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490732</v>
+        <v>490969</v>
       </c>
       <c r="R108" t="n">
-        <v>7017370</v>
+        <v>7017431</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13636,16 +13581,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499528</v>
+        <v>135499598</v>
       </c>
       <c r="B109" t="n">
-        <v>99099</v>
+        <v>98344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13653,21 +13598,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13685,10 +13630,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490867</v>
+        <v>490840</v>
       </c>
       <c r="R109" t="n">
-        <v>7017386</v>
+        <v>7017457</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13723,11 +13668,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13757,16 +13697,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499529</v>
+        <v>135499599</v>
       </c>
       <c r="B110" t="n">
-        <v>99099</v>
+        <v>98344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13774,21 +13714,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13806,10 +13746,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490807</v>
+        <v>490831</v>
       </c>
       <c r="R110" t="n">
-        <v>7017431</v>
+        <v>7017486</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13873,16 +13813,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499530</v>
+        <v>135499600</v>
       </c>
       <c r="B111" t="n">
-        <v>99099</v>
+        <v>98344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13890,28 +13830,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13922,10 +13862,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490932</v>
+        <v>490797</v>
       </c>
       <c r="R111" t="n">
-        <v>7017369</v>
+        <v>7017497</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13989,13 +13929,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499597</v>
+        <v>135499601</v>
       </c>
       <c r="B112" t="n">
         <v>98344</v>
@@ -14038,10 +13978,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490969</v>
+        <v>490797</v>
       </c>
       <c r="R112" t="n">
-        <v>7017431</v>
+        <v>7017511</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14105,13 +14045,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499598</v>
+        <v>135499602</v>
       </c>
       <c r="B113" t="n">
         <v>98344</v>
@@ -14154,10 +14094,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490840</v>
+        <v>490737</v>
       </c>
       <c r="R113" t="n">
-        <v>7017457</v>
+        <v>7017473</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14221,16 +14161,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499599</v>
+        <v>135499515</v>
       </c>
       <c r="B114" t="n">
-        <v>98344</v>
+        <v>102039</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14238,21 +14178,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223358</v>
+        <v>223366</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14270,10 +14210,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490831</v>
+        <v>490788</v>
       </c>
       <c r="R114" t="n">
-        <v>7017486</v>
+        <v>7017450</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14337,16 +14277,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499600</v>
+        <v>135499532</v>
       </c>
       <c r="B115" t="n">
-        <v>98344</v>
+        <v>101392</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14354,21 +14294,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14386,10 +14326,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490797</v>
+        <v>490889</v>
       </c>
       <c r="R115" t="n">
-        <v>7017497</v>
+        <v>7017459</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14453,16 +14393,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499601</v>
+        <v>135499533</v>
       </c>
       <c r="B116" t="n">
-        <v>98344</v>
+        <v>101392</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14470,21 +14410,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14502,10 +14442,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490797</v>
+        <v>490743</v>
       </c>
       <c r="R116" t="n">
-        <v>7017511</v>
+        <v>7017495</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14569,16 +14509,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499602</v>
+        <v>135499534</v>
       </c>
       <c r="B117" t="n">
-        <v>98344</v>
+        <v>101392</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14586,21 +14526,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14621,7 +14561,7 @@
         <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017473</v>
+        <v>7017474</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14685,16 +14625,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499515</v>
+        <v>135499535</v>
       </c>
       <c r="B118" t="n">
-        <v>102039</v>
+        <v>101392</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14702,21 +14642,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>223366</v>
+        <v>224885</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14734,10 +14674,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490788</v>
+        <v>490734</v>
       </c>
       <c r="R118" t="n">
-        <v>7017450</v>
+        <v>7017429</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14801,13 +14741,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499532</v>
+        <v>135499536</v>
       </c>
       <c r="B119" t="n">
         <v>101392</v>
@@ -14850,10 +14790,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490889</v>
+        <v>490780</v>
       </c>
       <c r="R119" t="n">
-        <v>7017459</v>
+        <v>7017405</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14917,13 +14857,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499533</v>
+        <v>135499537</v>
       </c>
       <c r="B120" t="n">
         <v>101392</v>
@@ -14966,10 +14906,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490743</v>
+        <v>490751</v>
       </c>
       <c r="R120" t="n">
-        <v>7017495</v>
+        <v>7017406</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15033,13 +14973,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499537</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499534</v>
+        <v>135499538</v>
       </c>
       <c r="B121" t="n">
         <v>101392</v>
@@ -15082,10 +15022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490737</v>
+        <v>490729</v>
       </c>
       <c r="R121" t="n">
-        <v>7017474</v>
+        <v>7017373</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15149,13 +15089,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499538</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499535</v>
+        <v>135499540</v>
       </c>
       <c r="B122" t="n">
         <v>101392</v>
@@ -15198,10 +15138,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490734</v>
+        <v>490847</v>
       </c>
       <c r="R122" t="n">
-        <v>7017429</v>
+        <v>7017345</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15265,13 +15205,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499540</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499536</v>
+        <v>135499541</v>
       </c>
       <c r="B123" t="n">
         <v>101392</v>
@@ -15314,10 +15254,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490780</v>
+        <v>490856</v>
       </c>
       <c r="R123" t="n">
-        <v>7017405</v>
+        <v>7017358</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15381,13 +15321,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499541</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499537</v>
+        <v>135499542</v>
       </c>
       <c r="B124" t="n">
         <v>101392</v>
@@ -15419,7 +15359,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -15430,10 +15370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490751</v>
+        <v>490840</v>
       </c>
       <c r="R124" t="n">
-        <v>7017406</v>
+        <v>7017433</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15496,470 +15436,6 @@
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>135499538</v>
-      </c>
-      <c r="B125" t="n">
-        <v>101392</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q125" t="n">
-        <v>490729</v>
-      </c>
-      <c r="R125" t="n">
-        <v>7017373</v>
-      </c>
-      <c r="S125" t="n">
-        <v>10</v>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="inlineStr"/>
-      <c r="AG125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT125" t="inlineStr"/>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>135499540</v>
-      </c>
-      <c r="B126" t="n">
-        <v>101392</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q126" t="n">
-        <v>490847</v>
-      </c>
-      <c r="R126" t="n">
-        <v>7017345</v>
-      </c>
-      <c r="S126" t="n">
-        <v>10</v>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="inlineStr"/>
-      <c r="AG126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT126" t="inlineStr"/>
-      <c r="AW126" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>135499541</v>
-      </c>
-      <c r="B127" t="n">
-        <v>101392</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q127" t="n">
-        <v>490856</v>
-      </c>
-      <c r="R127" t="n">
-        <v>7017358</v>
-      </c>
-      <c r="S127" t="n">
-        <v>10</v>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="inlineStr"/>
-      <c r="AG127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT127" t="inlineStr"/>
-      <c r="AW127" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>135499542</v>
-      </c>
-      <c r="B128" t="n">
-        <v>101392</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>Sydväst om Smedsta, Jmt</t>
-        </is>
-      </c>
-      <c r="Q128" t="n">
-        <v>490840</v>
-      </c>
-      <c r="R128" t="n">
-        <v>7017433</v>
-      </c>
-      <c r="S128" t="n">
-        <v>10</v>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AD128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="inlineStr"/>
-      <c r="AG128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT128" t="inlineStr"/>
-      <c r="AW128" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
-      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -16090,10 +15566,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ124"/>
+  <dimension ref="A1:AZ125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135499608</v>
+        <v>135499607</v>
       </c>
       <c r="B2" t="n">
         <v>99199</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490867</v>
+        <v>490869</v>
       </c>
       <c r="R2" t="n">
-        <v>7017387</v>
+        <v>7017370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
+          <t>Minst 92 stjälkar i flertalet knippen inom ca 30 m2 yta. Troligen utanför planerad snitslad hänsynsyta i avverkningsanmäld skog (A 29064-2026).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +790,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tydligt kalkpåverkat fuktstråk.</t>
+          <t>Kalkrikt fuktstråk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,58 +812,71 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499608</t>
+          <t>https://artportalen.se/Sighting/135499607</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135499603</v>
+        <v>135499608</v>
       </c>
       <c r="B3" t="n">
-        <v>92060</v>
+        <v>99199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490968</v>
+        <v>490867</v>
       </c>
       <c r="R3" t="n">
-        <v>7017430</v>
+        <v>7017387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +913,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta. Några plantor är skadade, troligen av vilda djur. Växer intill finbräken. Precis innanför kanten av en hänsynsyta som ger alldeles för lite skyddszon om skogen avverkas intill.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,24 +931,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tydligt kalkpåverkat fuktstråk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -952,13 +950,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499603</t>
+          <t>https://artportalen.se/Sighting/135499608</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135499604</v>
+        <v>135499603</v>
       </c>
       <c r="B4" t="n">
         <v>92060</v>
@@ -1000,10 +998,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490893</v>
+        <v>490968</v>
       </c>
       <c r="R4" t="n">
-        <v>7017459</v>
+        <v>7017430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,7 +1038,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,12 +1068,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,13 +1090,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499604</t>
+          <t>https://artportalen.se/Sighting/135499603</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135499605</v>
+        <v>135499604</v>
       </c>
       <c r="B5" t="n">
         <v>92060</v>
@@ -1140,10 +1138,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490741</v>
+        <v>490893</v>
       </c>
       <c r="R5" t="n">
-        <v>7017465</v>
+        <v>7017459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,7 +1178,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1232,13 +1230,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499605</t>
+          <t>https://artportalen.se/Sighting/135499604</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135499606</v>
+        <v>135499605</v>
       </c>
       <c r="B6" t="n">
         <v>92060</v>
@@ -1280,10 +1278,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490951</v>
+        <v>490741</v>
       </c>
       <c r="R6" t="n">
-        <v>7017411</v>
+        <v>7017465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1320,7 +1318,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet fruktkroppar i två stående döende granar varav den ena granen mäter 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,12 +1348,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1372,16 +1370,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499606</t>
+          <t>https://artportalen.se/Sighting/135499605</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75185503</v>
+        <v>135499606</v>
       </c>
       <c r="B7" t="n">
-        <v>87322</v>
+        <v>92060</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,34 +1387,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1988</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490758</v>
+        <v>490951</v>
       </c>
       <c r="R7" t="n">
-        <v>7017384</v>
+        <v>7017411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1443,12 +1448,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med 39 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,73 +1471,90 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185503</t>
+          <t>https://artportalen.se/Sighting/135499606</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135499557</v>
+        <v>75185503</v>
       </c>
       <c r="B8" t="n">
-        <v>96505</v>
+        <v>87322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2812</v>
+        <v>1988</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490738</v>
+        <v>490758</v>
       </c>
       <c r="R8" t="n">
-        <v>7017396</v>
+        <v>7017384</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,12 +1581,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,32 +1599,31 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499557</t>
+          <t>https://artportalen.se/Sighting/75185503</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135499558</v>
+        <v>135499557</v>
       </c>
       <c r="B9" t="n">
         <v>96505</v>
@@ -1636,10 +1662,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490991</v>
+        <v>490738</v>
       </c>
       <c r="R9" t="n">
-        <v>7017297</v>
+        <v>7017396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1703,13 +1729,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499558</t>
+          <t>https://artportalen.se/Sighting/135499557</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135499560</v>
+        <v>135499558</v>
       </c>
       <c r="B10" t="n">
         <v>96505</v>
@@ -1748,10 +1774,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490966</v>
+        <v>490991</v>
       </c>
       <c r="R10" t="n">
-        <v>7017426</v>
+        <v>7017297</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1801,11 +1827,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1820,13 +1841,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499560</t>
+          <t>https://artportalen.se/Sighting/135499558</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135499561</v>
+        <v>135499560</v>
       </c>
       <c r="B11" t="n">
         <v>96505</v>
@@ -1865,10 +1886,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490929</v>
+        <v>490966</v>
       </c>
       <c r="R11" t="n">
-        <v>7017441</v>
+        <v>7017426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1915,7 +1936,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1932,13 +1958,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499561</t>
+          <t>https://artportalen.se/Sighting/135499560</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135499562</v>
+        <v>135499561</v>
       </c>
       <c r="B12" t="n">
         <v>96505</v>
@@ -1977,10 +2003,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490910</v>
+        <v>490929</v>
       </c>
       <c r="R12" t="n">
-        <v>7017467</v>
+        <v>7017441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2044,13 +2070,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499562</t>
+          <t>https://artportalen.se/Sighting/135499561</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135499563</v>
+        <v>135499562</v>
       </c>
       <c r="B13" t="n">
         <v>96505</v>
@@ -2089,10 +2115,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490878</v>
+        <v>490910</v>
       </c>
       <c r="R13" t="n">
-        <v>7017474</v>
+        <v>7017467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2139,7 +2165,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2156,13 +2182,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499563</t>
+          <t>https://artportalen.se/Sighting/135499562</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135499564</v>
+        <v>135499563</v>
       </c>
       <c r="B14" t="n">
         <v>96505</v>
@@ -2201,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490883</v>
+        <v>490878</v>
       </c>
       <c r="R14" t="n">
-        <v>7017462</v>
+        <v>7017474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2251,7 +2277,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2268,13 +2294,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499564</t>
+          <t>https://artportalen.se/Sighting/135499563</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135499565</v>
+        <v>135499564</v>
       </c>
       <c r="B15" t="n">
         <v>96505</v>
@@ -2313,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490756</v>
+        <v>490883</v>
       </c>
       <c r="R15" t="n">
-        <v>7017472</v>
+        <v>7017462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2363,7 +2389,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2380,13 +2406,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499565</t>
+          <t>https://artportalen.se/Sighting/135499564</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135499566</v>
+        <v>135499565</v>
       </c>
       <c r="B16" t="n">
         <v>96505</v>
@@ -2425,10 +2451,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490790</v>
+        <v>490756</v>
       </c>
       <c r="R16" t="n">
-        <v>7017441</v>
+        <v>7017472</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2492,13 +2518,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499566</t>
+          <t>https://artportalen.se/Sighting/135499565</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135499567</v>
+        <v>135499566</v>
       </c>
       <c r="B17" t="n">
         <v>96505</v>
@@ -2537,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490732</v>
+        <v>490790</v>
       </c>
       <c r="R17" t="n">
-        <v>7017442</v>
+        <v>7017441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2587,7 +2613,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2604,13 +2630,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499567</t>
+          <t>https://artportalen.se/Sighting/135499566</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135499568</v>
+        <v>135499567</v>
       </c>
       <c r="B18" t="n">
         <v>96505</v>
@@ -2649,10 +2675,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490781</v>
+        <v>490732</v>
       </c>
       <c r="R18" t="n">
-        <v>7017407</v>
+        <v>7017442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2699,7 +2725,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,13 +2742,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499568</t>
+          <t>https://artportalen.se/Sighting/135499567</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135499569</v>
+        <v>135499568</v>
       </c>
       <c r="B19" t="n">
         <v>96505</v>
@@ -2761,10 +2787,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490731</v>
+        <v>490781</v>
       </c>
       <c r="R19" t="n">
-        <v>7017371</v>
+        <v>7017407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,11 +2840,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2833,13 +2854,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499569</t>
+          <t>https://artportalen.se/Sighting/135499568</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135499570</v>
+        <v>135499569</v>
       </c>
       <c r="B20" t="n">
         <v>96505</v>
@@ -2878,10 +2899,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490854</v>
+        <v>490731</v>
       </c>
       <c r="R20" t="n">
-        <v>7017345</v>
+        <v>7017371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,6 +2952,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2945,13 +2971,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499570</t>
+          <t>https://artportalen.se/Sighting/135499569</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135499571</v>
+        <v>135499570</v>
       </c>
       <c r="B21" t="n">
         <v>96505</v>
@@ -2990,10 +3016,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490878</v>
+        <v>490854</v>
       </c>
       <c r="R21" t="n">
-        <v>7017366</v>
+        <v>7017345</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3028,11 +3054,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3062,13 +3083,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499571</t>
+          <t>https://artportalen.se/Sighting/135499570</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135499572</v>
+        <v>135499571</v>
       </c>
       <c r="B22" t="n">
         <v>96505</v>
@@ -3107,10 +3128,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490867</v>
+        <v>490878</v>
       </c>
       <c r="R22" t="n">
-        <v>7017386</v>
+        <v>7017366</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,6 +3166,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer här i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3174,13 +3200,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499572</t>
+          <t>https://artportalen.se/Sighting/135499571</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135499573</v>
+        <v>135499572</v>
       </c>
       <c r="B23" t="n">
         <v>96505</v>
@@ -3219,10 +3245,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490840</v>
+        <v>490867</v>
       </c>
       <c r="R23" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3286,13 +3312,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499573</t>
+          <t>https://artportalen.se/Sighting/135499572</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135499574</v>
+        <v>135499573</v>
       </c>
       <c r="B24" t="n">
         <v>96505</v>
@@ -3331,10 +3357,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490844</v>
+        <v>490840</v>
       </c>
       <c r="R24" t="n">
-        <v>7017436</v>
+        <v>7017433</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3398,13 +3424,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499574</t>
+          <t>https://artportalen.se/Sighting/135499573</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135499575</v>
+        <v>135499574</v>
       </c>
       <c r="B25" t="n">
         <v>96505</v>
@@ -3443,10 +3469,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490872</v>
+        <v>490844</v>
       </c>
       <c r="R25" t="n">
-        <v>7017426</v>
+        <v>7017436</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3510,13 +3536,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499575</t>
+          <t>https://artportalen.se/Sighting/135499574</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135499576</v>
+        <v>135499575</v>
       </c>
       <c r="B26" t="n">
         <v>96505</v>
@@ -3555,10 +3581,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490917</v>
+        <v>490872</v>
       </c>
       <c r="R26" t="n">
-        <v>7017402</v>
+        <v>7017426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3622,13 +3648,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499576</t>
+          <t>https://artportalen.se/Sighting/135499575</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135499577</v>
+        <v>135499576</v>
       </c>
       <c r="B27" t="n">
         <v>96505</v>
@@ -3667,10 +3693,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490931</v>
+        <v>490917</v>
       </c>
       <c r="R27" t="n">
-        <v>7017371</v>
+        <v>7017402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3720,11 +3746,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3739,13 +3760,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499577</t>
+          <t>https://artportalen.se/Sighting/135499576</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135499578</v>
+        <v>135499577</v>
       </c>
       <c r="B28" t="n">
         <v>96505</v>
@@ -3784,10 +3805,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490951</v>
+        <v>490931</v>
       </c>
       <c r="R28" t="n">
-        <v>7017390</v>
+        <v>7017371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3856,13 +3877,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499578</t>
+          <t>https://artportalen.se/Sighting/135499577</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135499579</v>
+        <v>135499578</v>
       </c>
       <c r="B29" t="n">
         <v>96505</v>
@@ -3901,10 +3922,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490976</v>
+        <v>490951</v>
       </c>
       <c r="R29" t="n">
-        <v>7017311</v>
+        <v>7017390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3973,16 +3994,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499579</t>
+          <t>https://artportalen.se/Sighting/135499578</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>91488964</v>
+        <v>135499579</v>
       </c>
       <c r="B30" t="n">
-        <v>92632</v>
+        <v>96505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3990,37 +4011,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>2812</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490939</v>
+        <v>490976</v>
       </c>
       <c r="R30" t="n">
-        <v>7017412</v>
+        <v>7017311</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4044,12 +4069,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4058,59 +4083,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91488964</t>
+          <t>https://artportalen.se/Sighting/135499579</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>75185505</v>
+        <v>91488964</v>
       </c>
       <c r="B31" t="n">
-        <v>89156</v>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4412</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4120,13 +4152,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490781</v>
+        <v>490939</v>
       </c>
       <c r="R31" t="n">
-        <v>7017384</v>
+        <v>7017412</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4164,19 +4196,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4186,54 +4217,51 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185505</t>
+          <t>https://artportalen.se/Sighting/91488964</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135499609</v>
+        <v>75185505</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>89156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sydväst om Smedsta, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490849</v>
+        <v>490781</v>
       </c>
       <c r="R32" t="n">
-        <v>7017392</v>
+        <v>7017384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4260,17 +4288,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4283,52 +4306,31 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sofie Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499609</t>
+          <t>https://artportalen.se/Sighting/75185505</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135499610</v>
+        <v>135499609</v>
       </c>
       <c r="B33" t="n">
         <v>79443</v>
@@ -4366,10 +4368,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490859</v>
+        <v>490849</v>
       </c>
       <c r="R33" t="n">
-        <v>7017416</v>
+        <v>7017392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4404,6 +4406,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4431,12 +4438,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4453,67 +4460,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499610</t>
+          <t>https://artportalen.se/Sighting/135499609</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135499531</v>
+        <v>135499610</v>
       </c>
       <c r="B34" t="n">
-        <v>58096</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100090</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490781</v>
+        <v>490859</v>
       </c>
       <c r="R34" t="n">
-        <v>7017369</v>
+        <v>7017416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4548,23 +4542,39 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Synobservation av en individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4581,16 +4591,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499531</t>
+          <t>https://artportalen.se/Sighting/135499610</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135499510</v>
+        <v>135499531</v>
       </c>
       <c r="B35" t="n">
-        <v>57982</v>
+        <v>58096</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4598,16 +4608,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100090</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4615,12 +4625,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4634,10 +4648,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490891</v>
+        <v>490781</v>
       </c>
       <c r="R35" t="n">
-        <v>7017451</v>
+        <v>7017369</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4674,7 +4688,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
+          <t>Synobservation av en individ med lockläte.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4688,27 +4702,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4725,16 +4719,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499510</t>
+          <t>https://artportalen.se/Sighting/135499531</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499511</v>
+        <v>135499549</v>
       </c>
       <c r="B36" t="n">
-        <v>57982</v>
+        <v>58238</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,29 +4736,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102980</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4778,10 +4776,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490785</v>
+        <v>490804</v>
       </c>
       <c r="R36" t="n">
-        <v>7017521</v>
+        <v>7017502</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4818,7 +4816,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Minst 1 överflygande med sång.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4833,26 +4831,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4869,33 +4847,33 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499511</t>
+          <t>https://artportalen.se/Sighting/135499549</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499512</v>
+        <v>135499596</v>
       </c>
       <c r="B37" t="n">
-        <v>57982</v>
+        <v>58241</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>102981</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4903,29 +4881,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490783</v>
+        <v>490875</v>
       </c>
       <c r="R37" t="n">
-        <v>7017360</v>
+        <v>7017470</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4962,7 +4940,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4977,31 +4955,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5018,43 +4971,43 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499512</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499596</v>
+        <v>135499513</v>
       </c>
       <c r="B38" t="n">
-        <v>58241</v>
+        <v>58143</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102981</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5064,17 +5017,21 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490875</v>
+        <v>490763</v>
       </c>
       <c r="R38" t="n">
-        <v>7017470</v>
+        <v>7017499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5111,7 +5068,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5125,7 +5082,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5142,13 +5104,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499513</v>
+        <v>135499514</v>
       </c>
       <c r="B39" t="n">
         <v>58143</v>
@@ -5178,7 +5140,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5199,10 +5161,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490763</v>
+        <v>490875</v>
       </c>
       <c r="R39" t="n">
-        <v>7017499</v>
+        <v>7017397</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5239,7 +5201,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5253,12 +5215,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5275,67 +5237,59 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499514</v>
+        <v>135499611</v>
       </c>
       <c r="B40" t="n">
-        <v>58143</v>
+        <v>99210</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490875</v>
+        <v>490821</v>
       </c>
       <c r="R40" t="n">
-        <v>7017397</v>
+        <v>7017504</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5372,7 +5326,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5381,17 +5335,13 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5408,13 +5358,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499611</v>
+        <v>135499612</v>
       </c>
       <c r="B41" t="n">
         <v>99210</v>
@@ -5446,7 +5396,7 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5457,10 +5407,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490821</v>
+        <v>490848</v>
       </c>
       <c r="R41" t="n">
-        <v>7017504</v>
+        <v>7017375</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5495,11 +5445,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5529,13 +5474,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499612</v>
+        <v>135499613</v>
       </c>
       <c r="B42" t="n">
         <v>99210</v>
@@ -5567,7 +5512,7 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5578,10 +5523,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490848</v>
+        <v>490878</v>
       </c>
       <c r="R42" t="n">
-        <v>7017375</v>
+        <v>7017368</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5616,6 +5561,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5645,13 +5595,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499613</v>
+        <v>135499614</v>
       </c>
       <c r="B43" t="n">
         <v>99210</v>
@@ -5683,7 +5633,7 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5694,10 +5644,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490878</v>
+        <v>490867</v>
       </c>
       <c r="R43" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5766,13 +5716,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499614</v>
+        <v>135499615</v>
       </c>
       <c r="B44" t="n">
         <v>99210</v>
@@ -5804,7 +5754,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5815,7 +5765,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490867</v>
+        <v>490860</v>
       </c>
       <c r="R44" t="n">
         <v>7017386</v>
@@ -5887,16 +5837,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499615</v>
+        <v>135499509</v>
       </c>
       <c r="B45" t="n">
-        <v>99210</v>
+        <v>99317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5904,28 +5854,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -5936,10 +5886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490860</v>
+        <v>490880</v>
       </c>
       <c r="R45" t="n">
-        <v>7017386</v>
+        <v>7017365</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5976,7 +5926,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Flertalet plantor.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5994,6 +5944,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
@@ -6008,16 +5963,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499509</v>
+        <v>135499620</v>
       </c>
       <c r="B46" t="n">
-        <v>99317</v>
+        <v>108317</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6025,28 +5980,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6057,10 +6012,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490880</v>
+        <v>490853</v>
       </c>
       <c r="R46" t="n">
-        <v>7017365</v>
+        <v>7017483</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6095,11 +6050,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Flertalet plantor.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6115,11 +6065,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -6134,13 +6079,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499620</v>
+        <v>135499621</v>
       </c>
       <c r="B47" t="n">
         <v>108317</v>
@@ -6172,7 +6117,7 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6183,10 +6128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490853</v>
+        <v>490837</v>
       </c>
       <c r="R47" t="n">
-        <v>7017483</v>
+        <v>7017379</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,13 +6195,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499621</v>
+        <v>135499623</v>
       </c>
       <c r="B48" t="n">
         <v>108317</v>
@@ -6299,10 +6244,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490837</v>
+        <v>490848</v>
       </c>
       <c r="R48" t="n">
-        <v>7017379</v>
+        <v>7017376</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6366,13 +6311,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499623</v>
+        <v>135499624</v>
       </c>
       <c r="B49" t="n">
         <v>108317</v>
@@ -6415,10 +6360,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490848</v>
+        <v>490861</v>
       </c>
       <c r="R49" t="n">
-        <v>7017376</v>
+        <v>7017386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6482,13 +6427,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499624</v>
+        <v>135499625</v>
       </c>
       <c r="B50" t="n">
         <v>108317</v>
@@ -6520,7 +6465,7 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -6531,10 +6476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490861</v>
+        <v>490821</v>
       </c>
       <c r="R50" t="n">
-        <v>7017386</v>
+        <v>7017394</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6598,13 +6543,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499625</v>
+        <v>135499626</v>
       </c>
       <c r="B51" t="n">
         <v>108317</v>
@@ -6647,10 +6592,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490821</v>
+        <v>490841</v>
       </c>
       <c r="R51" t="n">
-        <v>7017394</v>
+        <v>7017433</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6714,16 +6659,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499626</v>
+        <v>135499550</v>
       </c>
       <c r="B52" t="n">
-        <v>108317</v>
+        <v>108387</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6731,28 +6676,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6763,10 +6708,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490841</v>
+        <v>490929</v>
       </c>
       <c r="R52" t="n">
-        <v>7017433</v>
+        <v>7017429</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6830,13 +6775,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499550</v>
+        <v>135499551</v>
       </c>
       <c r="B53" t="n">
         <v>108387</v>
@@ -6879,10 +6824,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490929</v>
+        <v>490853</v>
       </c>
       <c r="R53" t="n">
-        <v>7017429</v>
+        <v>7017480</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6917,6 +6862,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6946,13 +6896,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499551</v>
+        <v>135499552</v>
       </c>
       <c r="B54" t="n">
         <v>108387</v>
@@ -6995,7 +6945,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490853</v>
+        <v>490867</v>
       </c>
       <c r="R54" t="n">
         <v>7017480</v>
@@ -7033,11 +6983,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7067,13 +7012,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499552</v>
+        <v>135499553</v>
       </c>
       <c r="B55" t="n">
         <v>108387</v>
@@ -7116,10 +7061,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490867</v>
+        <v>490841</v>
       </c>
       <c r="R55" t="n">
-        <v>7017480</v>
+        <v>7017457</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7183,13 +7128,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499553</v>
+        <v>135499554</v>
       </c>
       <c r="B56" t="n">
         <v>108387</v>
@@ -7232,10 +7177,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490841</v>
+        <v>490737</v>
       </c>
       <c r="R56" t="n">
-        <v>7017457</v>
+        <v>7017474</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7299,13 +7244,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499554</v>
+        <v>135499555</v>
       </c>
       <c r="B57" t="n">
         <v>108387</v>
@@ -7348,10 +7293,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490737</v>
+        <v>490873</v>
       </c>
       <c r="R57" t="n">
-        <v>7017474</v>
+        <v>7017368</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7415,13 +7360,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499555</v>
+        <v>135499556</v>
       </c>
       <c r="B58" t="n">
         <v>108387</v>
@@ -7464,10 +7409,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490873</v>
+        <v>490863</v>
       </c>
       <c r="R58" t="n">
-        <v>7017368</v>
+        <v>7017386</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7517,6 +7462,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
@@ -7531,16 +7481,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499556</v>
+        <v>135499544</v>
       </c>
       <c r="B59" t="n">
-        <v>108387</v>
+        <v>111267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7548,28 +7498,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -7580,10 +7530,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490863</v>
+        <v>490844</v>
       </c>
       <c r="R59" t="n">
-        <v>7017386</v>
+        <v>7017468</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7633,11 +7583,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7652,13 +7597,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499544</v>
+        <v>135499546</v>
       </c>
       <c r="B60" t="n">
         <v>111267</v>
@@ -7701,10 +7646,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490844</v>
+        <v>490780</v>
       </c>
       <c r="R60" t="n">
-        <v>7017468</v>
+        <v>7017405</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7768,13 +7713,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499546</v>
+        <v>135499547</v>
       </c>
       <c r="B61" t="n">
         <v>111267</v>
@@ -7806,7 +7751,7 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7817,10 +7762,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490780</v>
+        <v>490858</v>
       </c>
       <c r="R61" t="n">
-        <v>7017405</v>
+        <v>7017416</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7884,13 +7829,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499547</v>
+        <v>135499548</v>
       </c>
       <c r="B62" t="n">
         <v>111267</v>
@@ -7922,7 +7867,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7933,10 +7878,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490858</v>
+        <v>490964</v>
       </c>
       <c r="R62" t="n">
-        <v>7017416</v>
+        <v>7017356</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7986,6 +7931,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -8000,16 +7950,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499548</v>
+        <v>135499617</v>
       </c>
       <c r="B63" t="n">
-        <v>111267</v>
+        <v>110263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8017,28 +7967,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220240</v>
+        <v>220294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -8049,10 +7999,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490964</v>
+        <v>490864</v>
       </c>
       <c r="R63" t="n">
-        <v>7017356</v>
+        <v>7017486</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8087,6 +8037,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8102,11 +8057,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8121,45 +8071,53 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499617</v>
+        <v>135499580</v>
       </c>
       <c r="B64" t="n">
-        <v>110263</v>
+        <v>99293</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220294</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -8170,10 +8128,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490864</v>
+        <v>490975</v>
       </c>
       <c r="R64" t="n">
-        <v>7017486</v>
+        <v>7017304</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8210,7 +8168,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8228,6 +8186,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
@@ -8242,13 +8205,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499580</v>
+        <v>135499581</v>
       </c>
       <c r="B65" t="n">
         <v>99293</v>
@@ -8278,7 +8241,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8299,10 +8262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490975</v>
+        <v>490951</v>
       </c>
       <c r="R65" t="n">
-        <v>7017304</v>
+        <v>7017428</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8339,7 +8302,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
+          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8357,11 +8320,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
@@ -8376,13 +8334,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499581</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499583</v>
+        <v>135499582</v>
       </c>
       <c r="B66" t="n">
         <v>99293</v>
@@ -8412,7 +8370,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8433,10 +8391,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490768</v>
+        <v>490884</v>
       </c>
       <c r="R66" t="n">
-        <v>7017376</v>
+        <v>7017471</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8473,7 +8431,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8488,12 +8446,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8510,13 +8463,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499582</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499584</v>
+        <v>135499583</v>
       </c>
       <c r="B67" t="n">
         <v>99293</v>
@@ -8546,7 +8499,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8567,10 +8520,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490839</v>
+        <v>490768</v>
       </c>
       <c r="R67" t="n">
-        <v>7017351</v>
+        <v>7017376</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8607,7 +8560,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8622,7 +8575,12 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8639,13 +8597,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499585</v>
+        <v>135499584</v>
       </c>
       <c r="B68" t="n">
         <v>99293</v>
@@ -8675,7 +8633,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8696,10 +8654,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490845</v>
+        <v>490839</v>
       </c>
       <c r="R68" t="n">
-        <v>7017392</v>
+        <v>7017351</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8736,7 +8694,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8768,13 +8726,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499586</v>
+        <v>135499585</v>
       </c>
       <c r="B69" t="n">
         <v>99293</v>
@@ -8804,7 +8762,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8825,10 +8783,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490812</v>
+        <v>490845</v>
       </c>
       <c r="R69" t="n">
-        <v>7017401</v>
+        <v>7017392</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8865,7 +8823,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8880,12 +8838,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8902,13 +8855,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499588</v>
+        <v>135499586</v>
       </c>
       <c r="B70" t="n">
         <v>99293</v>
@@ -8938,7 +8891,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8959,10 +8912,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490843</v>
+        <v>490812</v>
       </c>
       <c r="R70" t="n">
-        <v>7017436</v>
+        <v>7017401</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8999,7 +8952,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9036,13 +8989,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499589</v>
+        <v>135499588</v>
       </c>
       <c r="B71" t="n">
         <v>99293</v>
@@ -9072,7 +9025,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9093,10 +9046,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490967</v>
+        <v>490843</v>
       </c>
       <c r="R71" t="n">
-        <v>7017335</v>
+        <v>7017436</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9133,7 +9086,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9170,13 +9123,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499590</v>
+        <v>135499589</v>
       </c>
       <c r="B72" t="n">
         <v>99293</v>
@@ -9206,7 +9159,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9227,10 +9180,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490979</v>
+        <v>490967</v>
       </c>
       <c r="R72" t="n">
-        <v>7017360</v>
+        <v>7017335</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9267,7 +9220,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9304,13 +9257,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499591</v>
+        <v>135499590</v>
       </c>
       <c r="B73" t="n">
         <v>99293</v>
@@ -9340,7 +9293,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9361,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490973</v>
+        <v>490979</v>
       </c>
       <c r="R73" t="n">
-        <v>7017399</v>
+        <v>7017360</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9401,7 +9354,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9438,13 +9391,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499592</v>
+        <v>135499591</v>
       </c>
       <c r="B74" t="n">
         <v>99293</v>
@@ -9474,7 +9427,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9495,10 +9448,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490951</v>
+        <v>490973</v>
       </c>
       <c r="R74" t="n">
-        <v>7017408</v>
+        <v>7017399</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9535,7 +9488,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9572,13 +9525,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499593</v>
+        <v>135499592</v>
       </c>
       <c r="B75" t="n">
         <v>99293</v>
@@ -9608,7 +9561,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9632,7 +9585,7 @@
         <v>490951</v>
       </c>
       <c r="R75" t="n">
-        <v>7017396</v>
+        <v>7017408</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9669,7 +9622,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9706,13 +9659,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499594</v>
+        <v>135499593</v>
       </c>
       <c r="B76" t="n">
         <v>99293</v>
@@ -9742,7 +9695,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9763,10 +9716,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490957</v>
+        <v>490951</v>
       </c>
       <c r="R76" t="n">
-        <v>7017386</v>
+        <v>7017396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9803,7 +9756,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9840,43 +9793,55 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499519</v>
+        <v>135499594</v>
       </c>
       <c r="B77" t="n">
-        <v>98155</v>
+        <v>99293</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9885,10 +9850,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490752</v>
+        <v>490957</v>
       </c>
       <c r="R77" t="n">
-        <v>7017499</v>
+        <v>7017386</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9925,7 +9890,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9943,6 +9908,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
@@ -9957,16 +9927,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499516</v>
+        <v>135499519</v>
       </c>
       <c r="B78" t="n">
-        <v>99315</v>
+        <v>98155</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9974,30 +9944,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -10006,10 +9972,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490844</v>
+        <v>490752</v>
       </c>
       <c r="R78" t="n">
-        <v>7017394</v>
+        <v>7017499</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10044,6 +10010,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10073,13 +10044,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499517</v>
+        <v>135499516</v>
       </c>
       <c r="B79" t="n">
         <v>99315</v>
@@ -10122,10 +10093,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490814</v>
+        <v>490844</v>
       </c>
       <c r="R79" t="n">
-        <v>7017404</v>
+        <v>7017394</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10189,16 +10160,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499627</v>
+        <v>135499517</v>
       </c>
       <c r="B80" t="n">
-        <v>101502</v>
+        <v>99315</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10206,28 +10177,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10238,10 +10209,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490803</v>
+        <v>490814</v>
       </c>
       <c r="R80" t="n">
-        <v>7017492</v>
+        <v>7017404</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10305,13 +10276,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499628</v>
+        <v>135499627</v>
       </c>
       <c r="B81" t="n">
         <v>101502</v>
@@ -10354,10 +10325,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490792</v>
+        <v>490803</v>
       </c>
       <c r="R81" t="n">
-        <v>7017441</v>
+        <v>7017492</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10421,13 +10392,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499629</v>
+        <v>135499628</v>
       </c>
       <c r="B82" t="n">
         <v>101502</v>
@@ -10470,7 +10441,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490764</v>
+        <v>490792</v>
       </c>
       <c r="R82" t="n">
         <v>7017441</v>
@@ -10537,13 +10508,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499630</v>
+        <v>135499629</v>
       </c>
       <c r="B83" t="n">
         <v>101502</v>
@@ -10586,10 +10557,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490798</v>
+        <v>490764</v>
       </c>
       <c r="R83" t="n">
-        <v>7017366</v>
+        <v>7017441</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10653,13 +10624,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499631</v>
+        <v>135499630</v>
       </c>
       <c r="B84" t="n">
         <v>101502</v>
@@ -10702,10 +10673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490816</v>
+        <v>490798</v>
       </c>
       <c r="R84" t="n">
-        <v>7017378</v>
+        <v>7017366</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10769,13 +10740,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499632</v>
+        <v>135499631</v>
       </c>
       <c r="B85" t="n">
         <v>101502</v>
@@ -10818,10 +10789,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490796</v>
+        <v>490816</v>
       </c>
       <c r="R85" t="n">
-        <v>7017382</v>
+        <v>7017378</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10885,13 +10856,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499633</v>
+        <v>135499632</v>
       </c>
       <c r="B86" t="n">
         <v>101502</v>
@@ -10934,10 +10905,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490782</v>
+        <v>490796</v>
       </c>
       <c r="R86" t="n">
-        <v>7017407</v>
+        <v>7017382</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11001,13 +10972,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499634</v>
+        <v>135499633</v>
       </c>
       <c r="B87" t="n">
         <v>101502</v>
@@ -11050,10 +11021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490730</v>
+        <v>490782</v>
       </c>
       <c r="R87" t="n">
-        <v>7017371</v>
+        <v>7017407</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11117,13 +11088,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499635</v>
+        <v>135499634</v>
       </c>
       <c r="B88" t="n">
         <v>101502</v>
@@ -11166,10 +11137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490827</v>
+        <v>490730</v>
       </c>
       <c r="R88" t="n">
-        <v>7017356</v>
+        <v>7017371</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11233,13 +11204,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499636</v>
+        <v>135499635</v>
       </c>
       <c r="B89" t="n">
         <v>101502</v>
@@ -11282,10 +11253,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490844</v>
+        <v>490827</v>
       </c>
       <c r="R89" t="n">
-        <v>7017345</v>
+        <v>7017356</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11349,13 +11320,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499637</v>
+        <v>135499636</v>
       </c>
       <c r="B90" t="n">
         <v>101502</v>
@@ -11398,10 +11369,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490852</v>
+        <v>490844</v>
       </c>
       <c r="R90" t="n">
-        <v>7017373</v>
+        <v>7017345</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11448,7 +11419,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11465,13 +11436,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499638</v>
+        <v>135499637</v>
       </c>
       <c r="B91" t="n">
         <v>101502</v>
@@ -11514,10 +11485,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490882</v>
+        <v>490852</v>
       </c>
       <c r="R91" t="n">
-        <v>7017368</v>
+        <v>7017373</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11581,13 +11552,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499639</v>
+        <v>135499638</v>
       </c>
       <c r="B92" t="n">
         <v>101502</v>
@@ -11630,10 +11601,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490865</v>
+        <v>490882</v>
       </c>
       <c r="R92" t="n">
-        <v>7017386</v>
+        <v>7017368</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11680,7 +11651,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11697,13 +11668,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499640</v>
+        <v>135499639</v>
       </c>
       <c r="B93" t="n">
         <v>101502</v>
@@ -11746,10 +11717,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490840</v>
+        <v>490865</v>
       </c>
       <c r="R93" t="n">
-        <v>7017433</v>
+        <v>7017386</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11813,13 +11784,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499641</v>
+        <v>135499640</v>
       </c>
       <c r="B94" t="n">
         <v>101502</v>
@@ -11862,10 +11833,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490880</v>
+        <v>490840</v>
       </c>
       <c r="R94" t="n">
-        <v>7017422</v>
+        <v>7017433</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11929,16 +11900,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499618</v>
+        <v>135499641</v>
       </c>
       <c r="B95" t="n">
-        <v>98309</v>
+        <v>101502</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11946,21 +11917,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11978,10 +11949,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490791</v>
+        <v>490880</v>
       </c>
       <c r="R95" t="n">
-        <v>7017443</v>
+        <v>7017422</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12016,11 +11987,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -12050,13 +12016,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499619</v>
+        <v>135499618</v>
       </c>
       <c r="B96" t="n">
         <v>98309</v>
@@ -12084,16 +12050,8 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12107,10 +12065,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490868</v>
+        <v>490791</v>
       </c>
       <c r="R96" t="n">
-        <v>7017387</v>
+        <v>7017443</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12147,7 +12105,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+          <t>Relativt rikligt i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12165,11 +12123,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
@@ -12184,16 +12137,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499520</v>
+        <v>135499619</v>
       </c>
       <c r="B97" t="n">
-        <v>99099</v>
+        <v>98309</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12201,25 +12154,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12233,10 +12194,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490757</v>
+        <v>490868</v>
       </c>
       <c r="R97" t="n">
-        <v>7017472</v>
+        <v>7017387</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12271,6 +12232,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12286,6 +12252,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
@@ -12300,13 +12271,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499521</v>
+        <v>135499520</v>
       </c>
       <c r="B98" t="n">
         <v>99099</v>
@@ -12349,10 +12320,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490966</v>
+        <v>490757</v>
       </c>
       <c r="R98" t="n">
-        <v>7017430</v>
+        <v>7017472</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12416,13 +12387,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499522</v>
+        <v>135499521</v>
       </c>
       <c r="B99" t="n">
         <v>99099</v>
@@ -12465,10 +12436,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490920</v>
+        <v>490966</v>
       </c>
       <c r="R99" t="n">
-        <v>7017445</v>
+        <v>7017430</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12532,13 +12503,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499523</v>
+        <v>135499522</v>
       </c>
       <c r="B100" t="n">
         <v>99099</v>
@@ -12581,10 +12552,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490912</v>
+        <v>490920</v>
       </c>
       <c r="R100" t="n">
-        <v>7017466</v>
+        <v>7017445</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12648,13 +12619,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499524</v>
+        <v>135499523</v>
       </c>
       <c r="B101" t="n">
         <v>99099</v>
@@ -12697,10 +12668,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490858</v>
+        <v>490912</v>
       </c>
       <c r="R101" t="n">
-        <v>7017493</v>
+        <v>7017466</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12764,13 +12735,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499525</v>
+        <v>135499524</v>
       </c>
       <c r="B102" t="n">
         <v>99099</v>
@@ -12802,7 +12773,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12813,10 +12784,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490804</v>
+        <v>490858</v>
       </c>
       <c r="R102" t="n">
-        <v>7017492</v>
+        <v>7017493</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12880,13 +12851,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499526</v>
+        <v>135499525</v>
       </c>
       <c r="B103" t="n">
         <v>99099</v>
@@ -12918,7 +12889,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12929,10 +12900,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490740</v>
+        <v>490804</v>
       </c>
       <c r="R103" t="n">
-        <v>7017423</v>
+        <v>7017492</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12996,13 +12967,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499527</v>
+        <v>135499526</v>
       </c>
       <c r="B104" t="n">
         <v>99099</v>
@@ -13045,10 +13016,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490732</v>
+        <v>490740</v>
       </c>
       <c r="R104" t="n">
-        <v>7017370</v>
+        <v>7017423</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13112,13 +13083,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499528</v>
+        <v>135499527</v>
       </c>
       <c r="B105" t="n">
         <v>99099</v>
@@ -13161,10 +13132,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490867</v>
+        <v>490732</v>
       </c>
       <c r="R105" t="n">
-        <v>7017386</v>
+        <v>7017370</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13199,11 +13170,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -13233,13 +13199,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499529</v>
+        <v>135499528</v>
       </c>
       <c r="B106" t="n">
         <v>99099</v>
@@ -13282,10 +13248,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490807</v>
+        <v>490867</v>
       </c>
       <c r="R106" t="n">
-        <v>7017431</v>
+        <v>7017386</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13320,6 +13286,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -13349,13 +13320,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499530</v>
+        <v>135499529</v>
       </c>
       <c r="B107" t="n">
         <v>99099</v>
@@ -13387,7 +13358,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13398,10 +13369,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490932</v>
+        <v>490807</v>
       </c>
       <c r="R107" t="n">
-        <v>7017369</v>
+        <v>7017431</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13465,16 +13436,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499597</v>
+        <v>135499530</v>
       </c>
       <c r="B108" t="n">
-        <v>98344</v>
+        <v>99099</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13482,28 +13453,28 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -13514,10 +13485,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490969</v>
+        <v>490932</v>
       </c>
       <c r="R108" t="n">
-        <v>7017431</v>
+        <v>7017369</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13581,13 +13552,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499598</v>
+        <v>135499597</v>
       </c>
       <c r="B109" t="n">
         <v>98344</v>
@@ -13630,10 +13601,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490840</v>
+        <v>490969</v>
       </c>
       <c r="R109" t="n">
-        <v>7017457</v>
+        <v>7017431</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13697,13 +13668,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499599</v>
+        <v>135499598</v>
       </c>
       <c r="B110" t="n">
         <v>98344</v>
@@ -13746,10 +13717,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490831</v>
+        <v>490840</v>
       </c>
       <c r="R110" t="n">
-        <v>7017486</v>
+        <v>7017457</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13813,13 +13784,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499600</v>
+        <v>135499599</v>
       </c>
       <c r="B111" t="n">
         <v>98344</v>
@@ -13862,10 +13833,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490797</v>
+        <v>490831</v>
       </c>
       <c r="R111" t="n">
-        <v>7017497</v>
+        <v>7017486</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13929,13 +13900,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499601</v>
+        <v>135499600</v>
       </c>
       <c r="B112" t="n">
         <v>98344</v>
@@ -13981,7 +13952,7 @@
         <v>490797</v>
       </c>
       <c r="R112" t="n">
-        <v>7017511</v>
+        <v>7017497</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14045,13 +14016,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499602</v>
+        <v>135499601</v>
       </c>
       <c r="B113" t="n">
         <v>98344</v>
@@ -14094,10 +14065,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490737</v>
+        <v>490797</v>
       </c>
       <c r="R113" t="n">
-        <v>7017473</v>
+        <v>7017511</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14161,16 +14132,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499515</v>
+        <v>135499602</v>
       </c>
       <c r="B114" t="n">
-        <v>102039</v>
+        <v>98344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14178,21 +14149,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223366</v>
+        <v>223358</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14210,10 +14181,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490788</v>
+        <v>490737</v>
       </c>
       <c r="R114" t="n">
-        <v>7017450</v>
+        <v>7017473</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14277,16 +14248,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499532</v>
+        <v>135499515</v>
       </c>
       <c r="B115" t="n">
-        <v>101392</v>
+        <v>102039</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14294,21 +14265,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>224885</v>
+        <v>223366</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14326,10 +14297,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490889</v>
+        <v>490788</v>
       </c>
       <c r="R115" t="n">
-        <v>7017459</v>
+        <v>7017450</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14393,13 +14364,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499533</v>
+        <v>135499532</v>
       </c>
       <c r="B116" t="n">
         <v>101392</v>
@@ -14442,10 +14413,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490743</v>
+        <v>490889</v>
       </c>
       <c r="R116" t="n">
-        <v>7017495</v>
+        <v>7017459</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14509,13 +14480,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499534</v>
+        <v>135499533</v>
       </c>
       <c r="B117" t="n">
         <v>101392</v>
@@ -14558,10 +14529,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>490737</v>
+        <v>490743</v>
       </c>
       <c r="R117" t="n">
-        <v>7017474</v>
+        <v>7017495</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14625,13 +14596,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499535</v>
+        <v>135499534</v>
       </c>
       <c r="B118" t="n">
         <v>101392</v>
@@ -14674,10 +14645,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490734</v>
+        <v>490737</v>
       </c>
       <c r="R118" t="n">
-        <v>7017429</v>
+        <v>7017474</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14741,13 +14712,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499536</v>
+        <v>135499535</v>
       </c>
       <c r="B119" t="n">
         <v>101392</v>
@@ -14790,10 +14761,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490780</v>
+        <v>490734</v>
       </c>
       <c r="R119" t="n">
-        <v>7017405</v>
+        <v>7017429</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14857,13 +14828,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499537</v>
+        <v>135499536</v>
       </c>
       <c r="B120" t="n">
         <v>101392</v>
@@ -14906,10 +14877,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490751</v>
+        <v>490780</v>
       </c>
       <c r="R120" t="n">
-        <v>7017406</v>
+        <v>7017405</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14973,13 +14944,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499538</v>
+        <v>135499537</v>
       </c>
       <c r="B121" t="n">
         <v>101392</v>
@@ -15022,10 +14993,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490729</v>
+        <v>490751</v>
       </c>
       <c r="R121" t="n">
-        <v>7017373</v>
+        <v>7017406</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15089,13 +15060,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
+          <t>https://artportalen.se/Sighting/135499537</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499540</v>
+        <v>135499538</v>
       </c>
       <c r="B122" t="n">
         <v>101392</v>
@@ -15138,10 +15109,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490847</v>
+        <v>490729</v>
       </c>
       <c r="R122" t="n">
-        <v>7017345</v>
+        <v>7017373</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15205,13 +15176,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
+          <t>https://artportalen.se/Sighting/135499538</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499541</v>
+        <v>135499540</v>
       </c>
       <c r="B123" t="n">
         <v>101392</v>
@@ -15254,10 +15225,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490856</v>
+        <v>490847</v>
       </c>
       <c r="R123" t="n">
-        <v>7017358</v>
+        <v>7017345</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15321,13 +15292,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
+          <t>https://artportalen.se/Sighting/135499540</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499542</v>
+        <v>135499541</v>
       </c>
       <c r="B124" t="n">
         <v>101392</v>
@@ -15359,7 +15330,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -15370,10 +15341,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490840</v>
+        <v>490856</v>
       </c>
       <c r="R124" t="n">
-        <v>7017433</v>
+        <v>7017358</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15436,6 +15407,122 @@
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499541</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>135499542</v>
+      </c>
+      <c r="B125" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>490840</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7017433</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -15566,6 +15653,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ125"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4725,10 +4725,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135499549</v>
+        <v>135499510</v>
       </c>
       <c r="B36" t="n">
-        <v>58238</v>
+        <v>57982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,33 +4736,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102980</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4776,10 +4772,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490804</v>
+        <v>490891</v>
       </c>
       <c r="R36" t="n">
-        <v>7017502</v>
+        <v>7017451</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4816,7 +4812,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 1 överflygande med sång.</t>
+          <t>Ringhack, äldre, på en gran. Bedöms  vara 5 - 10 gamla. På/kring fyndplatsen finns stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett..</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4830,7 +4826,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4847,33 +4863,33 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499549</t>
+          <t>https://artportalen.se/Sighting/135499510</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135499596</v>
+        <v>135499511</v>
       </c>
       <c r="B37" t="n">
-        <v>58241</v>
+        <v>57982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102981</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4881,29 +4897,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490875</v>
+        <v>490785</v>
       </c>
       <c r="R37" t="n">
-        <v>7017470</v>
+        <v>7017521</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4940,7 +4956,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot kraftledning och ungskog. Stående död ved som indikerar minst högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4955,6 +4971,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4971,16 +5007,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499596</t>
+          <t>https://artportalen.se/Sighting/135499511</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135499513</v>
+        <v>135499512</v>
       </c>
       <c r="B38" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4988,33 +5024,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5028,10 +5060,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490763</v>
+        <v>490783</v>
       </c>
       <c r="R38" t="n">
-        <v>7017499</v>
+        <v>7017360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5068,7 +5100,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+          <t>Ringhack, färska, längs flera meter på en levande gran med avbruten topp.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5082,12 +5114,32 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Bitvis flerskiktad äldre granskog.</t>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5104,16 +5156,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499513</t>
+          <t>https://artportalen.se/Sighting/135499512</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135499514</v>
+        <v>135499549</v>
       </c>
       <c r="B39" t="n">
-        <v>58143</v>
+        <v>58238</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5121,33 +5173,33 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>102980</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5161,10 +5213,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490875</v>
+        <v>490804</v>
       </c>
       <c r="R39" t="n">
-        <v>7017397</v>
+        <v>7017502</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5201,7 +5253,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
+          <t>Minst 1 överflygande med sång.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5216,11 +5268,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5237,48 +5284,52 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499514</t>
+          <t>https://artportalen.se/Sighting/135499549</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135499611</v>
+        <v>135499596</v>
       </c>
       <c r="B40" t="n">
-        <v>99210</v>
+        <v>58241</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>102981</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5286,10 +5337,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490821</v>
+        <v>490875</v>
       </c>
       <c r="R40" t="n">
-        <v>7017504</v>
+        <v>7017470</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5326,7 +5377,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk.</t>
+          <t>Minst 3 överflygande individer med lockläte. Troligen även födosökande över krontaket.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5335,7 +5386,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5358,59 +5408,67 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499611</t>
+          <t>https://artportalen.se/Sighting/135499596</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135499612</v>
+        <v>135499513</v>
       </c>
       <c r="B41" t="n">
-        <v>99210</v>
+        <v>58143</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490848</v>
+        <v>490763</v>
       </c>
       <c r="R41" t="n">
-        <v>7017375</v>
+        <v>7017499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5445,19 +5503,28 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Murkna björkhögstubbar för talltitans bohål finns i skogsbeståndet kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5474,59 +5541,67 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499612</t>
+          <t>https://artportalen.se/Sighting/135499513</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135499613</v>
+        <v>135499514</v>
       </c>
       <c r="B42" t="n">
-        <v>99210</v>
+        <v>58143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst om Smedsta, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490878</v>
+        <v>490875</v>
       </c>
       <c r="R42" t="n">
-        <v>7017368</v>
+        <v>7017397</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5563,7 +5638,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Minst 2 individer med lockläte. Flerskiktade partier och flertalet murkna björkhögstubbar för talltitans bohål finns i området.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5572,13 +5647,17 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad och varierad äldre barrblandskog och granskog med inslag av björk, rönn, gråal och hägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5595,13 +5674,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499613</t>
+          <t>https://artportalen.se/Sighting/135499514</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135499614</v>
+        <v>135499611</v>
       </c>
       <c r="B43" t="n">
         <v>99210</v>
@@ -5633,7 +5712,7 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5644,10 +5723,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490867</v>
+        <v>490821</v>
       </c>
       <c r="R43" t="n">
-        <v>7017386</v>
+        <v>7017504</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5684,7 +5763,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+          <t>Växer i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5716,13 +5795,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499614</t>
+          <t>https://artportalen.se/Sighting/135499611</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135499615</v>
+        <v>135499612</v>
       </c>
       <c r="B44" t="n">
         <v>99210</v>
@@ -5754,7 +5833,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5765,10 +5844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490860</v>
+        <v>490848</v>
       </c>
       <c r="R44" t="n">
-        <v>7017386</v>
+        <v>7017375</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5803,11 +5882,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5837,16 +5911,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499615</t>
+          <t>https://artportalen.se/Sighting/135499612</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135499509</v>
+        <v>135499613</v>
       </c>
       <c r="B45" t="n">
-        <v>99317</v>
+        <v>99210</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5854,28 +5928,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -5886,10 +5960,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490880</v>
+        <v>490878</v>
       </c>
       <c r="R45" t="n">
-        <v>7017365</v>
+        <v>7017368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5926,7 +6000,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flertalet plantor.</t>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5944,11 +6018,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Fuktstråk med tydlig kalkpåverkan.</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
@@ -5963,16 +6032,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499509</t>
+          <t>https://artportalen.se/Sighting/135499613</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135499620</v>
+        <v>135499614</v>
       </c>
       <c r="B46" t="n">
-        <v>108317</v>
+        <v>99210</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5980,21 +6049,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220083</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6012,10 +6081,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490853</v>
+        <v>490867</v>
       </c>
       <c r="R46" t="n">
-        <v>7017483</v>
+        <v>7017386</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6050,6 +6119,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6079,16 +6153,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499620</t>
+          <t>https://artportalen.se/Sighting/135499614</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135499621</v>
+        <v>135499615</v>
       </c>
       <c r="B47" t="n">
-        <v>108317</v>
+        <v>99210</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6096,28 +6170,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220083</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6128,10 +6202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490837</v>
+        <v>490860</v>
       </c>
       <c r="R47" t="n">
-        <v>7017379</v>
+        <v>7017386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6166,6 +6240,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6195,16 +6274,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499621</t>
+          <t>https://artportalen.se/Sighting/135499615</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135499623</v>
+        <v>135499509</v>
       </c>
       <c r="B48" t="n">
-        <v>108317</v>
+        <v>99317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6212,28 +6291,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -6244,10 +6323,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490848</v>
+        <v>490880</v>
       </c>
       <c r="R48" t="n">
-        <v>7017376</v>
+        <v>7017365</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6282,6 +6361,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flertalet plantor.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6297,6 +6381,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Fuktstråk med tydlig kalkpåverkan.</t>
+        </is>
+      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
@@ -6311,13 +6400,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499623</t>
+          <t>https://artportalen.se/Sighting/135499509</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135499624</v>
+        <v>135499620</v>
       </c>
       <c r="B49" t="n">
         <v>108317</v>
@@ -6349,7 +6438,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6360,10 +6449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490861</v>
+        <v>490853</v>
       </c>
       <c r="R49" t="n">
-        <v>7017386</v>
+        <v>7017483</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6427,13 +6516,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499624</t>
+          <t>https://artportalen.se/Sighting/135499620</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135499625</v>
+        <v>135499621</v>
       </c>
       <c r="B50" t="n">
         <v>108317</v>
@@ -6465,7 +6554,7 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -6476,10 +6565,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490821</v>
+        <v>490837</v>
       </c>
       <c r="R50" t="n">
-        <v>7017394</v>
+        <v>7017379</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6543,13 +6632,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499625</t>
+          <t>https://artportalen.se/Sighting/135499621</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135499626</v>
+        <v>135499623</v>
       </c>
       <c r="B51" t="n">
         <v>108317</v>
@@ -6581,7 +6670,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -6592,10 +6681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490841</v>
+        <v>490848</v>
       </c>
       <c r="R51" t="n">
-        <v>7017433</v>
+        <v>7017376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6659,16 +6748,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499626</t>
+          <t>https://artportalen.se/Sighting/135499623</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135499550</v>
+        <v>135499624</v>
       </c>
       <c r="B52" t="n">
-        <v>108387</v>
+        <v>108317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6676,28 +6765,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -6708,10 +6797,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490929</v>
+        <v>490861</v>
       </c>
       <c r="R52" t="n">
-        <v>7017429</v>
+        <v>7017386</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6775,16 +6864,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499550</t>
+          <t>https://artportalen.se/Sighting/135499624</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135499551</v>
+        <v>135499625</v>
       </c>
       <c r="B53" t="n">
-        <v>108387</v>
+        <v>108317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6792,28 +6881,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -6824,10 +6913,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490853</v>
+        <v>490821</v>
       </c>
       <c r="R53" t="n">
-        <v>7017480</v>
+        <v>7017394</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6862,11 +6951,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Växer här i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6896,16 +6980,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499551</t>
+          <t>https://artportalen.se/Sighting/135499625</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135499552</v>
+        <v>135499626</v>
       </c>
       <c r="B54" t="n">
-        <v>108387</v>
+        <v>108317</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6913,28 +6997,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -6945,10 +7029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490867</v>
+        <v>490841</v>
       </c>
       <c r="R54" t="n">
-        <v>7017480</v>
+        <v>7017433</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7012,13 +7096,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499552</t>
+          <t>https://artportalen.se/Sighting/135499626</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135499553</v>
+        <v>135499550</v>
       </c>
       <c r="B55" t="n">
         <v>108387</v>
@@ -7061,10 +7145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490841</v>
+        <v>490929</v>
       </c>
       <c r="R55" t="n">
-        <v>7017457</v>
+        <v>7017429</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7128,13 +7212,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499553</t>
+          <t>https://artportalen.se/Sighting/135499550</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135499554</v>
+        <v>135499551</v>
       </c>
       <c r="B56" t="n">
         <v>108387</v>
@@ -7177,10 +7261,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490737</v>
+        <v>490853</v>
       </c>
       <c r="R56" t="n">
-        <v>7017474</v>
+        <v>7017480</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7215,6 +7299,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Växer här i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7244,13 +7333,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499554</t>
+          <t>https://artportalen.se/Sighting/135499551</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135499555</v>
+        <v>135499552</v>
       </c>
       <c r="B57" t="n">
         <v>108387</v>
@@ -7293,10 +7382,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490873</v>
+        <v>490867</v>
       </c>
       <c r="R57" t="n">
-        <v>7017368</v>
+        <v>7017480</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7360,13 +7449,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499555</t>
+          <t>https://artportalen.se/Sighting/135499552</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135499556</v>
+        <v>135499553</v>
       </c>
       <c r="B58" t="n">
         <v>108387</v>
@@ -7409,10 +7498,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490863</v>
+        <v>490841</v>
       </c>
       <c r="R58" t="n">
-        <v>7017386</v>
+        <v>7017457</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7462,11 +7551,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Fuktstråk.</t>
-        </is>
-      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
@@ -7481,16 +7565,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499556</t>
+          <t>https://artportalen.se/Sighting/135499553</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135499544</v>
+        <v>135499554</v>
       </c>
       <c r="B59" t="n">
-        <v>111267</v>
+        <v>108387</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7498,28 +7582,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -7530,10 +7614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490844</v>
+        <v>490737</v>
       </c>
       <c r="R59" t="n">
-        <v>7017468</v>
+        <v>7017474</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7597,16 +7681,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499544</t>
+          <t>https://artportalen.se/Sighting/135499554</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135499546</v>
+        <v>135499555</v>
       </c>
       <c r="B60" t="n">
-        <v>111267</v>
+        <v>108387</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7614,28 +7698,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -7646,10 +7730,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490780</v>
+        <v>490873</v>
       </c>
       <c r="R60" t="n">
-        <v>7017405</v>
+        <v>7017368</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7713,16 +7797,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499546</t>
+          <t>https://artportalen.se/Sighting/135499555</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135499547</v>
+        <v>135499556</v>
       </c>
       <c r="B61" t="n">
-        <v>111267</v>
+        <v>108387</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7730,21 +7814,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7762,10 +7846,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490858</v>
+        <v>490863</v>
       </c>
       <c r="R61" t="n">
-        <v>7017416</v>
+        <v>7017386</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7815,6 +7899,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Fuktstråk.</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -7829,13 +7918,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499547</t>
+          <t>https://artportalen.se/Sighting/135499556</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135499548</v>
+        <v>135499544</v>
       </c>
       <c r="B62" t="n">
         <v>111267</v>
@@ -7867,7 +7956,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7878,10 +7967,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490964</v>
+        <v>490844</v>
       </c>
       <c r="R62" t="n">
-        <v>7017356</v>
+        <v>7017468</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7931,11 +8020,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7950,16 +8034,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499548</t>
+          <t>https://artportalen.se/Sighting/135499544</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135499617</v>
+        <v>135499546</v>
       </c>
       <c r="B63" t="n">
-        <v>110263</v>
+        <v>111267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7967,28 +8051,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220294</v>
+        <v>220240</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -7999,10 +8083,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490864</v>
+        <v>490780</v>
       </c>
       <c r="R63" t="n">
-        <v>7017486</v>
+        <v>7017405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8037,11 +8121,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Växer i ett stråk med rikligt av högörter.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8071,50 +8150,42 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499617</t>
+          <t>https://artportalen.se/Sighting/135499546</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135499580</v>
+        <v>135499547</v>
       </c>
       <c r="B64" t="n">
-        <v>99293</v>
+        <v>111267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -8128,10 +8199,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490975</v>
+        <v>490858</v>
       </c>
       <c r="R64" t="n">
-        <v>7017304</v>
+        <v>7017416</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8166,11 +8237,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8186,11 +8252,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
@@ -8205,53 +8266,45 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499580</t>
+          <t>https://artportalen.se/Sighting/135499547</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135499581</v>
+        <v>135499548</v>
       </c>
       <c r="B65" t="n">
-        <v>99293</v>
+        <v>111267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -8262,10 +8315,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490951</v>
+        <v>490964</v>
       </c>
       <c r="R65" t="n">
-        <v>7017428</v>
+        <v>7017356</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8300,11 +8353,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8320,6 +8368,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
@@ -8334,53 +8387,45 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499581</t>
+          <t>https://artportalen.se/Sighting/135499548</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135499582</v>
+        <v>135499617</v>
       </c>
       <c r="B66" t="n">
-        <v>99293</v>
+        <v>110263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -8391,10 +8436,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490884</v>
+        <v>490864</v>
       </c>
       <c r="R66" t="n">
-        <v>7017471</v>
+        <v>7017486</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8431,7 +8476,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
+          <t>Växer i ett stråk med rikligt av högörter.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8446,7 +8491,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8463,13 +8508,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499582</t>
+          <t>https://artportalen.se/Sighting/135499617</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135499583</v>
+        <v>135499580</v>
       </c>
       <c r="B67" t="n">
         <v>99293</v>
@@ -8499,7 +8544,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8520,10 +8565,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490768</v>
+        <v>490975</v>
       </c>
       <c r="R67" t="n">
-        <v>7017376</v>
+        <v>7017304</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8560,7 +8605,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
+          <t>Minst 10 plantor och 1 blomställning inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8597,13 +8642,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499583</t>
+          <t>https://artportalen.se/Sighting/135499580</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135499584</v>
+        <v>135499581</v>
       </c>
       <c r="B68" t="n">
         <v>99293</v>
@@ -8633,7 +8678,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8654,10 +8699,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490839</v>
+        <v>490951</v>
       </c>
       <c r="R68" t="n">
-        <v>7017351</v>
+        <v>7017428</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8694,7 +8739,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 105 plantor och 22 blomställningar inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8709,7 +8754,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8726,13 +8771,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499584</t>
+          <t>https://artportalen.se/Sighting/135499581</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135499585</v>
+        <v>135499582</v>
       </c>
       <c r="B69" t="n">
         <v>99293</v>
@@ -8762,7 +8807,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8783,10 +8828,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490845</v>
+        <v>490884</v>
       </c>
       <c r="R69" t="n">
-        <v>7017392</v>
+        <v>7017471</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8823,7 +8868,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 70 plantor och 6 blomställningar inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8855,13 +8900,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499585</t>
+          <t>https://artportalen.se/Sighting/135499582</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135499586</v>
+        <v>135499583</v>
       </c>
       <c r="B70" t="n">
         <v>99293</v>
@@ -8891,7 +8936,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8912,10 +8957,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490812</v>
+        <v>490768</v>
       </c>
       <c r="R70" t="n">
-        <v>7017401</v>
+        <v>7017376</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8952,7 +8997,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
+          <t>Minst 4 plantor och 2 blomställningar inom ca 1 m2 yta intill färska maskin-körspår i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8989,13 +9034,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499586</t>
+          <t>https://artportalen.se/Sighting/135499583</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135499588</v>
+        <v>135499584</v>
       </c>
       <c r="B71" t="n">
         <v>99293</v>
@@ -9025,7 +9070,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9046,10 +9091,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490843</v>
+        <v>490839</v>
       </c>
       <c r="R71" t="n">
-        <v>7017436</v>
+        <v>7017351</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9086,7 +9131,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
+          <t>Minst 12 plantor och 5 blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9101,12 +9146,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9123,13 +9163,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499588</t>
+          <t>https://artportalen.se/Sighting/135499584</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135499589</v>
+        <v>135499585</v>
       </c>
       <c r="B72" t="n">
         <v>99293</v>
@@ -9159,7 +9199,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9180,10 +9220,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490967</v>
+        <v>490845</v>
       </c>
       <c r="R72" t="n">
-        <v>7017335</v>
+        <v>7017392</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9220,7 +9260,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
+          <t>Minst 30 plantor och 6 blomställningar inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9235,12 +9275,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9257,13 +9292,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499589</t>
+          <t>https://artportalen.se/Sighting/135499585</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135499590</v>
+        <v>135499586</v>
       </c>
       <c r="B73" t="n">
         <v>99293</v>
@@ -9293,7 +9328,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9314,10 +9349,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490979</v>
+        <v>490812</v>
       </c>
       <c r="R73" t="n">
-        <v>7017360</v>
+        <v>7017401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9354,7 +9389,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
+          <t>Minst 70 plantor och 15 blomställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9391,13 +9426,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499590</t>
+          <t>https://artportalen.se/Sighting/135499586</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135499591</v>
+        <v>135499588</v>
       </c>
       <c r="B74" t="n">
         <v>99293</v>
@@ -9427,7 +9462,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9448,10 +9483,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490973</v>
+        <v>490843</v>
       </c>
       <c r="R74" t="n">
-        <v>7017399</v>
+        <v>7017436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9488,7 +9523,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
+          <t>Minst 6 plantor och 2 blomställningar inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9525,13 +9560,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499591</t>
+          <t>https://artportalen.se/Sighting/135499588</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135499592</v>
+        <v>135499589</v>
       </c>
       <c r="B75" t="n">
         <v>99293</v>
@@ -9561,7 +9596,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9582,10 +9617,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490951</v>
+        <v>490967</v>
       </c>
       <c r="R75" t="n">
-        <v>7017408</v>
+        <v>7017335</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9622,7 +9657,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
+          <t>Minst 106 plantor, 24 blomställningar och 2 vinterståndare inom ca 4 x 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9659,13 +9694,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499592</t>
+          <t>https://artportalen.se/Sighting/135499589</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135499593</v>
+        <v>135499590</v>
       </c>
       <c r="B76" t="n">
         <v>99293</v>
@@ -9695,7 +9730,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9716,10 +9751,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490951</v>
+        <v>490979</v>
       </c>
       <c r="R76" t="n">
-        <v>7017396</v>
+        <v>7017360</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9756,7 +9791,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+          <t>Minst 15 plantor och 3 blomställningar inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9793,13 +9828,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499593</t>
+          <t>https://artportalen.se/Sighting/135499590</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135499594</v>
+        <v>135499591</v>
       </c>
       <c r="B77" t="n">
         <v>99293</v>
@@ -9829,7 +9864,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9850,10 +9885,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490957</v>
+        <v>490973</v>
       </c>
       <c r="R77" t="n">
-        <v>7017386</v>
+        <v>7017399</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9890,7 +9925,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+          <t>Minst 20 plantor och 6 blomställningar inom ca 2 x 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9927,43 +9962,55 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499594</t>
+          <t>https://artportalen.se/Sighting/135499591</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135499519</v>
+        <v>135499592</v>
       </c>
       <c r="B78" t="n">
-        <v>98155</v>
+        <v>99293</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -9972,10 +10019,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490752</v>
+        <v>490951</v>
       </c>
       <c r="R78" t="n">
-        <v>7017499</v>
+        <v>7017408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10012,7 +10059,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 15 plantor och 6 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10030,6 +10077,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
@@ -10044,45 +10096,53 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499519</t>
+          <t>https://artportalen.se/Sighting/135499592</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135499516</v>
+        <v>135499593</v>
       </c>
       <c r="B79" t="n">
-        <v>99315</v>
+        <v>99293</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -10093,10 +10153,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490844</v>
+        <v>490951</v>
       </c>
       <c r="R79" t="n">
-        <v>7017394</v>
+        <v>7017396</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10131,6 +10191,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Minst 65 plantor och 13 blomställningar inom ca 4 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10146,6 +10211,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
@@ -10160,45 +10230,53 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499516</t>
+          <t>https://artportalen.se/Sighting/135499593</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135499517</v>
+        <v>135499594</v>
       </c>
       <c r="B80" t="n">
-        <v>99315</v>
+        <v>99293</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10209,10 +10287,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490814</v>
+        <v>490957</v>
       </c>
       <c r="R80" t="n">
-        <v>7017404</v>
+        <v>7017386</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10247,6 +10325,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor och 3 blomställningar inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10262,6 +10345,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
@@ -10276,16 +10364,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499517</t>
+          <t>https://artportalen.se/Sighting/135499594</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135499627</v>
+        <v>135499519</v>
       </c>
       <c r="B81" t="n">
-        <v>101502</v>
+        <v>98155</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10293,30 +10381,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10325,10 +10409,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490803</v>
+        <v>490752</v>
       </c>
       <c r="R81" t="n">
-        <v>7017492</v>
+        <v>7017499</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10363,6 +10447,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10392,16 +10481,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499627</t>
+          <t>https://artportalen.se/Sighting/135499519</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135499628</v>
+        <v>135499516</v>
       </c>
       <c r="B82" t="n">
-        <v>101502</v>
+        <v>99315</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10409,28 +10498,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10441,10 +10530,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490792</v>
+        <v>490844</v>
       </c>
       <c r="R82" t="n">
-        <v>7017441</v>
+        <v>7017394</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10508,16 +10597,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499628</t>
+          <t>https://artportalen.se/Sighting/135499516</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135499629</v>
+        <v>135499517</v>
       </c>
       <c r="B83" t="n">
-        <v>101502</v>
+        <v>99315</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10525,28 +10614,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -10557,10 +10646,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490764</v>
+        <v>490814</v>
       </c>
       <c r="R83" t="n">
-        <v>7017441</v>
+        <v>7017404</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10624,13 +10713,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499629</t>
+          <t>https://artportalen.se/Sighting/135499517</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135499630</v>
+        <v>135499627</v>
       </c>
       <c r="B84" t="n">
         <v>101502</v>
@@ -10673,10 +10762,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490798</v>
+        <v>490803</v>
       </c>
       <c r="R84" t="n">
-        <v>7017366</v>
+        <v>7017492</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10740,13 +10829,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499630</t>
+          <t>https://artportalen.se/Sighting/135499627</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135499631</v>
+        <v>135499628</v>
       </c>
       <c r="B85" t="n">
         <v>101502</v>
@@ -10789,10 +10878,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490816</v>
+        <v>490792</v>
       </c>
       <c r="R85" t="n">
-        <v>7017378</v>
+        <v>7017441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10856,13 +10945,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499631</t>
+          <t>https://artportalen.se/Sighting/135499628</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135499632</v>
+        <v>135499629</v>
       </c>
       <c r="B86" t="n">
         <v>101502</v>
@@ -10905,10 +10994,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490796</v>
+        <v>490764</v>
       </c>
       <c r="R86" t="n">
-        <v>7017382</v>
+        <v>7017441</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10972,13 +11061,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499632</t>
+          <t>https://artportalen.se/Sighting/135499629</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135499633</v>
+        <v>135499630</v>
       </c>
       <c r="B87" t="n">
         <v>101502</v>
@@ -11021,10 +11110,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490782</v>
+        <v>490798</v>
       </c>
       <c r="R87" t="n">
-        <v>7017407</v>
+        <v>7017366</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11088,13 +11177,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499633</t>
+          <t>https://artportalen.se/Sighting/135499630</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135499634</v>
+        <v>135499631</v>
       </c>
       <c r="B88" t="n">
         <v>101502</v>
@@ -11137,10 +11226,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490730</v>
+        <v>490816</v>
       </c>
       <c r="R88" t="n">
-        <v>7017371</v>
+        <v>7017378</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11204,13 +11293,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499634</t>
+          <t>https://artportalen.se/Sighting/135499631</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135499635</v>
+        <v>135499632</v>
       </c>
       <c r="B89" t="n">
         <v>101502</v>
@@ -11253,10 +11342,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>490827</v>
+        <v>490796</v>
       </c>
       <c r="R89" t="n">
-        <v>7017356</v>
+        <v>7017382</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11320,13 +11409,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499635</t>
+          <t>https://artportalen.se/Sighting/135499632</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135499636</v>
+        <v>135499633</v>
       </c>
       <c r="B90" t="n">
         <v>101502</v>
@@ -11369,10 +11458,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>490844</v>
+        <v>490782</v>
       </c>
       <c r="R90" t="n">
-        <v>7017345</v>
+        <v>7017407</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11436,13 +11525,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499636</t>
+          <t>https://artportalen.se/Sighting/135499633</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135499637</v>
+        <v>135499634</v>
       </c>
       <c r="B91" t="n">
         <v>101502</v>
@@ -11485,10 +11574,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>490852</v>
+        <v>490730</v>
       </c>
       <c r="R91" t="n">
-        <v>7017373</v>
+        <v>7017371</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11535,7 +11624,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11552,13 +11641,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499637</t>
+          <t>https://artportalen.se/Sighting/135499634</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135499638</v>
+        <v>135499635</v>
       </c>
       <c r="B92" t="n">
         <v>101502</v>
@@ -11601,10 +11690,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>490882</v>
+        <v>490827</v>
       </c>
       <c r="R92" t="n">
-        <v>7017368</v>
+        <v>7017356</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11651,7 +11740,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11668,13 +11757,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499638</t>
+          <t>https://artportalen.se/Sighting/135499635</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135499639</v>
+        <v>135499636</v>
       </c>
       <c r="B93" t="n">
         <v>101502</v>
@@ -11717,10 +11806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>490865</v>
+        <v>490844</v>
       </c>
       <c r="R93" t="n">
-        <v>7017386</v>
+        <v>7017345</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11784,13 +11873,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499639</t>
+          <t>https://artportalen.se/Sighting/135499636</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135499640</v>
+        <v>135499637</v>
       </c>
       <c r="B94" t="n">
         <v>101502</v>
@@ -11833,10 +11922,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>490840</v>
+        <v>490852</v>
       </c>
       <c r="R94" t="n">
-        <v>7017433</v>
+        <v>7017373</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11883,7 +11972,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11900,13 +11989,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499640</t>
+          <t>https://artportalen.se/Sighting/135499637</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135499641</v>
+        <v>135499638</v>
       </c>
       <c r="B95" t="n">
         <v>101502</v>
@@ -11949,10 +12038,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>490880</v>
+        <v>490882</v>
       </c>
       <c r="R95" t="n">
-        <v>7017422</v>
+        <v>7017368</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11999,7 +12088,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12016,16 +12105,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499641</t>
+          <t>https://artportalen.se/Sighting/135499638</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135499618</v>
+        <v>135499639</v>
       </c>
       <c r="B96" t="n">
-        <v>98309</v>
+        <v>101502</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12033,21 +12122,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -12065,10 +12154,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490791</v>
+        <v>490865</v>
       </c>
       <c r="R96" t="n">
-        <v>7017443</v>
+        <v>7017386</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12103,11 +12192,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Relativt rikligt i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12137,16 +12221,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499618</t>
+          <t>https://artportalen.se/Sighting/135499639</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135499619</v>
+        <v>135499640</v>
       </c>
       <c r="B97" t="n">
-        <v>98309</v>
+        <v>101502</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12154,33 +12238,25 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12194,10 +12270,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490868</v>
+        <v>490840</v>
       </c>
       <c r="R97" t="n">
-        <v>7017387</v>
+        <v>7017433</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12232,11 +12308,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12252,11 +12323,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
-        </is>
-      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
@@ -12271,16 +12337,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499619</t>
+          <t>https://artportalen.se/Sighting/135499640</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135499520</v>
+        <v>135499641</v>
       </c>
       <c r="B98" t="n">
-        <v>99099</v>
+        <v>101502</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12288,21 +12354,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12320,10 +12386,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490757</v>
+        <v>490880</v>
       </c>
       <c r="R98" t="n">
-        <v>7017472</v>
+        <v>7017422</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12387,16 +12453,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499520</t>
+          <t>https://artportalen.se/Sighting/135499641</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135499521</v>
+        <v>135499618</v>
       </c>
       <c r="B99" t="n">
-        <v>99099</v>
+        <v>98309</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12404,21 +12470,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12436,10 +12502,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490966</v>
+        <v>490791</v>
       </c>
       <c r="R99" t="n">
-        <v>7017430</v>
+        <v>7017443</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12474,6 +12540,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Relativt rikligt i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -12503,16 +12574,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499521</t>
+          <t>https://artportalen.se/Sighting/135499618</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135499522</v>
+        <v>135499619</v>
       </c>
       <c r="B100" t="n">
-        <v>99099</v>
+        <v>98309</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12520,25 +12591,33 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12552,10 +12631,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490920</v>
+        <v>490868</v>
       </c>
       <c r="R100" t="n">
-        <v>7017445</v>
+        <v>7017387</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12590,6 +12669,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 4 m2 yta i granskog intill växtplats med guckusko.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12605,6 +12689,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>I ett kalkrikt frisk-fuktigt stråk.</t>
+        </is>
+      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
@@ -12619,13 +12708,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499522</t>
+          <t>https://artportalen.se/Sighting/135499619</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135499523</v>
+        <v>135499520</v>
       </c>
       <c r="B101" t="n">
         <v>99099</v>
@@ -12668,10 +12757,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490912</v>
+        <v>490757</v>
       </c>
       <c r="R101" t="n">
-        <v>7017466</v>
+        <v>7017472</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12735,13 +12824,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499523</t>
+          <t>https://artportalen.se/Sighting/135499520</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135499524</v>
+        <v>135499521</v>
       </c>
       <c r="B102" t="n">
         <v>99099</v>
@@ -12784,10 +12873,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490858</v>
+        <v>490966</v>
       </c>
       <c r="R102" t="n">
-        <v>7017493</v>
+        <v>7017430</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12851,13 +12940,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499524</t>
+          <t>https://artportalen.se/Sighting/135499521</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135499525</v>
+        <v>135499522</v>
       </c>
       <c r="B103" t="n">
         <v>99099</v>
@@ -12889,7 +12978,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12900,10 +12989,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490804</v>
+        <v>490920</v>
       </c>
       <c r="R103" t="n">
-        <v>7017492</v>
+        <v>7017445</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12967,13 +13056,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499525</t>
+          <t>https://artportalen.se/Sighting/135499522</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135499526</v>
+        <v>135499523</v>
       </c>
       <c r="B104" t="n">
         <v>99099</v>
@@ -13016,10 +13105,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490740</v>
+        <v>490912</v>
       </c>
       <c r="R104" t="n">
-        <v>7017423</v>
+        <v>7017466</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13083,13 +13172,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499526</t>
+          <t>https://artportalen.se/Sighting/135499523</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135499527</v>
+        <v>135499524</v>
       </c>
       <c r="B105" t="n">
         <v>99099</v>
@@ -13132,10 +13221,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490732</v>
+        <v>490858</v>
       </c>
       <c r="R105" t="n">
-        <v>7017370</v>
+        <v>7017493</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13199,13 +13288,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499527</t>
+          <t>https://artportalen.se/Sighting/135499524</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135499528</v>
+        <v>135499525</v>
       </c>
       <c r="B106" t="n">
         <v>99099</v>
@@ -13237,7 +13326,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -13248,10 +13337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490867</v>
+        <v>490804</v>
       </c>
       <c r="R106" t="n">
-        <v>7017386</v>
+        <v>7017492</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13286,11 +13375,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -13320,13 +13404,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499528</t>
+          <t>https://artportalen.se/Sighting/135499525</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135499529</v>
+        <v>135499526</v>
       </c>
       <c r="B107" t="n">
         <v>99099</v>
@@ -13369,10 +13453,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490807</v>
+        <v>490740</v>
       </c>
       <c r="R107" t="n">
-        <v>7017431</v>
+        <v>7017423</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13436,13 +13520,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499529</t>
+          <t>https://artportalen.se/Sighting/135499526</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135499530</v>
+        <v>135499527</v>
       </c>
       <c r="B108" t="n">
         <v>99099</v>
@@ -13474,7 +13558,7 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -13485,10 +13569,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490932</v>
+        <v>490732</v>
       </c>
       <c r="R108" t="n">
-        <v>7017369</v>
+        <v>7017370</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13552,16 +13636,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499530</t>
+          <t>https://artportalen.se/Sighting/135499527</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135499597</v>
+        <v>135499528</v>
       </c>
       <c r="B109" t="n">
-        <v>98344</v>
+        <v>99099</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13569,21 +13653,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13601,10 +13685,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490969</v>
+        <v>490867</v>
       </c>
       <c r="R109" t="n">
-        <v>7017431</v>
+        <v>7017386</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13639,6 +13723,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Växer i ett tydligt kalkpåverkat fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13668,16 +13757,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499597</t>
+          <t>https://artportalen.se/Sighting/135499528</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135499598</v>
+        <v>135499529</v>
       </c>
       <c r="B110" t="n">
-        <v>98344</v>
+        <v>99099</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13685,21 +13774,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13717,10 +13806,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>490840</v>
+        <v>490807</v>
       </c>
       <c r="R110" t="n">
-        <v>7017457</v>
+        <v>7017431</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13784,16 +13873,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499598</t>
+          <t>https://artportalen.se/Sighting/135499529</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135499599</v>
+        <v>135499530</v>
       </c>
       <c r="B111" t="n">
-        <v>98344</v>
+        <v>99099</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13801,28 +13890,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13833,10 +13922,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490831</v>
+        <v>490932</v>
       </c>
       <c r="R111" t="n">
-        <v>7017486</v>
+        <v>7017369</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13900,13 +13989,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499599</t>
+          <t>https://artportalen.se/Sighting/135499530</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135499600</v>
+        <v>135499597</v>
       </c>
       <c r="B112" t="n">
         <v>98344</v>
@@ -13949,10 +14038,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490797</v>
+        <v>490969</v>
       </c>
       <c r="R112" t="n">
-        <v>7017497</v>
+        <v>7017431</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14016,13 +14105,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499600</t>
+          <t>https://artportalen.se/Sighting/135499597</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135499601</v>
+        <v>135499598</v>
       </c>
       <c r="B113" t="n">
         <v>98344</v>
@@ -14065,10 +14154,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490797</v>
+        <v>490840</v>
       </c>
       <c r="R113" t="n">
-        <v>7017511</v>
+        <v>7017457</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14132,13 +14221,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499601</t>
+          <t>https://artportalen.se/Sighting/135499598</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135499602</v>
+        <v>135499599</v>
       </c>
       <c r="B114" t="n">
         <v>98344</v>
@@ -14181,10 +14270,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490737</v>
+        <v>490831</v>
       </c>
       <c r="R114" t="n">
-        <v>7017473</v>
+        <v>7017486</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14248,16 +14337,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499602</t>
+          <t>https://artportalen.se/Sighting/135499599</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135499515</v>
+        <v>135499600</v>
       </c>
       <c r="B115" t="n">
-        <v>102039</v>
+        <v>98344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14265,21 +14354,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>223366</v>
+        <v>223358</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14297,10 +14386,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490788</v>
+        <v>490797</v>
       </c>
       <c r="R115" t="n">
-        <v>7017450</v>
+        <v>7017497</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14364,16 +14453,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499515</t>
+          <t>https://artportalen.se/Sighting/135499600</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135499532</v>
+        <v>135499601</v>
       </c>
       <c r="B116" t="n">
-        <v>101392</v>
+        <v>98344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14381,21 +14470,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14413,10 +14502,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490889</v>
+        <v>490797</v>
       </c>
       <c r="R116" t="n">
-        <v>7017459</v>
+        <v>7017511</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14480,16 +14569,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499532</t>
+          <t>https://artportalen.se/Sighting/135499601</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135499533</v>
+        <v>135499602</v>
       </c>
       <c r="B117" t="n">
-        <v>101392</v>
+        <v>98344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14497,21 +14586,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14529,10 +14618,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>490743</v>
+        <v>490737</v>
       </c>
       <c r="R117" t="n">
-        <v>7017495</v>
+        <v>7017473</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14596,16 +14685,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499533</t>
+          <t>https://artportalen.se/Sighting/135499602</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135499534</v>
+        <v>135499515</v>
       </c>
       <c r="B118" t="n">
-        <v>101392</v>
+        <v>102039</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14613,21 +14702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>224885</v>
+        <v>223366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svarta vinbär</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Ribes nigrum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14645,10 +14734,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490737</v>
+        <v>490788</v>
       </c>
       <c r="R118" t="n">
-        <v>7017474</v>
+        <v>7017450</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14712,13 +14801,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499534</t>
+          <t>https://artportalen.se/Sighting/135499515</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135499535</v>
+        <v>135499532</v>
       </c>
       <c r="B119" t="n">
         <v>101392</v>
@@ -14761,10 +14850,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490734</v>
+        <v>490889</v>
       </c>
       <c r="R119" t="n">
-        <v>7017429</v>
+        <v>7017459</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14828,13 +14917,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499535</t>
+          <t>https://artportalen.se/Sighting/135499532</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135499536</v>
+        <v>135499533</v>
       </c>
       <c r="B120" t="n">
         <v>101392</v>
@@ -14877,10 +14966,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490780</v>
+        <v>490743</v>
       </c>
       <c r="R120" t="n">
-        <v>7017405</v>
+        <v>7017495</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14944,13 +15033,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499536</t>
+          <t>https://artportalen.se/Sighting/135499533</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135499537</v>
+        <v>135499534</v>
       </c>
       <c r="B121" t="n">
         <v>101392</v>
@@ -14993,10 +15082,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490751</v>
+        <v>490737</v>
       </c>
       <c r="R121" t="n">
-        <v>7017406</v>
+        <v>7017474</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15060,13 +15149,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499537</t>
+          <t>https://artportalen.se/Sighting/135499534</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135499538</v>
+        <v>135499535</v>
       </c>
       <c r="B122" t="n">
         <v>101392</v>
@@ -15109,10 +15198,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490729</v>
+        <v>490734</v>
       </c>
       <c r="R122" t="n">
-        <v>7017373</v>
+        <v>7017429</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15176,13 +15265,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499538</t>
+          <t>https://artportalen.se/Sighting/135499535</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135499540</v>
+        <v>135499536</v>
       </c>
       <c r="B123" t="n">
         <v>101392</v>
@@ -15225,10 +15314,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490847</v>
+        <v>490780</v>
       </c>
       <c r="R123" t="n">
-        <v>7017345</v>
+        <v>7017405</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15292,13 +15381,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499540</t>
+          <t>https://artportalen.se/Sighting/135499536</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135499541</v>
+        <v>135499537</v>
       </c>
       <c r="B124" t="n">
         <v>101392</v>
@@ -15341,10 +15430,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490856</v>
+        <v>490751</v>
       </c>
       <c r="R124" t="n">
-        <v>7017358</v>
+        <v>7017406</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15408,13 +15497,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135499541</t>
+          <t>https://artportalen.se/Sighting/135499537</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135499542</v>
+        <v>135499538</v>
       </c>
       <c r="B125" t="n">
         <v>101392</v>
@@ -15446,7 +15535,7 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -15457,10 +15546,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>490840</v>
+        <v>490729</v>
       </c>
       <c r="R125" t="n">
-        <v>7017433</v>
+        <v>7017373</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15523,6 +15612,354 @@
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499538</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>135499540</v>
+      </c>
+      <c r="B126" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>490847</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7017345</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499540</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>135499541</v>
+      </c>
+      <c r="B127" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>490856</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7017358</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499541</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>135499542</v>
+      </c>
+      <c r="B128" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Sydväst om Smedsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>490840</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7017433</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135499542</t>
         </is>
@@ -15654,6 +16091,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29064-2026 artfynd.xlsx
+++ b/artfynd/A 29064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135499607</v>
       </c>
       <c r="B2" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>135499608</v>
       </c>
       <c r="B3" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>135499603</v>
       </c>
       <c r="B4" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135499604</v>
       </c>
       <c r="B5" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135499605</v>
       </c>
       <c r="B6" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135499606</v>
       </c>
       <c r="B7" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135499557</v>
       </c>
       <c r="B9" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>135499558</v>
       </c>
       <c r="B10" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>135499560</v>
       </c>
       <c r="B11" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135499561</v>
       </c>
       <c r="B12" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>135499562</v>
       </c>
       <c r="B13" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135499563</v>
       </c>
       <c r="B14" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135499564</v>
       </c>
       <c r="B15" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>135499565</v>
       </c>
       <c r="B16" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>135499566</v>
       </c>
       <c r="B17" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>135499567</v>
       </c>
       <c r="B18" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135499568</v>
       </c>
       <c r="B19" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>135499569</v>
       </c>
       <c r="B20" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>135499570</v>
       </c>
       <c r="B21" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>135499571</v>
       </c>
       <c r="B22" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>135499572</v>
       </c>
       <c r="B23" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>135499573</v>
       </c>
       <c r="B24" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>135499574</v>
       </c>
       <c r="B25" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>135499575</v>
       </c>
       <c r="B26" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>135499576</v>
       </c>
       <c r="B27" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>135499577</v>
       </c>
       <c r="B28" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>135499578</v>
       </c>
       <c r="B29" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>135499579</v>
       </c>
       <c r="B30" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>135499609</v>
       </c>
       <c r="B33" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>135499610</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>135499611</v>
       </c>
       <c r="B43" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>135499612</v>
       </c>
       <c r="B44" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>135499613</v>
       </c>
       <c r="B45" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135499614</v>
       </c>
       <c r="B46" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>135499615</v>
       </c>
       <c r="B47" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>135499509</v>
       </c>
       <c r="B48" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>135499620</v>
       </c>
       <c r="B49" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>135499621</v>
       </c>
       <c r="B50" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>135499623</v>
       </c>
       <c r="B51" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>135499624</v>
       </c>
       <c r="B52" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>135499625</v>
       </c>
       <c r="B53" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>135499626</v>
       </c>
       <c r="B54" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>135499550</v>
       </c>
       <c r="B55" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>135499551</v>
       </c>
       <c r="B56" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>135499552</v>
       </c>
       <c r="B57" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>135499553</v>
       </c>
       <c r="B58" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>135499554</v>
       </c>
       <c r="B59" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>135499555</v>
       </c>
       <c r="B60" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>135499556</v>
       </c>
       <c r="B61" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135499544</v>
       </c>
       <c r="B62" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>135499546</v>
       </c>
       <c r="B63" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>135499547</v>
       </c>
       <c r="B64" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>135499548</v>
       </c>
       <c r="B65" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>135499617</v>
       </c>
       <c r="B66" t="n">
-        <v>110263</v>
+        <v>110265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>135499580</v>
       </c>
       <c r="B67" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>135499581</v>
       </c>
       <c r="B68" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135499582</v>
       </c>
       <c r="B69" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>135499583</v>
       </c>
       <c r="B70" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>135499584</v>
       </c>
       <c r="B71" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135499585</v>
       </c>
       <c r="B72" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>135499586</v>
       </c>
       <c r="B73" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>135499588</v>
       </c>
       <c r="B74" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>135499589</v>
       </c>
       <c r="B75" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>135499590</v>
       </c>
       <c r="B76" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>135499591</v>
       </c>
       <c r="B77" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>135499592</v>
       </c>
       <c r="B78" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>135499593</v>
       </c>
       <c r="B79" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>135499594</v>
       </c>
       <c r="B80" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>135499519</v>
       </c>
       <c r="B81" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>135499516</v>
       </c>
       <c r="B82" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>135499517</v>
       </c>
       <c r="B83" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>135499627</v>
       </c>
       <c r="B84" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>135499628</v>
       </c>
       <c r="B85" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>135499629</v>
       </c>
       <c r="B86" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>135499630</v>
       </c>
       <c r="B87" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>135499631</v>
       </c>
       <c r="B88" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>135499632</v>
       </c>
       <c r="B89" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>135499633</v>
       </c>
       <c r="B90" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>135499634</v>
       </c>
       <c r="B91" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>135499635</v>
       </c>
       <c r="B92" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>135499636</v>
       </c>
       <c r="B93" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>135499637</v>
       </c>
       <c r="B94" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>135499638</v>
       </c>
       <c r="B95" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>135499639</v>
       </c>
       <c r="B96" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>135499640</v>
       </c>
       <c r="B97" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>135499641</v>
       </c>
       <c r="B98" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>135499618</v>
       </c>
       <c r="B99" t="n">
-        <v>98309</v>
+        <v>98310</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>135499619</v>
       </c>
       <c r="B100" t="n">
-        <v>98309</v>
+        <v>98310</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>135499520</v>
       </c>
       <c r="B101" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>135499521</v>
       </c>
       <c r="B102" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>135499522</v>
       </c>
       <c r="B103" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>135499523</v>
       </c>
       <c r="B104" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>135499524</v>
       </c>
       <c r="B105" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>135499525</v>
       </c>
       <c r="B106" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>135499526</v>
       </c>
       <c r="B107" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>135499527</v>
       </c>
       <c r="B108" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>135499528</v>
       </c>
       <c r="B109" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>135499529</v>
       </c>
       <c r="B110" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>135499530</v>
       </c>
       <c r="B111" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>135499597</v>
       </c>
       <c r="B112" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>135499598</v>
       </c>
       <c r="B113" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>135499599</v>
       </c>
       <c r="B114" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135499600</v>
       </c>
       <c r="B115" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135499601</v>
       </c>
       <c r="B116" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135499602</v>
       </c>
       <c r="B117" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>135499515</v>
       </c>
       <c r="B118" t="n">
-        <v>102039</v>
+        <v>102041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
      